--- a/py/implementation/Doc/GPT Summarizer/data/summary_set_merged.xlsx
+++ b/py/implementation/Doc/GPT Summarizer/data/summary_set_merged.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,22 +1025,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>AerServ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>optOut</t>
+          <t>setGdprConsentFlag</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOut', 'class_name': ['', 'Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ['Users will not be tracked by the SDK, and no events or browsing history will be collected.', "Disables tracking of the user's events.", 'Disables tracking of events and user data', 'Disables tracking of events for the user opting out', "Users may wish to opt out of tracking entirely, which means Amplitude doesn't track any of their events or browsing history."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User wishes to opt out of tracking'], 'effects': ['Prevents Amplitude from tracking all events for the user.', 'Disables all event tracking for the user', 'Disables all tracking for the user who opted out.', 'Disables all tracking for the specified user']}, {'parameter_values': [False], 'conditions': ['User does not wish to opt out of tracking'], 'effects': ["Enables tracking of the user's events.", 'Enables tracking for the specified user', 'Enables tracking for the user, collecting events and browsing history.', 'Allows event tracking']}, {'parameter_values': [True, 'context'], 'conditions': [], 'effects': ['User opts out of tracking']}, {'parameter_values': [False, 'context'], 'conditions': [], 'effects': ['User is included in tracking']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://amplitude.com/docs/sdks/analytics/android/android-kotlin-sdk</t>
+          <t>https://d3tplke66d0j4g.cloudfront.net/documentation/documentation.html?platform=android&amp;adapters=admob,adcolony,appnext,applovin,chartboost,flurry,inmobi,mopub,rhythm,tremor,unity,vungle&amp;mode=zendesk</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>useAdvertisingIdForDeviceId</t>
+          <t>optOut</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'API_name': 'useAdvertisingIdForDeviceId', 'class_name': ['Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ['Uses the advertising ID as the device ID for tracking', 'Enables the use of the advertising ID as the device ID for tracking purposes.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Enables the use of advertising ID as device ID', 'Uses the advertising ID to uniquely identify the device.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Does not use the advertising ID for identifying the device.', 'Disables the use of advertising ID as device ID']}]}</t>
+          <t>{'API_name': 'optOut', 'class_name': ['', 'Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ['Users will not be tracked by the SDK, and no events or browsing history will be collected.', "Disables tracking of the user's events.", 'Disables tracking of events and user data', 'Disables tracking of events for the user opting out', "Users may wish to opt out of tracking entirely, which means Amplitude doesn't track any of their events or browsing history."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User wishes to opt out of tracking'], 'effects': ['Prevents Amplitude from tracking all events for the user.', 'Disables all event tracking for the user', 'Disables all tracking for the user who opted out.', 'Disables all tracking for the specified user']}, {'parameter_values': [False], 'conditions': ['User does not wish to opt out of tracking'], 'effects': ["Enables tracking of the user's events.", 'Enables tracking for the specified user', 'Enables tracking for the user, collecting events and browsing history.', 'Allows event tracking']}, {'parameter_values': [True, 'context'], 'conditions': [], 'effects': ['User opts out of tracking']}, {'parameter_values': [False, 'context'], 'conditions': [], 'effects': ['User is included in tracking']}]}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>useAppSetIdForDeviceId</t>
+          <t>setEnableCoppaControl</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'API_name': 'useAppSetIdForDeviceId', 'class_name': ['Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ['Allows the option to use the App Set ID as a privacy-friendly identifier.', 'Uses the app set ID as the device ID for tracking'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Uses App Set ID for device identification, which resets when the app is uninstalled.', 'Enables the use of app set ID as device ID']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Does not use the App Set ID for device identification.', 'Disables the use of app set ID as device ID']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>locationListening</t>
+          <t>useAdvertisingIdForDeviceId</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'API_name': 'locationListening', 'class_name': ['', 'Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ["Enables tracking of the user's location", 'Enables the tracking of user location to provide more contextual analytics.', "Allows the SDK to track user's location."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ["Allows the SDK to access and track user's location information", "Enables the SDK to access and log the user's geographic coordinates.", 'The SDK tracks IP-based location data.']}, {'parameter_values': [False], 'conditions': [], 'effects': ["Prevents the SDK from accessing or tracking user's location information", 'Disables location tracking for the user.', 'Disables the SDK from tracking location data.']}]}</t>
+          <t>{'API_name': 'useAdvertisingIdForDeviceId', 'class_name': ['Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ['Uses the advertising ID as the device ID for tracking', 'Enables the use of the advertising ID as the device ID for tracking purposes.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Enables the use of advertising ID as device ID', 'Uses the advertising ID to uniquely identify the device.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Does not use the advertising ID for identifying the device.', 'Disables the use of advertising ID as device ID']}]}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1113,88 +1113,88 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AppBrain SDK</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tagForChildDirectedTreatment</t>
+          <t>useAppSetIdForDeviceId</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'API_name': 'tagForChildDirectedTreatment', 'class_name': ['AppBrain', 'AppBrain.Ads', 'AppBrain.getAds()'], 'conditions': ['app must be directed to children under 13', 'Know that a certain installation or use of your app falls under COPPA rule', 'requires COPPA compliance if called', 'Enable COPPA compliance when the app is installed on a child’s device', 'You know that a certain installation or use of your app falls under the COPPA rule', 'COPPA compliance is required when the app is directed to children', 'COPPA compliance is required, and the app is directed to children'], 'effects': ['enables COPPA compliance for SDK requests', 'Enables COPPA compliance for child-directed treatment', 'removes personal information from requests', 'enables COPPA compliance for all SDK requests', 'Indicates that the app is directed to children, enforcing additional privacy constraints', 'Enables COPPA compliancy for all SDK requests regarding child-directed apps'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The app is directed to children', 'The app is known to be used by children', 'The app knows it is installed on a child’s device', 'if the installation or use case falls under COPPA', "Called in Application.onCreate() when the app installation is on a child's device"], 'effects': ['Child-directed treatment is enforced', 'all requests will treat the app as COPPA compliant', 'enables child-directed treatment', 'Ensures that the app is compliant with COPPA requirements', 'COPPA compliance is enabled for all SDK requests']}, {'parameter_values': [False], 'conditions': [], 'effects': ['disables child-directed treatment']}]}</t>
+          <t>{'API_name': 'useAppSetIdForDeviceId', 'class_name': ['Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ['Allows the option to use the App Set ID as a privacy-friendly identifier.', 'Uses the app set ID as the device ID for tracking'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Uses App Set ID for device identification, which resets when the app is uninstalled.', 'Enables the use of app set ID as device ID']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Does not use the App Set ID for device identification.', 'Disables the use of app set ID as device ID']}]}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.appbrain.com/info/help/sdk/coppa.html</t>
+          <t>https://amplitude.com/docs/sdks/analytics/android/android-kotlin-sdk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AppBrain SDK</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>setUserData</t>
+          <t>locationListening</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserData', 'class_name': ['AppBrain', 'AppBrain.Ads', 'AppBrain.getAds()'], 'conditions': ["You explicitly want to inform the SDK about the current user's age", 'age information must be available to determine COPPA compliance', "the user's age must be explicitly indicated", "User's age must be specified for COPPA compliance", 'A user under 13 is using the app'], 'effects': ['Automatically enables COPPA compliance if the device carrier is based in the US', 'enables automatic COPPA compliance if the user is under 13 and the SIM-card or carrier-network is US based', 'automatically enables COPPA compliance if user is under 13 and network is in the US', 'COPPA compliance is automatically enabled for users under 13 if the SIM-card or carrier-network is based in the US', "indicates the user's age to the SDK", 'Automatically enables COPPA compliance if user is under 13 and detected in the US'], 'parameter_configurations': [{'parameter_values': ['user age'], 'conditions': [], 'effects': ['age-based COPPA compliance is enabled']}, {'parameter_values': ['user_age'], 'conditions': ['The user is under 13', 'User under 13 years old'], 'effects': ["COPPA compliance is enabled automatically based on user's SIM-card or network carrier", 'enables COPPA compliance if SIM-card or carrier-network is US based']}, {'parameter_values': [None], 'conditions': [], 'effects': []}, {'parameter_values': ['age under 13'], 'conditions': ['Explicitly enabling COPPA compliance is recommended'], 'effects': ['Ensures compliance with COPPA regulations']}, {'parameter_values': ['age 13 or older'], 'conditions': [], 'effects': []}, {'parameter_values': ['age'], 'conditions': ['The user is under 13 years old and automatic detection is based on the SIM-card or carrier-network'], 'effects': ['Recommendations to explicitly enable COPPA compliance are followed']}]}</t>
+          <t>{'API_name': 'locationListening', 'class_name': ['', 'Amplitude.Configuration', 'Amplitude'], 'conditions': [], 'effects': ["Enables tracking of the user's location", 'Enables the tracking of user location to provide more contextual analytics.', "Allows the SDK to track user's location."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ["Allows the SDK to access and track user's location information", "Enables the SDK to access and log the user's geographic coordinates.", 'The SDK tracks IP-based location data.']}, {'parameter_values': [False], 'conditions': [], 'effects': ["Prevents the SDK from accessing or tracking user's location information", 'Disables location tracking for the user.', 'Disables the SDK from tracking location data.']}]}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.appbrain.com/info/help/sdk/coppa.html</t>
+          <t>https://amplitude.com/docs/sdks/analytics/android/android-kotlin-sdk</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>AppBrain SDK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>setHasUserConsent</t>
+          <t>tagForChildDirectedTreatment</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'API_name': 'setHasUserConsent', 'class_name': ['AppLovinPrivacySettings'], 'conditions': ['Consent value must be set before initializing the AppLovin SDK', 'Consent flag must be set before initializing the AppLovin SDK', 'User must provide consent for interest-based advertising', 'User must provide consent for collecting and using personal data for interest-based advertising', 'Permission must be collected from users to process personal data', 'user must set the consent value before initializing the AppLovin SDK'], 'effects': ['Indicates whether a user has given consent to collect and use their personal data for advertising', 'the SDK respects the user consent for the lifetime of the application or until the user revokes consent', 'Indicates whether the user consented to interest-based advertising', 'Determines whether or not to request ads based on user consent', 'AppLovin SDK will respect the consent value for the lifetime of the application or until it is revoked', 'Indicates whether the user has consented to interest-based advertising'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User consents to interest-based advertising', 'User grants consent to interest-based advertising', 'user consents to interest-based advertising'], 'effects': ['allows request for ads to be made according to user consent', 'User data can be processed for interest-based advertising', 'AppLovin will continue to respect that value for the lifetime of the application or until the user revokes consent', 'User will receive ads based on interest-based targeting', 'Start requesting ads with user consent']}, {'parameter_values': [False, 'context'], 'conditions': ['User does not consent to interest-based advertising', 'User does not grant consent to interest-based advertising', 'user does not consent to interest-based advertising'], 'effects': ['User data cannot be processed for interest-based advertising', 'does not allow request for ads to be made according to user consent', 'Ads will be requested without including user data for interest-based advertising', 'User will not receive ads based on interest-based targeting', 'User will not receive personalized ads']}]}</t>
+          <t>{'API_name': 'tagForChildDirectedTreatment', 'class_name': ['AppBrain', 'AppBrain.Ads', 'AppBrain.getAds()'], 'conditions': ['app must be directed to children under 13', 'Know that a certain installation or use of your app falls under COPPA rule', 'requires COPPA compliance if called', 'Enable COPPA compliance when the app is installed on a child’s device', 'You know that a certain installation or use of your app falls under the COPPA rule', 'COPPA compliance is required when the app is directed to children', 'COPPA compliance is required, and the app is directed to children'], 'effects': ['enables COPPA compliance for SDK requests', 'Enables COPPA compliance for child-directed treatment', 'removes personal information from requests', 'enables COPPA compliance for all SDK requests', 'Indicates that the app is directed to children, enforcing additional privacy constraints', 'Enables COPPA compliancy for all SDK requests regarding child-directed apps'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The app is directed to children', 'The app is known to be used by children', 'The app knows it is installed on a child’s device', 'if the installation or use case falls under COPPA', "Called in Application.onCreate() when the app installation is on a child's device"], 'effects': ['Child-directed treatment is enforced', 'all requests will treat the app as COPPA compliant', 'enables child-directed treatment', 'Ensures that the app is compliant with COPPA requirements', 'COPPA compliance is enabled for all SDK requests']}, {'parameter_values': [False], 'conditions': [], 'effects': ['disables child-directed treatment']}]}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://developers.applovin.com/en/max/android/overview/privacy</t>
+          <t>https://www.appbrain.com/info/help/sdk/coppa.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>AppBrain SDK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>setIsAgeRestrictedUser</t>
+          <t>setUserData</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'API_name': 'setIsAgeRestrictedUser', 'class_name': ['AppLovinPrivacySettings'], 'conditions': ['user must indicate if they are in an age-restricted category', 'Must be set correctly to comply with COPPA, GDPR, and other age restrictions', 'User is under the age of 16 or as defined by applicable laws', 'Requires compliance with COPPA and GDPR age-related requirements', 'Age-related flags must be set before initializing the AppLovin SDK', 'Must indicate whether the user is under age restrictions under COPPA or applicable laws'], 'effects': ['Indicates that the user is in an age-restricted category', 'Ensures compliance with age-related advertising restrictions', 'Indicates whether the user is in an age-restricted category', 'prevents the collection of personal information from users identified as age-restricted'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User is confirmed to be in an age-restricted category', 'user is under the age of 16 or otherwise defined by applicable laws', 'User is under the age of 16 or as defined by applicable laws', 'User is under the age of 16 or defined by applicable laws as age-restricted', 'User is under age restrictions'], 'effects': ['Prohibits collection of personal information from the user and serving ads to them', 'AppLovin does not serve ads to this user', 'AppLovin will not collect personal information or serve ads to the user', 'AppLovin will not collect personal information from the user and will not serve ads to them', 'No personal information will be collected or ads served to the user']}, {'parameter_values': [False, 'context'], 'conditions': ['User is confirmed not to be in an age-restricted category', 'User is not under age restrictions', 'User is not in an age-restricted category', 'user is not in an age-restricted category'], 'effects': ['AppLovin can serve ads to this user', 'Allows the user to view ads as normal', 'User is eligible to see ads and have personal information collected', 'Personal information can be collected and ads can be served to the user', 'Permits collection of personal information and serving ads to the user']}]}</t>
+          <t>{'API_name': 'setUserData', 'class_name': ['AppBrain', 'AppBrain.Ads', 'AppBrain.getAds()'], 'conditions': ["You explicitly want to inform the SDK about the current user's age", 'age information must be available to determine COPPA compliance', "the user's age must be explicitly indicated", "User's age must be specified for COPPA compliance", 'A user under 13 is using the app'], 'effects': ['Automatically enables COPPA compliance if the device carrier is based in the US', 'enables automatic COPPA compliance if the user is under 13 and the SIM-card or carrier-network is US based', 'automatically enables COPPA compliance if user is under 13 and network is in the US', 'COPPA compliance is automatically enabled for users under 13 if the SIM-card or carrier-network is based in the US', "indicates the user's age to the SDK", 'Automatically enables COPPA compliance if user is under 13 and detected in the US'], 'parameter_configurations': [{'parameter_values': ['user age'], 'conditions': [], 'effects': ['age-based COPPA compliance is enabled']}, {'parameter_values': ['user_age'], 'conditions': ['The user is under 13', 'User under 13 years old'], 'effects': ["COPPA compliance is enabled automatically based on user's SIM-card or network carrier", 'enables COPPA compliance if SIM-card or carrier-network is US based']}, {'parameter_values': [None], 'conditions': [], 'effects': []}, {'parameter_values': ['age under 13'], 'conditions': ['Explicitly enabling COPPA compliance is recommended'], 'effects': ['Ensures compliance with COPPA regulations']}, {'parameter_values': ['age 13 or older'], 'conditions': [], 'effects': []}, {'parameter_values': ['age'], 'conditions': ['The user is under 13 years old and automatic detection is based on the SIM-card or carrier-network'], 'effects': ['Recommendations to explicitly enable COPPA compliance are followed']}]}</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://developers.applovin.com/en/max/android/overview/privacy</t>
+          <t>https://www.appbrain.com/info/help/sdk/coppa.html</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>setDoNotSell</t>
+          <t>setHasUserConsent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDoNotSell', 'class_name': ['AppLovinPrivacySettings'], 'conditions': ['Required to comply with state laws that allow users to opt-out of the sale of personal information', 'User must be from a state that requires opt-out options for personal information sale', 'Users in certain states must be allowed to opt out of data selling/sharing', "Do not sell flag must be set according to user's choice", 'required to comply with multi-state consumer privacy laws', 'Requires compliance with multi-state privacy laws in the USA'], 'effects': ['Indicates whether user opts out of the sale of their personal information', 'users can opt out of interest-based advertising and the sale of their personal information', 'Indicates whether the user opts out of the sale of their personal information', 'Indicates whether the user has opted out of the sale of their personal information'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User opts out of the sale of personal information', 'User opts out of interest-based advertising', 'User opts out of the sale of their personal information', 'user opts out of interest-based advertising'], 'effects': ["User's personal information will not be sold", "User's data will not be sold or shared", 'Personal information cannot be sold to third parties', 'User will not have their data sold or shared for advertising purposes', 'User opts out of both interest-based advertising and the sale of their personal information']}, {'parameter_values': [False, 'context'], 'conditions': ['User does not opt out of interest-based advertising', 'User does not opt out of the sale of their personal information', 'User does not opt out of the sale of personal information', 'user does not opt out of interest-based advertising'], 'effects': ['Personal information can be sold to third parties', "User's data may be sold or shared", "User's data may be sold or shared for advertising purposes", "User's information can be sold or shared", "User's personal information may be sold"]}]}</t>
+          <t>{'API_name': 'setHasUserConsent', 'class_name': ['AppLovinPrivacySettings'], 'conditions': ['Consent value must be set before initializing the AppLovin SDK', 'Consent flag must be set before initializing the AppLovin SDK', 'User must provide consent for interest-based advertising', 'User must provide consent for collecting and using personal data for interest-based advertising', 'Permission must be collected from users to process personal data', 'user must set the consent value before initializing the AppLovin SDK'], 'effects': ['Indicates whether a user has given consent to collect and use their personal data for advertising', 'the SDK respects the user consent for the lifetime of the application or until the user revokes consent', 'Indicates whether the user consented to interest-based advertising', 'Determines whether or not to request ads based on user consent', 'AppLovin SDK will respect the consent value for the lifetime of the application or until it is revoked', 'Indicates whether the user has consented to interest-based advertising'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User consents to interest-based advertising', 'User grants consent to interest-based advertising', 'user consents to interest-based advertising'], 'effects': ['allows request for ads to be made according to user consent', 'User data can be processed for interest-based advertising', 'AppLovin will continue to respect that value for the lifetime of the application or until the user revokes consent', 'User will receive ads based on interest-based targeting', 'Start requesting ads with user consent']}, {'parameter_values': [False, 'context'], 'conditions': ['User does not consent to interest-based advertising', 'User does not grant consent to interest-based advertising', 'user does not consent to interest-based advertising'], 'effects': ['User data cannot be processed for interest-based advertising', 'does not allow request for ads to be made according to user consent', 'Ads will be requested without including user data for interest-based advertising', 'User will not receive ads based on interest-based targeting', 'User will not receive personalized ads']}]}</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1223,66 +1223,66 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AppNext</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>setConsent</t>
+          <t>setIsAgeRestrictedUser</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsent', 'class_name': [''], 'conditions': ['The publisher must check the consent status on each SDK session', 'the publisher must implement a CMP if required', 'The publisher checks the consent status on each SDK session', 'required to check the consent status on each SDK session', 'The publisher should check the consent status on each SDK session', 'The consent boolean value must be passed on each SDK session'], 'effects': ['Sets the consent status for the Appnext SDK', 'Marks whether the end-user has given positive or negative consent for data processing', 'Sets the consent status for the user regarding data collection', 'sets the consent boolean value for the SDK session', 'Sets the consent status for data processing in accordance with GDPR'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['Positive consent is provided by the end-user'], 'effects': ['Allows the processing of personal data as per GDPR consent requirements', 'Appnext will proceed with data processing under the given consent.', 'Confirms the user has given consent for data collection', 'Allows Appnext SDK to process user data']}, {'parameter_values': [False, 'context'], 'conditions': ['Negative consent is provided by the end-user'], 'effects': ['Appnext will limit data processing based on the lack of consent.', 'Indicates the user has not given consent for data collection', 'Prohibits Appnext SDK from processing user data', 'Prevents the processing of personal data']}, {'parameter_values': ['context', True], 'conditions': ['Positive consent is provided by the end-user'], 'effects': ['The SDK will operate under the assumption that consent to collect personal data has been granted']}, {'parameter_values': ['context', False], 'conditions': ['Negative consent is provided by the end-user'], 'effects': ['The SDK will refrain from collecting personal data']}]}</t>
+          <t>{'API_name': 'setIsAgeRestrictedUser', 'class_name': ['AppLovinPrivacySettings'], 'conditions': ['user must indicate if they are in an age-restricted category', 'Must be set correctly to comply with COPPA, GDPR, and other age restrictions', 'User is under the age of 16 or as defined by applicable laws', 'Requires compliance with COPPA and GDPR age-related requirements', 'Age-related flags must be set before initializing the AppLovin SDK', 'Must indicate whether the user is under age restrictions under COPPA or applicable laws'], 'effects': ['Indicates that the user is in an age-restricted category', 'Ensures compliance with age-related advertising restrictions', 'Indicates whether the user is in an age-restricted category', 'prevents the collection of personal information from users identified as age-restricted'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User is confirmed to be in an age-restricted category', 'user is under the age of 16 or otherwise defined by applicable laws', 'User is under the age of 16 or as defined by applicable laws', 'User is under the age of 16 or defined by applicable laws as age-restricted', 'User is under age restrictions'], 'effects': ['Prohibits collection of personal information from the user and serving ads to them', 'AppLovin does not serve ads to this user', 'AppLovin will not collect personal information or serve ads to the user', 'AppLovin will not collect personal information from the user and will not serve ads to them', 'No personal information will be collected or ads served to the user']}, {'parameter_values': [False, 'context'], 'conditions': ['User is confirmed not to be in an age-restricted category', 'User is not under age restrictions', 'User is not in an age-restricted category', 'user is not in an age-restricted category'], 'effects': ['AppLovin can serve ads to this user', 'Allows the user to view ads as normal', 'User is eligible to see ads and have personal information collected', 'Personal information can be collected and ads can be served to the user', 'Permits collection of personal information and serving ads to the user']}]}</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://developers.appnext.com/docs/appnext-android-sdk-gdpr</t>
+          <t>https://developers.applovin.com/en/max/android/overview/privacy</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AppNexus(Xandr)</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>setConsentRequired</t>
+          <t>setDoNotSell</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsentRequired', 'class_name': ['ANGDPRSettings'], 'conditions': ['required to comply with GDPR regulations', 'The SDK is required to comply with GDPR regulations', 'Required to comply with GDPR regulations', 'User is located in the European Economic Area (EEA) and GDPR regulations should apply.', 'User is located in the European Economic Area (EEA)'], 'effects': ["indicates whether the consent is required based on user's location in the EEA", 'indicates whether GDPR regulations apply', 'Sets a flag indicating whether consent is required under GDPR.', 'Indicates whether user consent is required for processing personal data', 'Indicates whether GDPR regulations apply and is required for proper handling of user consent'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['If the user is located in the European Economic Area', 'User is located in the European Economic Area (EEA)'], 'effects': ['Data processing will comply with GDPR.', 'SDK will pass device info only when purpose consents are adequately defined', 'The SDK will pass device info only when consent is given', 'Device information will be passed to the ad server', 'the SDK will pass device info based on consent']}, {'parameter_values': [False, 'context'], 'conditions': ['If the user is not located in the European Economic Area'], 'effects': ['The SDK will pass device info regardless of user consent', 'SDK will pass device info', 'Device information will not be passed to the ad server', 'Data processing will not comply with GDPR.', 'the SDK will pass device info regardless of consent']}]}</t>
+          <t>{'API_name': 'setDoNotSell', 'class_name': ['AppLovinPrivacySettings'], 'conditions': ['Required to comply with state laws that allow users to opt-out of the sale of personal information', 'User must be from a state that requires opt-out options for personal information sale', 'Users in certain states must be allowed to opt out of data selling/sharing', "Do not sell flag must be set according to user's choice", 'required to comply with multi-state consumer privacy laws', 'Requires compliance with multi-state privacy laws in the USA'], 'effects': ['Indicates whether user opts out of the sale of their personal information', 'users can opt out of interest-based advertising and the sale of their personal information', 'Indicates whether the user opts out of the sale of their personal information', 'Indicates whether the user has opted out of the sale of their personal information'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User opts out of the sale of personal information', 'User opts out of interest-based advertising', 'User opts out of the sale of their personal information', 'user opts out of interest-based advertising'], 'effects': ["User's personal information will not be sold", "User's data will not be sold or shared", 'Personal information cannot be sold to third parties', 'User will not have their data sold or shared for advertising purposes', 'User opts out of both interest-based advertising and the sale of their personal information']}, {'parameter_values': [False, 'context'], 'conditions': ['User does not opt out of interest-based advertising', 'User does not opt out of the sale of their personal information', 'User does not opt out of the sale of personal information', 'user does not opt out of interest-based advertising'], 'effects': ['Personal information can be sold to third parties', "User's data may be sold or shared", "User's data may be sold or shared for advertising purposes", "User's information can be sold or shared", "User's personal information may be sold"]}]}</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/xandr/mobile-sdk/sdk-privacy-for-android</t>
+          <t>https://developers.applovin.com/en/max/android/overview/privacy</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AppNexus(Xandr)</t>
+          <t>AppNext</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>setConsentString</t>
+          <t>setConsent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsentString', 'class_name': ['ANGDPRSettings'], 'conditions': ['Consent string must be valid and follow the specified format', 'the consent string must be valid and Base64 encoded as per IAB framework', 'Consent string must be a valid Base64 encoded string'], 'effects': ['Sets the consent string that will be sent to the ad server', 'Sets the consent string that will be passed with ad calls', 'sets the consent string that will be sent with ad requests', 'sets the consent string for GDPR compliance', 'Sets the Base64 encoded consent string in the SDK.'], 'parameter_configurations': [{'parameter_values': ['BOMyQRvOMyQRvABABBAAABAAAAAAEA', 'context'], 'conditions': ['The consent string must be valid as per the IAB Framework.'], 'effects': ['The consent string is established in the SDK', 'The SDK will include this consent string in ad calls.', 'consent string enables proper ad targeting based on user permissions']}]}</t>
+          <t>{'API_name': 'setConsent', 'class_name': [''], 'conditions': ['The publisher must check the consent status on each SDK session', 'the publisher must implement a CMP if required', 'The publisher checks the consent status on each SDK session', 'required to check the consent status on each SDK session', 'The publisher should check the consent status on each SDK session', 'The consent boolean value must be passed on each SDK session'], 'effects': ['Sets the consent status for the Appnext SDK', 'Marks whether the end-user has given positive or negative consent for data processing', 'Sets the consent status for the user regarding data collection', 'sets the consent boolean value for the SDK session', 'Sets the consent status for data processing in accordance with GDPR'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['Positive consent is provided by the end-user'], 'effects': ['Allows the processing of personal data as per GDPR consent requirements', 'Appnext will proceed with data processing under the given consent.', 'Confirms the user has given consent for data collection', 'Allows Appnext SDK to process user data']}, {'parameter_values': [False, 'context'], 'conditions': ['Negative consent is provided by the end-user'], 'effects': ['Appnext will limit data processing based on the lack of consent.', 'Indicates the user has not given consent for data collection', 'Prohibits Appnext SDK from processing user data', 'Prevents the processing of personal data']}, {'parameter_values': ['context', True], 'conditions': ['Positive consent is provided by the end-user'], 'effects': ['The SDK will operate under the assumption that consent to collect personal data has been granted']}, {'parameter_values': ['context', False], 'conditions': ['Negative consent is provided by the end-user'], 'effects': ['The SDK will refrain from collecting personal data']}]}</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/xandr/mobile-sdk/sdk-privacy-for-android</t>
+          <t>https://developers.appnext.com/docs/appnext-android-sdk-gdpr</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>setPurposeConsents</t>
+          <t>setConsentRequired</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPurposeConsents', 'class_name': ['ANGDPRSettings'], 'conditions': ['the binary string must correctly represent consent statuses for each purpose ID', 'Purpose consents must be provided as a valid binary string'], 'effects': ['sets consent for specific purposes according to GDPR', 'sets user consent for specific purposes impacting handling of personal data', 'Indicates user consent for specific purposes defined by IAB', 'Defines the consent statuses for various purposes based on the provided binary string', 'Sets the purpose consents for various data processing purposes.'], 'parameter_configurations': [{'parameter_values': ['101010001', 'context'], 'conditions': [], 'effects': ['determines whether device information is shared based on consent for each purpose', 'The purpose consents are set in the SDK', 'The SDK will respect the purpose consents set for advertisements.']}]}</t>
+          <t>{'API_name': 'setConsentRequired', 'class_name': ['ANGDPRSettings'], 'conditions': ['required to comply with GDPR regulations', 'The SDK is required to comply with GDPR regulations', 'Required to comply with GDPR regulations', 'User is located in the European Economic Area (EEA) and GDPR regulations should apply.', 'User is located in the European Economic Area (EEA)'], 'effects': ["indicates whether the consent is required based on user's location in the EEA", 'indicates whether GDPR regulations apply', 'Sets a flag indicating whether consent is required under GDPR.', 'Indicates whether user consent is required for processing personal data', 'Indicates whether GDPR regulations apply and is required for proper handling of user consent'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['If the user is located in the European Economic Area', 'User is located in the European Economic Area (EEA)'], 'effects': ['Data processing will comply with GDPR.', 'SDK will pass device info only when purpose consents are adequately defined', 'The SDK will pass device info only when consent is given', 'Device information will be passed to the ad server', 'the SDK will pass device info based on consent']}, {'parameter_values': [False, 'context'], 'conditions': ['If the user is not located in the European Economic Area'], 'effects': ['The SDK will pass device info regardless of user consent', 'SDK will pass device info', 'Device information will not be passed to the ad server', 'Data processing will not comply with GDPR.', 'the SDK will pass device info regardless of consent']}]}</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>setUSPrivacyString</t>
+          <t>setConsentString</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUSPrivacyString', 'class_name': ['ANUSPrivacySettings'], 'conditions': ['Privacy string must comply with IAB US Privacy framework', 'PrivacyString must be valid for user signal mechanism controls according to US laws', "the privacy string must adhere to IAB's US Privacy Compliance Mechanism"], 'effects': ['Sets the IAB US Privacy String in the SDK.', 'Sets the US Privacy String that will be sent in ad requests', 'sets the IAB US Privacy String for CCPA compliance', 'Sets the IAB US Privacy String which will be sent with ad requests', 'sets the US privacy string to communicate user preferences under CCPA'], 'parameter_configurations': [{'parameter_values': ['1YNN', 'context'], 'conditions': [], 'effects': ['The privacy considerations under CCPA will be applied.', 'influences data handling practices in accordance with user privacy preferences', 'US Privacy settings are defined in the SDK']}]}</t>
+          <t>{'API_name': 'setConsentString', 'class_name': ['ANGDPRSettings'], 'conditions': ['Consent string must be valid and follow the specified format', 'the consent string must be valid and Base64 encoded as per IAB framework', 'Consent string must be a valid Base64 encoded string'], 'effects': ['Sets the consent string that will be sent to the ad server', 'Sets the consent string that will be passed with ad calls', 'sets the consent string that will be sent with ad requests', 'sets the consent string for GDPR compliance', 'Sets the Base64 encoded consent string in the SDK.'], 'parameter_configurations': [{'parameter_values': ['BOMyQRvOMyQRvABABBAAABAAAAAAEA', 'context'], 'conditions': ['The consent string must be valid as per the IAB Framework.'], 'effects': ['The consent string is established in the SDK', 'The SDK will include this consent string in ad calls.', 'consent string enables proper ad targeting based on user permissions']}]}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>getUSPrivacyString</t>
+          <t>setPurposeConsents</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'API_name': 'getUSPrivacyString', 'class_name': ['ANUSPrivacySettings'], 'conditions': [], 'effects': ['Retrieves the currently set IAB US Privacy String', 'Retrieves the IAB US Privacy String set by the publisher', 'retrieves the currently set US privacy string', 'Retrieves the IAB US Privacy String currently set.', 'retrieves the IAB US Privacy String set by Publisher'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setPurposeConsents', 'class_name': ['ANGDPRSettings'], 'conditions': ['the binary string must correctly represent consent statuses for each purpose ID', 'Purpose consents must be provided as a valid binary string'], 'effects': ['sets consent for specific purposes according to GDPR', 'sets user consent for specific purposes impacting handling of personal data', 'Indicates user consent for specific purposes defined by IAB', 'Defines the consent statuses for various purposes based on the provided binary string', 'Sets the purpose consents for various data processing purposes.'], 'parameter_configurations': [{'parameter_values': ['101010001', 'context'], 'conditions': [], 'effects': ['determines whether device information is shared based on consent for each purpose', 'The purpose consents are set in the SDK', 'The SDK will respect the purpose consents set for advertisements.']}]}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>setUSPrivacyString</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'API_name': 'reset', 'class_name': ['ANUSPrivacySettings'], 'conditions': [], 'effects': ['Clears the previously set IAB US Privacy String', 'clears the previously set IAB US Privacy String', 'Clears the IAB US Privacy String that was previously set.', 'clears the previously set US privacy string', 'Clears previously set IAB US Privacy String'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setUSPrivacyString', 'class_name': ['ANUSPrivacySettings'], 'conditions': ['Privacy string must comply with IAB US Privacy framework', 'PrivacyString must be valid for user signal mechanism controls according to US laws', "the privacy string must adhere to IAB's US Privacy Compliance Mechanism"], 'effects': ['Sets the IAB US Privacy String in the SDK.', 'Sets the US Privacy String that will be sent in ad requests', 'sets the IAB US Privacy String for CCPA compliance', 'Sets the IAB US Privacy String which will be sent with ad requests', 'sets the US privacy string to communicate user preferences under CCPA'], 'parameter_configurations': [{'parameter_values': ['1YNN', 'context'], 'conditions': [], 'effects': ['The privacy considerations under CCPA will be applied.', 'influences data handling practices in accordance with user privacy preferences', 'US Privacy settings are defined in the SDK']}]}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>setDSARequired</t>
+          <t>getUSPrivacyString</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDSARequired', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['Sets the requirement level for DSA information in ad requests', 'sets the requirement level for DSA information in ad responses', 'Sets DSA information requirement for ad responses', 'sets the DSA information requirement value', 'Sets the requirement for DSA information in ad requests.'], 'parameter_configurations': [{'parameter_values': [1], 'conditions': [], 'effects': ['Indicates that DSA information is required', 'Bid responses without DSA object will be accepted.', 'indicates that bid responses will be accepted whether or not DSA information is included']}]}</t>
+          <t>{'API_name': 'getUSPrivacyString', 'class_name': ['ANUSPrivacySettings'], 'conditions': [], 'effects': ['Retrieves the currently set IAB US Privacy String', 'Retrieves the IAB US Privacy String set by the publisher', 'retrieves the currently set US privacy string', 'Retrieves the IAB US Privacy String currently set.', 'retrieves the IAB US Privacy String set by Publisher'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>setPubRender</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPubRender', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['indicates whether the publisher can render DSA transparency information', 'Indicates if the publisher can render DSA transparency information', 'sets whether the publisher can render DSA transparency info', 'Sets whether the publisher can render DSA transparency information.', 'Sets whether the publisher can render DSA transparency info'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['Indicates that the publisher cannot render DSA information', 'Publisher cannot render DSA transparency information.', 'denotes that the publisher cannot render transparency information']}]}</t>
+          <t>{'API_name': 'reset', 'class_name': ['ANUSPrivacySettings'], 'conditions': [], 'effects': ['Clears the previously set IAB US Privacy String', 'clears the previously set IAB US Privacy String', 'Clears the IAB US Privacy String that was previously set.', 'clears the previously set US privacy string', 'Clears previously set IAB US Privacy String'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>setTransparencyList</t>
+          <t>setDSARequired</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'API_name': 'setTransparencyList', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['sets the transparency list for DSA compliance', 'establishes the list of transparency information regarding ad delivery', 'Sets the transparency list for ad rendering.', 'Sets the transparency list with user parameters in the SDK', 'Sets the transparency list for ad responses containing DSA information'], 'parameter_configurations': [{'parameter_values': ['example.com', [1, 2, 3]], 'conditions': [], 'effects': ['provides specific transparency information to be included in ad calls']}, {'parameter_values': ['example.net', [4, 5, 6]], 'conditions': [], 'effects': []}, {'parameter_values': [['example.com', [1, 2, 3]], ['example.net', [4, 5, 6]]], 'conditions': [], 'effects': ['Transparency information will be passed to ad calls.']}, {'parameter_values': ['example.com', '[1, 2, 3]'], 'conditions': [], 'effects': ['Sets the specified transparency info for the domain']}]}</t>
+          <t>{'API_name': 'setDSARequired', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['Sets the requirement level for DSA information in ad requests', 'sets the requirement level for DSA information in ad responses', 'Sets DSA information requirement for ad responses', 'sets the DSA information requirement value', 'Sets the requirement for DSA information in ad requests.'], 'parameter_configurations': [{'parameter_values': [1], 'conditions': [], 'effects': ['Indicates that DSA information is required', 'Bid responses without DSA object will be accepted.', 'indicates that bid responses will be accepted whether or not DSA information is included']}]}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>getDSARequired</t>
+          <t>setPubRender</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'API_name': 'getDSARequired', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['retrieves the DSA information requirement value', 'Retrieves the DSA requirement value set in the SDK', 'Retrieves the DSA information requirement level set in the SDK', 'Retrieves the DSA information requirement value set in the SDK.', 'retrieves the current DSA requirement setting'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setPubRender', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['indicates whether the publisher can render DSA transparency information', 'Indicates if the publisher can render DSA transparency information', 'sets whether the publisher can render DSA transparency info', 'Sets whether the publisher can render DSA transparency information.', 'Sets whether the publisher can render DSA transparency info'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['Indicates that the publisher cannot render DSA information', 'Publisher cannot render DSA transparency information.', 'denotes that the publisher cannot render transparency information']}]}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>getPubRender</t>
+          <t>setTransparencyList</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'API_name': 'getPubRender', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['retrieves the DSA render status', 'Retrieves whether the publisher can render DSA transparency information.', 'Retrieves whether the publisher is able to render DSA transparency info', 'Retrieves the publishing rendering details for DSA info', 'retrieves the current publisher render setting for DSA transparency'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setTransparencyList', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['sets the transparency list for DSA compliance', 'establishes the list of transparency information regarding ad delivery', 'Sets the transparency list for ad rendering.', 'Sets the transparency list with user parameters in the SDK', 'Sets the transparency list for ad responses containing DSA information'], 'parameter_configurations': [{'parameter_values': ['example.com', [1, 2, 3]], 'conditions': [], 'effects': ['provides specific transparency information to be included in ad calls']}, {'parameter_values': ['example.net', [4, 5, 6]], 'conditions': [], 'effects': []}, {'parameter_values': [['example.com', [1, 2, 3]], ['example.net', [4, 5, 6]]], 'conditions': [], 'effects': ['Transparency information will be passed to ad calls.']}, {'parameter_values': ['example.com', '[1, 2, 3]'], 'conditions': [], 'effects': ['Sets the specified transparency info for the domain']}]}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>getTransparencyList</t>
+          <t>getDSARequired</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'API_name': 'getTransparencyList', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['retrieves the list of transparency information previously set', 'Retrieves the transparency list set in the SDK', 'Retrieves the transparency list set in the SDK.', 'retrieves the DSA transparency list values', 'Retrieves the transparency list that was set in the SDK'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'getDSARequired', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['retrieves the DSA information requirement value', 'Retrieves the DSA requirement value set in the SDK', 'Retrieves the DSA information requirement level set in the SDK', 'Retrieves the DSA information requirement value set in the SDK.', 'retrieves the current DSA requirement setting'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1509,44 +1509,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Appodeal</t>
+          <t>AppNexus(Xandr)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>setChildDirectedTreatment</t>
+          <t>getPubRender</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'API_name': 'setChildDirectedTreatment', 'class_name': ['Appodeal'], 'conditions': ['If your app is designed for kids', 'Call with true for child-directed content under COPPA regulations', 'if your app is designed for kids', 'should be called before the SDK initialization', 'Should be called before the SDK initialization', 'If the app is designed for kids'], 'effects': ['Indicates whether the content is treated as child-directed for purposes of COPPA', 'indicates whether the content is treated as child-directed for purposes of COPPA', 'disables sending user data to ad networks if set to true', 'Disables sending user data to ad networks if set to true', 'Indicates whether to treat content as child-directed for purposes of COPPA', 'indicates whether content is treated as child-directed for purposes of COPPA'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['app is designed for kids', 'indicates content is child-directed according to COPPA', 'If content is child-directed', 'Use this value if the app is designed for kids'], 'effects': ['User data will not be sent to ad networks', 'user data is not sent to ad networks', 'disables sending user data to ad networks for a child-directed app']}, {'parameter_values': [False], 'conditions': ['Use this value if the app is not designed for kids', 'indicates content is not child-directed according to COPPA', 'If content is not child-directed'], 'effects': ['User data may be sent to ad networks', 'user data may be sent to ad networks', 'indicates that the app is not directed towards children, allowing data collection']}, {'parameter_values': [None], 'conditions': ["uses the COPPA parameter from the application's settings", "Indicates to use COPPA parameter from app's settings"], 'effects': ["Uses the COPPA parameter from the application's settings", "uses the COPPA parameter from the application's settings", "Uses the COPPA parameter from the application's settings on Appodeal", 'follows the COPPA parameter defined in app settings']}]}</t>
+          <t>{'API_name': 'getPubRender', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['retrieves the DSA render status', 'Retrieves whether the publisher can render DSA transparency information.', 'Retrieves whether the publisher is able to render DSA transparency info', 'Retrieves the publishing rendering details for DSA info', 'retrieves the current publisher render setting for DSA transparency'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://docs.appodeal.com/android/data-protection/gdpr-and-ccpa;https://docs.appodeal.com/android/data-protection/coppa</t>
+          <t>https://learn.microsoft.com/en-us/xandr/mobile-sdk/sdk-privacy-for-android</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Appodeal</t>
+          <t>AppNexus(Xandr)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>requestConsentInfoUpdate</t>
+          <t>getTransparencyList</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'API_name': 'requestConsentInfoUpdate', 'class_name': ['ConsentManager'], 'conditions': ['can be requested at any moment of the application lifecycle', 'recommended to call at application launch', 'Required parameters must include YOUR_APP_KEY', 'recommended to be called at application launch', 'Consent can be requested at any moment of the application lifecycle', 'Required parameters: YOUR_APP_KEY must be provided', 'Can be requested at any moment of the application lifecycle', 'Multiple request calls are allowed'], 'effects': ["Updates the user's consent status effectively", "Updates the user's consent status successfully or fails to do so", "updates the user's consent status based on current settings", 'Multiple request calls are allowed', "Updates the user's consent status", 'updates the consent status of the user'], 'parameter_configurations': [{'parameter_values': ['YOUR_APP_KEY', False, 'Appodeal', 'Appodeal.getVersion()'], 'conditions': [], 'effects': ["User's consent status successfully updated", 'initiates a consent update request']}, {'parameter_values': ['YourActivity', 'YOUR_APP_KEY', False, 'Appodeal', 'Appodeal.getVersion()'], 'conditions': ['requires valid Appodeal app key', 'Can be called at any point during the application lifecycle', 'Recommended to call at application launch'], 'effects': ["User's consent status successfully updated", 'updates consent status for the user associated with the provided key']}]}</t>
+          <t>{'API_name': 'getTransparencyList', 'class_name': ['ANDSASettings'], 'conditions': [], 'effects': ['retrieves the list of transparency information previously set', 'Retrieves the transparency list set in the SDK', 'Retrieves the transparency list set in the SDK.', 'retrieves the DSA transparency list values', 'Retrieves the transparency list that was set in the SDK'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://docs.appodeal.com/android/data-protection/gdpr-and-ccpa;https://docs.appodeal.com/android/data-protection/coppa</t>
+          <t>https://learn.microsoft.com/en-us/xandr/mobile-sdk/sdk-privacy-for-android</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>revoke</t>
+          <t>setChildDirectedTreatment</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'API_name': 'revoke', 'class_name': ['ConsentManager'], 'conditions': ['Context must be provided', 'Context must be provided in which consent is revoked', 'requires the context in which consent is revoked', 'requires context for which consent is being revoked'], 'effects': ['sets the consent status back to unknown', 'resets the consent status to unknown', 'Resets the consent status to unknown'], 'parameter_configurations': [{'parameter_values': ['YourActivity.this'], 'conditions': [], 'effects': ['User consent is revoked']}, {'parameter_values': ['YourActivity'], 'conditions': [], 'effects': ["revokes the user's consent status", 'state of consent switches to unknown after revocation']}, {'parameter_values': ['YourActivity@this'], 'conditions': [], 'effects': ['Consent status is revoked']}]}</t>
+          <t>{'API_name': 'setChildDirectedTreatment', 'class_name': ['Appodeal'], 'conditions': ['If your app is designed for kids', 'Call with true for child-directed content under COPPA regulations', 'if your app is designed for kids', 'should be called before the SDK initialization', 'Should be called before the SDK initialization', 'If the app is designed for kids'], 'effects': ['Indicates whether the content is treated as child-directed for purposes of COPPA', 'indicates whether the content is treated as child-directed for purposes of COPPA', 'disables sending user data to ad networks if set to true', 'Disables sending user data to ad networks if set to true', 'Indicates whether to treat content as child-directed for purposes of COPPA', 'indicates whether content is treated as child-directed for purposes of COPPA'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['app is designed for kids', 'indicates content is child-directed according to COPPA', 'If content is child-directed', 'Use this value if the app is designed for kids'], 'effects': ['User data will not be sent to ad networks', 'user data is not sent to ad networks', 'disables sending user data to ad networks for a child-directed app']}, {'parameter_values': [False], 'conditions': ['Use this value if the app is not designed for kids', 'indicates content is not child-directed according to COPPA', 'If content is not child-directed'], 'effects': ['User data may be sent to ad networks', 'user data may be sent to ad networks', 'indicates that the app is not directed towards children, allowing data collection']}, {'parameter_values': [None], 'conditions': ["uses the COPPA parameter from the application's settings", "Indicates to use COPPA parameter from app's settings"], 'effects': ["Uses the COPPA parameter from the application's settings", "uses the COPPA parameter from the application's settings", "Uses the COPPA parameter from the application's settings on Appodeal", 'follows the COPPA parameter defined in app settings']}]}</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1575,44 +1575,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AppsFlyer</t>
+          <t>Appodeal</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>anonymizeUser</t>
+          <t>requestConsentInfoUpdate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'API_name': 'anonymizeUser', 'class_name': ['AppsFlyerLib'], 'conditions': ['The user prefers to anonymize their personal data.'], 'effects': ['All identifying data (such as personal identifiers, AppsFlyer ID, and IP address) is deleted or hashed before being sent to AppsFlyer.', "Anonymizes a user's installs, events, and sessions by removing or hashing identifiers", "Anonymizes user's installs, events, and sessions by deleting or hashing identifying information.", 'Anonymizes user installs, events, and sessions by deleting or hashing identifying information.', "Anonymizes a user's installs, events, and sessions."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['All personal identifiers (GAID, IDFA, IDFV, and CUID) will be deleted and AppsFlyer ID and IP address will be hashed.', 'All identifiers, including IP address, are deleted or hashed.', 'User data is anonymized when sent to AppsFlyer.', 'Sends data to AppsFlyer with all identifiers deleted or hashed.', 'Personal identifiers are deleted and AppsFlyer ID and IP address are hashed.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['No anonymization of user data.', 'User data is not anonymized when sent to AppsFlyer.']}]}</t>
+          <t>{'API_name': 'requestConsentInfoUpdate', 'class_name': ['ConsentManager'], 'conditions': ['can be requested at any moment of the application lifecycle', 'recommended to call at application launch', 'Required parameters must include YOUR_APP_KEY', 'recommended to be called at application launch', 'Consent can be requested at any moment of the application lifecycle', 'Required parameters: YOUR_APP_KEY must be provided', 'Can be requested at any moment of the application lifecycle', 'Multiple request calls are allowed'], 'effects': ["Updates the user's consent status effectively", "Updates the user's consent status successfully or fails to do so", "updates the user's consent status based on current settings", 'Multiple request calls are allowed', "Updates the user's consent status", 'updates the consent status of the user'], 'parameter_configurations': [{'parameter_values': ['YOUR_APP_KEY', False, 'Appodeal', 'Appodeal.getVersion()'], 'conditions': [], 'effects': ["User's consent status successfully updated", 'initiates a consent update request']}, {'parameter_values': ['YourActivity', 'YOUR_APP_KEY', False, 'Appodeal', 'Appodeal.getVersion()'], 'conditions': ['requires valid Appodeal app key', 'Can be called at any point during the application lifecycle', 'Recommended to call at application launch'], 'effects': ["User's consent status successfully updated", 'updates consent status for the user associated with the provided key']}]}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://dev.appsflyer.com/hc/docs/preserve-user-privacy-android;https://dev.appsflyer.com/hc/docs/android-sdk-reference-appsflyerlib#anonymizeuser;https://dev.appsflyer.com/hc/docs/android-send-consent-for-dma-compliance</t>
+          <t>https://docs.appodeal.com/android/data-protection/gdpr-and-ccpa;https://docs.appodeal.com/android/data-protection/coppa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AppsFlyer</t>
+          <t>Appodeal</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>setSharingFilterForPartners</t>
+          <t>revoke</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSharingFilterForPartners', 'class_name': ['AppsFlyerLib'], 'conditions': ["Call this method before 'start' to prevent data sharing."], 'effects': ['Excludes certain partners from receiving user data.', 'Excludes specified partners from receiving data.', 'Prevents sharing install and in-app event information with specified partners.'], 'parameter_configurations': [{'parameter_values': ['partner1_int', 'partner2_int'], 'conditions': [], 'effects': ['Selected partners will not receive data.', 'Specified partners will not receive data through postbacks, APIs, or reports.']}, {'parameter_values': ['all'], 'conditions': [], 'effects': ['All partners are excluded from data sharing.', 'Excludes all partners from data sharing.', 'Prevents all partners from receiving data.']}, {'parameter_values': ['partner1_int'], 'conditions': [], 'effects': ['Specified partner is excluded from data sharing.']}, {'parameter_values': ['String... partners'], 'conditions': ['This method must be called before the SDK is started.'], 'effects': ['Data is not shared with the specified partners.', 'Specified partners will not receive data through APIs or raw data reports.']}]}</t>
+          <t>{'API_name': 'revoke', 'class_name': ['ConsentManager'], 'conditions': ['Context must be provided', 'Context must be provided in which consent is revoked', 'requires the context in which consent is revoked', 'requires context for which consent is being revoked'], 'effects': ['sets the consent status back to unknown', 'resets the consent status to unknown', 'Resets the consent status to unknown'], 'parameter_configurations': [{'parameter_values': ['YourActivity.this'], 'conditions': [], 'effects': ['User consent is revoked']}, {'parameter_values': ['YourActivity'], 'conditions': [], 'effects': ["revokes the user's consent status", 'state of consent switches to unknown after revocation']}, {'parameter_values': ['YourActivity@this'], 'conditions': [], 'effects': ['Consent status is revoked']}]}</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://dev.appsflyer.com/hc/docs/preserve-user-privacy-android;https://dev.appsflyer.com/hc/docs/android-sdk-reference-appsflyerlib#anonymizeuser;https://dev.appsflyer.com/hc/docs/android-send-consent-for-dma-compliance</t>
+          <t>https://docs.appodeal.com/android/data-protection/gdpr-and-ccpa;https://docs.appodeal.com/android/data-protection/coppa</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>setDisableAdvertisingIdentifiers</t>
+          <t>anonymizeUser</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDisableAdvertisingIdentifiers', 'class_name': ['AppsFlyerLib'], 'conditions': ['Should be set before calling start.'], 'effects': ['Disables collection of various Advertising IDs.', 'Disables collection of all advertising IDs.', 'Disables collection of advertising identifiers like GAID and OAID.', 'Disables the collection of various Advertising IDs by the SDK.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts out of providing advertising identifiers.'], 'effects': ['Prevents the SDK from collecting Google Advertising ID (GAID), OAID, and Amazon Advertising ID (AAID).', 'All advertising IDs will not be collected.', 'Prevents the collection of Google Advertising ID (GAID), OAID, and Amazon Advertising ID (AAID).', 'No advertising identifiers (GAID, OAID, and AAID) will be collected by the SDK.', 'Advertising identifiers collection is disabled.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Advertising identifiers collection is enabled.', 'The SDK will collect advertising identifiers.']}]}</t>
+          <t>{'API_name': 'anonymizeUser', 'class_name': ['AppsFlyerLib'], 'conditions': ['The user prefers to anonymize their personal data.'], 'effects': ['All identifying data (such as personal identifiers, AppsFlyer ID, and IP address) is deleted or hashed before being sent to AppsFlyer.', "Anonymizes a user's installs, events, and sessions by removing or hashing identifiers", "Anonymizes user's installs, events, and sessions by deleting or hashing identifying information.", 'Anonymizes user installs, events, and sessions by deleting or hashing identifying information.', "Anonymizes a user's installs, events, and sessions."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['All personal identifiers (GAID, IDFA, IDFV, and CUID) will be deleted and AppsFlyer ID and IP address will be hashed.', 'All identifiers, including IP address, are deleted or hashed.', 'User data is anonymized when sent to AppsFlyer.', 'Sends data to AppsFlyer with all identifiers deleted or hashed.', 'Personal identifiers are deleted and AppsFlyer ID and IP address are hashed.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['No anonymization of user data.', 'User data is not anonymized when sent to AppsFlyer.']}]}</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>setCollectOaid</t>
+          <t>setSharingFilterForPartners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCollectOaid', 'class_name': ['AppsFlyerLib'], 'conditions': [], 'effects': ['Enables or disables the collection of OAID.', 'Opt-in/opt-out of OAID collection.'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': [], 'effects': ['SDK does not collect OAID.', 'OAID will not be collected by the SDK.']}, {'parameter_values': [True], 'conditions': [], 'effects': ['SDK collects OAID.']}]}</t>
+          <t>{'API_name': 'setSharingFilterForPartners', 'class_name': ['AppsFlyerLib'], 'conditions': ["Call this method before 'start' to prevent data sharing."], 'effects': ['Excludes certain partners from receiving user data.', 'Excludes specified partners from receiving data.', 'Prevents sharing install and in-app event information with specified partners.'], 'parameter_configurations': [{'parameter_values': ['partner1_int', 'partner2_int'], 'conditions': [], 'effects': ['Selected partners will not receive data.', 'Specified partners will not receive data through postbacks, APIs, or reports.']}, {'parameter_values': ['all'], 'conditions': [], 'effects': ['All partners are excluded from data sharing.', 'Excludes all partners from data sharing.', 'Prevents all partners from receiving data.']}, {'parameter_values': ['partner1_int'], 'conditions': [], 'effects': ['Specified partner is excluded from data sharing.']}, {'parameter_values': ['String... partners'], 'conditions': ['This method must be called before the SDK is started.'], 'effects': ['Data is not shared with the specified partners.', 'Specified partners will not receive data through APIs or raw data reports.']}]}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>enableTCFDataCollection</t>
+          <t>setDisableAdvertisingIdentifiers</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'API_name': 'enableTCFDataCollection', 'class_name': ['AppsFlyerLib'], 'conditions': ['Requires initialization of the SDK before this call.', 'The app must be using a TCF v2.2 compliant Consent Management Platform.'], 'effects': ['Enables the collection of Transparency and Consent Framework (TCF) data.', 'Allows the SDK to automatically retrieve TCF consent data from SharedPreferences.', 'Enables the collection of Transparency and Consent Framework (TCF) data from SharedPreferences.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['When TCF data is available in SharedPreferences.', 'A TCF v2.2 compatible Consent Management Platform (CMP) is being used'], 'effects': ['SDK collects TCF data from SharedPreferences.', 'The SDK collects TCF data when set to true.', 'SDK starts collecting TCF data.', 'TCF data collection is enabled, and the SDK starts collecting consent data.', 'The SDK collects TCF consent data from the device.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Disables TCF data collection', 'TCF data collection is disabled.']}]}</t>
+          <t>{'API_name': 'setDisableAdvertisingIdentifiers', 'class_name': ['AppsFlyerLib'], 'conditions': ['Should be set before calling start.'], 'effects': ['Disables collection of various Advertising IDs.', 'Disables collection of all advertising IDs.', 'Disables collection of advertising identifiers like GAID and OAID.', 'Disables the collection of various Advertising IDs by the SDK.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts out of providing advertising identifiers.'], 'effects': ['Prevents the SDK from collecting Google Advertising ID (GAID), OAID, and Amazon Advertising ID (AAID).', 'All advertising IDs will not be collected.', 'Prevents the collection of Google Advertising ID (GAID), OAID, and Amazon Advertising ID (AAID).', 'No advertising identifiers (GAID, OAID, and AAID) will be collected by the SDK.', 'Advertising identifiers collection is disabled.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Advertising identifiers collection is enabled.', 'The SDK will collect advertising identifiers.']}]}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>setConsentData</t>
+          <t>setCollectOaid</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsentData', 'class_name': ['AppsFlyerLib'], 'conditions': ['GDPR applies to the user or user consent is necessary.', 'The app must be initialized to collect consent data.'], 'effects': ['Transfers consent data to the SDK, impacting how user data is handled.', 'Transfers the consent data to the SDK.', 'Enables AppsFlyer to respect user consent preferences for data usage and personalization.', 'Transfers consent data to the SDK.'], 'parameter_configurations': [{'parameter_values': ['AppsFlyerConsent object for GDPR user'], 'conditions': ['GDPR applies'], 'effects': ['Sets the consent data for GDPR compliance.']}, {'parameter_values': ['AppsFlyerConsent object for non-GDPR user'], 'conditions': ['GDPR does not apply'], 'effects': ['Sets the consent data for non-GDPR compliance.']}, {'parameter_values': ['AppsFlyerConsent'], 'conditions': ['The app is compliant with GDPR if applicable.'], 'effects': ['Consent data is sent to AppsFlyer with every event.']}, {'parameter_values': ['AppsFlyerConsent object'], 'conditions': ['Must provide user consent data.', 'User has provided consent.'], 'effects': ['Consent data is sent with every event logged by the SDK.', 'Consent data is sent with each event.']}, {'parameter_values': ['AppsFlyerConsent.forGDPRUser(hasConsentForDataUsage, hasConsentForAdsPersonalization)'], 'conditions': ['GDPR applies to the user.'], 'effects': ['Sets consent data for GDPR compliance.']}, {'parameter_values': ['AppsFlyerConsent.forNonGDPRUser()'], 'conditions': ['GDPR does not apply to the user.'], 'effects': ['Sets consent data for users not subject to GDPR.']}]}</t>
+          <t>{'API_name': 'setCollectOaid', 'class_name': ['AppsFlyerLib'], 'conditions': [], 'effects': ['Enables or disables the collection of OAID.', 'Opt-in/opt-out of OAID collection.'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': [], 'effects': ['SDK does not collect OAID.', 'OAID will not be collected by the SDK.']}, {'parameter_values': [True], 'conditions': [], 'effects': ['SDK collects OAID.']}]}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1707,44 +1707,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>AppsFlyer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>disableTracking</t>
+          <t>enableTCFDataCollection</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'API_name': 'disableTracking', 'class_name': ['Branch'], 'conditions': [], 'effects': ['If disabled, the Branch Android SDK will not track any user data or state.', 'The SDK will not send any network calls, except for deep linking, when tracking is disabled.', 'The Branch Android SDK will not track any user data or state.', 'When set to true, Branch SDK will not track any user data or state.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Tracking is disabled.', 'SDK will not send any network calls, except for deep linking.', 'No tracking of user data results in reduced analytics capabilities.', 'No network calls will be sent except for deep linking.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Tracking is enabled.', 'Tracking is enabled for the Branch SDK.', 'Tracking is enabled, allowing the collection of user data.', 'SDK resumes tracking user data and state.']}]}</t>
+          <t>{'API_name': 'enableTCFDataCollection', 'class_name': ['AppsFlyerLib'], 'conditions': ['Requires initialization of the SDK before this call.', 'The app must be using a TCF v2.2 compliant Consent Management Platform.'], 'effects': ['Enables the collection of Transparency and Consent Framework (TCF) data.', 'Allows the SDK to automatically retrieve TCF consent data from SharedPreferences.', 'Enables the collection of Transparency and Consent Framework (TCF) data from SharedPreferences.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['When TCF data is available in SharedPreferences.', 'A TCF v2.2 compatible Consent Management Platform (CMP) is being used'], 'effects': ['SDK collects TCF data from SharedPreferences.', 'The SDK collects TCF data when set to true.', 'SDK starts collecting TCF data.', 'TCF data collection is enabled, and the SDK starts collecting consent data.', 'The SDK collects TCF consent data from the device.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Disables TCF data collection', 'TCF data collection is disabled.']}]}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://help.branch.io/developers-hub/docs/android-full-reference#disabletracking</t>
+          <t>https://dev.appsflyer.com/hc/docs/preserve-user-privacy-android;https://dev.appsflyer.com/hc/docs/android-sdk-reference-appsflyerlib#anonymizeuser;https://dev.appsflyer.com/hc/docs/android-send-consent-for-dma-compliance</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>AppsFlyer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>setLimitFacebookTracking</t>
+          <t>setConsentData</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLimitFacebookTracking', 'class_name': ['Branch'], 'conditions': [], 'effects': ['Enables or disables app tracking with Branch or any other third parties that Branch uses internally.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Limits app tracking, potentially impacting data collection and advertising capabilities.', 'App tracking is limited.', 'Limits app tracking.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['App tracking is not limited.', 'Allows app tracking.', 'No limits on tracking, allowing comprehensive data collection and usage.', 'Does not limit app tracking.', 'Allows full app tracking.']}]}</t>
+          <t>{'API_name': 'setConsentData', 'class_name': ['AppsFlyerLib'], 'conditions': ['GDPR applies to the user or user consent is necessary.', 'The app must be initialized to collect consent data.'], 'effects': ['Transfers consent data to the SDK, impacting how user data is handled.', 'Transfers the consent data to the SDK.', 'Enables AppsFlyer to respect user consent preferences for data usage and personalization.', 'Transfers consent data to the SDK.'], 'parameter_configurations': [{'parameter_values': ['AppsFlyerConsent object for GDPR user'], 'conditions': ['GDPR applies'], 'effects': ['Sets the consent data for GDPR compliance.']}, {'parameter_values': ['AppsFlyerConsent object for non-GDPR user'], 'conditions': ['GDPR does not apply'], 'effects': ['Sets the consent data for non-GDPR compliance.']}, {'parameter_values': ['AppsFlyerConsent'], 'conditions': ['The app is compliant with GDPR if applicable.'], 'effects': ['Consent data is sent to AppsFlyer with every event.']}, {'parameter_values': ['AppsFlyerConsent object'], 'conditions': ['Must provide user consent data.', 'User has provided consent.'], 'effects': ['Consent data is sent with every event logged by the SDK.', 'Consent data is sent with each event.']}, {'parameter_values': ['AppsFlyerConsent.forGDPRUser(hasConsentForDataUsage, hasConsentForAdsPersonalization)'], 'conditions': ['GDPR applies to the user.'], 'effects': ['Sets consent data for GDPR compliance.']}, {'parameter_values': ['AppsFlyerConsent.forNonGDPRUser()'], 'conditions': ['GDPR does not apply to the user.'], 'effects': ['Sets consent data for users not subject to GDPR.']}]}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://help.branch.io/developers-hub/docs/android-full-reference#disabletracking</t>
+          <t>https://dev.appsflyer.com/hc/docs/preserve-user-privacy-android;https://dev.appsflyer.com/hc/docs/android-sdk-reference-appsflyerlib#anonymizeuser;https://dev.appsflyer.com/hc/docs/android-send-consent-for-dma-compliance</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>setDMAParamsForEEA</t>
+          <t>disableTracking</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDMAParamsForEEA', 'class_name': ['Branch'], 'conditions': ['Must provide user consent regarding ad personalization and data usage.', 'Must include user consent signals to avoid attribution or campaign performance degradation.'], 'effects': ['Sets parameters required for DMA Compliance in the EEA region.', 'Sets the value of parameters required by Google Conversion APIs for DMA Compliance in the EEA region.', 'Sets parameters required by Google Conversion APIs for DMA Compliance in the EEA region.'], 'parameter_configurations': [{'parameter_values': [True, True, True], 'conditions': ['User is included in EEA regulations and has granted both ad personalization and data usage consent.', 'User is in EEA and has granted both ad personalization and data usage consent.', 'User is in EEA and granted consent for ads personalization and user data usage.'], 'effects': ['User is in EEA with consent for ads personalization and data usage consent.', 'Compliance with DMA regulations.', 'User is in EEA and has granted consent for ads personalization and data usage.', 'Full compliance for advertising targeting in EEA.', 'Complies with DMA regulations allowing full data processing.']}, {'parameter_values': [True, False, False], 'conditions': ['User is included in EEA regulations but has denied both ad personalization and data usage consent.', 'User is in EEA but denied both ad personalization and data usage consent.', 'User is in EEA but denied consent for ads personalization and user data usage.'], 'effects': ['User is in EEA, denied ads personalization and data usage consent.', 'Restricts data collection to comply with user preferences.', 'User is in EEA and has denied both ads personalization and data usage.', 'No personalization allowed.', 'Non-compliance with DMA regulations.']}, {'parameter_values': [False, False, False], 'conditions': ['User is excluded from EEA regulations.'], 'effects': ['User is excluded from EEA regulations.', 'Compliance requirements for EEA do not apply.']}, {'parameter_values': [True, True, False], 'conditions': [], 'effects': ['User is in EEA and has granted consent for ads personalization but denied data usage.', 'User is in EEA, consented to ads personalization but denied data usage consent.']}, {'parameter_values': [True, False, True], 'conditions': [], 'effects': ['User is in EEA, denied ads personalization but consented to data usage consent.', 'User is in EEA and has denied ads personalization but granted data usage.']}]}</t>
+          <t>{'API_name': 'disableTracking', 'class_name': ['Branch'], 'conditions': [], 'effects': ['If disabled, the Branch Android SDK will not track any user data or state.', 'The SDK will not send any network calls, except for deep linking, when tracking is disabled.', 'The Branch Android SDK will not track any user data or state.', 'When set to true, Branch SDK will not track any user data or state.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Tracking is disabled.', 'SDK will not send any network calls, except for deep linking.', 'No tracking of user data results in reduced analytics capabilities.', 'No network calls will be sent except for deep linking.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Tracking is enabled.', 'Tracking is enabled for the Branch SDK.', 'Tracking is enabled, allowing the collection of user data.', 'SDK resumes tracking user data and state.']}]}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1773,44 +1773,44 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>setLastKnownLocation</t>
+          <t>setLimitFacebookTracking</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLastKnownLocation', 'class_name': ['BrazeUser'], 'conditions': ['Location permissions must be obtained from the user if using runtime permissions in Android M or later', 'Location permissions must be granted by the user', 'Requires permission for location data to be granted', 'User must grant location permissions according to device requirements'], 'effects': ['Records the current location manually even when automatic tracking is disabled', 'Logs a single location data point manually.', 'Logs the last known location for the user', 'Allows manual logging of a location even when automatic tracking is disabled', 'Logs the last known user location data'], 'parameter_configurations': [{'parameter_values': ['LATITUDE_DOUBLE_VALUE', 'LONGITUDE_DOUBLE_VALUE', 'ALTITUDE_DOUBLE_VALUE', 'ACCURACY_DOUBLE_VALUE'], 'conditions': ['Automatic location tracking is disabled', 'User must provide valid latitude and longitude values'], 'effects': ['Sets the last known location for the user in the application', 'Records the specified location with latitude, longitude, altitude, and accuracy.', 'Records a specific location point for the user', 'Manually logs the specified location without automatic tracking', 'Logs the provided location as the last known location']}]}</t>
+          <t>{'API_name': 'setLimitFacebookTracking', 'class_name': ['Branch'], 'conditions': [], 'effects': ['Enables or disables app tracking with Branch or any other third parties that Branch uses internally.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Limits app tracking, potentially impacting data collection and advertising capabilities.', 'App tracking is limited.', 'Limits app tracking.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['App tracking is not limited.', 'Allows app tracking.', 'No limits on tracking, allowing comprehensive data collection and usage.', 'Does not limit app tracking.', 'Allows full app tracking.']}]}</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/location_tracking/#compile-time-option;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/disabling_tracking;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/logging_purchases/#tracking-purchases-and-revenue</t>
+          <t>https://help.branch.io/developers-hub/docs/android-full-reference#disabletracking</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>logPurchase</t>
+          <t>setDMAParamsForEEA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'API_name': 'logPurchase', 'class_name': ['IBraze', 'Braze'], 'conditions': ['Product Identifier must not be empty', 'Product Identifier must not be empty to log the purchase', 'Product Identifier cannot be empty, it means a purchase will not be logged'], 'effects': ['Records an in-app purchase to Braze for analytics and revenue tracking', 'Records in-app purchases for tracking revenue and user segmentation', 'Records in-app purchases to track revenue over time and segment users by their lifetime value', 'Logs an in-app purchase for tracking revenue and user lifetime value', 'Records an in-app purchase, including product ID, currency, price, and quantity.'], 'parameter_configurations': [{'parameter_values': ['productId', 'currencyCode', 'price', 'quantity'], 'conditions': ['Product Identifier must not be empty', 'quantity must be less than or equal to 100', 'Quantity must be less than or equal to 100', 'The productIdentifier must not be empty to log the purchase.'], 'effects': ["Logs the purchase to the user's profile", "Logs the purchase into the user's profile and can be segmented for analytics.", 'Logs the purchase with details about product ID, currency, price, and quantity', 'Logs the specified product purchase, including currency and price details']}, {'parameter_values': ['String productId', 'String currencyCode', 'BigDecimal price', 'int quantity'], 'conditions': ['Can log purchases in multiple currencies, rounded to USD based on the exchange rate'], 'effects': ['Records the specified purchase with correct segmentation options']}, {'parameter_values': ['productId', 'currencyCode', 'price', 'quantity', 'purchaseProperties'], 'conditions': [], 'effects': ['Logs purchase with added metadata about the purchase']}]}</t>
+          <t>{'API_name': 'setDMAParamsForEEA', 'class_name': ['Branch'], 'conditions': ['Must provide user consent regarding ad personalization and data usage.', 'Must include user consent signals to avoid attribution or campaign performance degradation.'], 'effects': ['Sets parameters required for DMA Compliance in the EEA region.', 'Sets the value of parameters required by Google Conversion APIs for DMA Compliance in the EEA region.', 'Sets parameters required by Google Conversion APIs for DMA Compliance in the EEA region.'], 'parameter_configurations': [{'parameter_values': [True, True, True], 'conditions': ['User is included in EEA regulations and has granted both ad personalization and data usage consent.', 'User is in EEA and has granted both ad personalization and data usage consent.', 'User is in EEA and granted consent for ads personalization and user data usage.'], 'effects': ['User is in EEA with consent for ads personalization and data usage consent.', 'Compliance with DMA regulations.', 'User is in EEA and has granted consent for ads personalization and data usage.', 'Full compliance for advertising targeting in EEA.', 'Complies with DMA regulations allowing full data processing.']}, {'parameter_values': [True, False, False], 'conditions': ['User is included in EEA regulations but has denied both ad personalization and data usage consent.', 'User is in EEA but denied both ad personalization and data usage consent.', 'User is in EEA but denied consent for ads personalization and user data usage.'], 'effects': ['User is in EEA, denied ads personalization and data usage consent.', 'Restricts data collection to comply with user preferences.', 'User is in EEA and has denied both ads personalization and data usage.', 'No personalization allowed.', 'Non-compliance with DMA regulations.']}, {'parameter_values': [False, False, False], 'conditions': ['User is excluded from EEA regulations.'], 'effects': ['User is excluded from EEA regulations.', 'Compliance requirements for EEA do not apply.']}, {'parameter_values': [True, True, False], 'conditions': [], 'effects': ['User is in EEA and has granted consent for ads personalization but denied data usage.', 'User is in EEA, consented to ads personalization but denied data usage consent.']}, {'parameter_values': [True, False, True], 'conditions': [], 'effects': ['User is in EEA, denied ads personalization but consented to data usage consent.', 'User is in EEA and has denied ads personalization but granted data usage.']}]}</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/location_tracking/#compile-time-option;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/disabling_tracking;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/logging_purchases/#tracking-purchases-and-revenue</t>
+          <t>https://help.branch.io/developers-hub/docs/android-full-reference#disabletracking</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>disableSDK</t>
+          <t>setIsLocationCollectionEnabled</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'API_name': 'disableSDK', 'class_name': ['Braze'], 'conditions': ['Must be called to stop all SDK data tracking', 'User wants to stop data tracking to comply with data privacy regulations', 'To comply with data privacy regulations.', 'Intended to comply with data privacy regulations'], 'effects': ['Stops all data collection and cancels network connections to Braze servers', 'Disables all network connections and ceases data transfer to Braze servers', 'Stops all data collection and communication with Braze servers', 'Stops data tracking and cancels all network connections to Braze servers.', 'Stops all network connections to Braze servers and prevents data from being sent'], 'parameter_configurations': []}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>enableSDK</t>
+          <t>setLastKnownLocation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'API_name': 'enableSDK', 'class_name': ['Braze'], 'conditions': ['Data tracking needs to resume after being disabled', 'Must be called after disableSDK to resume data collection.', 'SDK tracking was previously disabled and needs to be re-enabled', 'Must be called after disableSDK if data collection needs to be resumed'], 'effects': ['Resumes data collection and sends stored user data to Braze servers', 'Resumes data collection after being disabled', 'Resumes data collection', 'Resumes data tracking after previously being disabled.', 'Resumes data collection after it has been disabled'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setLastKnownLocation', 'class_name': ['BrazeUser'], 'conditions': ['Location permissions must be obtained from the user if using runtime permissions in Android M or later', 'Location permissions must be granted by the user', 'Requires permission for location data to be granted', 'User must grant location permissions according to device requirements'], 'effects': ['Records the current location manually even when automatic tracking is disabled', 'Logs a single location data point manually.', 'Logs the last known location for the user', 'Allows manual logging of a location even when automatic tracking is disabled', 'Logs the last known user location data'], 'parameter_configurations': [{'parameter_values': ['LATITUDE_DOUBLE_VALUE', 'LONGITUDE_DOUBLE_VALUE', 'ALTITUDE_DOUBLE_VALUE', 'ACCURACY_DOUBLE_VALUE'], 'conditions': ['Automatic location tracking is disabled', 'User must provide valid latitude and longitude values'], 'effects': ['Sets the last known location for the user in the application', 'Records the specified location with latitude, longitude, altitude, and accuracy.', 'Records a specific location point for the user', 'Manually logs the specified location without automatic tracking', 'Logs the provided location as the last known location']}]}</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>wipeData</t>
+          <t>logPurchase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'API_name': 'wipeData', 'class_name': ['Braze'], 'conditions': ['User wishes to clear all saved client-side data before changing the SDK state'], 'effects': ['Clears all user data stored on the device', 'Fully clears all client-side data stored on the device', 'Clears all client-side data stored on the device.', 'Clears all client-side data stored on the device'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'logPurchase', 'class_name': ['IBraze', 'Braze'], 'conditions': ['Product Identifier must not be empty', 'Product Identifier must not be empty to log the purchase', 'Product Identifier cannot be empty, it means a purchase will not be logged'], 'effects': ['Records an in-app purchase to Braze for analytics and revenue tracking', 'Records in-app purchases for tracking revenue and user segmentation', 'Records in-app purchases to track revenue over time and segment users by their lifetime value', 'Logs an in-app purchase for tracking revenue and user lifetime value', 'Records an in-app purchase, including product ID, currency, price, and quantity.'], 'parameter_configurations': [{'parameter_values': ['productId', 'currencyCode', 'price', 'quantity'], 'conditions': ['Product Identifier must not be empty', 'quantity must be less than or equal to 100', 'Quantity must be less than or equal to 100', 'The productIdentifier must not be empty to log the purchase.'], 'effects': ["Logs the purchase to the user's profile", "Logs the purchase into the user's profile and can be segmented for analytics.", 'Logs the purchase with details about product ID, currency, price, and quantity', 'Logs the specified product purchase, including currency and price details']}, {'parameter_values': ['String productId', 'String currencyCode', 'BigDecimal price', 'int quantity'], 'conditions': ['Can log purchases in multiple currencies, rounded to USD based on the exchange rate'], 'effects': ['Records the specified purchase with correct segmentation options']}, {'parameter_values': ['productId', 'currencyCode', 'price', 'quantity', 'purchaseProperties'], 'conditions': [], 'effects': ['Logs purchase with added metadata about the purchase']}]}</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1883,110 +1883,110 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chartboost</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>addDataUseConsent</t>
+          <t>disableSDK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'API_name': 'addDataUseConsent', 'class_name': ['Chartboost'], 'conditions': ['Apps under the Google Play Designed for Families policy MUST set the COPPA privacy flag to true', 'Publishers must obtain consent from their users in order to process personal data and provide relevant ads', 'publishers must obtain consent from their users in order to process personal data', 'Apps under the Google Play Designed for Families policy must set the COPPA privacy flag to true', 'must obtain user consent to process personal data', 'Publishers must obtain consent from users to process personal data', 'apps under Google Play Designed for Families policy must set the COPPA privacy flag to true', 'If an app is child-directed under Google Play Designed for Families, COPPA privacy flag must be set to true', 'If under Google Play Designed for Families policy, the COPPA privacy flag must be set to true', 'publishers must obtain consent from users to process personal data'], 'effects': ['Sets user consent data for privacy laws such as GDPR, CCPA, and COPPA', 'provides user consent data for privacy laws currently in existence or future laws', 'sets user consent data for privacy laws like GDPR, CCPA, and COPPA', 'It sets user consent data for privacy laws (GDPR, CCPA, COPPA) currently in existence or future laws', 'sets consent values for GDPR, CCPA, COPPA, and custom values', 'Controls whether behavioral and contextual ads can be shown based on user consent'], 'parameter_configurations': [{'parameter_values': ['context', 'GDPR(GDPR.GDPR_CONSENT.BEHAVIORAL)'], 'conditions': ['user consents to Behavioral and Contextual Ads', 'user consents to behavioral targeting'], 'effects': ['enables behavioral and contextual advertising', 'the user consents to behavioral and contextual ads under GDPR', 'allows behavioral and contextual ads']}, {'parameter_values': ['context', 'GDPR(GDPR.GDPR_CONSENT.NON_BEHAVIORAL)'], 'conditions': ['user does not consent to targeting'], 'effects': ['the user does not consent to targeting, only contextual ads under GDPR', 'only contextual ads are shown', 'only contextual ads are allowed']}, {'parameter_values': ['context', 'CCPA(CCPA.CCPA_CONSENT.OPT_IN_SALE)'], 'conditions': ['user consents to the sale of personal data', 'user opts in to the sale'], 'effects': ['enables behavioral and contextual advertising', 'allows behavioral and contextual ads', 'the user consents to the sale of their personal information for behavioral and contextual ads under CCPA']}, {'parameter_values': ['context', 'CCPA(CCPA.CCPA_CONSENT.OPT_OUT_SALE)'], 'conditions': ['user does not consent to the sale of personal data', 'user opts out of the sale'], 'effects': ['the user does not consent to the sale of their personal information, only receives contextual ads under CCPA', 'only contextual ads are shown', 'only contextual ads are allowed']}, {'parameter_values': ['context', 'COPPA(true)'], 'conditions': ['app is child-directed', 'if the app is child-directed'], 'effects': ['COPPA restrictions apply, android advertising identifier is not transmitted, only contextual ads allowed', 'COPPA restrictions apply; android advertising identifier is not transmitted', 'COPPA restrictions apply; advertising identifier is not transmitted']}, {'parameter_values': ['context', 'COPPA(false)'], 'conditions': ['app is not child-directed', 'if the app is child-directed'], 'effects': ['enables behavioral and contextual advertising', 'no COPPA restrictions apply; behavioral and contextual ads are allowed', 'COPPA restrictions do not apply, behavioral and contextual ads are allowed']}, {'parameter_values': ['context', "Custom('name', 'value')"], 'conditions': ['valid IAB’s U.S. Privacy String'], 'effects': ['allows publishers to set custom consent information for the CCPA standard']}, {'parameter_values': ['context', 'Custom("name", "value")'], 'conditions': ['publishers provide custom consent information'], 'effects': ['provides custom consent information', "sets custom consent values according to valid IAB's U.S. Privacy String"]}, {'parameter_values': ['GDPR.GDPR_CONSENT.BEHAVIORAL', 'context'], 'conditions': ['User consents to behavioral and contextual ads'], 'effects': ['User will see both behavioral and contextual ads']}, {'parameter_values': ['GDPR.GDPR_CONSENT.NON_BEHAVIORAL', 'context'], 'conditions': ['User does not consent to behavioral targeting'], 'effects': ['User will only see contextual ads']}, {'parameter_values': ['CCPA.CCPA_CONSENT.OPT_IN_SALE', 'context'], 'conditions': ['User consents to the sale of personal data'], 'effects': ['User will see both behavioral and contextual ads']}, {'parameter_values': ['CCPA.CCPA_CONSENT.OPT_OUT_SALE', 'context'], 'conditions': ['User does not consent to the sale of personal data'], 'effects': ['User will only see contextual ads']}, {'parameter_values': [True, 'context'], 'conditions': ['App is child-directed under COPPA'], 'effects': ['Transmits no android advertising identifier; only contextual ads are served']}, {'parameter_values': [False, 'context'], 'conditions': ['COPPA does not apply'], 'effects': ['Both behavioral and contextual ads can be served']}, {'parameter_values': ['Custom("name", "value")', 'context'], 'conditions': ['Providing custom consent information beyond predefined values'], 'effects': ['User consent is set based on custom consent value']}, {'parameter_values': ['context', 'dataUseConsent'], 'conditions': ['User must provide consent as per relevant privacy laws'], 'effects': ['Consent value is recorded for the specified privacy standard']}]}</t>
+          <t>{'API_name': 'disableSDK', 'class_name': ['Braze'], 'conditions': ['Must be called to stop all SDK data tracking', 'User wants to stop data tracking to comply with data privacy regulations', 'To comply with data privacy regulations.', 'Intended to comply with data privacy regulations'], 'effects': ['Stops all data collection and cancels network connections to Braze servers', 'Disables all network connections and ceases data transfer to Braze servers', 'Stops all data collection and communication with Braze servers', 'Stops data tracking and cancels all network connections to Braze servers.', 'Stops all network connections to Braze servers and prevents data from being sent'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://docs.chartboost.com/en/monetization/integrate/android/sdk-privacy-methods/</t>
+          <t>https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/location_tracking/#compile-time-option;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/disabling_tracking;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/logging_purchases/#tracking-purchases-and-revenue</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chartboost</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>clearDataUseConsent</t>
+          <t>enableSDK</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'API_name': 'clearDataUseConsent', 'class_name': ['Chartboost'], 'conditions': [], 'effects': ['Clears any previously set privacy data use consent for specified privacy standards', 'clears any of the privacy data use consent', 'clears previously set data use consent values', 'clears any of the privacy data use consent for GDPR, CCPA, COPPA, or Custom Consent', 'Clears any previously set privacy data use consent'], 'parameter_configurations': [{'parameter_values': ['context', 'dataUseConsent.privacyStandard'], 'conditions': [], 'effects': ['removes consent related to the specified privacy standard', 'removes the specified privacy standard consent', "Removes the specified privacy standard's consent"]}, {'parameter_values': ['dataUseConsent.privacyStandard', 'context'], 'conditions': [], 'effects': ['Privacy consent data is cleared for the specified standard']}]}</t>
+          <t>{'API_name': 'enableSDK', 'class_name': ['Braze'], 'conditions': ['Data tracking needs to resume after being disabled', 'Must be called after disableSDK to resume data collection.', 'SDK tracking was previously disabled and needs to be re-enabled', 'Must be called after disableSDK if data collection needs to be resumed'], 'effects': ['Resumes data collection and sends stored user data to Braze servers', 'Resumes data collection after being disabled', 'Resumes data collection', 'Resumes data tracking after previously being disabled.', 'Resumes data collection after it has been disabled'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://docs.chartboost.com/en/monetization/integrate/android/sdk-privacy-methods/</t>
+          <t>https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/location_tracking/#compile-time-option;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/disabling_tracking;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/logging_purchases/#tracking-purchases-and-revenue</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CleverTap</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>setOptOut</t>
+          <t>wipeData</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'API_name': 'setOptOut', 'class_name': ['CleverTapAPI'], 'conditions': ['User must choose to opt out of sharing their data', 'User wants to opt out of data sharing', 'Required to comply with GDPR', 'user wants to stop sharing their data'], 'effects': ['Stops sending events to CleverTap', 'Stops sending events to CleverTap when set to true', 'Stops sending events to CleverTap if set to true', 'the app stops sending events to CleverTap'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User data will not be shared with CleverTap', 'Stops sending events to CleverTap', 'The application will no longer send any events to CleverTap', 'Events will not be sent to CleverTap']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User data will be shared with CleverTap again', 'The application will resume sending events to CleverTap', 'Resumes sending events to CleverTap', 'User has opted in again to share their data']}]}</t>
+          <t>{'API_name': 'wipeData', 'class_name': ['Braze'], 'conditions': ['User wishes to clear all saved client-side data before changing the SDK state'], 'effects': ['Clears all user data stored on the device', 'Fully clears all client-side data stored on the device', 'Clears all client-side data stored on the device.', 'Clears all client-side data stored on the device'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://developer.clevertap.com/docs/android-advanced-features</t>
+          <t>https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/location_tracking/#compile-time-option;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/disabling_tracking;https://www.braze.com/docs/developer_guide/platform_integration_guides/android/analytics/logging_purchases/#tracking-purchases-and-revenue</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CleverTap</t>
+          <t>Chartboost</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>enableDeviceNetworkInfoReporting</t>
+          <t>addDataUseConsent</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'API_name': 'enableDeviceNetworkInfoReporting', 'class_name': ['CleverTapAPI'], 'conditions': ['Requires user permission to enable reporting', 'User must grant permission to access network information', 'User has opted in to share device network information', 'the user has opted to capture device network information', 'User must allow the app to capture device network information'], 'effects': ['Enables capturing of device network information', 'Enables the capturing and reporting of device networking information', 'enables capturing of device network information', 'Enables capturing of personal information like WiFi, Bluetooth, Network Information and user IP information', 'Captures personal information such as WiFi, Bluetooth, Network Information, and user IP information'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User wants to capture device network information'], 'effects': ['Device network information will be sent to CleverTap', 'Device network information like WiFi, Bluetooth, and user IP will be captured', 'Captures WiFi, Bluetooth, Network Information, and user IP information']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Does not capture device network information', 'Device network information will not be sent to CleverTap', 'Device network information will not be captured']}]}</t>
+          <t>{'API_name': 'addDataUseConsent', 'class_name': ['Chartboost'], 'conditions': ['Apps under the Google Play Designed for Families policy MUST set the COPPA privacy flag to true', 'Publishers must obtain consent from their users in order to process personal data and provide relevant ads', 'publishers must obtain consent from their users in order to process personal data', 'Apps under the Google Play Designed for Families policy must set the COPPA privacy flag to true', 'must obtain user consent to process personal data', 'Publishers must obtain consent from users to process personal data', 'apps under Google Play Designed for Families policy must set the COPPA privacy flag to true', 'If an app is child-directed under Google Play Designed for Families, COPPA privacy flag must be set to true', 'If under Google Play Designed for Families policy, the COPPA privacy flag must be set to true', 'publishers must obtain consent from users to process personal data'], 'effects': ['Sets user consent data for privacy laws such as GDPR, CCPA, and COPPA', 'provides user consent data for privacy laws currently in existence or future laws', 'sets user consent data for privacy laws like GDPR, CCPA, and COPPA', 'It sets user consent data for privacy laws (GDPR, CCPA, COPPA) currently in existence or future laws', 'sets consent values for GDPR, CCPA, COPPA, and custom values', 'Controls whether behavioral and contextual ads can be shown based on user consent'], 'parameter_configurations': [{'parameter_values': ['context', 'GDPR(GDPR.GDPR_CONSENT.BEHAVIORAL)'], 'conditions': ['user consents to Behavioral and Contextual Ads', 'user consents to behavioral targeting'], 'effects': ['enables behavioral and contextual advertising', 'the user consents to behavioral and contextual ads under GDPR', 'allows behavioral and contextual ads']}, {'parameter_values': ['context', 'GDPR(GDPR.GDPR_CONSENT.NON_BEHAVIORAL)'], 'conditions': ['user does not consent to targeting'], 'effects': ['the user does not consent to targeting, only contextual ads under GDPR', 'only contextual ads are shown', 'only contextual ads are allowed']}, {'parameter_values': ['context', 'CCPA(CCPA.CCPA_CONSENT.OPT_IN_SALE)'], 'conditions': ['user consents to the sale of personal data', 'user opts in to the sale'], 'effects': ['enables behavioral and contextual advertising', 'allows behavioral and contextual ads', 'the user consents to the sale of their personal information for behavioral and contextual ads under CCPA']}, {'parameter_values': ['context', 'CCPA(CCPA.CCPA_CONSENT.OPT_OUT_SALE)'], 'conditions': ['user does not consent to the sale of personal data', 'user opts out of the sale'], 'effects': ['the user does not consent to the sale of their personal information, only receives contextual ads under CCPA', 'only contextual ads are shown', 'only contextual ads are allowed']}, {'parameter_values': ['context', 'COPPA(true)'], 'conditions': ['app is child-directed', 'if the app is child-directed'], 'effects': ['COPPA restrictions apply, android advertising identifier is not transmitted, only contextual ads allowed', 'COPPA restrictions apply; android advertising identifier is not transmitted', 'COPPA restrictions apply; advertising identifier is not transmitted']}, {'parameter_values': ['context', 'COPPA(false)'], 'conditions': ['app is not child-directed', 'if the app is child-directed'], 'effects': ['enables behavioral and contextual advertising', 'no COPPA restrictions apply; behavioral and contextual ads are allowed', 'COPPA restrictions do not apply, behavioral and contextual ads are allowed']}, {'parameter_values': ['context', "Custom('name', 'value')"], 'conditions': ['valid IAB’s U.S. Privacy String'], 'effects': ['allows publishers to set custom consent information for the CCPA standard']}, {'parameter_values': ['context', 'Custom("name", "value")'], 'conditions': ['publishers provide custom consent information'], 'effects': ['provides custom consent information', "sets custom consent values according to valid IAB's U.S. Privacy String"]}, {'parameter_values': ['GDPR.GDPR_CONSENT.BEHAVIORAL', 'context'], 'conditions': ['User consents to behavioral and contextual ads'], 'effects': ['User will see both behavioral and contextual ads']}, {'parameter_values': ['GDPR.GDPR_CONSENT.NON_BEHAVIORAL', 'context'], 'conditions': ['User does not consent to behavioral targeting'], 'effects': ['User will only see contextual ads']}, {'parameter_values': ['CCPA.CCPA_CONSENT.OPT_IN_SALE', 'context'], 'conditions': ['User consents to the sale of personal data'], 'effects': ['User will see both behavioral and contextual ads']}, {'parameter_values': ['CCPA.CCPA_CONSENT.OPT_OUT_SALE', 'context'], 'conditions': ['User does not consent to the sale of personal data'], 'effects': ['User will only see contextual ads']}, {'parameter_values': [True, 'context'], 'conditions': ['App is child-directed under COPPA'], 'effects': ['Transmits no android advertising identifier; only contextual ads are served']}, {'parameter_values': [False, 'context'], 'conditions': ['COPPA does not apply'], 'effects': ['Both behavioral and contextual ads can be served']}, {'parameter_values': ['Custom("name", "value")', 'context'], 'conditions': ['Providing custom consent information beyond predefined values'], 'effects': ['User consent is set based on custom consent value']}, {'parameter_values': ['context', 'dataUseConsent'], 'conditions': ['User must provide consent as per relevant privacy laws'], 'effects': ['Consent value is recorded for the specified privacy standard']}]}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://developer.clevertap.com/docs/android-advanced-features</t>
+          <t>https://docs.chartboost.com/en/monetization/integrate/android/sdk-privacy-methods/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CleverTap</t>
+          <t>Chartboost</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>setOffline</t>
+          <t>clearDataUseConsent</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'API_name': 'setOffline', 'class_name': ['CleverTapAPI'], 'conditions': ['the user wishes to stop sending events/profile information'], 'effects': ['sets the user as offline, preventing data transmission', 'Sets the user as offline, preventing any events/profile information from being sent', 'No user events/profile information will be sent to CleverTap', 'No events/profile information will be sent to CleverTap while offline', 'Prevents any events/profile information from being sent to CleverTap'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User is marked as offline', 'User set as offline', 'No events/profile information will be sent to CleverTap', 'No events or profile information will be sent to CleverTap', 'User is set as offline; no data is sent']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Events and profile information will be sent to CleverTap again', 'Resumes sending events/profile information to CleverTap', 'User is back online; data can be sent', 'User set back online', 'User is marked as online, and events/profile information will be sent to CleverTap']}]}</t>
+          <t>{'API_name': 'clearDataUseConsent', 'class_name': ['Chartboost'], 'conditions': [], 'effects': ['Clears any previously set privacy data use consent for specified privacy standards', 'clears any of the privacy data use consent', 'clears previously set data use consent values', 'clears any of the privacy data use consent for GDPR, CCPA, COPPA, or Custom Consent', 'Clears any previously set privacy data use consent'], 'parameter_configurations': [{'parameter_values': ['context', 'dataUseConsent.privacyStandard'], 'conditions': [], 'effects': ['removes consent related to the specified privacy standard', 'removes the specified privacy standard consent', "Removes the specified privacy standard's consent"]}, {'parameter_values': ['dataUseConsent.privacyStandard', 'context'], 'conditions': [], 'effects': ['Privacy consent data is cleared for the specified standard']}]}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://developer.clevertap.com/docs/android-advanced-features</t>
+          <t>https://docs.chartboost.com/en/monetization/integrate/android/sdk-privacy-methods/</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>setEncryptionLevel</t>
+          <t>setOptOut</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'API_name': 'setEncryptionLevel', 'class_name': ['CleverTapAPI', 'CleverTapInstanceConfig'], 'conditions': ['the application wishes to encrypt PII data', 'Must be set in AndroidManifest.xml for the default instance', 'Required to comply with data protection laws regarding handling PII data', 'The encryption level setting must be included in AndroidManifest.xml', 'Must be set in the AndroidManifest.xml for the default instance'], 'effects': ['Sets the level of encryption for PII data stored across the SDK', 'Encrypts PII data such as Email, Identity, Name, and Phone', 'Controls the encryption level of PII data stored by the SDK', 'sets the encryption level for PII data', 'Determines how personally identifiable information (PII) is stored'], 'parameter_configurations': [{'parameter_values': ['None'], 'conditions': [], 'effects': ['All stored data is in plaintext']}, {'parameter_values': ['Medium'], 'conditions': [], 'effects': ['PII data is encrypted completely']}, {'parameter_values': [0], 'conditions': [], 'effects': ['Stored data is in plaintext', 'All stored data is in plaintext', 'PII data is stored in plaintext']}, {'parameter_values': [1], 'conditions': [], 'effects': ['PII data is fully encrypted', 'PII data is completely encrypted', 'PII data is encrypted completely']}]}</t>
+          <t>{'API_name': 'setOptOut', 'class_name': ['CleverTapAPI'], 'conditions': ['User must choose to opt out of sharing their data', 'User wants to opt out of data sharing', 'Required to comply with GDPR', 'user wants to stop sharing their data'], 'effects': ['Stops sending events to CleverTap', 'Stops sending events to CleverTap when set to true', 'Stops sending events to CleverTap if set to true', 'the app stops sending events to CleverTap'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User data will not be shared with CleverTap', 'Stops sending events to CleverTap', 'The application will no longer send any events to CleverTap', 'Events will not be sent to CleverTap']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User data will be shared with CleverTap again', 'The application will resume sending events to CleverTap', 'Resumes sending events to CleverTap', 'User has opted in again to share their data']}]}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>setLocation</t>
+          <t>enableDeviceNetworkInfoReporting</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLocation', 'class_name': ['CleverTapAPI'], 'conditions': ['User must grant permission to access location data', "The application must request and obtain user's permission for location access", 'User must grant permission to use location services', 'User has granted permission for location access', "the application has the user's location permission"], 'effects': ["Updates the user's location in CleverTap", "User's location is passed to CleverTap", 'Updates user location in CleverTap', "updates the user's location in CleverTap", 'Sends user location to CleverTap'], 'parameter_configurations': [{'parameter_values': ['location'], 'conditions': ['User has granted permission to access their location', 'Permission to access location is granted', 'Location permission granted'], 'effects': ['The location is sent to CleverTap', "CleverTap updates the user's location", "User's location is set in CleverTap, enabling location-based features", 'User location will be reported to CleverTap']}, {'parameter_values': ['android.location.Location'], 'conditions': [], 'effects': ["CleverTap receives the user's location"]}]}</t>
+          <t>{'API_name': 'enableDeviceNetworkInfoReporting', 'class_name': ['CleverTapAPI'], 'conditions': ['Requires user permission to enable reporting', 'User must grant permission to access network information', 'User has opted in to share device network information', 'the user has opted to capture device network information', 'User must allow the app to capture device network information'], 'effects': ['Enables capturing of device network information', 'Enables the capturing and reporting of device networking information', 'enables capturing of device network information', 'Enables capturing of personal information like WiFi, Bluetooth, Network Information and user IP information', 'Captures personal information such as WiFi, Bluetooth, Network Information, and user IP information'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User wants to capture device network information'], 'effects': ['Device network information will be sent to CleverTap', 'Device network information like WiFi, Bluetooth, and user IP will be captured', 'Captures WiFi, Bluetooth, Network Information, and user IP information']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Does not capture device network information', 'Device network information will not be sent to CleverTap', 'Device network information will not be captured']}]}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2037,66 +2037,66 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Countly</t>
+          <t>CleverTap</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>setLocation</t>
+          <t>setOffline</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLocation', 'class_name': ['Countly', 'CountlyConfig'], 'conditions': ['Must be called during the initialization of the SDK.', 'Should be called during SDK initialization', 'Set during initialization', 'The SDK is initialized'], 'effects': ["Sets location data to be sent during the user's session start", 'Sets user location information to be sent during the start of the user session', 'Sets user location information to be sent during the start of the user session.', 'Sets location info that will be sent during the start of the user session', 'Update user location information'], 'parameter_configurations': [{'parameter_values': ['us', 'Houston', '29.634933,-95.220255', None], 'conditions': ['User wants to track location', 'Requires the country code, city name, and latitude/longitude values.', 'countryCode must be provided with at least city', 'Country code must be set together with city name'], 'effects': ['Sends separate requests to update location information.', 'Sends country code, city, GPS coordinates, and IP address to Countly server', "A separate request will be created to send the user's location.", 'Sends location details as separate requests', 'Sends user location to the Countly server']}, {'parameter_values': [None, None, None, None], 'conditions': ['User does not want to track location'], 'effects': ['Does not send any location data']}]}</t>
+          <t>{'API_name': 'setOffline', 'class_name': ['CleverTapAPI'], 'conditions': ['the user wishes to stop sending events/profile information'], 'effects': ['sets the user as offline, preventing data transmission', 'Sets the user as offline, preventing any events/profile information from being sent', 'No user events/profile information will be sent to CleverTap', 'No events/profile information will be sent to CleverTap while offline', 'Prevents any events/profile information from being sent to CleverTap'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User is marked as offline', 'User set as offline', 'No events/profile information will be sent to CleverTap', 'No events or profile information will be sent to CleverTap', 'User is set as offline; no data is sent']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Events and profile information will be sent to CleverTap again', 'Resumes sending events/profile information to CleverTap', 'User is back online; data can be sent', 'User set back online', 'User is marked as online, and events/profile information will be sent to CleverTap']}]}</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://support.countly.com/hc/en-us/articles/360037754031-Android#h_01HAVQDM5V1ZB8ECYTH1SPR3Q7</t>
+          <t>https://developer.clevertap.com/docs/android-advanced-features</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Countly</t>
+          <t>CleverTap</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>setDisableLocation</t>
+          <t>setEncryptionLevel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDisableLocation', 'class_name': ['CountlyConfig'], 'conditions': [], 'effects': ['Disables location tracking'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setEncryptionLevel', 'class_name': ['CleverTapAPI', 'CleverTapInstanceConfig'], 'conditions': ['the application wishes to encrypt PII data', 'Must be set in AndroidManifest.xml for the default instance', 'Required to comply with data protection laws regarding handling PII data', 'The encryption level setting must be included in AndroidManifest.xml', 'Must be set in the AndroidManifest.xml for the default instance'], 'effects': ['Sets the level of encryption for PII data stored across the SDK', 'Encrypts PII data such as Email, Identity, Name, and Phone', 'Controls the encryption level of PII data stored by the SDK', 'sets the encryption level for PII data', 'Determines how personally identifiable information (PII) is stored'], 'parameter_configurations': [{'parameter_values': ['None'], 'conditions': [], 'effects': ['All stored data is in plaintext']}, {'parameter_values': ['Medium'], 'conditions': [], 'effects': ['PII data is encrypted completely']}, {'parameter_values': [0], 'conditions': [], 'effects': ['Stored data is in plaintext', 'All stored data is in plaintext', 'PII data is stored in plaintext']}, {'parameter_values': [1], 'conditions': [], 'effects': ['PII data is fully encrypted', 'PII data is completely encrypted', 'PII data is encrypted completely']}]}</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://support.countly.com/hc/en-us/articles/360037754031-Android#h_01HAVQDM5V1ZB8ECYTH1SPR3Q7</t>
+          <t>https://developer.clevertap.com/docs/android-advanced-features</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Countly</t>
+          <t>CleverTap</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>disableLocation</t>
+          <t>setLocation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'API_name': 'disableLocation', 'class_name': ['Countly'], 'conditions': ['User opts-out of location tracking'], 'effects': ['Erases cached location data from the device and the server.', 'Erases cached location data from the device and server', 'Erases cached location data from the device and the server'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setLocation', 'class_name': ['CleverTapAPI'], 'conditions': ['User must grant permission to access location data', "The application must request and obtain user's permission for location access", 'User must grant permission to use location services', 'User has granted permission for location access', "the application has the user's location permission"], 'effects': ["Updates the user's location in CleverTap", "User's location is passed to CleverTap", 'Updates user location in CleverTap', "updates the user's location in CleverTap", 'Sends user location to CleverTap'], 'parameter_configurations': [{'parameter_values': ['location'], 'conditions': ['User has granted permission to access their location', 'Permission to access location is granted', 'Location permission granted'], 'effects': ['The location is sent to CleverTap', "CleverTap updates the user's location", "User's location is set in CleverTap, enabling location-based features", 'User location will be reported to CleverTap']}, {'parameter_values': ['android.location.Location'], 'conditions': [], 'effects': ["CleverTap receives the user's location"]}]}</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://support.countly.com/hc/en-us/articles/360037754031-Android#h_01HAVQDM5V1ZB8ECYTH1SPR3Q7</t>
+          <t>https://developer.clevertap.com/docs/android-advanced-features</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>setParameterTamperingProtectionSalt</t>
+          <t>setLocation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'API_name': 'setParameterTamperingProtectionSalt', 'class_name': ['CountlyConfig'], 'conditions': [], 'effects': ['Enables tamper protection for request parameters', 'Sets the salt for calculating checksum to verify parameters in requests', 'Sets the optional salt for calculating checksums for protection against parameter tampering.', 'Protects parameters from tampering.', 'Sets a salt for calculating checksums for requested data'], 'parameter_configurations': [{'parameter_values': ['salt'], 'conditions': ['Must match the server salt value.'], 'effects': ['Requests will be validated against the salt provided', 'Each request includes checksum for data integrity.', 'All requests will be checked for the validity of the checksum field.', 'Includes a checksum field in each request for data integrity verification on the server']}, {'parameter_values': ['mySalt'], 'conditions': [], 'effects': ['Protects requests from tampering']}]}</t>
+          <t>{'API_name': 'setLocation', 'class_name': ['Countly', 'CountlyConfig'], 'conditions': ['Must be called during the initialization of the SDK.', 'Should be called during SDK initialization', 'Set during initialization', 'The SDK is initialized'], 'effects': ["Sets location data to be sent during the user's session start", 'Sets user location information to be sent during the start of the user session', 'Sets user location information to be sent during the start of the user session.', 'Sets location info that will be sent during the start of the user session', 'Update user location information'], 'parameter_configurations': [{'parameter_values': ['us', 'Houston', '29.634933,-95.220255', None], 'conditions': ['User wants to track location', 'Requires the country code, city name, and latitude/longitude values.', 'countryCode must be provided with at least city', 'Country code must be set together with city name'], 'effects': ['Sends separate requests to update location information.', 'Sends country code, city, GPS coordinates, and IP address to Countly server', "A separate request will be created to send the user's location.", 'Sends location details as separate requests', 'Sends user location to the Countly server']}, {'parameter_values': [None, None, None, None], 'conditions': ['User does not want to track location'], 'effects': ['Does not send any location data']}]}</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>setRequiresConsent</t>
+          <t>setDisableLocation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'API_name': 'setRequiresConsent', 'class_name': ['CountlyConfig'], 'conditions': ['Should be set to true before initializing Countly'], 'effects': ['Requires user consent for data collection', 'Enables or disables the requirement for user consent', 'If set to true, no event or session data will be sent unless the user provides consent.', 'Requires user consent for various features of the SDK', 'Sets whether the SDK requires user consent for data collection'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Set during SDK configuration'], 'effects': ['SDK functionalities will be disabled until consent is given', 'Consent is required for Countly to track data and send requests', 'All functions require explicit consent before operation.', 'SDK will not collect data unless consent is provided', 'The SDK will require consent for all features.']}, {'parameter_values': [False], 'conditions': ['Consent requirement is turned off.'], 'effects': ['Countly can track data without requiring user consent', 'Countly functions operate without needing user consent.', 'The SDK will not require user consent and will send data normally.', 'SDK can collect data without requiring explicit consent']}]}</t>
+          <t>{'API_name': 'setDisableLocation', 'class_name': ['CountlyConfig'], 'conditions': [], 'effects': ['Disables location tracking'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>giveConsent</t>
+          <t>disableLocation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'API_name': 'giveConsent', 'class_name': ['Countly'], 'conditions': [], 'effects': ['Gives consent to a specific feature which allows that feature to function', 'Gives consent for specific features to be enabled', 'Provides consent for a specific feature, allowing related functions to operate.', 'Gives consent for the specified features in Countly'], 'parameter_configurations': [{'parameter_values': [['sessions']], 'conditions': [], 'effects': ['Allows the SDK to track sessions.', 'Allows session tracking to happen', 'Enables tracking for the sessions feature in Countly']}, {'parameter_values': [['sessions', 'events']], 'conditions': [], 'effects': ['Enables tracking sessions and events']}]}</t>
+          <t>{'API_name': 'disableLocation', 'class_name': ['Countly'], 'conditions': ['User opts-out of location tracking'], 'effects': ['Erases cached location data from the device and the server.', 'Erases cached location data from the device and server', 'Erases cached location data from the device and the server'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>removeConsent</t>
+          <t>setParameterTamperingProtectionSalt</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'API_name': 'removeConsent', 'class_name': ['Countly'], 'conditions': [], 'effects': ['Removes consent for a specific feature, stopping it from functioning', 'Removes consent for a specific feature, disabling related functions.', 'Removes consent for specific features', 'Removes consent for the specified features in Countly'], 'parameter_configurations': [{'parameter_values': [['sessions']], 'conditions': [], 'effects': ['Stops session tracking from occurring', 'Disables tracking sessions', 'Disables tracking for the sessions feature in Countly', 'Prevents the SDK from tracking sessions.']}]}</t>
+          <t>{'API_name': 'setParameterTamperingProtectionSalt', 'class_name': ['CountlyConfig'], 'conditions': [], 'effects': ['Enables tamper protection for request parameters', 'Sets the salt for calculating checksum to verify parameters in requests', 'Sets the optional salt for calculating checksums for protection against parameter tampering.', 'Protects parameters from tampering.', 'Sets a salt for calculating checksums for requested data'], 'parameter_configurations': [{'parameter_values': ['salt'], 'conditions': ['Must match the server salt value.'], 'effects': ['Requests will be validated against the salt provided', 'Each request includes checksum for data integrity.', 'All requests will be checked for the validity of the checksum field.', 'Includes a checksum field in each request for data integrity verification on the server']}, {'parameter_values': ['mySalt'], 'conditions': [], 'effects': ['Protects requests from tampering']}]}</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2191,682 +2191,682 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>Countly</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>setUsPrivacyOptOut</t>
+          <t>setRequiresConsent</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUsPrivacyOptOut', 'class_name': ['Criteo'], 'conditions': ["Called as soon as the app receives consent, or when applicable users' consent status changes.", 'user has provided consent for data collection or the user opts out of data sharing', 'Must be passed to Criteo as soon as your app receives consent from applicable users', 'User consent must be received before calling this API', "Called as soon as the app receives user consent or in accordance with applicable users' consent"], 'effects': ["Updates the Criteo SDK with the user's opt-out preference.", 'indicates whether a user has opted out of data sharing under CCPA', "Sets the user's opt-out value for Criteo's data collection practices", 'Indicates whether the user has opted out of personal data sales or sharing', 'Updates Criteo SDK opt-out value based on user consent'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opted out', 'User opted out of data sharing', 'User has opted out'], 'effects': ['User has opted out', 'The user will not be served personalized ads', "User's data will not be collected or used for advertising purposes", 'Criteo SDK reflects that the user opted out', "Criteo will no longer share user's personal information for advertising purposes"]}, {'parameter_values': [False], 'conditions': ['User has not opted out of data sharing', 'User did not opt out of data sharing', 'User has not opted out'], 'effects': ['Criteo SDK reflects that the user has not opted out', 'User has not opted out', "Criteo is allowed to share user's personal information for advertising purposes", "User's data may be collected and used for advertising purposes", 'The user needs to be served ads as per normal consent']}]}</t>
+          <t>{'API_name': 'setRequiresConsent', 'class_name': ['CountlyConfig'], 'conditions': ['Should be set to true before initializing Countly'], 'effects': ['Requires user consent for data collection', 'Enables or disables the requirement for user consent', 'If set to true, no event or session data will be sent unless the user provides consent.', 'Requires user consent for various features of the SDK', 'Sets whether the SDK requires user consent for data collection'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Set during SDK configuration'], 'effects': ['SDK functionalities will be disabled until consent is given', 'Consent is required for Countly to track data and send requests', 'All functions require explicit consent before operation.', 'SDK will not collect data unless consent is provided', 'The SDK will require consent for all features.']}, {'parameter_values': [False], 'conditions': ['Consent requirement is turned off.'], 'effects': ['Countly can track data without requiring user consent', 'Countly functions operate without needing user consent.', 'The SDK will not require user consent and will send data normally.', 'SDK can collect data without requiring explicit consent']}]}</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://publisherdocs.criteotilt.com/app/android/privacy/</t>
+          <t>https://support.countly.com/hc/en-us/articles/360037754031-Android#h_01HAVQDM5V1ZB8ECYTH1SPR3Q7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>Countly</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>setTagForChildDirectedTreatment</t>
+          <t>giveConsent</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'API_name': 'setTagForChildDirectedTreatment', 'class_name': ['Criteo'], 'conditions': ['Required to specify when targeting children under 13 years of age under COPPA regulations', 'Required to comply with COPPA regulations for children under 13', 'compliance with COPPA regulations when the app is directed at users under 13', 'Required to comply with COPPA for apps directed towards children', 'Required to comply with COPPA for apps directed to children under 13.'], 'effects': ['Indicates whether the content is directed toward children', 'Indicates whether the app is directed towards children', 'Indicates that the app is directed towards users under 13 years of age', 'ensures that the app complies with COPPA by tagging for child-directed treatment', 'Indicates that the app is directed to or collects information from children.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The content of the app is directed to users under 13 years of age', 'The app is directed towards children under the age of 13', 'App is directed to children under 13', 'When the app is directed to users under 13 years of age'], 'effects': ["The Criteo ads will be restricted to comply with regulations applicable to children's online privacy", 'Triggers compliance measures under COPPA', 'App is treated as directed to children under COPPA regulations', 'Criteo SDK will adjust ad targeting to comply with COPPA regulations', 'Tagging the content as directed toward children']}, {'parameter_values': [False], 'conditions': ['The content of the app is not directed to users under 13 years of age', 'App is not directed to children under 13', 'The app is not directed towards children under the age of 13', 'When the app is not directed to users under 13 years of age'], 'effects': ['Non-applicability of COPPA compliance measures', 'Criteo SDK will not apply COPPA-specific targeting', "Criteo ads may be served to all users, without special restrictions for children's online privacy", 'Content is not tagged as directed toward children', 'App is not treated as directed to children under COPPA regulations']}]}</t>
+          <t>{'API_name': 'giveConsent', 'class_name': ['Countly'], 'conditions': [], 'effects': ['Gives consent to a specific feature which allows that feature to function', 'Gives consent for specific features to be enabled', 'Provides consent for a specific feature, allowing related functions to operate.', 'Gives consent for the specified features in Countly'], 'parameter_configurations': [{'parameter_values': [['sessions']], 'conditions': [], 'effects': ['Allows the SDK to track sessions.', 'Allows session tracking to happen', 'Enables tracking for the sessions feature in Countly']}, {'parameter_values': [['sessions', 'events']], 'conditions': [], 'effects': ['Enables tracking sessions and events']}]}</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://publisherdocs.criteotilt.com/app/android/privacy/</t>
+          <t>https://support.countly.com/hc/en-us/articles/360037754031-Android#h_01HAVQDM5V1ZB8ECYTH1SPR3Q7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Facebook Audience Network</t>
+          <t>Countly</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>setDataProcessingOptions</t>
+          <t>removeConsent</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDataProcessingOptions', 'class_name': ['FBSDKSettings'], 'conditions': ['Data must be from users in California, Colorado, or Connecticut.', 'Compliance with Limited Data Use (LDU) requirements in specific U.S. states', 'must comply with Limited Data Use requirements for applicable states'], 'effects': ['Manages data processing preferences for individuals in certain states', 'Specifies how data is processed, especially concerning Limited Data Use', 'Limits data use and provides compliance with state-specific privacy regulations.', 'enables Limited Data Use (LDU) for specific states or countries', 'Enables or disables Limited Data Use (LDU) for compliant processing of user data.'], 'parameter_configurations': [{'parameter_values': [['LDU'], 0, 0], 'conditions': ['Enable LDU with automatic geolocation', 'enabling LDU and allowing Meta to perform geolocation', 'Data processing options for location-based processing.'], 'effects': ['Meta processes the data in compliance with state-specific regulations.', 'Data is processed with Limited Data Use protocols', 'Data is processed as a service provider and adheres to state-specific terms']}, {'parameter_values': [['LDU'], 1, 1000], 'conditions': ['Enable LDU with specified location (e.g., California)', 'Data processing options for manual specification of location, e.g., California.', 'enabling LDU specifies a location, e.g., for California', 'to enable LDU and specify location, e.g., California'], 'effects': ['data will be processed under LDU for California', 'Limited Data Use is enabled and location is specified for processing.', 'Data is processed as specified for the designated state', 'Meta processes the data with a specified state in compliance with privacy laws.', 'Data is processed under LDU protocols for California']}, {'parameter_values': [[]], 'conditions': ['explicitly choosing not to enable Limited Data Use'], 'effects': ['No LDU processing is applied', 'Explicitly indicates that Limited Data Use is not enabled']}, {'parameter_values': [[], 0, 0], 'conditions': ['to not enable Limited Data Use'], 'effects': ['data will be processed without LDU', 'Limited Data Use is not enabled.']}]}</t>
+          <t>{'API_name': 'removeConsent', 'class_name': ['Countly'], 'conditions': [], 'effects': ['Removes consent for a specific feature, stopping it from functioning', 'Removes consent for a specific feature, disabling related functions.', 'Removes consent for specific features', 'Removes consent for the specified features in Countly'], 'parameter_configurations': [{'parameter_values': [['sessions']], 'conditions': [], 'effects': ['Stops session tracking from occurring', 'Disables tracking sessions', 'Disables tracking for the sessions feature in Countly', 'Prevents the SDK from tracking sessions.']}]}</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://developers.facebook.com/docs/app-events/gdpr-compliance;https://developers.facebook.com/docs/app-events/guides/data-processing-options;https://developers.facebook.com/docs/app-events/guides/advertising-tracking-enabled;https://developers.facebook.com/docs/audience-network/optimization/best-practices/coppa/</t>
+          <t>https://support.countly.com/hc/en-us/articles/360037754031-Android#h_01HAVQDM5V1ZB8ECYTH1SPR3Q7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Facebook Audience Network</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>setAutoLogAppEventsEnabled</t>
+          <t>setUsPrivacyOptOut</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAutoLogAppEventsEnabled', 'class_name': ['FBSDKSettings'], 'conditions': ['end user provides consent for event logging'], 'effects': ['Controls the automatic logging of app events, influencing what data is sent to Facebook.', 'Enables or disables automatic logging of app events'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['end user consented to event logging', 'End user provides consent after an in-app consent flow.'], 'effects': ['Automatic logging of predefined app events resumes', 'Automatic event logging is enabled, logging common mobile events.']}, {'parameter_values': [False], 'conditions': ['end user has not provided consent for event logging'], 'effects': ['Automatic event logging is disabled, stopping any data transmission.', 'Prevents automatic logging of events']}]}</t>
+          <t>{'API_name': 'setUsPrivacyOptOut', 'class_name': ['Criteo'], 'conditions': ["Called as soon as the app receives consent, or when applicable users' consent status changes.", 'user has provided consent for data collection or the user opts out of data sharing', 'Must be passed to Criteo as soon as your app receives consent from applicable users', 'User consent must be received before calling this API', "Called as soon as the app receives user consent or in accordance with applicable users' consent"], 'effects': ["Updates the Criteo SDK with the user's opt-out preference.", 'indicates whether a user has opted out of data sharing under CCPA', "Sets the user's opt-out value for Criteo's data collection practices", 'Indicates whether the user has opted out of personal data sales or sharing', 'Updates Criteo SDK opt-out value based on user consent'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opted out', 'User opted out of data sharing', 'User has opted out'], 'effects': ['User has opted out', 'The user will not be served personalized ads', "User's data will not be collected or used for advertising purposes", 'Criteo SDK reflects that the user opted out', "Criteo will no longer share user's personal information for advertising purposes"]}, {'parameter_values': [False], 'conditions': ['User has not opted out of data sharing', 'User did not opt out of data sharing', 'User has not opted out'], 'effects': ['Criteo SDK reflects that the user has not opted out', 'User has not opted out', "Criteo is allowed to share user's personal information for advertising purposes", "User's data may be collected and used for advertising purposes", 'The user needs to be served ads as per normal consent']}]}</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://developers.facebook.com/docs/app-events/gdpr-compliance;https://developers.facebook.com/docs/app-events/guides/data-processing-options;https://developers.facebook.com/docs/app-events/guides/advertising-tracking-enabled;https://developers.facebook.com/docs/audience-network/optimization/best-practices/coppa/</t>
+          <t>https://publisherdocs.criteotilt.com/app/android/privacy/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Facebook Audience Network</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>setAdvertiserTrackingEnabled</t>
+          <t>setTagForChildDirectedTreatment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAdvertiserTrackingEnabled', 'class_name': ['FBSDKSettings'], 'conditions': ['User permission for advertiser tracking must be provided', 'permission is provided by the user to allow tracking', 'user provides permission for tracking', 'Permission is provided by the device to allow tracking.', 'User must provide permission for advertiser tracking.'], 'effects': ['Allows the application to enable or disable advertiser tracking based on user preferences', 'Allows advertiser tracking for app events', 'enables or disables advertiser tracking based on user consent', 'Tracks user events for advertising purposes based on user consent.', 'The method returns a boolean value indicating whether the method is set successfully or not.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Permission provided by the user to allow tracking', 'permission is granted by the user', 'User provides permission for advertiser tracking.', 'device provides permission for tracking', 'User has given permission for tracking.'], 'effects': ['Enables advertiser tracking for the app', 'Initiate advertiser tracking', 'advertiser tracking is enabled', 'Advertiser tracking is enabled.', 'SDK can track user events effectively.']}, {'parameter_values': [False], 'conditions': ['Device does not allow tracking.', 'Permission not provided by the user to allow tracking', 'User has not given permission for tracking.', 'device does not allow tracking', 'permission is denied by the user'], 'effects': ['SDK will not track user events, limiting advertising effectiveness.', 'Prohibit advertiser tracking', 'Disables advertiser tracking for the app', 'Advertiser tracking is disabled.', 'advertiser tracking is disabled']}]}</t>
+          <t>{'API_name': 'setTagForChildDirectedTreatment', 'class_name': ['Criteo'], 'conditions': ['Required to specify when targeting children under 13 years of age under COPPA regulations', 'Required to comply with COPPA regulations for children under 13', 'compliance with COPPA regulations when the app is directed at users under 13', 'Required to comply with COPPA for apps directed towards children', 'Required to comply with COPPA for apps directed to children under 13.'], 'effects': ['Indicates whether the content is directed toward children', 'Indicates whether the app is directed towards children', 'Indicates that the app is directed towards users under 13 years of age', 'ensures that the app complies with COPPA by tagging for child-directed treatment', 'Indicates that the app is directed to or collects information from children.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The content of the app is directed to users under 13 years of age', 'The app is directed towards children under the age of 13', 'App is directed to children under 13', 'When the app is directed to users under 13 years of age'], 'effects': ["The Criteo ads will be restricted to comply with regulations applicable to children's online privacy", 'Triggers compliance measures under COPPA', 'App is treated as directed to children under COPPA regulations', 'Criteo SDK will adjust ad targeting to comply with COPPA regulations', 'Tagging the content as directed toward children']}, {'parameter_values': [False], 'conditions': ['The content of the app is not directed to users under 13 years of age', 'App is not directed to children under 13', 'The app is not directed towards children under the age of 13', 'When the app is not directed to users under 13 years of age'], 'effects': ['Non-applicability of COPPA compliance measures', 'Criteo SDK will not apply COPPA-specific targeting', "Criteo ads may be served to all users, without special restrictions for children's online privacy", 'Content is not tagged as directed toward children', 'App is not treated as directed to children under COPPA regulations']}]}</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://developers.facebook.com/docs/app-events/gdpr-compliance;https://developers.facebook.com/docs/app-events/guides/data-processing-options;https://developers.facebook.com/docs/app-events/guides/advertising-tracking-enabled;https://developers.facebook.com/docs/audience-network/optimization/best-practices/coppa/</t>
+          <t>https://publisherdocs.criteotilt.com/app/android/privacy/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Facebook Audience Network</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>setUserProperty</t>
+          <t>setDataProcessingOptions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserProperty', 'class_name': ['FirebaseAnalytics'], 'conditions': [], 'effects': ['Sets a user property to a given value.'], 'parameter_configurations': [{'parameter_values': ['user_property_name', 'user_property_value'], 'conditions': [], 'effects': ['Persistently assigns the specified property value to the user.']}]}</t>
+          <t>{'API_name': 'setDataProcessingOptions', 'class_name': ['FBSDKSettings'], 'conditions': ['Data must be from users in California, Colorado, or Connecticut.', 'Compliance with Limited Data Use (LDU) requirements in specific U.S. states', 'must comply with Limited Data Use requirements for applicable states'], 'effects': ['Manages data processing preferences for individuals in certain states', 'Specifies how data is processed, especially concerning Limited Data Use', 'Limits data use and provides compliance with state-specific privacy regulations.', 'enables Limited Data Use (LDU) for specific states or countries', 'Enables or disables Limited Data Use (LDU) for compliant processing of user data.'], 'parameter_configurations': [{'parameter_values': [['LDU'], 0, 0], 'conditions': ['Enable LDU with automatic geolocation', 'enabling LDU and allowing Meta to perform geolocation', 'Data processing options for location-based processing.'], 'effects': ['Meta processes the data in compliance with state-specific regulations.', 'Data is processed with Limited Data Use protocols', 'Data is processed as a service provider and adheres to state-specific terms']}, {'parameter_values': [['LDU'], 1, 1000], 'conditions': ['Enable LDU with specified location (e.g., California)', 'Data processing options for manual specification of location, e.g., California.', 'enabling LDU specifies a location, e.g., for California', 'to enable LDU and specify location, e.g., California'], 'effects': ['data will be processed under LDU for California', 'Limited Data Use is enabled and location is specified for processing.', 'Data is processed as specified for the designated state', 'Meta processes the data with a specified state in compliance with privacy laws.', 'Data is processed under LDU protocols for California']}, {'parameter_values': [[]], 'conditions': ['explicitly choosing not to enable Limited Data Use'], 'effects': ['No LDU processing is applied', 'Explicitly indicates that Limited Data Use is not enabled']}, {'parameter_values': [[], 0, 0], 'conditions': ['to not enable Limited Data Use'], 'effects': ['data will be processed without LDU', 'Limited Data Use is not enabled.']}]}</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://firebase.google.com/docs/analytics/configure-data-collection?platform=android#setConsent(java.util.Map%3Ccom.google.firebase.analytics.FirebaseAnalytics.ConsentType,%20com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus%3E);https://firebase.google.com/docs/reference/android/com/google/firebase/analytics/FirebaseAnalytics#setConsent(java.util.Map&lt;com.google.firebase.analytics.FirebaseAnalytics.ConsentType, com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus&gt;)</t>
+          <t>https://developers.facebook.com/docs/app-events/gdpr-compliance;https://developers.facebook.com/docs/app-events/guides/data-processing-options;https://developers.facebook.com/docs/app-events/guides/advertising-tracking-enabled;https://developers.facebook.com/docs/audience-network/optimization/best-practices/coppa/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Facebook Audience Network</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>setConsent</t>
+          <t>setAutoLogAppEventsEnabled</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsent', 'class_name': ['FirebaseAnalytics'], 'conditions': ['Consent state needs to be defined for analytics storage and advertisement storage.'], 'effects': ['Sets the applicable end user consent state for this app on this device.', 'Sets the applicable end user consent state for this app on this device', 'Settings are persisted across app sessions', 'Sets the applicable end user consent state for device identifiers.', 'Sets the consent state for various data collection types.'], 'parameter_configurations': [{'parameter_values': [{'AD_STORAGE': 'GRANTED', 'ANALYTICS_STORAGE': 'GRANTED', 'AD_USER_DATA': 'GRANTED', 'AD_PERSONALIZATION': 'GRANTED'}], 'conditions': [], 'effects': ['Indicates that consent is granted for ad storage, analytics storage, ad user data, and ad personalization.', 'User consent is granted for advertising and analytics.', 'User has granted consent for all types of data collection', 'Enables analytics and ad storage.', 'Users grant consent for all types of data collection.']}, {'parameter_values': [{'AD_STORAGE': 'DENIED', 'ANALYTICS_STORAGE': 'DENIED', 'AD_USER_DATA': 'DENIED', 'AD_PERSONALIZATION': 'DENIED'}], 'conditions': [], 'effects': ['User consent is denied for advertising and analytics.', 'Users deny consent for all types of data collection.', 'Disables analytics and ad storage.', 'Indicates that consent is denied for ad storage, analytics storage, ad user data, and ad personalization.', 'User has denied consent for all types of data collection']}]}</t>
+          <t>{'API_name': 'setAutoLogAppEventsEnabled', 'class_name': ['FBSDKSettings'], 'conditions': ['end user provides consent for event logging'], 'effects': ['Controls the automatic logging of app events, influencing what data is sent to Facebook.', 'Enables or disables automatic logging of app events'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['end user consented to event logging', 'End user provides consent after an in-app consent flow.'], 'effects': ['Automatic logging of predefined app events resumes', 'Automatic event logging is enabled, logging common mobile events.']}, {'parameter_values': [False], 'conditions': ['end user has not provided consent for event logging'], 'effects': ['Automatic event logging is disabled, stopping any data transmission.', 'Prevents automatic logging of events']}]}</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://firebase.google.com/docs/analytics/configure-data-collection?platform=android#setConsent(java.util.Map%3Ccom.google.firebase.analytics.FirebaseAnalytics.ConsentType,%20com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus%3E);https://firebase.google.com/docs/reference/android/com/google/firebase/analytics/FirebaseAnalytics#setConsent(java.util.Map&lt;com.google.firebase.analytics.FirebaseAnalytics.ConsentType, com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus&gt;)</t>
+          <t>https://developers.facebook.com/docs/app-events/gdpr-compliance;https://developers.facebook.com/docs/app-events/guides/data-processing-options;https://developers.facebook.com/docs/app-events/guides/advertising-tracking-enabled;https://developers.facebook.com/docs/audience-network/optimization/best-practices/coppa/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Flurry Analytics</t>
+          <t>Facebook Audience Network</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>setDataSaleOptOut</t>
+          <t>setAdvertiserTrackingEnabled</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDataSaleOptOut', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['Allows the user to opt-out or opt-in for data sale', 'sets user preference for opting out or opting in for data sale', 'Sets the opt-out/opt-in status for data sale.', "Sets the user's preference for data sale, either opting-out or opting-in.", "Sets the user's opt-out/opt-in preference for data sale."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User has opted-out of data sale.', 'User opts-out of data sale.', 'user opts out of data sale', 'User opts out of data sale', 'User opts out of data sale.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User opts in for data sale', 'User opts-in for data sale.', 'User opts into data sale.', 'User has opted-in for data sale.', 'user opts in for data sale']}]}</t>
+          <t>{'API_name': 'setAdvertiserTrackingEnabled', 'class_name': ['FBSDKSettings'], 'conditions': ['User permission for advertiser tracking must be provided', 'permission is provided by the user to allow tracking', 'user provides permission for tracking', 'Permission is provided by the device to allow tracking.', 'User must provide permission for advertiser tracking.'], 'effects': ['Allows the application to enable or disable advertiser tracking based on user preferences', 'Allows advertiser tracking for app events', 'enables or disables advertiser tracking based on user consent', 'Tracks user events for advertising purposes based on user consent.', 'The method returns a boolean value indicating whether the method is set successfully or not.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Permission provided by the user to allow tracking', 'permission is granted by the user', 'User provides permission for advertiser tracking.', 'device provides permission for tracking', 'User has given permission for tracking.'], 'effects': ['Enables advertiser tracking for the app', 'Initiate advertiser tracking', 'advertiser tracking is enabled', 'Advertiser tracking is enabled.', 'SDK can track user events effectively.']}, {'parameter_values': [False], 'conditions': ['Device does not allow tracking.', 'Permission not provided by the user to allow tracking', 'User has not given permission for tracking.', 'device does not allow tracking', 'permission is denied by the user'], 'effects': ['SDK will not track user events, limiting advertising effectiveness.', 'Prohibit advertiser tracking', 'Disables advertiser tracking for the app', 'Advertiser tracking is disabled.', 'advertiser tracking is disabled']}]}</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
+          <t>https://developers.facebook.com/docs/app-events/gdpr-compliance;https://developers.facebook.com/docs/app-events/guides/data-processing-options;https://developers.facebook.com/docs/app-events/guides/advertising-tracking-enabled;https://developers.facebook.com/docs/audience-network/optimization/best-practices/coppa/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Flurry Analytics</t>
+          <t>Firebase</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>deleteData</t>
+          <t>setAutoLogAppEventsEnabled</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'API_name': 'deleteData', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['deletes data collected by Flurry', 'Deletes data collected by Flurry', 'Deletes all data collected by Flurry for this session.', 'Deletes data collected by Flurry.'], 'parameter_configurations': []}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
+          <t>https://firebase.google.com/docs/analytics/configure-data-collection?platform=android#setConsent(java.util.Map%3Ccom.google.firebase.analytics.FirebaseAnalytics.ConsentType,%20com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus%3E);https://firebase.google.com/docs/reference/android/com/google/firebase/analytics/FirebaseAnalytics#setConsent(java.util.Map&lt;com.google.firebase.analytics.FirebaseAnalytics.ConsentType, com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus&gt;)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Flurry Analytics</t>
+          <t>Firebase</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>setGppConsent</t>
+          <t>setUserProperty</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGppConsent', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['sets Flurry Consent for the IAB Global Privacy Platform', 'Sets Flurry Consent for the IAB Global Privacy Platform (GPP)', 'Sets Flurry Consent for the IAB Global Privacy Platform (GPP).', 'Sets Flurry consent for the IAB Global Privacy Platform (GPP).', 'Sets the Flurry consent according to the IAB Global Privacy Platform.'], 'parameter_configurations': [{'parameter_values': ['gppString', 'gppSectionIds'], 'conditions': [], 'effects': ['Consent is validated and recorded.', 'Sets valid GPP consent if the inputs are correct', 'Updates consent status based on provided GPP string and section IDs.', 'Consent for data handling under GPP is established.', 'sets consent based on the provided GPP string and section IDs']}]}</t>
+          <t>{'API_name': 'setUserProperty', 'class_name': ['FirebaseAnalytics'], 'conditions': [], 'effects': ['Sets a user property to a given value.'], 'parameter_configurations': [{'parameter_values': ['user_property_name', 'user_property_value'], 'conditions': [], 'effects': ['Persistently assigns the specified property value to the user.']}]}</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
+          <t>https://firebase.google.com/docs/analytics/configure-data-collection?platform=android#setConsent(java.util.Map%3Ccom.google.firebase.analytics.FirebaseAnalytics.ConsentType,%20com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus%3E);https://firebase.google.com/docs/reference/android/com/google/firebase/analytics/FirebaseAnalytics#setConsent(java.util.Map&lt;com.google.firebase.analytics.FirebaseAnalytics.ConsentType, com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus&gt;)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Flurry Analytics</t>
+          <t>Firebase</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>updateFlurryConsent</t>
+          <t>setConsent</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'API_name': 'updateFlurryConsent', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['updates Flurry consent', 'Updates Flurry consent', 'Updates Flurry consent.', 'Updates the Flurry consent.'], 'parameter_configurations': [{'parameter_values': ['flurryConsent'], 'conditions': [], 'effects': ["evaluates whether the new consent is valid and updates Flurry's consent state", 'Consent is updated successfully.', 'Validity of the consent state is checked and updated.', 'Returns true if consent is valid, false otherwise']}, {'parameter_values': ['Consent'], 'conditions': [], 'effects': ['Validates and updates consent.']}]}</t>
+          <t>{'API_name': 'setConsent', 'class_name': ['FirebaseAnalytics'], 'conditions': ['Consent state needs to be defined for analytics storage and advertisement storage.'], 'effects': ['Sets the applicable end user consent state for this app on this device.', 'Sets the applicable end user consent state for this app on this device', 'Settings are persisted across app sessions', 'Sets the applicable end user consent state for device identifiers.', 'Sets the consent state for various data collection types.'], 'parameter_configurations': [{'parameter_values': [{'AD_STORAGE': 'GRANTED', 'ANALYTICS_STORAGE': 'GRANTED', 'AD_USER_DATA': 'GRANTED', 'AD_PERSONALIZATION': 'GRANTED'}], 'conditions': [], 'effects': ['Indicates that consent is granted for ad storage, analytics storage, ad user data, and ad personalization.', 'User consent is granted for advertising and analytics.', 'User has granted consent for all types of data collection', 'Enables analytics and ad storage.', 'Users grant consent for all types of data collection.']}, {'parameter_values': [{'AD_STORAGE': 'DENIED', 'ANALYTICS_STORAGE': 'DENIED', 'AD_USER_DATA': 'DENIED', 'AD_PERSONALIZATION': 'DENIED'}], 'conditions': [], 'effects': ['User consent is denied for advertising and analytics.', 'Users deny consent for all types of data collection.', 'Disables analytics and ad storage.', 'Indicates that consent is denied for ad storage, analytics storage, ad user data, and ad personalization.', 'User has denied consent for all types of data collection']}]}</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
+          <t>https://firebase.google.com/docs/analytics/configure-data-collection?platform=android#setConsent(java.util.Map%3Ccom.google.firebase.analytics.FirebaseAnalytics.ConsentType,%20com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus%3E);https://firebase.google.com/docs/reference/android/com/google/firebase/analytics/FirebaseAnalytics#setConsent(java.util.Map&lt;com.google.firebase.analytics.FirebaseAnalytics.ConsentType, com.google.firebase.analytics.FirebaseAnalytics.ConsentStatus&gt;)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GameAnalytics</t>
+          <t>Flurry Analytics</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>setEnabledEventSubmission</t>
+          <t>setDataSaleOptOut</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'API_name': 'setEnabledEventSubmission', 'class_name': ['GameAnalytics'], 'conditions': ['Required to disable event submission for GDPR purposes', 'required for GDPR purposes to disable event submission', 'required for GDPR purposes', 'required to comply with GDPR', 'Applicable in regions with privacy regulations requiring user consent before data submission', 'GDPR purposes'], 'effects': ['disables or enables event submission for user events', 'Disables or enables submission of events to GameAnalytics', 'disables event submission for GameAnalytics events', 'Manually turns off event submission for GameAnalytics events', 'controls whether event submission is enabled or disabled'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['If event submission needs to be disabled for GDPR compliance', 'When you need to comply with GDPR and do not have user consent', 'When compliance with GDPR is necessary', 'Event submission should be turned off'], 'effects': ['Events will not be submitted until event submission is enabled again', 'Disables event submission for GDPR purposes', 'No events will be submitted to the GameAnalytics server', 'event submission is disabled']}, {'parameter_values': [True], 'conditions': ['After obtaining user consent', 'Event submission should be enabled'], 'effects': ['Events will be submitted to the GameAnalytics server', 'Enables event submission by default', 'Enables event submissions to the GameAnalytics server', 'event submission is enabled', 'Events will be submitted to GameAnalytics']}]}</t>
+          <t>{'API_name': 'setDataSaleOptOut', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['Allows the user to opt-out or opt-in for data sale', 'sets user preference for opting out or opting in for data sale', 'Sets the opt-out/opt-in status for data sale.', "Sets the user's preference for data sale, either opting-out or opting-in.", "Sets the user's opt-out/opt-in preference for data sale."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User has opted-out of data sale.', 'User opts-out of data sale.', 'user opts out of data sale', 'User opts out of data sale', 'User opts out of data sale.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User opts in for data sale', 'User opts-in for data sale.', 'User opts into data sale.', 'User has opted-in for data sale.', 'user opts in for data sale']}]}</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://docs.gameanalytics.com/integrations/sdk/unity/sdk-features/</t>
+          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Flurry Analytics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>setAppOptOut</t>
+          <t>deleteData</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAppOptOut', 'class_name': ['GoogleAnalytics'], 'conditions': ['The application-level opt out flag should be set when initialization code is executed.'], 'effects': ['Sets or resets the application-level opt out flag. If set, no hits will be sent to Google Analytics.', 'No hits will be sent to Google Analytics.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Prevents any data from being sent to Google Analytics.', 'Application-level opt out is enforced, and no hits will be sent to Google Analytics.', 'Enforces application-level opt out.', 'Enforces application-level opt-out', 'Application-level opt out is enforced. No hits will be sent to Google Analytics.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Allows hits to be sent to Google Analytics', 'Application-level opt out is removed, and hits can be sent to Google Analytics.', 'Application-level opt out is not enforced. Hits can be sent to Google Analytics.', 'Allows data to be sent to Google Analytics.', 'Resets the application-level opt out.']}]}</t>
+          <t>{'API_name': 'deleteData', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['deletes data collected by Flurry', 'Deletes data collected by Flurry', 'Deletes all data collected by Flurry for this session.', 'Deletes data collected by Flurry.'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://developers.google.com/android/reference/com/google/android/gms/analytics/GoogleAnalytics</t>
+          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HyprMX</t>
+          <t>Flurry Analytics</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>setConsentStatus</t>
+          <t>setGppConsent</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsentStatus', 'class_name': ['HyprMX'], 'conditions': ['Publisher must comply with applicable privacy laws and regulations including GDPR, CPRA, etc.', 'Jurisdictions that require passing consent', 'If the user did not provide consent in jurisdictions that require opt-in consent or opted out in jurisdictions that require opt-out consent', 'Publishers need to comply with GDPR, CPRA, and other applicable privacy laws.', 'If consent status for the user is unknown', 'The jurisdiction requires passing consent status regarding personal data collection', 'If the user provided consent in jurisdictions that require opt-in consent or did not opt out in jurisdictions that require opt-out consent', 'Must determine user consent before using personal data', 'app must collect user consent according to GDPR, CPRA, and other applicable laws'], 'effects': ['Indicates a user’s opt-in or opt-out consent for the collection and use of personal data under applicable laws', 'Indicates a user’s opt-in or opt-out consent for the collection and use of personal data.', "Indicates a user's opt-in or opt-out consent for the collection and use of personal data", 'indicates a user’s opt-in or opt-out consent for the collection and use of personal data'], 'parameter_configurations': [{'parameter_values': ['ConsentStatus.CONSENT_GIVEN'], 'conditions': ['If user provided consent in jurisdictions requiring opt-in consent', 'User provided consent in jurisdictions requiring opt-in consent.', 'User has provided consent in jurisdictions that require opt-in consent', 'User provided consent', 'User did not opt out of collection or usage of personal data in jurisdictions that require opt-out consent', 'User provided consent in jurisdictions that require opt-in consent'], 'effects': ["User's consent status is set to CONSENT_GIVEN", 'User consent is acknowledged as given.', 'User consent is recorded as given', 'Status reflects that user has consented to personal data usage']}, {'parameter_values': ['ConsentStatus.CONSENT_DECLINED'], 'conditions': ['User opted out in jurisdictions requiring opt-out consent', 'If user did not provide consent in jurisdictions requiring opt-in consent', 'User did not provide consent', 'User did not provide consent in jurisdictions requiring opt-in consent or opted out in jurisdictions requiring opt-out consent.', 'User did not provide consent in jurisdictions requiring opt-in consent', 'User did not provide consent in jurisdictions that require opt-in consent'], 'effects': ['User consent is recorded as declined', 'Status reflects that user has declined consent for personal data usage', "User's consent status is set to CONSENT_DECLINED", 'User consent is acknowledged as declined.']}, {'parameter_values': ['ConsentStatus.CONSENT_STATUS_UNKNOWN'], 'conditions': ["User's consent status is unknown", 'Consent status of user is unknown', 'User consent status is not known.', 'If the consent status for the user is not known', 'Consent status for the user is unknown'], 'effects': ['User consent status remains unknown.', "User's consent status is set to CONSENT_STATUS_UNKNOWN", "Status reflects uncertainty regarding user's consent", 'User consent status is recorded as unknown']}]}</t>
+          <t>{'API_name': 'setGppConsent', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['sets Flurry Consent for the IAB Global Privacy Platform', 'Sets Flurry Consent for the IAB Global Privacy Platform (GPP)', 'Sets Flurry Consent for the IAB Global Privacy Platform (GPP).', 'Sets Flurry consent for the IAB Global Privacy Platform (GPP).', 'Sets the Flurry consent according to the IAB Global Privacy Platform.'], 'parameter_configurations': [{'parameter_values': ['gppString', 'gppSectionIds'], 'conditions': [], 'effects': ['Consent is validated and recorded.', 'Sets valid GPP consent if the inputs are correct', 'Updates consent status based on provided GPP string and section IDs.', 'Consent for data handling under GPP is established.', 'sets consent based on the provided GPP string and section IDs']}]}</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://documentation.hyprmx.com/android-sdk/getting-started/privacy</t>
+          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HyprMX</t>
+          <t>Flurry Analytics</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>setAgeRestrictedUser</t>
+          <t>updateFlurryConsent</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAgeRestrictedUser', 'class_name': ['HyprMX'], 'conditions': ["Publishers are responsible for determining a user's age and adhering to applicable laws and policies, such as COPPA.", 'Applicable regional laws and regulations such as COPPA, GDPR, and Google Play Store policies must be adhered to', 'User under 16 or requires child-directed treatment', 'The user is under 16 or requires child-directed treatment according to applicable laws', 'Publisher must comply with COPPA, GDPR, and Google Play Store policies regarding child-directed treatment', 'Publisher must determine when to flag the user as age-restricted', 'Publisher is responsible for determining if the user requires child-directed treatment according to COPPA, GDPR, and other applicable laws'], 'effects': ['Flags users under 16 as needing child-directed treatment, affecting data access', 'Assists publishers in adhering to privacy laws regarding child-directed treatment', 'Indicates whether a user requires child-directed treatment.', 'Flags the user as requiring child-directed treatment', 'Flags the user as age-restricted to comply with privacy laws'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under 16 or requires child-directed treatment', 'If the user is under 16 or requires child-directed treatment', 'User is under 16 years old or requires child-directed treatment.'], 'effects': ['User is flagged for child-directed treatment and access to AAID is restricted', 'User is treated as age-restricted for compliance.', 'Prevents access to Advertising ID for flagged end-users', 'User is flagged as requiring child-directed treatment', 'User is flagged requiring child-directed treatment']}, {'parameter_values': [False], 'conditions': ["If the user is not under 16 or if the app developer does not know the user's age restriction status", 'User is not under 16 or the age status is unknown', 'User is not under 16 or if it is unknown whether the user is age restricted', "User is not under 16, or publisher does not know the user's age."], 'effects': ['User is not flagged as requiring child-directed treatment', 'User is not flagged as age-restricted', 'User is not flagged for child-directed treatment', 'Allows normal access to Advertising ID', 'User is not treated as age-restricted.']}]}</t>
+          <t>{'API_name': 'updateFlurryConsent', 'class_name': ['FlurryAgent'], 'conditions': [], 'effects': ['updates Flurry consent', 'Updates Flurry consent', 'Updates Flurry consent.', 'Updates the Flurry consent.'], 'parameter_configurations': [{'parameter_values': ['flurryConsent'], 'conditions': [], 'effects': ["evaluates whether the new consent is valid and updates Flurry's consent state", 'Consent is updated successfully.', 'Validity of the consent state is checked and updated.', 'Returns true if consent is valid, false otherwise']}, {'parameter_values': ['Consent'], 'conditions': [], 'effects': ['Validates and updates consent.']}]}</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://documentation.hyprmx.com/android-sdk/getting-started/privacy</t>
+          <t>https://flurry.github.io/flurry-android-sdk/analytics/com/flurry/android/FlurryAgent.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>InMobi</t>
+          <t>GameAnalytics</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>setDoNotSell</t>
+          <t>setEnabledEventSubmission</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDoNotSell', 'class_name': ['InMobiPrivacyCompliance'], 'conditions': ['The user must indicate opt-out of interest-based advertising.', 'User opts out of the sale of data;', 'User opts out of the sale of their personal data.', 'User opts out of selling their personal data', 'User opts out of interest-based advertising.'], 'effects': ['Informs InMobi and their ad partners not to sell personal data.', 'User is opted out of interest-based advertising.', 'Indicates to InMobi that the user does not wish to sell or share their personal information.', 'Users will be opted out of the sale of their personal data, affecting advertisement targeting.', 'User data will not be sold to third parties'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The user opts out of interest-based advertising.', 'User has opted out of the sale of their personal data.', 'The user has opted out'], 'effects': ["User's personal information will not be sold or shared.", "The user's data is effectively opted out from being sold.", 'Indicates to InMobi that the user does not wish to have their personal data sold.']}, {'parameter_values': [False], 'conditions': ['The user chooses not to opt-out.', 'User has not opted out of the sale of their personal data.', 'The user has not opted out'], 'effects': ['User data can be utilized for targeted advertising.', "User's personal information may be sold or shared.", 'Standard data processing is applied, and data might still be sold.']}]}</t>
+          <t>{'API_name': 'setEnabledEventSubmission', 'class_name': ['GameAnalytics'], 'conditions': ['Required to disable event submission for GDPR purposes', 'required for GDPR purposes to disable event submission', 'required for GDPR purposes', 'required to comply with GDPR', 'Applicable in regions with privacy regulations requiring user consent before data submission', 'GDPR purposes'], 'effects': ['disables or enables event submission for user events', 'Disables or enables submission of events to GameAnalytics', 'disables event submission for GameAnalytics events', 'Manually turns off event submission for GameAnalytics events', 'controls whether event submission is enabled or disabled'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['If event submission needs to be disabled for GDPR compliance', 'When you need to comply with GDPR and do not have user consent', 'When compliance with GDPR is necessary', 'Event submission should be turned off'], 'effects': ['Events will not be submitted until event submission is enabled again', 'Disables event submission for GDPR purposes', 'No events will be submitted to the GameAnalytics server', 'event submission is disabled']}, {'parameter_values': [True], 'conditions': ['After obtaining user consent', 'Event submission should be enabled'], 'effects': ['Events will be submitted to the GameAnalytics server', 'Enables event submission by default', 'Enables event submissions to the GameAnalytics server', 'event submission is enabled', 'Events will be submitted to GameAnalytics']}]}</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://support.inmobi.com/monetize/privacy/gdpr;https://support.inmobi.com/monetize/privacy/lgpd;https://support.inmobi.com/monetize/privacy/coppa;https://support.inmobi.com/monetize/privacy/us-privacy/ccpa#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/cpra#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/vcdpa;https://support.inmobi.com/monetize/privacy/us-privacy/cpa;https://support.inmobi.com/monetize/privacy/us-privacy/opt-out-mechanism;https://support.inmobi.com/monetize/android-guidelines/#optimization</t>
+          <t>https://docs.gameanalytics.com/integrations/sdk/unity/sdk-features/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>InMobi</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>setUSPrivacyString</t>
+          <t>setAppOptOut</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUSPrivacyString', 'class_name': ['InMobiPrivacyCompliance'], 'conditions': ['The user must provide relevant consent for their personal data processing.', 'User is from a state that requires privacy strings for compliance.', 'The value passed must comply with the IAB specification', 'Must comply with U.S. privacy regulations.'], 'effects': ["The user's preferences regarding the sale of personal information will be reflected.", "The privacy string is populated as per the user's opt-out or consent status.", 'Sets the privacy string for compliance with CCPA.', 'Sets the U.S. Privacy String which affects user data handling per privacy regulations.'], 'parameter_configurations': [{'parameter_values': [''], 'conditions': ['Ensure string value complies with IAB specification.', "User's U.S. privacy information must comply with privacy regulations.", 'The privacy string is valid according to IAB specification'], 'effects': ['The U.S. Privacy String must comply with the IAB specifications.', 'Sets an empty U.S. Privacy String.', "User's choices about data selling are correctly applied.", 'Updates the privacy string indicating user consent status.']}]}</t>
+          <t>{'API_name': 'setAppOptOut', 'class_name': ['GoogleAnalytics'], 'conditions': ['The application-level opt out flag should be set when initialization code is executed.'], 'effects': ['Sets or resets the application-level opt out flag. If set, no hits will be sent to Google Analytics.', 'No hits will be sent to Google Analytics.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Prevents any data from being sent to Google Analytics.', 'Application-level opt out is enforced, and no hits will be sent to Google Analytics.', 'Enforces application-level opt out.', 'Enforces application-level opt-out', 'Application-level opt out is enforced. No hits will be sent to Google Analytics.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Allows hits to be sent to Google Analytics', 'Application-level opt out is removed, and hits can be sent to Google Analytics.', 'Application-level opt out is not enforced. Hits can be sent to Google Analytics.', 'Allows data to be sent to Google Analytics.', 'Resets the application-level opt out.']}]}</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://support.inmobi.com/monetize/privacy/gdpr;https://support.inmobi.com/monetize/privacy/lgpd;https://support.inmobi.com/monetize/privacy/coppa;https://support.inmobi.com/monetize/privacy/us-privacy/ccpa#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/cpra#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/vcdpa;https://support.inmobi.com/monetize/privacy/us-privacy/cpa;https://support.inmobi.com/monetize/privacy/us-privacy/opt-out-mechanism;https://support.inmobi.com/monetize/android-guidelines/#optimization</t>
+          <t>https://developers.google.com/android/reference/com/google/android/gms/analytics/GoogleAnalytics</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>InMobi</t>
+          <t>HyprMX</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>setIsAgeRestricted</t>
+          <t>setConsentStatus</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'API_name': 'setIsAgeRestricted', 'class_name': ['InMobiSdk'], 'conditions': ['Required to comply with COPPA if the app is directed at children under 16 years old.', "The application's audience is general, which may include children under the age of 16.", "The user's application is directed to children under the age of 16.", 'The app is directed at children under the age of 16 or to a general audience which may include children under the age of 16', 'If the app is directed to children under the age of 16 or to a general audience which may include children.', 'User app is directed to children under the age of 16.'], 'effects': ['AKSIGLO: The request will be treated as child-directed, hence sensitive data handling may be altered.', 'Sets the age-restriction status for the app, affecting data handling practices for compliance.', 'Indicates whether the request will be treated as child-directed. If True, device identifiers will not be transmitted.', 'If set to true, the app will be treated as child-directed and certain identifiers such as AAID will not be transmitted.', 'The request will be treated as child-directed if the value is set to true; otherwise treated as not child-directed.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The app targets children under the age of 16.', 'The app targets users under the age of 16.', 'If the app is directed to children', 'The application is confirmed to be child-directed.'], 'effects': ['The SDK will not transmit device identifiers such as Android Advertising ID (AAID) or IDFA.', 'Prevents transmission of device identifiers.', 'The request is treated as child-directed.', 'InMobi will not transmit device identifiers such as Android Advertising ID.', 'The app will be treated as child-directed, affecting data processing under laws like COPPA.']}, {'parameter_values': [False], 'conditions': ['If the app is not directed to children', 'The app does not target users under the age of 16.', 'The app does not target children or is a mixed audience app.'], 'effects': ['The request is not treated as child-directed.', 'Allows transmission of device identifiers.', 'The app will not be treated as child-directed.']}]}</t>
+          <t>{'API_name': 'setConsentStatus', 'class_name': ['HyprMX'], 'conditions': ['Publisher must comply with applicable privacy laws and regulations including GDPR, CPRA, etc.', 'Jurisdictions that require passing consent', 'If the user did not provide consent in jurisdictions that require opt-in consent or opted out in jurisdictions that require opt-out consent', 'Publishers need to comply with GDPR, CPRA, and other applicable privacy laws.', 'If consent status for the user is unknown', 'The jurisdiction requires passing consent status regarding personal data collection', 'If the user provided consent in jurisdictions that require opt-in consent or did not opt out in jurisdictions that require opt-out consent', 'Must determine user consent before using personal data', 'app must collect user consent according to GDPR, CPRA, and other applicable laws'], 'effects': ['Indicates a user’s opt-in or opt-out consent for the collection and use of personal data under applicable laws', 'Indicates a user’s opt-in or opt-out consent for the collection and use of personal data.', "Indicates a user's opt-in or opt-out consent for the collection and use of personal data", 'indicates a user’s opt-in or opt-out consent for the collection and use of personal data'], 'parameter_configurations': [{'parameter_values': ['ConsentStatus.CONSENT_GIVEN'], 'conditions': ['If user provided consent in jurisdictions requiring opt-in consent', 'User provided consent in jurisdictions requiring opt-in consent.', 'User has provided consent in jurisdictions that require opt-in consent', 'User provided consent', 'User did not opt out of collection or usage of personal data in jurisdictions that require opt-out consent', 'User provided consent in jurisdictions that require opt-in consent'], 'effects': ["User's consent status is set to CONSENT_GIVEN", 'User consent is acknowledged as given.', 'User consent is recorded as given', 'Status reflects that user has consented to personal data usage']}, {'parameter_values': ['ConsentStatus.CONSENT_DECLINED'], 'conditions': ['User opted out in jurisdictions requiring opt-out consent', 'If user did not provide consent in jurisdictions requiring opt-in consent', 'User did not provide consent', 'User did not provide consent in jurisdictions requiring opt-in consent or opted out in jurisdictions requiring opt-out consent.', 'User did not provide consent in jurisdictions requiring opt-in consent', 'User did not provide consent in jurisdictions that require opt-in consent'], 'effects': ['User consent is recorded as declined', 'Status reflects that user has declined consent for personal data usage', "User's consent status is set to CONSENT_DECLINED", 'User consent is acknowledged as declined.']}, {'parameter_values': ['ConsentStatus.CONSENT_STATUS_UNKNOWN'], 'conditions': ["User's consent status is unknown", 'Consent status of user is unknown', 'User consent status is not known.', 'If the consent status for the user is not known', 'Consent status for the user is unknown'], 'effects': ['User consent status remains unknown.', "User's consent status is set to CONSENT_STATUS_UNKNOWN", "Status reflects uncertainty regarding user's consent", 'User consent status is recorded as unknown']}]}</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://support.inmobi.com/monetize/privacy/gdpr;https://support.inmobi.com/monetize/privacy/lgpd;https://support.inmobi.com/monetize/privacy/coppa;https://support.inmobi.com/monetize/privacy/us-privacy/ccpa#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/cpra#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/vcdpa;https://support.inmobi.com/monetize/privacy/us-privacy/cpa;https://support.inmobi.com/monetize/privacy/us-privacy/opt-out-mechanism;https://support.inmobi.com/monetize/android-guidelines/#optimization</t>
+          <t>https://documentation.hyprmx.com/android-sdk/getting-started/privacy</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ironsource</t>
+          <t>HyprMX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>setConsent</t>
+          <t>setAgeRestrictedUser</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsent', 'class_name': ['IronSource'], 'conditions': ["GDPR compliance requires the user's consent status to be communicated to the mediation platform", 'GDPR consent is required when providing personalized ads', 'User must provide consent before using the API', 'The user provided consent', 'The user did not provide consent', 'User has provided consent or not'], 'effects': ["Stores the user's consent status for GDPR compliance", "Updates the user's consent status for data processing", "Updates the user's consent status for GDPR compliance", 'Sets the consent status for GDPR compliance', 'Updates the consent status for user data processing under GDPR'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User provided consent', 'If the user provided consent'], 'effects': ['Sets the consent flag to true', 'Indicates the user provided consent', 'User consent is registered as true', 'User data can be processed for personalized ads', 'Indicates that the user has given consent']}, {'parameter_values': [False], 'conditions': ['User did not consent', 'If the user did not consent', 'If the user did not provide consent'], 'effects': ['User data cannot be processed for personalized ads', 'Sets the consent flag to false', 'User consent is registered as false', 'Indicates the user did not provide consent', 'Indicates that the user has not given consent']}]}</t>
+          <t>{'API_name': 'setAgeRestrictedUser', 'class_name': ['HyprMX'], 'conditions': ["Publishers are responsible for determining a user's age and adhering to applicable laws and policies, such as COPPA.", 'Applicable regional laws and regulations such as COPPA, GDPR, and Google Play Store policies must be adhered to', 'User under 16 or requires child-directed treatment', 'The user is under 16 or requires child-directed treatment according to applicable laws', 'Publisher must comply with COPPA, GDPR, and Google Play Store policies regarding child-directed treatment', 'Publisher must determine when to flag the user as age-restricted', 'Publisher is responsible for determining if the user requires child-directed treatment according to COPPA, GDPR, and other applicable laws'], 'effects': ['Flags users under 16 as needing child-directed treatment, affecting data access', 'Assists publishers in adhering to privacy laws regarding child-directed treatment', 'Indicates whether a user requires child-directed treatment.', 'Flags the user as requiring child-directed treatment', 'Flags the user as age-restricted to comply with privacy laws'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under 16 or requires child-directed treatment', 'If the user is under 16 or requires child-directed treatment', 'User is under 16 years old or requires child-directed treatment.'], 'effects': ['User is flagged for child-directed treatment and access to AAID is restricted', 'User is treated as age-restricted for compliance.', 'Prevents access to Advertising ID for flagged end-users', 'User is flagged as requiring child-directed treatment', 'User is flagged requiring child-directed treatment']}, {'parameter_values': [False], 'conditions': ["If the user is not under 16 or if the app developer does not know the user's age restriction status", 'User is not under 16 or the age status is unknown', 'User is not under 16 or if it is unknown whether the user is age restricted', "User is not under 16, or publisher does not know the user's age."], 'effects': ['User is not flagged as requiring child-directed treatment', 'User is not flagged as age-restricted', 'User is not flagged for child-directed treatment', 'Allows normal access to Advertising ID', 'User is not treated as age-restricted.']}]}</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://developers.is.com/ironsource-mobile/android/regulation-advanced-settings/#step-1</t>
+          <t>https://documentation.hyprmx.com/android-sdk/getting-started/privacy</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ironsource</t>
+          <t>InMobi</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>setMetaData</t>
+          <t>setDoNotSell</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'API_name': 'setMetaData', 'class_name': ['IronSource'], 'conditions': ["User opts out of 'sale' or 'sharing' of personal information", 'API should be set before initializing the SDK', 'Should be set before initializing the SDK', 'API must be called before initializing the SDK', 'Must be set before initializing the SDK to comply with U.S. state privacy laws, such as the CPRA.', 'U.S. state privacy laws compliance is required when notifying personal information handling', 'Applicable law (e.g., COPPA) requires indicating if the user is a child'], 'effects': ['Flags users as children or not for appropriate data handling', "Handles the 'do not sell or share' setting for U.S. state privacy laws", 'Controls the sale or sharing of end-users personal information as per state laws', 'Controls the handling of personal information under U.S. state privacy laws', 'Sets privacy-related metadata for the user', 'Updates the specified metadata for the user regarding personal information sale'], 'parameter_configurations': [{'parameter_values': ['do_not_sell', 'true'], 'conditions': ['If the user has opted out of sale or sharing of their personal information', 'User has opted out of sale or sharing of personal information', 'User has opted out of the sale or sharing of personal information', "If the user has opted out of 'sale' or 'sharing' of personal information"], 'effects': ["Restricts the sale or sharing of user's personal information", 'Denotes that personal information should not be sold or shared', "Sale or sharing of the user's personal information is prohibited", "Restricts the sale or sharing of the user's personal information", 'Marks the user to not sell or share their personal information']}, {'parameter_values': ['do_not_sell', 'false'], 'conditions': ['User permits the sale of personal information', 'If the sale of personal information is permitted', 'User has permitted the sale of personal information', 'User has not opted out of sale or sharing of personal information', "If 'sale' of personal information is permitted"], 'effects': ["Allows the sale or sharing of user's personal information", 'Allows the sale or sharing of personal information', "Allows the sale of the user's personal information", "Sale or sharing of the user's personal information is permitted", 'Permits the sale of personal information']}, {'parameter_values': ['is_child_directed', 'true'], 'conditions': ['The end-user is identified as a child under applicable regulations', 'If the end-user is a child', 'End-user is classified as a child according to applicable regulations', 'If the end-user is a child according to applicable regulations', 'End-user is a child as defined by applicable regulations'], 'effects': ['Flags the user as child-directed', 'Treats the end-user as a child for compliance with child-related regulations', 'Flags the end-user as child-directed for apps that cater to children', 'Flags the end-user as a child for compliance', 'Flags the end-user as child-directed for compliance with laws like COPPA']}, {'parameter_values': ['is_child_directed', 'false'], 'conditions': ['If the end-user is not a child', 'End-user is not classified as a child', 'End-user is not a child', 'The end-user is not identified as a child'], 'effects': ['Flags the end-user as not a child', 'Flags the end-user as not child-directed', 'Flags the user as not child-directed', 'Does not treat the end-user as a child']}, {'parameter_values': ['is_deviceid_optout', 'true'], 'conditions': ['User is flagged as child and must prevent access to AAID', 'Applicable for users flagged as children', 'Required for configurations directed at children'], 'effects': ['Prevents access to the Android Advertising ID']}, {'parameter_values': ['is_deviceid_optout', 'false'], 'conditions': ['Not directed at children'], 'effects': ['Permits access to the Android Advertising ID']}, {'parameter_values': ['Google_Family_Self_Certified_SDKS', 'true'], 'conditions': ['User is part of mixed audience directed apps'], 'effects': ['Allows initialization only of Families Self-Certified Ads SDKs']}]}</t>
+          <t>{'API_name': 'setDoNotSell', 'class_name': ['InMobiPrivacyCompliance'], 'conditions': ['The user must indicate opt-out of interest-based advertising.', 'User opts out of the sale of data;', 'User opts out of the sale of their personal data.', 'User opts out of selling their personal data', 'User opts out of interest-based advertising.'], 'effects': ['Informs InMobi and their ad partners not to sell personal data.', 'User is opted out of interest-based advertising.', 'Indicates to InMobi that the user does not wish to sell or share their personal information.', 'Users will be opted out of the sale of their personal data, affecting advertisement targeting.', 'User data will not be sold to third parties'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The user opts out of interest-based advertising.', 'User has opted out of the sale of their personal data.', 'The user has opted out'], 'effects': ["User's personal information will not be sold or shared.", "The user's data is effectively opted out from being sold.", 'Indicates to InMobi that the user does not wish to have their personal data sold.']}, {'parameter_values': [False], 'conditions': ['The user chooses not to opt-out.', 'User has not opted out of the sale of their personal data.', 'The user has not opted out'], 'effects': ['User data can be utilized for targeted advertising.', "User's personal information may be sold or shared.", 'Standard data processing is applied, and data might still be sold.']}]}</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://developers.is.com/ironsource-mobile/android/regulation-advanced-settings/#step-1</t>
+          <t>https://support.inmobi.com/monetize/privacy/gdpr;https://support.inmobi.com/monetize/privacy/lgpd;https://support.inmobi.com/monetize/privacy/coppa;https://support.inmobi.com/monetize/privacy/us-privacy/ccpa#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/cpra#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/vcdpa;https://support.inmobi.com/monetize/privacy/us-privacy/cpa;https://support.inmobi.com/monetize/privacy/us-privacy/opt-out-mechanism;https://support.inmobi.com/monetize/android-guidelines/#optimization</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kochava</t>
+          <t>InMobi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>setAppLimitAdTracking</t>
+          <t>setUSPrivacyString</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAppLimitAdTracking', 'class_name': ['Tracker'], 'conditions': ['Application-level control to limit ad tracking'], 'effects': ['Limits ad tracking at the application level', 'Limits the use of the advertising identifier for tracking purposes'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Ad tracking is limited', 'Ad tracking is disabled for the application']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Ad tracking is enabled for the application', 'Ad tracking is not limited']}]}</t>
+          <t>{'API_name': 'setUSPrivacyString', 'class_name': ['InMobiPrivacyCompliance'], 'conditions': ['The user must provide relevant consent for their personal data processing.', 'User is from a state that requires privacy strings for compliance.', 'The value passed must comply with the IAB specification', 'Must comply with U.S. privacy regulations.'], 'effects': ["The user's preferences regarding the sale of personal information will be reflected.", "The privacy string is populated as per the user's opt-out or consent status.", 'Sets the privacy string for compliance with CCPA.', 'Sets the U.S. Privacy String which affects user data handling per privacy regulations.'], 'parameter_configurations': [{'parameter_values': [''], 'conditions': ['Ensure string value complies with IAB specification.', "User's U.S. privacy information must comply with privacy regulations.", 'The privacy string is valid according to IAB specification'], 'effects': ['The U.S. Privacy String must comply with the IAB specifications.', 'Sets an empty U.S. Privacy String.', "User's choices about data selling are correctly applied.", 'Updates the privacy string indicating user consent status.']}]}</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
+          <t>https://support.inmobi.com/monetize/privacy/gdpr;https://support.inmobi.com/monetize/privacy/lgpd;https://support.inmobi.com/monetize/privacy/coppa;https://support.inmobi.com/monetize/privacy/us-privacy/ccpa#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/cpra#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/vcdpa;https://support.inmobi.com/monetize/privacy/us-privacy/cpa;https://support.inmobi.com/monetize/privacy/us-privacy/opt-out-mechanism;https://support.inmobi.com/monetize/android-guidelines/#optimization</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kochava</t>
+          <t>InMobi</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>setIntelligentConsentGranted</t>
+          <t>setIsAgeRestricted</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'API_name': 'setIntelligentConsentGranted', 'class_name': ['Tracker'], 'conditions': ['User granted consent', 'User must provide consent', 'user must respond to consent prompt', 'if the user dismisses or ignores the dialog no action should be taken', 'The user has responded to the consent prompt'], 'effects': ['Enables data collection and tracking', 'notifies SDK of consent result, impacts data transmission', "notifies the SDK of the user's consent decision", 'SDK will track data if consent is granted', 'restricts data transmission based on consent', 'The system will start or stop tracking based on user consent'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User grants consent', 'user granted consent', 'User has granted consent'], 'effects': ['Allows data collection as user granted consent', 'Tracking data can be sent to Kochava', 'enables data collection and transmission to Kochava', 'Enables tracking for the user', 'allows tracking and data collection']}, {'parameter_values': [False], 'conditions': ['user denied consent', 'User has declined consent', 'User declines consent'], 'effects': ['Disables data collection as user declined consent', 'prevents tracking and data collection, can trigger shutdown if required', 'Disables tracking for the user', 'stops data collection and transmission to Kochava', 'Tracking immediately stops and does not send any data to Kochava']}]}</t>
+          <t>{'API_name': 'setIsAgeRestricted', 'class_name': ['InMobiSdk'], 'conditions': ['Required to comply with COPPA if the app is directed at children under 16 years old.', "The application's audience is general, which may include children under the age of 16.", "The user's application is directed to children under the age of 16.", 'The app is directed at children under the age of 16 or to a general audience which may include children under the age of 16', 'If the app is directed to children under the age of 16 or to a general audience which may include children.', 'User app is directed to children under the age of 16.'], 'effects': ['AKSIGLO: The request will be treated as child-directed, hence sensitive data handling may be altered.', 'Sets the age-restriction status for the app, affecting data handling practices for compliance.', 'Indicates whether the request will be treated as child-directed. If True, device identifiers will not be transmitted.', 'If set to true, the app will be treated as child-directed and certain identifiers such as AAID will not be transmitted.', 'The request will be treated as child-directed if the value is set to true; otherwise treated as not child-directed.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The app targets children under the age of 16.', 'The app targets users under the age of 16.', 'If the app is directed to children', 'The application is confirmed to be child-directed.'], 'effects': ['The SDK will not transmit device identifiers such as Android Advertising ID (AAID) or IDFA.', 'Prevents transmission of device identifiers.', 'The request is treated as child-directed.', 'InMobi will not transmit device identifiers such as Android Advertising ID.', 'The app will be treated as child-directed, affecting data processing under laws like COPPA.']}, {'parameter_values': [False], 'conditions': ['If the app is not directed to children', 'The app does not target users under the age of 16.', 'The app does not target children or is a mixed audience app.'], 'effects': ['The request is not treated as child-directed.', 'Allows transmission of device identifiers.', 'The app will not be treated as child-directed.']}]}</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
+          <t>https://support.inmobi.com/monetize/privacy/gdpr;https://support.inmobi.com/monetize/privacy/lgpd;https://support.inmobi.com/monetize/privacy/coppa;https://support.inmobi.com/monetize/privacy/us-privacy/ccpa#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/cpra#introduction;https://support.inmobi.com/monetize/privacy/us-privacy/vcdpa;https://support.inmobi.com/monetize/privacy/us-privacy/cpa;https://support.inmobi.com/monetize/privacy/us-privacy/opt-out-mechanism;https://support.inmobi.com/monetize/android-guidelines/#optimization</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kochava</t>
+          <t>Ironsource</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>registerPrivacyProfile</t>
+          <t>setConsent</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'API_name': 'registerPrivacyProfile', 'class_name': ['Tracker'], 'conditions': ['Need to restrict data for certain user types', 'privacy profiles must be created prior to enabling', 'The SDK must be initialized before creating a privacy profile'], 'effects': ['creates a named collection of datapoints which may be restricted for the current user', 'A named collection of datapoints is created which may be restricted', 'Creates a privacy profile that restricts egress of specified data points', 'defines a named collection of data points for user data restriction', 'Creates a profile that groups specific datapoints for privacy restrictions'], 'parameter_configurations': [{'parameter_values': ['restrict ids', ['adid', 'android_id']], 'conditions': ['create profile to restrict identifiers', 'set to restrict data egress for all users'], 'effects': ['disables egress of certain device identifiers for the app', 'Prevents transmission of device identifiers from the device for all users', 'Restricts egress of device identifiers from the SDK for all users', 'Sets up a privacy profile that restricts device identifiers', 'prevents transmission of device identifiers for all users']}, {'parameter_values': ['child', ['adid', 'android_id']], 'conditions': ['used when specific conditions apply to restrict data collection', 'create profile for conditional restriction based on user type', 'User is identified as a child'], 'effects': ['enables restricted tracking for users identified as children', 'conditionally restrict egress of identifiers for child users', 'Restricts egress of device identifiers for child users', 'Prevents transmission of device identifiers from the device only for children']}]}</t>
+          <t>{'API_name': 'setConsent', 'class_name': ['IronSource'], 'conditions': ["GDPR compliance requires the user's consent status to be communicated to the mediation platform", 'GDPR consent is required when providing personalized ads', 'User must provide consent before using the API', 'The user provided consent', 'The user did not provide consent', 'User has provided consent or not'], 'effects': ["Stores the user's consent status for GDPR compliance", "Updates the user's consent status for data processing", "Updates the user's consent status for GDPR compliance", 'Sets the consent status for GDPR compliance', 'Updates the consent status for user data processing under GDPR'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User provided consent', 'If the user provided consent'], 'effects': ['Sets the consent flag to true', 'Indicates the user provided consent', 'User consent is registered as true', 'User data can be processed for personalized ads', 'Indicates that the user has given consent']}, {'parameter_values': [False], 'conditions': ['User did not consent', 'If the user did not consent', 'If the user did not provide consent'], 'effects': ['User data cannot be processed for personalized ads', 'Sets the consent flag to false', 'User consent is registered as false', 'Indicates the user did not provide consent', 'Indicates that the user has not given consent']}]}</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
+          <t>https://developers.is.com/ironsource-mobile/android/regulation-advanced-settings/#step-1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Kochava</t>
+          <t>Ironsource</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>setPrivacyProfileEnabled</t>
+          <t>setMetaData</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPrivacyProfileEnabled', 'class_name': ['Tracker'], 'conditions': ['must invoke this function after defining privacy profiles to apply restrictions', 'Created privacy profile must be enabled for certain users', 'The privacy profile must be created before it can be enabled', 'privacy profile must be created and called before enabling'], 'effects': ['Enables or disables a privacy profile for the current user', 'Restricts data transmission based on the profile', 'applies the created privacy profile, restricting specified datapoints', 'applies data point restrictions for the specified user', 'Enables or disables the specified privacy profile to restrict data egress'], 'parameter_configurations': [{'parameter_values': ['restrict ids', True], 'conditions': ['enable profile to restrict all users', 'Must have previously registered the privacy profile'], 'effects': ['starts restricting transmission of specified data points', 'restricts the egress of specified datapoints for the user', 'Stops egress of specified datapoints', 'Device identifiers will no longer egress from the device', 'Prevents the specified data points from being transmitted from the device']}, {'parameter_values': ['child', True], 'conditions': ['User is determined to be a child', 'enable profile only if user is identified as a child'], 'effects': ['restricts transmission of identifiers specifically for child users', 'Restricts device identifiers from being transmitted for child users']}, {'parameter_values': ['child', False], 'conditions': [], 'effects': ['Resumes egress of specified datapoints for children', 'removes restrictions on datapoint egress for the child privacy profile']}]}</t>
+          <t>{'API_name': 'setMetaData', 'class_name': ['IronSource'], 'conditions': ["User opts out of 'sale' or 'sharing' of personal information", 'API should be set before initializing the SDK', 'Should be set before initializing the SDK', 'API must be called before initializing the SDK', 'Must be set before initializing the SDK to comply with U.S. state privacy laws, such as the CPRA.', 'U.S. state privacy laws compliance is required when notifying personal information handling', 'Applicable law (e.g., COPPA) requires indicating if the user is a child'], 'effects': ['Flags users as children or not for appropriate data handling', "Handles the 'do not sell or share' setting for U.S. state privacy laws", 'Controls the sale or sharing of end-users personal information as per state laws', 'Controls the handling of personal information under U.S. state privacy laws', 'Sets privacy-related metadata for the user', 'Updates the specified metadata for the user regarding personal information sale'], 'parameter_configurations': [{'parameter_values': ['do_not_sell', 'true'], 'conditions': ['If the user has opted out of sale or sharing of their personal information', 'User has opted out of sale or sharing of personal information', 'User has opted out of the sale or sharing of personal information', "If the user has opted out of 'sale' or 'sharing' of personal information"], 'effects': ["Restricts the sale or sharing of user's personal information", 'Denotes that personal information should not be sold or shared', "Sale or sharing of the user's personal information is prohibited", "Restricts the sale or sharing of the user's personal information", 'Marks the user to not sell or share their personal information']}, {'parameter_values': ['do_not_sell', 'false'], 'conditions': ['User permits the sale of personal information', 'If the sale of personal information is permitted', 'User has permitted the sale of personal information', 'User has not opted out of sale or sharing of personal information', "If 'sale' of personal information is permitted"], 'effects': ["Allows the sale or sharing of user's personal information", 'Allows the sale or sharing of personal information', "Allows the sale of the user's personal information", "Sale or sharing of the user's personal information is permitted", 'Permits the sale of personal information']}, {'parameter_values': ['is_child_directed', 'true'], 'conditions': ['The end-user is identified as a child under applicable regulations', 'If the end-user is a child', 'End-user is classified as a child according to applicable regulations', 'If the end-user is a child according to applicable regulations', 'End-user is a child as defined by applicable regulations'], 'effects': ['Flags the user as child-directed', 'Treats the end-user as a child for compliance with child-related regulations', 'Flags the end-user as child-directed for apps that cater to children', 'Flags the end-user as a child for compliance', 'Flags the end-user as child-directed for compliance with laws like COPPA']}, {'parameter_values': ['is_child_directed', 'false'], 'conditions': ['If the end-user is not a child', 'End-user is not classified as a child', 'End-user is not a child', 'The end-user is not identified as a child'], 'effects': ['Flags the end-user as not a child', 'Flags the end-user as not child-directed', 'Flags the user as not child-directed', 'Does not treat the end-user as a child']}, {'parameter_values': ['is_deviceid_optout', 'true'], 'conditions': ['User is flagged as child and must prevent access to AAID', 'Applicable for users flagged as children', 'Required for configurations directed at children'], 'effects': ['Prevents access to the Android Advertising ID']}, {'parameter_values': ['is_deviceid_optout', 'false'], 'conditions': ['Not directed at children'], 'effects': ['Permits access to the Android Advertising ID']}, {'parameter_values': ['Google_Family_Self_Certified_SDKS', 'true'], 'conditions': ['User is part of mixed audience directed apps'], 'effects': ['Allows initialization only of Families Self-Certified Ads SDKs']}]}</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
+          <t>https://developers.is.com/ironsource-mobile/android/regulation-advanced-settings/#step-1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Leanplum</t>
+          <t>Kochava</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>disableLocationCollection</t>
+          <t>setAppLimitAdTracking</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'API_name': 'disableLocationCollection', 'class_name': ['', 'Leanplum', 'Android location services'], 'conditions': [], 'effects': ['Disables automatic location tracking for the user in Leanplum.', 'Prevents Leanplum from collecting GPS/Cell location.', 'Prevents Leanplum from collecting user location data.'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setAppLimitAdTracking', 'class_name': ['Tracker'], 'conditions': ['Application-level control to limit ad tracking'], 'effects': ['Limits ad tracking at the application level', 'Limits the use of the advertising identifier for tracking purposes'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Ad tracking is limited', 'Ad tracking is disabled for the application']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Ad tracking is enabled for the application', 'Ad tracking is not limited']}]}</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://docs.leanplum.com/reference/user-ids;https://docs.leanplum.com/reference/device-ids;https://docs.leanplum.com/reference/user-attributes;https://docs.leanplum.com/reference/events;https://docs.leanplum.com/reference/android-location-services;https://docs.leanplum.com/reference/gdpr-overview</t>
+          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Leanplum</t>
+          <t>Kochava</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>setDeviceLocation</t>
+          <t>setIntelligentConsentGranted</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDeviceLocation', 'class_name': ['', 'Leanplum', 'Android location services'], 'conditions': ['Must call disableLocationCollection before setting a custom location.', 'Must call disableLocationCollection before setting location if location tracking is not desired.'], 'effects': ['Sets the user’s device location for geolocation features.', 'Manually sets the user location in Leanplum, overriding default collection.', 'Manually sets the user’s location for tracking purposes.'], 'parameter_configurations': [{'parameter_values': ['location', 'type'], 'conditions': ['must be called after the Leanplum.start() method.'], 'effects': ['Updates user’s device location for geolocation-based messaging.']}, {'parameter_values': ['Location Object', 'Cell or GPS'], 'conditions': ['disableLocationCollection must be called before manually setting the location.'], 'effects': ['Sets the specified location for future targeting.']}, {'parameter_values': ['locationObject', 'CELL'], 'conditions': [], 'effects': ['Location is manually set to the provided values.']}, {'parameter_values': ['locationObject', 'GPS'], 'conditions': [], 'effects': ['Location set to GPS type.']}]}</t>
+          <t>{'API_name': 'setIntelligentConsentGranted', 'class_name': ['Tracker'], 'conditions': ['User granted consent', 'User must provide consent', 'user must respond to consent prompt', 'if the user dismisses or ignores the dialog no action should be taken', 'The user has responded to the consent prompt'], 'effects': ['Enables data collection and tracking', 'notifies SDK of consent result, impacts data transmission', "notifies the SDK of the user's consent decision", 'SDK will track data if consent is granted', 'restricts data transmission based on consent', 'The system will start or stop tracking based on user consent'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User grants consent', 'user granted consent', 'User has granted consent'], 'effects': ['Allows data collection as user granted consent', 'Tracking data can be sent to Kochava', 'enables data collection and transmission to Kochava', 'Enables tracking for the user', 'allows tracking and data collection']}, {'parameter_values': [False], 'conditions': ['user denied consent', 'User has declined consent', 'User declines consent'], 'effects': ['Disables data collection as user declined consent', 'prevents tracking and data collection, can trigger shutdown if required', 'Disables tracking for the user', 'stops data collection and transmission to Kochava', 'Tracking immediately stops and does not send any data to Kochava']}]}</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://docs.leanplum.com/reference/user-ids;https://docs.leanplum.com/reference/device-ids;https://docs.leanplum.com/reference/user-attributes;https://docs.leanplum.com/reference/events;https://docs.leanplum.com/reference/android-location-services;https://docs.leanplum.com/reference/gdpr-overview</t>
+          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Leanplum</t>
+          <t>Kochava</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>setUserAttributes</t>
+          <t>registerPrivacyProfile</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserAttributes', 'class_name': ['', 'Leanplum'], 'conditions': ['User must provide explicit consent before collection', 'Up to 200 unique attributes can be defined per Leanplum app.', 'User must opt-in to data collection under GDPR &amp; CCPA before any user attributes can be set.'], 'effects': ['Updates user attributes for targeted messaging and analytics.', 'User attributes are updated, which can be used for personalization, segmentation, and reporting.', 'Allows clear identification and segmentation of users based on attributes.'], 'parameter_configurations': [{'parameter_values': [{'gender': 'Female', 'age': 29}], 'conditions': ['User is logged in and in a session', 'Ensure attributes conform to limitations where names must be strings and values can only be strings or numbers.'], 'effects': ['Attributes are set and can be used in campaigns and personalized messages.', 'User attributes are set for personalized content delivery.']}, {'parameter_values': [{'email': 'example@example.com'}], 'conditions': ['Email attribute is required for running email campaigns.'], 'effects': ['User can be targeted in email campaigns.']}, {'parameter_values': [{'gender': None, 'age': None}], 'conditions': [], 'effects': ['User attribute is cleared.']}, {'parameter_values': [{'email': '[[email\xa0protected]]'}], 'conditions': ['Required for email campaigns'], 'effects': ['Email attribute is set for targeting in email campaigns.']}]}</t>
+          <t>{'API_name': 'registerPrivacyProfile', 'class_name': ['Tracker'], 'conditions': ['Need to restrict data for certain user types', 'privacy profiles must be created prior to enabling', 'The SDK must be initialized before creating a privacy profile'], 'effects': ['creates a named collection of datapoints which may be restricted for the current user', 'A named collection of datapoints is created which may be restricted', 'Creates a privacy profile that restricts egress of specified data points', 'defines a named collection of data points for user data restriction', 'Creates a profile that groups specific datapoints for privacy restrictions'], 'parameter_configurations': [{'parameter_values': ['restrict ids', ['adid', 'android_id']], 'conditions': ['create profile to restrict identifiers', 'set to restrict data egress for all users'], 'effects': ['disables egress of certain device identifiers for the app', 'Prevents transmission of device identifiers from the device for all users', 'Restricts egress of device identifiers from the SDK for all users', 'Sets up a privacy profile that restricts device identifiers', 'prevents transmission of device identifiers for all users']}, {'parameter_values': ['child', ['adid', 'android_id']], 'conditions': ['used when specific conditions apply to restrict data collection', 'create profile for conditional restriction based on user type', 'User is identified as a child'], 'effects': ['enables restricted tracking for users identified as children', 'conditionally restrict egress of identifiers for child users', 'Restricts egress of device identifiers for child users', 'Prevents transmission of device identifiers from the device only for children']}]}</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://docs.leanplum.com/reference/user-ids;https://docs.leanplum.com/reference/device-ids;https://docs.leanplum.com/reference/user-attributes;https://docs.leanplum.com/reference/events;https://docs.leanplum.com/reference/android-location-services;https://docs.leanplum.com/reference/gdpr-overview</t>
+          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Localytics</t>
+          <t>Kochava</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>setOptedOut</t>
+          <t>setPrivacyProfileEnabled</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'API_name': 'setOptedOut', 'class_name': ['', 'Localytics'], 'conditions': ['The user opts out of data collection', 'The user has requested to opt out of data collection.', 'User has opted out of data collection.', 'Call this method to stop the Localytics SDK from collecting any additional data.', 'user opts out of data collection'], 'effects': ['Prevents any future data from being collected, closes current session, and tags an opt out event.', 'Immediately closes the current session and tags an opt-out event indicating that the device is no longer reporting any further data.', 'Stops the Localytics SDK from collecting any additional data', 'Stops the Localytics SDK from collecting any additional data and closes the current session.', 'stops the Localytics SDK from collecting any additional data, closes the current session, and tags an opt out event'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['any subsequent calls that would generate a datapoint (e.g., tagEvent) will be dropped', 'All data collection is ceased; no further datapoints are generated.', 'Subsequent data collection methods such as tagEvent and setProfileAttribute will be dropped.', 'Triggers an opt-out event indicating that the device is no longer reporting any future data']}, {'parameter_values': [False], 'conditions': ['The user wants to opt back into data collection'], 'effects': ['Allows data collection to resume', 'data collection resumes', 'Resumes data collection for the user.']}]}</t>
+          <t>{'API_name': 'setPrivacyProfileEnabled', 'class_name': ['Tracker'], 'conditions': ['must invoke this function after defining privacy profiles to apply restrictions', 'Created privacy profile must be enabled for certain users', 'The privacy profile must be created before it can be enabled', 'privacy profile must be created and called before enabling'], 'effects': ['Enables or disables a privacy profile for the current user', 'Restricts data transmission based on the profile', 'applies the created privacy profile, restricting specified datapoints', 'applies data point restrictions for the specified user', 'Enables or disables the specified privacy profile to restrict data egress'], 'parameter_configurations': [{'parameter_values': ['restrict ids', True], 'conditions': ['enable profile to restrict all users', 'Must have previously registered the privacy profile'], 'effects': ['starts restricting transmission of specified data points', 'restricts the egress of specified datapoints for the user', 'Stops egress of specified datapoints', 'Device identifiers will no longer egress from the device', 'Prevents the specified data points from being transmitted from the device']}, {'parameter_values': ['child', True], 'conditions': ['User is determined to be a child', 'enable profile only if user is identified as a child'], 'effects': ['restricts transmission of identifiers specifically for child users', 'Restricts device identifiers from being transmitted for child users']}, {'parameter_values': ['child', False], 'conditions': [], 'effects': ['Resumes egress of specified datapoints for children', 'removes restrictions on datapoint egress for the child privacy profile']}]}</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
+          <t>https://support.kochava.com/sdk-integration/android-sdk-integration/android-using-the-sdk/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Localytics</t>
+          <t>Leanplum</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>setPrivacyOptedOut</t>
+          <t>disableLocationCollection</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPrivacyOptedOut', 'class_name': ['', 'Localytics'], 'conditions': ['Triggered by an end user request to be forgotten under GDPR.', 'The user requests to be forgotten under GDPR.', "Call this method to delete all of the end user's data in accordance with GDPR.", 'user requests to be forgotten under GDPR', 'The user requests to be forgotten in accordance with GDPR'], 'effects': ["Deletes all of the end user's data and prevents any further data from being collected.", 'Deletes all end-user data and prevents further data collection.', "Prevents future data collection and triggers the user's Right To Be Forgotten request.", "deletes all of the end user's data and prevents any further data from being collected, as well as triggering a user's Right To Be Forgotten request", "Deletes all of the end user's data and prevents any further data from being collected"], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ["Triggers the user's Right To Be Forgotten request, deleting historical data", 'an indication that the user is no longer being tracked and all historical data will be deleted', 'Deletes all historical data of the user and stops all data collection immediately.', "Trigers a user's Right To Be Forgotten request and clears all historical data."]}, {'parameter_values': [False], 'conditions': ['The user wishes to resume data collection'], 'effects': ['Resumes normal data collection.', 'the Localytics SDK may continue to collect and process data for the user', 'Restores the state for data collection under a new customer ID']}]}</t>
+          <t>{'API_name': 'disableLocationCollection', 'class_name': ['', 'Leanplum', 'Android location services'], 'conditions': [], 'effects': ['Disables automatic location tracking for the user in Leanplum.', 'Prevents Leanplum from collecting GPS/Cell location.', 'Prevents Leanplum from collecting user location data.'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
+          <t>https://docs.leanplum.com/reference/user-ids;https://docs.leanplum.com/reference/device-ids;https://docs.leanplum.com/reference/user-attributes;https://docs.leanplum.com/reference/events;https://docs.leanplum.com/reference/android-location-services;https://docs.leanplum.com/reference/gdpr-overview</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Localytics</t>
+          <t>Leanplum</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>pauseDataUploading</t>
+          <t>setDeviceLocation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'API_name': 'pauseDataUploading', 'class_name': ['', 'Localytics'], 'conditions': ["Should be called during the application's user consent journey.", "Call this to pause data uploading while checking a user's opt-out status.", "User's data collection opt-in status is not determined.", "user's data collection opt-in status is unknown", "When determining the end user's opt-out status"], 'effects': ['Pauses all data uploads while still collecting information.', 'Pauses data uploading to Localytics while continuing to collect data.', 'Pauses any data uploading to Localytics while still collecting information.', 'pauses any data uploading to Localytics while still collecting information about the end user', 'Pauses data uploads and prevents data from being sent to Localytics'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['no data is uploaded until uploads are resumed', 'Prevents data from being uploaded while consent is being verified', 'Data will not be uploaded until resumed.', 'Prevents any data from being uploaded until uploading is resumed.']}, {'parameter_values': [False], 'conditions': ['Consent has been verified'], 'effects': ['Resumes the data upload process.', 'Resumes data uploads', 'resumes data uploads to Localytics', 'Resumes normal data uploading to Localytics.']}]}</t>
+          <t>{'API_name': 'setDeviceLocation', 'class_name': ['', 'Leanplum', 'Android location services'], 'conditions': ['Must call disableLocationCollection before setting a custom location.', 'Must call disableLocationCollection before setting location if location tracking is not desired.'], 'effects': ['Sets the user’s device location for geolocation features.', 'Manually sets the user location in Leanplum, overriding default collection.', 'Manually sets the user’s location for tracking purposes.'], 'parameter_configurations': [{'parameter_values': ['location', 'type'], 'conditions': ['must be called after the Leanplum.start() method.'], 'effects': ['Updates user’s device location for geolocation-based messaging.']}, {'parameter_values': ['Location Object', 'Cell or GPS'], 'conditions': ['disableLocationCollection must be called before manually setting the location.'], 'effects': ['Sets the specified location for future targeting.']}, {'parameter_values': ['locationObject', 'CELL'], 'conditions': [], 'effects': ['Location is manually set to the provided values.']}, {'parameter_values': ['locationObject', 'GPS'], 'conditions': [], 'effects': ['Location set to GPS type.']}]}</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
+          <t>https://docs.leanplum.com/reference/user-ids;https://docs.leanplum.com/reference/device-ids;https://docs.leanplum.com/reference/user-attributes;https://docs.leanplum.com/reference/events;https://docs.leanplum.com/reference/android-location-services;https://docs.leanplum.com/reference/gdpr-overview</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Localytics</t>
+          <t>Leanplum</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>setCustomerIdWithPrivacyOptedOut</t>
+          <t>setUserAttributes</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCustomerIdWithPrivacyOptedOut', 'class_name': ['', 'Localytics'], 'conditions': ['When logging in a user and determining their privacy opt-out status.', 'user logs into the application and their privacy opt-out status is determined', 'User logs in or settings change that may affect data collection status.', 'The user is logging in and consent verification is performed', 'Called during the login process to manage customer ID and privacy opt-out status.'], 'effects': ['Updates the customer ID and sets the data collection opt-out status.', 'updates the current customer ID and the data collection opt-out status', 'Updates the current customer ID and the data collection opt-out status', "Updates the customer's ID and adjusts the data collection opt-out status.", 'Updates the customer ID and their data collection opt-out status.'], 'parameter_configurations': [{'parameter_values': ['customerId', True], 'conditions': ['when verifying consent via your back-end'], 'effects': ["allow the application to adjust data collection according to the user's preferences"]}, {'parameter_values': ['customerId', False], 'conditions': [], 'effects': ['resumes collecting user data']}, {'parameter_values': ['CID', True], 'conditions': [], 'effects': ["Sets the customer's ID and marks the user as opted out of data collection."]}, {'parameter_values': ['CID', False], 'conditions': [], 'effects': ["Restores the user's data collection status."]}, {'parameter_values': ['newCustomerId', True], 'conditions': ['The user has opted out'], 'effects': ['The user ID is updated, and the opt-out status is recorded']}, {'parameter_values': ['newCustomerId', False], 'conditions': ['The user is opting back into data collection'], 'effects': ['Begins new data collection while ensuring previous data remains forgotten']}]}</t>
+          <t>{'API_name': 'setUserAttributes', 'class_name': ['', 'Leanplum'], 'conditions': ['User must provide explicit consent before collection', 'Up to 200 unique attributes can be defined per Leanplum app.', 'User must opt-in to data collection under GDPR &amp; CCPA before any user attributes can be set.'], 'effects': ['Updates user attributes for targeted messaging and analytics.', 'User attributes are updated, which can be used for personalization, segmentation, and reporting.', 'Allows clear identification and segmentation of users based on attributes.'], 'parameter_configurations': [{'parameter_values': [{'gender': 'Female', 'age': 29}], 'conditions': ['User is logged in and in a session', 'Ensure attributes conform to limitations where names must be strings and values can only be strings or numbers.'], 'effects': ['Attributes are set and can be used in campaigns and personalized messages.', 'User attributes are set for personalized content delivery.']}, {'parameter_values': [{'email': 'example@example.com'}], 'conditions': ['Email attribute is required for running email campaigns.'], 'effects': ['User can be targeted in email campaigns.']}, {'parameter_values': [{'gender': None, 'age': None}], 'conditions': [], 'effects': ['User attribute is cleared.']}, {'parameter_values': [{'email': '[[email\xa0protected]]'}], 'conditions': ['Required for email campaigns'], 'effects': ['Email attribute is set for targeting in email campaigns.']}]}</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
+          <t>https://docs.leanplum.com/reference/user-ids;https://docs.leanplum.com/reference/device-ids;https://docs.leanplum.com/reference/user-attributes;https://docs.leanplum.com/reference/events;https://docs.leanplum.com/reference/android-location-services;https://docs.leanplum.com/reference/gdpr-overview</t>
         </is>
       </c>
     </row>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>setLocationMonitoringEnabled</t>
+          <t>setOptedOut</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLocationMonitoringEnabled', 'class_name': ['', 'Localytics'], 'conditions': ['Required to enable location services after the Localytics SDK is integrated.', 'Application requests to monitor user location, provided user consent is obtained.'], 'effects': ['Enables location updates and geofence monitoring.', 'Enables the monitoring of user location for geofencing features.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User location monitoring is enabled.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User location monitoring is disabled.']}]}</t>
+          <t>{'API_name': 'setOptedOut', 'class_name': ['', 'Localytics'], 'conditions': ['The user opts out of data collection', 'The user has requested to opt out of data collection.', 'User has opted out of data collection.', 'Call this method to stop the Localytics SDK from collecting any additional data.', 'user opts out of data collection'], 'effects': ['Prevents any future data from being collected, closes current session, and tags an opt out event.', 'Immediately closes the current session and tags an opt-out event indicating that the device is no longer reporting any further data.', 'Stops the Localytics SDK from collecting any additional data', 'Stops the Localytics SDK from collecting any additional data and closes the current session.', 'stops the Localytics SDK from collecting any additional data, closes the current session, and tags an opt out event'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['any subsequent calls that would generate a datapoint (e.g., tagEvent) will be dropped', 'All data collection is ceased; no further datapoints are generated.', 'Subsequent data collection methods such as tagEvent and setProfileAttribute will be dropped.', 'Triggers an opt-out event indicating that the device is no longer reporting any future data']}, {'parameter_values': [False], 'conditions': ['The user wants to opt back into data collection'], 'effects': ['Allows data collection to resume', 'data collection resumes', 'Resumes data collection for the user.']}]}</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2895,154 +2895,154 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MyTarget</t>
+          <t>Localytics</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>setPrivacyOptedOut</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': ['MyTargetPrivacy'], 'conditions': ['User must provide consent for personal data collection.', 'User must provide consent before collecting personal data.', 'User must be provided with information about data collection practices.'], 'effects': ['If consent is not given, no personal data will be collected or sent to the server.', 'Sets whether the user has consented to data collection, affecting whether personal data is collected and sent to the server.', 'If consent is set to false, no personal data will be collected or sent to the server.', 'Sets whether the user has consented to the collection of personal data', 'Sets whether the user has consented to the collection of personal data.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User agrees to allow data collection.'], 'effects': ['Personal data will be collected and sent to the server if the user consents.', 'Personal data can be collected and sent to the server.', 'User consents to data collection.', 'User consented to data collection.', 'Enables the collection of personal data']}, {'parameter_values': [False], 'conditions': ['User does not agree to allow data collection.'], 'effects': ['Disables the collection of personal data', 'No personal data will be collected or sent to the server if the user does not consent.', 'User does not consent to data collection.', 'User did not consent to data collection.', 'No personal data will be collected or sent to the server.']}]}</t>
+          <t>{'API_name': 'setPrivacyOptedOut', 'class_name': ['', 'Localytics'], 'conditions': ['Triggered by an end user request to be forgotten under GDPR.', 'The user requests to be forgotten under GDPR.', "Call this method to delete all of the end user's data in accordance with GDPR.", 'user requests to be forgotten under GDPR', 'The user requests to be forgotten in accordance with GDPR'], 'effects': ["Deletes all of the end user's data and prevents any further data from being collected.", 'Deletes all end-user data and prevents further data collection.', "Prevents future data collection and triggers the user's Right To Be Forgotten request.", "deletes all of the end user's data and prevents any further data from being collected, as well as triggering a user's Right To Be Forgotten request", "Deletes all of the end user's data and prevents any further data from being collected"], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ["Triggers the user's Right To Be Forgotten request, deleting historical data", 'an indication that the user is no longer being tracked and all historical data will be deleted', 'Deletes all historical data of the user and stops all data collection immediately.', "Trigers a user's Right To Be Forgotten request and clears all historical data."]}, {'parameter_values': [False], 'conditions': ['The user wishes to resume data collection'], 'effects': ['Resumes normal data collection.', 'the Localytics SDK may continue to collect and process data for the user', 'Restores the state for data collection under a new customer ID']}]}</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://target.vk.ru/help/partners/mob/gdpr_compliant/en;https://developers.google.com/admob/android/mediation/mytarget</t>
+          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MyTarget</t>
+          <t>Localytics</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>setUserAgeRestricted</t>
+          <t>pauseDataUploading</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserAgeRestricted', 'class_name': ['MyTargetPrivacy'], 'conditions': ['User is known to be in an age-restricted category (under the age of 16).', 'User must be identified as being under the age of 16.', 'User must be known to be in an age-restricted category (e.g., under the age of 16).'], 'effects': ['Sets whether the user is known to be in an age-restricted category', 'If true, it indicates that the user should be considered age-restricted.', 'Sets a flag that indicates that the user is in an age-restricted category.', 'If set to true, indicates that the user is in an age-restricted category.', 'Indicates whether the user is in an age-restricted category, specifically for users under the age of 16.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is confirmed to be under the age of 16.', 'User is under the age of 16'], 'effects': ['Confirms that the user is in an age-restricted category, limiting data collection as needed.', 'Triggers age-restriction related data handling practices.', 'Indicates the user has age restrictions in place', 'User is recognized as an age-restricted individual and thus may limit data collection or utilization.', 'Establishes that the user is age-restricted.']}, {'parameter_values': [False], 'conditions': ['User is 16 years of age or older.'], 'effects': ['Establishes that the user is not age-restricted.', 'Indicates the user does not have age restrictions in place', 'Indicates that the user is not in an age-restricted category.', 'User is not considered age-restricted.', 'No age-restriction related data handling practices applied.']}]}</t>
+          <t>{'API_name': 'pauseDataUploading', 'class_name': ['', 'Localytics'], 'conditions': ["Should be called during the application's user consent journey.", "Call this to pause data uploading while checking a user's opt-out status.", "User's data collection opt-in status is not determined.", "user's data collection opt-in status is unknown", "When determining the end user's opt-out status"], 'effects': ['Pauses all data uploads while still collecting information.', 'Pauses data uploading to Localytics while continuing to collect data.', 'Pauses any data uploading to Localytics while still collecting information.', 'pauses any data uploading to Localytics while still collecting information about the end user', 'Pauses data uploads and prevents data from being sent to Localytics'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['no data is uploaded until uploads are resumed', 'Prevents data from being uploaded while consent is being verified', 'Data will not be uploaded until resumed.', 'Prevents any data from being uploaded until uploading is resumed.']}, {'parameter_values': [False], 'conditions': ['Consent has been verified'], 'effects': ['Resumes the data upload process.', 'Resumes data uploads', 'resumes data uploads to Localytics', 'Resumes normal data uploading to Localytics.']}]}</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://target.vk.ru/help/partners/mob/gdpr_compliant/en;https://developers.google.com/admob/android/mediation/mytarget</t>
+          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MyTarget</t>
+          <t>Localytics</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>setCcpaUserConsent</t>
+          <t>setCustomerIdWithPrivacyOptedOut</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCcpaUserConsent', 'class_name': ['MyTargetPrivacy'], 'conditions': ['User must provide consent for data collection under CCPA compliance.', 'Applicable U.S. privacy laws require user consent for data collection.'], 'effects': ["Sets the user's consent status for the California Consumer Privacy Act (CCPA).", 'If consent is set to false, no personal data will be collected or sent to the server.', 'Sets whether the user has consented to the sale of their personal information under CCPA', 'Sets whether the user has consented to data collection under CCPA.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts in to allow personal data collection for CCPA compliance.'], 'effects': ['Enables the sale of personal information', 'Personal data may be collected and shared according to CCPA.', 'User consents to the sale of personal information under CCPA.', 'User consents to data collection under CCPA.']}, {'parameter_values': [False], 'conditions': ['User opts out of allowing personal data collection for CCPA compliance.'], 'effects': ['Disables the sale of personal information', 'No personal data will be collected or shared under CCPA.', 'User does not consent to the sale of personal information under CCPA.', 'User does not consent to data collection under CCPA.']}]}</t>
+          <t>{'API_name': 'setCustomerIdWithPrivacyOptedOut', 'class_name': ['', 'Localytics'], 'conditions': ['When logging in a user and determining their privacy opt-out status.', 'user logs into the application and their privacy opt-out status is determined', 'User logs in or settings change that may affect data collection status.', 'The user is logging in and consent verification is performed', 'Called during the login process to manage customer ID and privacy opt-out status.'], 'effects': ['Updates the customer ID and sets the data collection opt-out status.', 'updates the current customer ID and the data collection opt-out status', 'Updates the current customer ID and the data collection opt-out status', "Updates the customer's ID and adjusts the data collection opt-out status.", 'Updates the customer ID and their data collection opt-out status.'], 'parameter_configurations': [{'parameter_values': ['customerId', True], 'conditions': ['when verifying consent via your back-end'], 'effects': ["allow the application to adjust data collection according to the user's preferences"]}, {'parameter_values': ['customerId', False], 'conditions': [], 'effects': ['resumes collecting user data']}, {'parameter_values': ['CID', True], 'conditions': [], 'effects': ["Sets the customer's ID and marks the user as opted out of data collection."]}, {'parameter_values': ['CID', False], 'conditions': [], 'effects': ["Restores the user's data collection status."]}, {'parameter_values': ['newCustomerId', True], 'conditions': ['The user has opted out'], 'effects': ['The user ID is updated, and the opt-out status is recorded']}, {'parameter_values': ['newCustomerId', False], 'conditions': ['The user is opting back into data collection'], 'effects': ['Begins new data collection while ensuring previous data remains forgotten']}]}</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://target.vk.ru/help/partners/mob/gdpr_compliant/en;https://developers.google.com/admob/android/mediation/mytarget</t>
+          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>Localytics</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>setAdContentThreshold</t>
+          <t>setLocationMonitoringEnabled</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAdContentThreshold', 'class_name': ['OguryAdRequests'], 'conditions': [], 'effects': ['Filters ad content based on the specified threshold', 'Applies content filtering on ad requests', 'Sets the ad content filtering level for Ogury ad requests'], 'parameter_configurations': [{'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_G'], 'conditions': [], 'effects': ['Only ads suitable for general audiences, including families, are displayed']}, {'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_PG'], 'conditions': [], 'effects': ['Ads suitable for most audiences with parental guidance are displayed']}, {'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_T'], 'conditions': [], 'effects': ['Ads suitable for teen and older audiences are displayed']}, {'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_MA'], 'conditions': [], 'effects': ['Only mature audience ads are displayed']}]}</t>
+          <t>{'API_name': 'setLocationMonitoringEnabled', 'class_name': ['', 'Localytics'], 'conditions': ['Required to enable location services after the Localytics SDK is integrated.', 'Application requests to monitor user location, provided user consent is obtained.'], 'effects': ['Enables location updates and geofence monitoring.', 'Enables the monitoring of user location for geofencing features.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User location monitoring is enabled.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User location monitoring is disabled.']}]}</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
+          <t>https://help.uplandsoftware.com/localytics/dev/android.html#gdpr</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>MyTarget</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>setConsent</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsent', 'class_name': ['OguryChoiceManagerExternal', 'OguryChoiceManagerExternal.TcfV2'], 'conditions': ['Must be compliant with last GDPR requirements', 'Make sure the Ogury SDK is initialized beforehand', 'CMP must be initialized before doing any ad request', 'Ogury SDK must be initialized before calling this method', 'The IAB-specified Consent String must be valid and generated by a whitelisted CMP', 'Third-party CMP must be initialized before calling this method', 'The consent string must be generated by a whitelisted CMP', 'The consent notice is registered in the IAB CMP list and produces IAB-specified consent string', 'Your CMP generates a TCFv2 consent string'], 'effects': ['Transmits the user consent to Ogury SDK', 'The consent must be valid to avoid being ignored', 'Transmits the user consent to the Ogury SDK', 'Indicates whether the user has consented or not', 'Transmits the consent of the vendors registered inside the IAB Global Vendor List', 'Call must be made again if user consent changes'], 'parameter_configurations': [{'parameter_values': ['iabString', 'new Integer[0]'], 'conditions': ['The CMP generates a TCFv2 consent string and is not leveraging the IAB GDPR Consent Framework', 'CMP is listed in the IAB CMP list and produces an IAB-specified consent string', 'User consent needs to be collected before calling', 'User has provided a valid IAB-specified consent string'], 'effects': ['Consent for vendors registered in the IAB Global Vendor List is transmitted to the Ogury SDK', 'User consent is synchronized for ad requests', 'The consent is synchronized with Ogury SDK']}, {'parameter_values': ['consentBoolean', 'CUSTOM'], 'conditions': ['Consent from a CMP that is not compatible with TCFv2'], 'effects': ['Sets the consent status for the Ogury SDK']}, {'parameter_values': ['consentBoolean', 'consentManagerName'], 'conditions': ['Using a third-party CMP that is not compatible with TCFv2'], 'effects': ['Sets the user consent to Ogury SDK']}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': ['MyTargetPrivacy'], 'conditions': ['User must provide consent for personal data collection.', 'User must provide consent before collecting personal data.', 'User must be provided with information about data collection practices.'], 'effects': ['If consent is not given, no personal data will be collected or sent to the server.', 'Sets whether the user has consented to data collection, affecting whether personal data is collected and sent to the server.', 'If consent is set to false, no personal data will be collected or sent to the server.', 'Sets whether the user has consented to the collection of personal data', 'Sets whether the user has consented to the collection of personal data.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User agrees to allow data collection.'], 'effects': ['Personal data will be collected and sent to the server if the user consents.', 'Personal data can be collected and sent to the server.', 'User consents to data collection.', 'User consented to data collection.', 'Enables the collection of personal data']}, {'parameter_values': [False], 'conditions': ['User does not agree to allow data collection.'], 'effects': ['Disables the collection of personal data', 'No personal data will be collected or sent to the server if the user does not consent.', 'User does not consent to data collection.', 'User did not consent to data collection.', 'No personal data will be collected or sent to the server.']}]}</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
+          <t>https://target.vk.ru/help/partners/mob/gdpr_compliant/en;https://developers.google.com/admob/android/mediation/mytarget</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>MyTarget</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>setUserAgeRestricted</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'API_name': 'ask', 'class_name': ['OguryChoiceManager'], 'conditions': ['Must be called at the launch of the application to ensure up-to-date consent', 'Must call ask method at each launch of the application'], 'effects': ['Synchronizes consent status or displays the consent notice if needed', 'Shows consent notice if needed and synchronizes consent signal'], 'parameter_configurations': [{'parameter_values': ['activity', 'oguryConsentListener'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'setUserAgeRestricted', 'class_name': ['MyTargetPrivacy'], 'conditions': ['User is known to be in an age-restricted category (under the age of 16).', 'User must be identified as being under the age of 16.', 'User must be known to be in an age-restricted category (e.g., under the age of 16).'], 'effects': ['Sets whether the user is known to be in an age-restricted category', 'If true, it indicates that the user should be considered age-restricted.', 'Sets a flag that indicates that the user is in an age-restricted category.', 'If set to true, indicates that the user is in an age-restricted category.', 'Indicates whether the user is in an age-restricted category, specifically for users under the age of 16.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is confirmed to be under the age of 16.', 'User is under the age of 16'], 'effects': ['Confirms that the user is in an age-restricted category, limiting data collection as needed.', 'Triggers age-restriction related data handling practices.', 'Indicates the user has age restrictions in place', 'User is recognized as an age-restricted individual and thus may limit data collection or utilization.', 'Establishes that the user is age-restricted.']}, {'parameter_values': [False], 'conditions': ['User is 16 years of age or older.'], 'effects': ['Establishes that the user is not age-restricted.', 'Indicates the user does not have age restrictions in place', 'Indicates that the user is not in an age-restricted category.', 'User is not considered age-restricted.', 'No age-restriction related data handling practices applied.']}]}</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
+          <t>https://target.vk.ru/help/partners/mob/gdpr_compliant/en;https://developers.google.com/admob/android/mediation/mytarget</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>MyTarget</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>setCcpaUserConsent</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'API_name': 'edit', 'class_name': ['OguryChoiceManager'], 'conditions': ['Users need to be in a location where GDPR applies', 'Publishers need to ensure users can access and edit their consent choices'], 'effects': ['Allows users to edit their previously given consent', 'Allows users to edit their consent at any time'], 'parameter_configurations': [{'parameter_values': ['activity', 'oguryConsentListener'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'setCcpaUserConsent', 'class_name': ['MyTargetPrivacy'], 'conditions': ['User must provide consent for data collection under CCPA compliance.', 'Applicable U.S. privacy laws require user consent for data collection.'], 'effects': ["Sets the user's consent status for the California Consumer Privacy Act (CCPA).", 'If consent is set to false, no personal data will be collected or sent to the server.', 'Sets whether the user has consented to the sale of their personal information under CCPA', 'Sets whether the user has consented to data collection under CCPA.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts in to allow personal data collection for CCPA compliance.'], 'effects': ['Enables the sale of personal information', 'Personal data may be collected and shared according to CCPA.', 'User consents to the sale of personal information under CCPA.', 'User consents to data collection under CCPA.']}, {'parameter_values': [False], 'conditions': ['User opts out of allowing personal data collection for CCPA compliance.'], 'effects': ['Disables the sale of personal information', 'No personal data will be collected or shared under CCPA.', 'User does not consent to the sale of personal information under CCPA.', 'User does not consent to data collection under CCPA.']}]}</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
+          <t>https://target.vk.ru/help/partners/mob/gdpr_compliant/en;https://developers.google.com/admob/android/mediation/mytarget</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>applyChildPrivacy</t>
+          <t>setAdContentThreshold</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'API_name': 'applyChildPrivacy', 'class_name': ['', 'Ogury'], 'conditions': [], 'effects': ['Indicates that the current user is a child, hence applying COPPA and GDPR compliance', 'Indicates that the current user is a child for privacy treatment under COPPA and GDPR', 'Applies appropriate privacy treatment based on COPPA and GDPR for child users'], 'parameter_configurations': [{'parameter_values': ['OguryChildPrivacyTreatment.UNSPECIFIED'], 'conditions': [], 'effects': []}, {'parameter_values': ['OguryChildPrivacyTreatment.CHILD_UNDER_COPPA_TREATMENT_FALSE'], 'conditions': [], 'effects': []}, {'parameter_values': ['OguryChildPrivacyTreatment.CHILD_UNDER_COPPA_TREATMENT_TRUE'], 'conditions': [], 'effects': ['User receives treatment for users under COPPA']}, {'parameter_values': ['OguryChildPrivacyTreatment.UNDER_AGE_OF_GDPR_CONSENT_TREATMENT_FALSE'], 'conditions': [], 'effects': []}, {'parameter_values': ['OguryChildPrivacyTreatment.UNDER_AGE_OF_GDPR_CONSENT_TREATMENT_TRUE'], 'conditions': [], 'effects': ['User receives treatment for users under the age of GDPR consent']}]}</t>
+          <t>{'API_name': 'setAdContentThreshold', 'class_name': ['OguryAdRequests'], 'conditions': [], 'effects': ['Filters ad content based on the specified threshold', 'Applies content filtering on ad requests', 'Sets the ad content filtering level for Ogury ad requests'], 'parameter_configurations': [{'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_G'], 'conditions': [], 'effects': ['Only ads suitable for general audiences, including families, are displayed']}, {'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_PG'], 'conditions': [], 'effects': ['Ads suitable for most audiences with parental guidance are displayed']}, {'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_T'], 'conditions': [], 'effects': ['Ads suitable for teen and older audiences are displayed']}, {'parameter_values': ['OguryAdRequests.AD_CONTENT_THRESHOLD_MA'], 'conditions': [], 'effects': ['Only mature audience ads are displayed']}]}</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3071,535 +3071,535 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Pollfish</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>advertisingOptOut</t>
+          <t>setConsent</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'API_name': 'advertisingOptOut', 'class_name': ['InitOptions.Builder'], 'conditions': [], 'effects': ["Opt-out from using the device's advertising identifier"], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Prodege SDK will use a unique session identifier instead of the advertising identifier']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Prodege SDK uses default advertising identifier behavior']}]}</t>
+          <t>{'API_name': 'setConsent', 'class_name': ['OguryChoiceManagerExternal', 'OguryChoiceManagerExternal.TcfV2'], 'conditions': ['Must be compliant with last GDPR requirements', 'Make sure the Ogury SDK is initialized beforehand', 'CMP must be initialized before doing any ad request', 'Ogury SDK must be initialized before calling this method', 'The IAB-specified Consent String must be valid and generated by a whitelisted CMP', 'Third-party CMP must be initialized before calling this method', 'The consent string must be generated by a whitelisted CMP', 'The consent notice is registered in the IAB CMP list and produces IAB-specified consent string', 'Your CMP generates a TCFv2 consent string'], 'effects': ['Transmits the user consent to Ogury SDK', 'The consent must be valid to avoid being ignored', 'Transmits the user consent to the Ogury SDK', 'Indicates whether the user has consented or not', 'Transmits the consent of the vendors registered inside the IAB Global Vendor List', 'Call must be made again if user consent changes'], 'parameter_configurations': [{'parameter_values': ['iabString', 'new Integer[0]'], 'conditions': ['The CMP generates a TCFv2 consent string and is not leveraging the IAB GDPR Consent Framework', 'CMP is listed in the IAB CMP list and produces an IAB-specified consent string', 'User consent needs to be collected before calling', 'User has provided a valid IAB-specified consent string'], 'effects': ['Consent for vendors registered in the IAB Global Vendor List is transmitted to the Ogury SDK', 'User consent is synchronized for ad requests', 'The consent is synchronized with Ogury SDK']}, {'parameter_values': ['consentBoolean', 'CUSTOM'], 'conditions': ['Consent from a CMP that is not compatible with TCFv2'], 'effects': ['Sets the consent status for the Ogury SDK']}, {'parameter_values': ['consentBoolean', 'consentManagerName'], 'conditions': ['Using a third-party CMP that is not compatible with TCFv2'], 'effects': ['Sets the user consent to Ogury SDK']}]}</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.pollfish.com/docs/android-v7</t>
+          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PubNative(verve)</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>setLocationTrackingEnabled</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLocationTrackingEnabled', 'class_name': ['HyBid'], 'conditions': ['The user has given location permissions', 'User has given location permissions'], 'effects': ['Enables or disables location tracking for more targeted ads', "Enables or disables the feature of using the user's location for targeted ads", 'Allows the SDK to use the user location for better-targeted ads', 'Enables or disables the HyBid SDK from using the available user location for targeted ads', 'Enables or disables location tracking for providing targeted ads'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['User wants to disable location tracking'], 'effects': ['User location is not used for targeted ads', 'SDK will not utilize user location to provide targeted ads', 'Location tracking is disabled globally for HyBid SDK', 'Disables location tracking', 'Location tracking will be disabled globally for the HyBid SDK']}, {'parameter_values': [True], 'conditions': ['Location tracking is desired'], 'effects': ['User location is used for better targeted ads', 'Enables location tracking', 'SDK will utilize user location to provide better targeted ads', 'HyBid SDK uses user location to improve ad targeting']}]}</t>
+          <t>{'API_name': 'ask', 'class_name': ['OguryChoiceManager'], 'conditions': ['Must be called at the launch of the application to ensure up-to-date consent', 'Must call ask method at each launch of the application'], 'effects': ['Synchronizes consent status or displays the consent notice if needed', 'Shows consent notice if needed and synchronizes consent signal'], 'parameter_configurations': [{'parameter_values': ['activity', 'oguryConsentListener'], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://developers.verve.com/reference/hybid-android-configuration</t>
+          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PubNative(verve)</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>setLocationUpdatesEnabled</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLocationUpdatesEnabled', 'class_name': ['HyBid'], 'conditions': ['Location tracking is enabled'], 'effects': ['Controls whether the SDK refreshes the user location after every ad request', 'Controls whether the SDK refreshes user location after every ad request', 'Controls the frequency of location updates after each ad request to improve accuracy', 'Controls frequency of location updates during ad requests'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['User wants to disable frequent location updates', 'Location tracking is enabled'], 'effects': ['SDK will not refresh user location after every ad request', 'Location updates will not be as frequent, reducing potential intrusiveness', 'Reduces the frequency of location updates during ad requests', 'User location updates are disabled, preventing intrusive updates', 'Disables frequent location updates']}, {'parameter_values': [True], 'conditions': ['Location tracking is enabled', 'Location tracking is already enabled and ongoing location updates are desired'], 'effects': ['User location updates are frequent after every ad request', 'Enables frequent location updates', 'SDK will refresh user location after every ad request', 'Location is refreshed after every ad request, potentially causing intrusive updates']}]}</t>
+          <t>{'API_name': 'edit', 'class_name': ['OguryChoiceManager'], 'conditions': ['Users need to be in a location where GDPR applies', 'Publishers need to ensure users can access and edit their consent choices'], 'effects': ['Allows users to edit their previously given consent', 'Allows users to edit their consent at any time'], 'parameter_configurations': [{'parameter_values': ['activity', 'oguryConsentListener'], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://developers.verve.com/reference/hybid-android-configuration</t>
+          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PubNative(verve)</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>setCoppaEnabled</t>
+          <t>applyChildPrivacy</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCoppaEnabled', 'class_name': ['HyBid'], 'conditions': ['The app is intended for children', 'App is intended for children'], 'effects': ["Enables COPPA compliance to protect children's information", "Enables COPPA compatibility to protect the privacy of children's information", "Enables compliance with COPPA to protect children's information", "Ensures compliance with COPPA to protect children's privacy", 'Enables compliance with COPPA for apps intended for children'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The application is designed for children'], 'effects': ['COPPA compliance is enabled', 'COPPA compatibility is enabled', 'The app will comply with COPPA regulations', "Protects the privacy of children's information", 'Enables COPPA compatibility']}, {'parameter_values': [False], 'conditions': [], 'effects': ['COPPA compliance is not enabled', 'Disables COPPA compatibility', 'COPPA compatibility is not enabled', 'COPPA compliance and protections are disabled']}]}</t>
+          <t>{'API_name': 'applyChildPrivacy', 'class_name': ['', 'Ogury'], 'conditions': [], 'effects': ['Indicates that the current user is a child, hence applying COPPA and GDPR compliance', 'Indicates that the current user is a child for privacy treatment under COPPA and GDPR', 'Applies appropriate privacy treatment based on COPPA and GDPR for child users'], 'parameter_configurations': [{'parameter_values': ['OguryChildPrivacyTreatment.UNSPECIFIED'], 'conditions': [], 'effects': []}, {'parameter_values': ['OguryChildPrivacyTreatment.CHILD_UNDER_COPPA_TREATMENT_FALSE'], 'conditions': [], 'effects': []}, {'parameter_values': ['OguryChildPrivacyTreatment.CHILD_UNDER_COPPA_TREATMENT_TRUE'], 'conditions': [], 'effects': ['User receives treatment for users under COPPA']}, {'parameter_values': ['OguryChildPrivacyTreatment.UNDER_AGE_OF_GDPR_CONSENT_TREATMENT_FALSE'], 'conditions': [], 'effects': []}, {'parameter_values': ['OguryChildPrivacyTreatment.UNDER_AGE_OF_GDPR_CONSENT_TREATMENT_TRUE'], 'conditions': [], 'effects': ['User receives treatment for users under the age of GDPR consent']}]}</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://developers.verve.com/reference/hybid-android-configuration</t>
+          <t>https://ogury-ltd.gitbook.io/android/ogury-choice-manager/collect-the-user-consent;https://ogury-ltd.gitbook.io/android/ogury-choice-manager/third-party-consent-manager;https://ogury-ltd.gitbook.io/android</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Quantcast</t>
+          <t>Pollfish</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>setCollectionEnabled</t>
+          <t>advertisingOptOut</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCollectionEnabled', 'class_name': ['QuantcastClient'], 'conditions': ['User opts out of Quantcast Measure', 'Called to manage user opt-out preference', 'When a user opts out of Quantcast Measure'], 'effects': ['Enables or disables the collection of user data by the Quantcast SDK', 'Enables or disables the collection of user data for Quantcast Measure.', "Stops transmitting information to or from the user's device and deletes any cached information.", "When set to false, the SDK stops transmitting information to or from the user's device and deletes any cached information.", "Stops transmitting information to or from the user's device and deletes any cached information that may have been retained"], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['User opts out of Quantcast Measure', 'User opts out', 'User wishes to opt out of data collection'], 'effects': ["When set to false, the SDK immediately stops transmitting information to or from the user's device and deletes any cached information.", 'Collects no data from the user', 'Stops the SDK from transmitting information and deletes any cached information', 'Users are opted out of Quantcast Measure for this app and all other apps integrated with Quantcast Measure on the device.', 'Data collection is disabled.']}, {'parameter_values': [True], 'conditions': [], 'effects': ['Begins collecting user data again', 'Data collection is enabled.', 'Users are opted back into Quantcast Measure.', 'When set to true, it resumes transmission of information to Quantcast.', 'Resumes the collection of data']}]}</t>
+          <t>{'API_name': 'advertisingOptOut', 'class_name': ['InitOptions.Builder'], 'conditions': [], 'effects': ["Opt-out from using the device's advertising identifier"], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Prodege SDK will use a unique session identifier instead of the advertising identifier']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Prodege SDK uses default advertising identifier behavior']}]}</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://github.com/quantcast/android-measurement</t>
+          <t>https://www.pollfish.com/docs/android-v7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Quantcast</t>
+          <t>PubNative(verve)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>recordUserIdentifier</t>
+          <t>setLocationTrackingEnabled</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'API_name': 'recordUserIdentifier', 'class_name': ['QuantcastClient'], 'conditions': ['User identifier must have been generated'], 'effects': ['Records a unique user identifier for cross-platform audience measurement.', 'Updates the user identifier in the Quantcast SDK', 'Updates the user identifier for tracking.'], 'parameter_configurations': [{'parameter_values': ['userIdentifier'], 'conditions': [], 'effects': ['The user identifier is anonymized with a 1-way hash before transmission.']}, {'parameter_values': ['userIdentifierString'], 'conditions': [], 'effects': ['The user identifier is hashed and stored securely']}]}</t>
+          <t>{'API_name': 'setLocationTrackingEnabled', 'class_name': ['HyBid'], 'conditions': ['The user has given location permissions', 'User has given location permissions'], 'effects': ['Enables or disables location tracking for more targeted ads', "Enables or disables the feature of using the user's location for targeted ads", 'Allows the SDK to use the user location for better-targeted ads', 'Enables or disables the HyBid SDK from using the available user location for targeted ads', 'Enables or disables location tracking for providing targeted ads'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['User wants to disable location tracking'], 'effects': ['User location is not used for targeted ads', 'SDK will not utilize user location to provide targeted ads', 'Location tracking is disabled globally for HyBid SDK', 'Disables location tracking', 'Location tracking will be disabled globally for the HyBid SDK']}, {'parameter_values': [True], 'conditions': ['Location tracking is desired'], 'effects': ['User location is used for better targeted ads', 'Enables location tracking', 'SDK will utilize user location to provide better targeted ads', 'HyBid SDK uses user location to improve ad targeting']}]}</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://github.com/quantcast/android-measurement</t>
+          <t>https://developers.verve.com/reference/hybid-android-configuration</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>PubNative(verve)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>optOut</t>
+          <t>setLocationUpdatesEnabled</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOut', 'class_name': ['Analytics'], 'conditions': ['The audience for the app may require the ability to opt-out of analytics data collection, especially for children or in certain countries like the EU.', 'Audience requires ability to opt-out of analytics data collection', 'for children or regions needing explicit consent', 'Audience requires option to opt-out of analytics data collection', 'for audiences that require compliance with data collection regulations', 'Applicable in countries with regulations requiring opt-out options', 'Depending on the audience for your app (for example, children) or the countries where you sell your app (for example, the EU)'], 'effects': ['prevents the collection of analytics data for that device', 'persists across device reboots', "When called, this method turns off ALL destinations including Segment itself, preventing any analytics data collection for the user's device.", 'Turns off all destinations including Segment itself', 'Disables data collection for the device and client', 'Turn off ALL destinations including Segment itself'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['All data collection stops, including from Segment itself', 'Sets opt-out status for current device and analytics client combination', "The user's device is opted out of analytics tracking.", 'All destinations including Segment itself will not collect any data', 'Set the opt-out status for the current device and analytics client combination. This flag persists across device reboots.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Data collection resumes for the device', 'Re-enable analytics tracking for the current device and analytics client combination', "The user's device is included in analytics tracking.", 'Data collection resumes after being disabled', 'Restores normal data collection']}]}</t>
+          <t>{'API_name': 'setLocationUpdatesEnabled', 'class_name': ['HyBid'], 'conditions': ['Location tracking is enabled'], 'effects': ['Controls whether the SDK refreshes the user location after every ad request', 'Controls whether the SDK refreshes user location after every ad request', 'Controls the frequency of location updates after each ad request to improve accuracy', 'Controls frequency of location updates during ad requests'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['User wants to disable frequent location updates', 'Location tracking is enabled'], 'effects': ['SDK will not refresh user location after every ad request', 'Location updates will not be as frequent, reducing potential intrusiveness', 'Reduces the frequency of location updates during ad requests', 'User location updates are disabled, preventing intrusive updates', 'Disables frequent location updates']}, {'parameter_values': [True], 'conditions': ['Location tracking is enabled', 'Location tracking is already enabled and ongoing location updates are desired'], 'effects': ['User location updates are frequent after every ad request', 'Enables frequent location updates', 'SDK will refresh user location after every ad request', 'Location is refreshed after every ad request, potentially causing intrusive updates']}]}</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://segment.com/docs/connections/sources/catalog/libraries/mobile/android/</t>
+          <t>https://developers.verve.com/reference/hybid-android-configuration</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Smaato</t>
+          <t>PubNative(verve)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>setLgpdConsentEnabled</t>
+          <t>setCoppaEnabled</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLgpdConsentEnabled', 'class_name': ['SmaatoSdk'], 'conditions': ['LGPD consent must be set after Smaato SDK initialization.', 'Publisher must request LGPD user consent.', 'Publisher should pass LGPD user consent to Smaato SDK', 'Publisher must choose to pass LGPD user consent', 'Publisher as a user must have LGPD compliance.'], 'effects': ["Smaato SDK will determine whether to display targeted ads based on the user's consent.", 'Sets LGPD consent to enable or disable targeted advertising based on user consent.', 'Enables or disables user consent for LGPD. If set to true, Smaato will process personal information. If set to false, Smaato will run contextual ads with no personal information.', 'Explicit signal that user has given or not given consent under LGPD', 'Sets the LGPD user consent to either true (given) or false (not given), which impacts how personal information can be processed.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User has given consent.', 'User has given explicit consent.', 'The user has given explicit consent.', 'User has given explicit consent'], 'effects': ['Advertise with user data for targeted advertising.', 'Smaato SDK will show targeted ads.', 'Allows the use of personal data for targeted advertising.', 'User data can be used for targeted advertising', 'Explicit Signal that user has given Consent.']}, {'parameter_values': [False], 'conditions': ['User has not given consent.', 'The user has not given explicit consent.', 'User has not given consent'], 'effects': ['Runs contextual ads with dropped personally identifiable information (PII).', 'Explicit Signal that user has not given Consent.', 'Smaato SDK will run contextual ads with dropped PII.', 'Only contextual ads will be served without PII.', 'Only contextual ads can be shown with dropped PII']}, {'parameter_values': [None], 'conditions': ['If no explicit signal is set', 'User consent is not explicitly set.', 'No explicit signal set.'], 'effects': ['Publisher only calls Smaato if they have enough legal basis for targeted advertising under LGPD.', 'If no explicit Signal is set, Smaato chooses to only call if there is enough legal basis for Targeted Advertising under LGPD.', 'Smaato SDK chooses to call only if there is enough legal basis for targeted advertising under LGPD.', 'Publisher chooses to only call Smaato if they have enough legal basis for targeted advertising under LGPD']}]}</t>
+          <t>{'API_name': 'setCoppaEnabled', 'class_name': ['HyBid'], 'conditions': ['The app is intended for children', 'App is intended for children'], 'effects': ["Enables COPPA compliance to protect children's information", "Enables COPPA compatibility to protect the privacy of children's information", "Enables compliance with COPPA to protect children's information", "Ensures compliance with COPPA to protect children's privacy", 'Enables compliance with COPPA for apps intended for children'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The application is designed for children'], 'effects': ['COPPA compliance is enabled', 'COPPA compatibility is enabled', 'The app will comply with COPPA regulations', "Protects the privacy of children's information", 'Enables COPPA compatibility']}, {'parameter_values': [False], 'conditions': [], 'effects': ['COPPA compliance is not enabled', 'Disables COPPA compatibility', 'COPPA compatibility is not enabled', 'COPPA compliance and protections are disabled']}]}</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://developers.smaato.com/publishers/android-nextgen-sdk-integration/#NextGenSDK%7CAndroid%7CSmaatoasprimary-ImportantDetailsAboutLGPDUserConsent</t>
+          <t>https://developers.verve.com/reference/hybid-android-configuration</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Smaato</t>
+          <t>Quantcast</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>setUsPrivacyString</t>
+          <t>setCollectionEnabled</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUsPrivacyString', 'class_name': ['SmaatoSdk'], 'conditions': ['Required for compliance with CCPA when dealing with California residents.', 'Publisher must ensure compliance with CCPA for California-based users.', 'Publishers must request consent from California-based users', 'Publisher must request consent from California-based users regarding the private data transfer.', 'California-based publishers must comply with CCPA.'], 'effects': ['Stores the US Privacy String which directs the ad requests for compliance.', 'Maintains compliance with CCPA by storing user consent as a privacy string', 'The application will handle CCPA compliance by using the provided US Privacy String.', 'Sets the US Privacy String for handling user privacy choices.', 'Sets the US Privacy String for California-based users.'], 'parameter_configurations': [{'parameter_values': ['iab string'], 'conditions': ['Consent for personal data transfer is provided by the user', 'Privacy string is provided by the publisher.'], 'effects': ['SDK uses the provided US Privacy String during ad requests.', 'Allows Smaato SDK to use the privacy string for ad requests']}, {'parameter_values': ['some_us_privacy_string'], 'conditions': ['Privacy string needs to be set for California-based users.'], 'effects': ['Smaato SDK reads this value for all ad requests to manage user privacy compliance.']}, {'parameter_values': ['iab privacy string'], 'conditions': ['Publisher has obtained user consent regarding data transfer.'], 'effects': ['Allows targeted advertising based on user consent.']}]}</t>
+          <t>{'API_name': 'setCollectionEnabled', 'class_name': ['QuantcastClient'], 'conditions': ['User opts out of Quantcast Measure', 'Called to manage user opt-out preference', 'When a user opts out of Quantcast Measure'], 'effects': ['Enables or disables the collection of user data by the Quantcast SDK', 'Enables or disables the collection of user data for Quantcast Measure.', "Stops transmitting information to or from the user's device and deletes any cached information.", "When set to false, the SDK stops transmitting information to or from the user's device and deletes any cached information.", "Stops transmitting information to or from the user's device and deletes any cached information that may have been retained"], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['User opts out of Quantcast Measure', 'User opts out', 'User wishes to opt out of data collection'], 'effects': ["When set to false, the SDK immediately stops transmitting information to or from the user's device and deletes any cached information.", 'Collects no data from the user', 'Stops the SDK from transmitting information and deletes any cached information', 'Users are opted out of Quantcast Measure for this app and all other apps integrated with Quantcast Measure on the device.', 'Data collection is disabled.']}, {'parameter_values': [True], 'conditions': [], 'effects': ['Begins collecting user data again', 'Data collection is enabled.', 'Users are opted back into Quantcast Measure.', 'When set to true, it resumes transmission of information to Quantcast.', 'Resumes the collection of data']}]}</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://developers.smaato.com/publishers/android-nextgen-sdk-integration/#NextGenSDK%7CAndroid%7CSmaatoasprimary-ImportantDetailsAboutLGPDUserConsent</t>
+          <t>https://github.com/quantcast/android-measurement</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Smaato</t>
+          <t>Quantcast</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>setCoppa</t>
+          <t>setEnableLocationGathering</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCoppa', 'class_name': ['SmaatoSdk'], 'conditions': ['Required when targeting users under the age of 13.', 'Integrate if COPPA compliance is required.'], 'effects': ['Indicates whether the app is directed to children under the age of 13.', 'Indicates whether the application complies with COPPA regulations.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ["User's app is designed for children."], 'effects': ['Restricts collection of personal data in accordance with COPPA regulations.', 'Indicates that COPPA regulations apply.']}, {'parameter_values': [False], 'conditions': ["User's app is not directed towards children."], 'effects': ['No restrictions on personal data collection apply.', 'Indicates that COPPA regulations do not apply.']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://developers.smaato.com/publishers/android-nextgen-sdk-integration/#NextGenSDK%7CAndroid%7CSmaatoasprimary-ImportantDetailsAboutLGPDUserConsent</t>
+          <t>https://github.com/quantcast/android-measurement</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Splunk MINT</t>
+          <t>Quantcast</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>setUserIdentifier</t>
+          <t>recordUserIdentifier</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserIdentifier', 'class_name': ['Mint'], 'conditions': ['Do not transmit personally identifiable or sensitive data.', 'Must provide a user identifier such as an ID number from a database, an email address, a push ID, or a username.', 'Must provide a user identifier such as an ID number, email address, push ID, or username.', 'A user identifier such as an ID number, email address, push ID, or username should be provided.', 'A user identifier such as an ID number, email address, push ID, or username must be provided.'], 'effects': ['sets a user identifier for tracking user experience and crash data', 'Allows tracking the experience of a specific user, which can be used for investigating complaints.', 'Allows tracking of user experience and error investigation for a specific user.', 'Tracks the experience of a specific user within the application, enabling investigation of issues.', 'Allows tracking of user-specific data to investigate issues or complaints.'], 'parameter_configurations': [{'parameter_values': ['12345'], 'conditions': ['user identifier should be valid'], 'effects': ["Sets the user identifier to '12345'.", 'Allows searching for errors that affect the specific user ID in the Splunk MINT Management Console', 'Sets the user identifier for data tracking']}, {'parameter_values': ['someone@domain.com'], 'conditions': ['user identifier should be valid'], 'effects': ['Allows searching for errors that affect the specific user email in the Splunk MINT Management Console', "Sets the user identifier to 'someone@domain.com'.", 'Sets the user identifier for data tracking']}, {'parameter_values': ['"12345"'], 'conditions': [], 'effects': []}, {'parameter_values': ['"someone@domain.com"'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'recordUserIdentifier', 'class_name': ['QuantcastClient'], 'conditions': ['User identifier must have been generated'], 'effects': ['Records a unique user identifier for cross-platform audience measurement.', 'Updates the user identifier in the Quantcast SDK', 'Updates the user identifier for tracking.'], 'parameter_configurations': [{'parameter_values': ['userIdentifier'], 'conditions': [], 'effects': ['The user identifier is anonymized with a 1-way hash before transmission.']}, {'parameter_values': ['userIdentifierString'], 'conditions': [], 'effects': ['The user identifier is hashed and stored securely']}]}</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://docs.splunk.com/Documentation/MintAndroidSDK/5.2.x/DevGuide/Reportuser-specificdata</t>
+          <t>https://github.com/quantcast/android-measurement</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Splunk MINT</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>setUserOptOut</t>
+          <t>optOut</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserOptOut', 'class_name': ['Mint'], 'conditions': ['Called before initAndStartSession.', 'User chooses to opt out of tracking.', 'Must be called before invoking initAndStartSession to prevent MINT from saving or sending any data.', 'Must be called before initAndStartSession to prevent data from being saved or sent for a user.', 'Must be called before initAndStartSession to prevent data saving or sending for the user.'], 'effects': ['Prevents MINT from saving or sending any data related to the specified user.', 'Prevents MINT from saving or sending any data for the user.', 'Prevents MINT from saving or sending any user data.', 'prevents MINT from saving or sending any data for a user', 'Prevents MINT from saving or sending any data related to the opted-out user.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User has opted out of data collection', 'must be called before invoking initAndStartSession'], 'effects': ['MINT will not track or report any user data.', 'No data will be collected for the user', 'Stops any data collection for the user who opted out']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Allows data collection for the user', 'MINT will track and report user data.']}]}</t>
+          <t>{'API_name': 'optOut', 'class_name': ['Analytics'], 'conditions': ['The audience for the app may require the ability to opt-out of analytics data collection, especially for children or in certain countries like the EU.', 'Audience requires ability to opt-out of analytics data collection', 'for children or regions needing explicit consent', 'Audience requires option to opt-out of analytics data collection', 'for audiences that require compliance with data collection regulations', 'Applicable in countries with regulations requiring opt-out options', 'Depending on the audience for your app (for example, children) or the countries where you sell your app (for example, the EU)'], 'effects': ['prevents the collection of analytics data for that device', 'persists across device reboots', "When called, this method turns off ALL destinations including Segment itself, preventing any analytics data collection for the user's device.", 'Turns off all destinations including Segment itself', 'Disables data collection for the device and client', 'Turn off ALL destinations including Segment itself'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['All data collection stops, including from Segment itself', 'Sets opt-out status for current device and analytics client combination', "The user's device is opted out of analytics tracking.", 'All destinations including Segment itself will not collect any data', 'Set the opt-out status for the current device and analytics client combination. This flag persists across device reboots.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Data collection resumes for the device', 'Re-enable analytics tracking for the current device and analytics client combination', "The user's device is included in analytics tracking.", 'Data collection resumes after being disabled', 'Restores normal data collection']}]}</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://docs.splunk.com/Documentation/MintAndroidSDK/5.2.x/DevGuide/Reportuser-specificdata</t>
+          <t>https://segment.com/docs/connections/sources/catalog/libraries/mobile/android/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Startapp</t>
+          <t>Smaato</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>setLgpdConsentEnabled</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': ['StartAppSDK'], 'conditions': ['User must be within the EU for GDPR compliance', 'The user is based in the EU and consent requirements under GDPR apply', 'In case of any consent change during the user activity, it needs to be re-submitted', 'The consent flag with the correct timestamp is generated', 'User consent must be collected in accordance with GDPR if user is from EU.', 'User must provide consent for sharing their data, especially in countries covered by GDPR.', 'Consent needs to be reported after initializing the SDK', 'GDPR applies to the user'], 'effects': ['Allows personalized ads to be shown if consent is given.', 'If consent is not provided, personalized ads will not be shown to this user', 'Indicates whether user has consented for personal data processing for ads personalization', 'Determines whether personalized ads can be shown based on user consent', 'Indicates whether a user based in the EU has provided consent for sharing their app data for personalized ads', 'Indicates whether a user has consented to share app data for personalized advertising.'], 'parameter_configurations': [{'parameter_values': ['this', 'pas', 'timestamp', True], 'conditions': ['User has consented', 'The user has consented to share personal data.'], 'effects': ['User ad data can be processed for personalized advertising.', 'User data will be processed for personalized advertising']}, {'parameter_values': ['this', 'pas', 'timestamp', False], 'conditions': ['The user has not consented to share personal data.', 'User has not consented'], 'effects': ['No personalized ads will be shown to the user.', 'User data will not be used for personalized advertising']}, {'parameter_values': ['this', 'pas', 'System.currentTimeMillis()', True], 'conditions': ['User has consented to share personal data', 'User has consented'], 'effects': ["User's consent is registered, allowing personalized ads to be displayed", 'Personalized ads are allowed for this user', 'Personalized ads will be shown to the user.']}, {'parameter_values': ['this', 'pas', 'System.currentTimeMillis()', False], 'conditions': ['User has not consented to share personal data', 'User has not consented'], 'effects': ['Personalized ads will not be shown to the user.', "User's consent is registered as false, preventing personalized ads from being shown", 'Personalized ads are not shown to this user']}]}</t>
+          <t>{'API_name': 'setLgpdConsentEnabled', 'class_name': ['SmaatoSdk'], 'conditions': ['LGPD consent must be set after Smaato SDK initialization.', 'Publisher must request LGPD user consent.', 'Publisher should pass LGPD user consent to Smaato SDK', 'Publisher must choose to pass LGPD user consent', 'Publisher as a user must have LGPD compliance.'], 'effects': ["Smaato SDK will determine whether to display targeted ads based on the user's consent.", 'Sets LGPD consent to enable or disable targeted advertising based on user consent.', 'Enables or disables user consent for LGPD. If set to true, Smaato will process personal information. If set to false, Smaato will run contextual ads with no personal information.', 'Explicit signal that user has given or not given consent under LGPD', 'Sets the LGPD user consent to either true (given) or false (not given), which impacts how personal information can be processed.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User has given consent.', 'User has given explicit consent.', 'The user has given explicit consent.', 'User has given explicit consent'], 'effects': ['Advertise with user data for targeted advertising.', 'Smaato SDK will show targeted ads.', 'Allows the use of personal data for targeted advertising.', 'User data can be used for targeted advertising', 'Explicit Signal that user has given Consent.']}, {'parameter_values': [False], 'conditions': ['User has not given consent.', 'The user has not given explicit consent.', 'User has not given consent'], 'effects': ['Runs contextual ads with dropped personally identifiable information (PII).', 'Explicit Signal that user has not given Consent.', 'Smaato SDK will run contextual ads with dropped PII.', 'Only contextual ads will be served without PII.', 'Only contextual ads can be shown with dropped PII']}, {'parameter_values': [None], 'conditions': ['If no explicit signal is set', 'User consent is not explicitly set.', 'No explicit signal set.'], 'effects': ['Publisher only calls Smaato if they have enough legal basis for targeted advertising under LGPD.', 'If no explicit Signal is set, Smaato chooses to only call if there is enough legal basis for Targeted Advertising under LGPD.', 'Smaato SDK chooses to call only if there is enough legal basis for targeted advertising under LGPD.', 'Publisher chooses to only call Smaato if they have enough legal basis for targeted advertising under LGPD']}]}</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://support.start.io/hc/en-us/articles/360014774799-Integration-via-Maven#h_01HF6J2VHPEBVC6X1WZ6VTTX9G</t>
+          <t>https://developers.smaato.com/publishers/android-nextgen-sdk-integration/#NextGenSDK%7CAndroid%7CSmaatoasprimary-ImportantDetailsAboutLGPDUserConsent</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Startapp</t>
+          <t>Smaato</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>getExtras</t>
+          <t>setUsPrivacyString</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'API_name': 'getExtras', 'class_name': ['StartAppSDK'], 'conditions': ['The user is located in California for CCPA compliance', 'The user is located in California', 'To restrict the sale of personal information under CCPA.', 'Users must be located in California to apply the CCPA opt-out provisions.'], 'effects': ['Allows the application to set the IAB US privacy string for CCPA compliance.', 'Allows publishers to restrict the sale of end users’ personal information under CCPA', 'Sets the IAB US privacy string.', 'Allows the setting of the IAB US privacy string for opt-out purposes'], 'parameter_configurations': [{'parameter_values': ['this'], 'conditions': ['User chooses to opt-out of advertising'], 'effects': ["User's personal information is not sold", 'Returns extras allowing the developer to set the IAB US Privacy String', 'Sets up the extras needed for CCPA compliance.']}]}</t>
+          <t>{'API_name': 'setUsPrivacyString', 'class_name': ['SmaatoSdk'], 'conditions': ['Required for compliance with CCPA when dealing with California residents.', 'Publisher must ensure compliance with CCPA for California-based users.', 'Publishers must request consent from California-based users', 'Publisher must request consent from California-based users regarding the private data transfer.', 'California-based publishers must comply with CCPA.'], 'effects': ['Stores the US Privacy String which directs the ad requests for compliance.', 'Maintains compliance with CCPA by storing user consent as a privacy string', 'The application will handle CCPA compliance by using the provided US Privacy String.', 'Sets the US Privacy String for handling user privacy choices.', 'Sets the US Privacy String for California-based users.'], 'parameter_configurations': [{'parameter_values': ['iab string'], 'conditions': ['Consent for personal data transfer is provided by the user', 'Privacy string is provided by the publisher.'], 'effects': ['SDK uses the provided US Privacy String during ad requests.', 'Allows Smaato SDK to use the privacy string for ad requests']}, {'parameter_values': ['some_us_privacy_string'], 'conditions': ['Privacy string needs to be set for California-based users.'], 'effects': ['Smaato SDK reads this value for all ad requests to manage user privacy compliance.']}, {'parameter_values': ['iab privacy string'], 'conditions': ['Publisher has obtained user consent regarding data transfer.'], 'effects': ['Allows targeted advertising based on user consent.']}]}</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://support.start.io/hc/en-us/articles/360014774799-Integration-via-Maven#h_01HF6J2VHPEBVC6X1WZ6VTTX9G</t>
+          <t>https://developers.smaato.com/publishers/android-nextgen-sdk-integration/#NextGenSDK%7CAndroid%7CSmaatoasprimary-ImportantDetailsAboutLGPDUserConsent</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Supersonic</t>
+          <t>Smaato</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>setCoppa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'API_name': 'init', 'class_name': ['supersonic'], 'conditions': ['User must provide an app key retrieved from the Supersonic developer portal', 'Compliance with GDPR is required for users in applicable regions', 'user must provide an adListener function'], 'effects': ['initializes the Supersonic plugin', 'Initializes the Supersonic plugin for ad loading and showing', 'initializes the Supersonic plugin for ad loading and showing', 'Controls GDPR data collection based on hasUserConsent parameter', 'enables GDPR data collection restrictions if hasUserConsent is set to false'], 'parameter_configurations': [{'parameter_values': ['adListener', {'appKey': 'YOUR_APP_KEY', 'hasUserConsent': False}], 'conditions': ['The appKey must be retrieved from the Supersonic developer portal'], 'effects': ['enables GDPR data collection restrictions if hasUserConsent is false', 'If hasUserConsent is set to false, GDPR data collection restrictions will be enabled.']}, {'parameter_values': ['adListener', {'appKey': 'YOUR_APP_KEY', 'hasUserConsent': True}], 'conditions': ['The appKey must be retrieved from the Supersonic developer portal'], 'effects': ['If hasUserConsent is set to true, GDPR data collection restrictions will be disabled.', 'allows data collection unrestricted by GDPR']}, {'parameter_values': ['YOUR_APP_KEY', False], 'conditions': ['hasUserConsent is set to false', 'User has not provided consent under GDPR regulations'], 'effects': ['Enables GDPR data collection restrictions', 'Chartboost will enable GDPR data collection restrictions']}, {'parameter_values': ['YOUR_APP_KEY', True], 'conditions': ['hasUserConsent is set to true', 'User has provided consent under GDPR regulations'], 'effects': ['Chartboost will not enable GDPR data collection restrictions', 'Allows data collection without GDPR restrictions']}]}</t>
+          <t>{'API_name': 'setCoppa', 'class_name': ['SmaatoSdk'], 'conditions': ['Required when targeting users under the age of 13.', 'Integrate if COPPA compliance is required.'], 'effects': ['Indicates whether the app is directed to children under the age of 13.', 'Indicates whether the application complies with COPPA regulations.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ["User's app is designed for children."], 'effects': ['Restricts collection of personal data in accordance with COPPA regulations.', 'Indicates that COPPA regulations apply.']}, {'parameter_values': [False], 'conditions': ["User's app is not directed towards children."], 'effects': ['No restrictions on personal data collection apply.', 'Indicates that COPPA regulations do not apply.']}]}</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://docs.coronalabs.com/plugin/supersonic/init.html#supersonic.init</t>
+          <t>https://developers.smaato.com/publishers/android-nextgen-sdk-integration/#NextGenSDK%7CAndroid%7CSmaatoasprimary-ImportantDetailsAboutLGPDUserConsent</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Splunk MINT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>setExtraProperties</t>
+          <t>setUserIdentifier</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'API_name': 'setExtraProperties', 'class_name': ['taboolaWidget'], 'conditions': ['User must be a CCPA subject to pass the Do Not Sell status', 'User must be a GDPR subject to pass the consent status', 'The end-user is subject to GDPR when passing the consent status', 'The end-user is subject to CCPA when passing the dns status'], 'effects': ['Passes the CCPA Do Not Sell status to the Taboola SDK for data handling', 'Sets the CCPA Do Not Sell status for users', 'Sets the GDPR consent status for users', 'Enables or disables the use of personal data based on user consent', "Passes the user's consent status to the Taboola SDK for data handling", 'Enables or disables the sale of personal data based on user consent'], 'parameter_configurations': [{'parameter_values': [{'cdns': 'false'}, {'cdns': 'true'}, {'cdns': 'none'}], 'conditions': ['The CCPA applies to the user'], 'effects': ["When cdns is false, Taboola can use the user's data as the user consented", "When cdns is true, Taboola must not use the user's data as the user did not consent", 'When cdns is none, CCPA does not apply and data usage is allowed']}, {'parameter_values': [{'cex': 'true'}, {'cex': 'false'}], 'conditions': ['The user is subject to GDPR', 'GDPR applies'], 'effects': ["When cex is false, Taboola must not use the user's data as the user did not provide consent", 'Indicates whether Taboola is allowed to process personal data based on user consent', "When cex is true, Taboola can use the user's data as the user provided consent"]}, {'parameter_values': [{'cdns': 'true'}, {'cdns': 'false'}, {'cdns': 'none'}], 'conditions': ['CCPA applies'], 'effects': ['Indicates whether Taboola is allowed to sell personal data or not, based on user consent']}]}</t>
+          <t>{'API_name': 'setUserIdentifier', 'class_name': ['Mint'], 'conditions': ['Do not transmit personally identifiable or sensitive data.', 'Must provide a user identifier such as an ID number from a database, an email address, a push ID, or a username.', 'Must provide a user identifier such as an ID number, email address, push ID, or username.', 'A user identifier such as an ID number, email address, push ID, or username should be provided.', 'A user identifier such as an ID number, email address, push ID, or username must be provided.'], 'effects': ['sets a user identifier for tracking user experience and crash data', 'Allows tracking the experience of a specific user, which can be used for investigating complaints.', 'Allows tracking of user experience and error investigation for a specific user.', 'Tracks the experience of a specific user within the application, enabling investigation of issues.', 'Allows tracking of user-specific data to investigate issues or complaints.'], 'parameter_configurations': [{'parameter_values': ['12345'], 'conditions': ['user identifier should be valid'], 'effects': ["Sets the user identifier to '12345'.", 'Allows searching for errors that affect the specific user ID in the Splunk MINT Management Console', 'Sets the user identifier for data tracking']}, {'parameter_values': ['someone@domain.com'], 'conditions': ['user identifier should be valid'], 'effects': ['Allows searching for errors that affect the specific user email in the Splunk MINT Management Console', "Sets the user identifier to 'someone@domain.com'.", 'Sets the user identifier for data tracking']}, {'parameter_values': ['"12345"'], 'conditions': [], 'effects': []}, {'parameter_values': ['"someone@domain.com"'], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://developers.taboola.com/taboolasdk/v2/docs/android-sdk-gdpr;https://developers.taboola.com/taboolasdk/v2/docs/taboola-android-sdk-ccpa</t>
+          <t>https://docs.splunk.com/Documentation/MintAndroidSDK/5.2.x/DevGuide/Reportuser-specificdata</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tapjoy</t>
+          <t>Splunk MINT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>setUserOptOut</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': ['TJPrivacyPolicy'], 'conditions': ['Application has made its own determination as to whether GDPR is applicable to the user', 'The application has made its own determination regarding the applicability of GDPR', 'The application must make its own determination as to whether GDPR is applicable to the user.', 'The application has made its own determination as to whether GDPR is applicable to the user or not', 'Application must determine whether GDPR is applicable to the user'], 'effects': ['Sets the user consent status for data processing.', "Determines the user's consent status for data processing", "Sets the user's consent status for data processing", 'Sets user consent status for data processing', 'Sets the user consent status for data collection and processing'], 'parameter_configurations': [{'parameter_values': ['TJStatus.FALSE'], 'conditions': ['User does not consent to data processing.', 'User does not consent'], 'effects': ['Indicates that the user does not consent to data processing', "User's data will not be processed for interest-based advertising", 'Restricts the use of personal data for processing.', "User's data will not be processed based on consent"]}, {'parameter_values': ['TJStatus.TRUE'], 'conditions': ['User consents to data processing', 'User consents to data processing.', 'User consents'], 'effects': ['Allows for the use of personal data for processing.', "User's data can be processed based on consent", "User's data will be processed for interest-based advertising", 'Indicates that the user consents to data processing']}]}</t>
+          <t>{'API_name': 'setUserOptOut', 'class_name': ['Mint'], 'conditions': ['Called before initAndStartSession.', 'User chooses to opt out of tracking.', 'Must be called before invoking initAndStartSession to prevent MINT from saving or sending any data.', 'Must be called before initAndStartSession to prevent data from being saved or sent for a user.', 'Must be called before initAndStartSession to prevent data saving or sending for the user.'], 'effects': ['Prevents MINT from saving or sending any data related to the specified user.', 'Prevents MINT from saving or sending any data for the user.', 'Prevents MINT from saving or sending any user data.', 'prevents MINT from saving or sending any data for a user', 'Prevents MINT from saving or sending any data related to the opted-out user.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User has opted out of data collection', 'must be called before invoking initAndStartSession'], 'effects': ['MINT will not track or report any user data.', 'No data will be collected for the user', 'Stops any data collection for the user who opted out']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Allows data collection for the user', 'MINT will track and report user data.']}]}</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
+          <t>https://docs.splunk.com/Documentation/MintAndroidSDK/5.2.x/DevGuide/Reportuser-specificdata</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tapjoy</t>
+          <t>Startapp</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>setSubjectToGDPR</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['TJPrivacyPolicy'], 'conditions': ['Application has made its own determination as to whether GDPR is applicable to the user', 'The application must determine whether GDPR rules are applicable to the user.', 'The application has made its own determination as to whether GDPR is applicable to the user or not', 'Application must determine if GDPR rules apply to the user'], 'effects': ['Determines if the user is subject to GDPR rules', 'Specifies whether the user is subject to GDPR rules', 'Indicates whether the user is subject to GDPR', 'Indicates whether user data processing is subject to GDPR compliance.'], 'parameter_configurations': [{'parameter_values': ['TJStatus.TRUE'], 'conditions': ['User is determined to be subject to GDPR', 'User is subject to GDPR', 'User is determined to be subject to GDPR.', 'User is determined to be subject to GDPR rules'], 'effects': ["Enforces GDPR compliance for the user's data.", 'Tapjoy assumes GDPR rules apply to the user', "Tapjoy will handle the user's consent according to GDPR", 'Informs Tapjoy to treat the user as being subject to GDPR', 'Indicates that the user is subject to GDPR']}, {'parameter_values': ['TJStatus.FALSE'], 'conditions': ['User is determined to not be subject to GDPR rules', 'User is determined not to be subject to GDPR', 'User is not subject to GDPR', 'User is determined not to be subject to GDPR.'], 'effects': ['Informs Tapjoy to treat the user as not being subject to GDPR', 'No GDPR compliance enforcement required.', 'Indicates that the user is not subject to GDPR', 'Tapjoy assumes GDPR rules do not apply to the user', 'Tapjoy will assume user is not covered by GDPR']}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': ['StartAppSDK'], 'conditions': ['User must be within the EU for GDPR compliance', 'The user is based in the EU and consent requirements under GDPR apply', 'In case of any consent change during the user activity, it needs to be re-submitted', 'The consent flag with the correct timestamp is generated', 'User consent must be collected in accordance with GDPR if user is from EU.', 'User must provide consent for sharing their data, especially in countries covered by GDPR.', 'Consent needs to be reported after initializing the SDK', 'GDPR applies to the user'], 'effects': ['Allows personalized ads to be shown if consent is given.', 'If consent is not provided, personalized ads will not be shown to this user', 'Indicates whether user has consented for personal data processing for ads personalization', 'Determines whether personalized ads can be shown based on user consent', 'Indicates whether a user based in the EU has provided consent for sharing their app data for personalized ads', 'Indicates whether a user has consented to share app data for personalized advertising.'], 'parameter_configurations': [{'parameter_values': ['this', 'pas', 'timestamp', True], 'conditions': ['User has consented', 'The user has consented to share personal data.'], 'effects': ['User ad data can be processed for personalized advertising.', 'User data will be processed for personalized advertising']}, {'parameter_values': ['this', 'pas', 'timestamp', False], 'conditions': ['The user has not consented to share personal data.', 'User has not consented'], 'effects': ['No personalized ads will be shown to the user.', 'User data will not be used for personalized advertising']}, {'parameter_values': ['this', 'pas', 'System.currentTimeMillis()', True], 'conditions': ['User has consented to share personal data', 'User has consented'], 'effects': ["User's consent is registered, allowing personalized ads to be displayed", 'Personalized ads are allowed for this user', 'Personalized ads will be shown to the user.']}, {'parameter_values': ['this', 'pas', 'System.currentTimeMillis()', False], 'conditions': ['User has not consented to share personal data', 'User has not consented'], 'effects': ['Personalized ads will not be shown to the user.', "User's consent is registered as false, preventing personalized ads from being shown", 'Personalized ads are not shown to this user']}]}</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
+          <t>https://support.start.io/hc/en-us/articles/360014774799-Integration-via-Maven#h_01HF6J2VHPEBVC6X1WZ6VTTX9G</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tapjoy</t>
+          <t>Startapp</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>setBelowConsentAge</t>
+          <t>getExtras</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'API_name': 'setBelowConsentAge', 'class_name': ['TJPrivacyPolicy'], 'conditions': [], 'effects': ['Indicates compliance with laws related to user age and consent', "Informs Tapjoy about the user's age with respect to legal compliance.", 'Informs whether the user is below the consent age for COPPA and other applicable laws', "Informs compliance regarding the user's age under COPPA or other regulations", "Informs Tapjoy of user's age related to consent requirements"], 'parameter_configurations': [{'parameter_values': ['TJStatus.TRUE'], 'conditions': [], 'effects': ['Indicates that the user is below the consent age', 'Indicates the user is below the consent age', 'Indicates user is below the consent age', 'Informs Tapjoy that this user is below the consent age for data processing.']}, {'parameter_values': ['TJStatus.FALSE'], 'conditions': [], 'effects': ['Indicates user is above the consent age', 'Indicates the user is above the consent age', 'Indicates that the user is above the consent age', 'Informs Tapjoy that this user is above the consent age for data processing.']}]}</t>
+          <t>{'API_name': 'getExtras', 'class_name': ['StartAppSDK'], 'conditions': ['The user is located in California for CCPA compliance', 'The user is located in California', 'To restrict the sale of personal information under CCPA.', 'Users must be located in California to apply the CCPA opt-out provisions.'], 'effects': ['Allows the application to set the IAB US privacy string for CCPA compliance.', 'Allows publishers to restrict the sale of end users’ personal information under CCPA', 'Sets the IAB US privacy string.', 'Allows the setting of the IAB US privacy string for opt-out purposes'], 'parameter_configurations': [{'parameter_values': ['this'], 'conditions': ['User chooses to opt-out of advertising'], 'effects': ["User's personal information is not sold", 'Returns extras allowing the developer to set the IAB US Privacy String', 'Sets up the extras needed for CCPA compliance.']}]}</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
+          <t>https://support.start.io/hc/en-us/articles/360014774799-Integration-via-Maven#h_01HF6J2VHPEBVC6X1WZ6VTTX9G</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tapjoy</t>
+          <t>Supersonic</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>setUSPrivacy</t>
+          <t>init</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUSPrivacy', 'class_name': ['TJPrivacyPolicy'], 'conditions': [], 'effects': ['Sets the US privacy status according to IAB’s US Privacy String Format', 'Sets the US Privacy flag for the user.', 'Sets the US privacy compliance status using the IAB’s US Privacy String Format', 'Sets the US privacy string status', "Sets the US privacy compliance status using IAB's US Privacy String Format"], 'parameter_configurations': [{'parameter_values': ['1YNN'], 'conditions': [], 'effects': ["Sets the user's privacy preferences according to IAB format", "Indicates the user's privacy preferences under US law", "Indicates the user's privacy status under US privacy regulations"]}, {'parameter_values': ['1YYY'], 'conditions': [], 'effects': ['Sets US privacy status based on the provided US Privacy String', "Indicates the user's privacy preferences in accordance with IAB's US Privacy String Format."]}]}</t>
+          <t>{'API_name': 'init', 'class_name': ['supersonic'], 'conditions': ['User must provide an app key retrieved from the Supersonic developer portal', 'Compliance with GDPR is required for users in applicable regions', 'user must provide an adListener function'], 'effects': ['initializes the Supersonic plugin', 'Initializes the Supersonic plugin for ad loading and showing', 'initializes the Supersonic plugin for ad loading and showing', 'Controls GDPR data collection based on hasUserConsent parameter', 'enables GDPR data collection restrictions if hasUserConsent is set to false'], 'parameter_configurations': [{'parameter_values': ['adListener', {'appKey': 'YOUR_APP_KEY', 'hasUserConsent': False}], 'conditions': ['The appKey must be retrieved from the Supersonic developer portal'], 'effects': ['enables GDPR data collection restrictions if hasUserConsent is false', 'If hasUserConsent is set to false, GDPR data collection restrictions will be enabled.']}, {'parameter_values': ['adListener', {'appKey': 'YOUR_APP_KEY', 'hasUserConsent': True}], 'conditions': ['The appKey must be retrieved from the Supersonic developer portal'], 'effects': ['If hasUserConsent is set to true, GDPR data collection restrictions will be disabled.', 'allows data collection unrestricted by GDPR']}, {'parameter_values': ['YOUR_APP_KEY', False], 'conditions': ['hasUserConsent is set to false', 'User has not provided consent under GDPR regulations'], 'effects': ['Enables GDPR data collection restrictions', 'Chartboost will enable GDPR data collection restrictions']}, {'parameter_values': ['YOUR_APP_KEY', True], 'conditions': ['hasUserConsent is set to true', 'User has provided consent under GDPR regulations'], 'effects': ['Chartboost will not enable GDPR data collection restrictions', 'Allows data collection without GDPR restrictions']}]}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
+          <t>https://docs.coronalabs.com/plugin/supersonic/init.html#supersonic.init</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tapjoy</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>optOutAdvertisingID</t>
+          <t>setExtraProperties</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOutAdvertisingID', 'class_name': ['Tapjoy'], 'conditions': ['User has elected to opt-out of allowing the app to access their advertising ID.'], 'effects': ['Sets a flag to prevent access to the advertising ID', "Indicates the user's choice to opt-out from using the advertising ID", 'Prevents the SDK from using the advertising ID for targeted advertising.', 'Opt-out of using the advertising ID for tracking', 'Opt-out the user from accessing the advertising ID'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User chooses to opt-out.', 'Application is targeting children'], 'effects': ['Disables the collection of the advertising ID.', 'User is opted out from accessing the advertising ID', 'Complies with Google Families Program rules', 'User opts out of advertising ID tracking']}, {'parameter_values': [False], 'conditions': ['User does not opt-out.'], 'effects': ['Enables the collection of the advertising ID.', 'User is not opted out from accessing the advertising ID', 'Allows access to the advertising ID', 'User does not opt out of advertising ID tracking']}, {'parameter_values': ['this', True], 'conditions': [], 'effects': ['Prevents the SDK from accessing the advertising ID']}, {'parameter_values': ['this', False], 'conditions': [], 'effects': ['Allows the SDK to access the advertising ID again']}]}</t>
+          <t>{'API_name': 'setExtraProperties', 'class_name': ['taboolaWidget'], 'conditions': ['User must be a CCPA subject to pass the Do Not Sell status', 'User must be a GDPR subject to pass the consent status', 'The end-user is subject to GDPR when passing the consent status', 'The end-user is subject to CCPA when passing the dns status'], 'effects': ['Passes the CCPA Do Not Sell status to the Taboola SDK for data handling', 'Sets the CCPA Do Not Sell status for users', 'Sets the GDPR consent status for users', 'Enables or disables the use of personal data based on user consent', "Passes the user's consent status to the Taboola SDK for data handling", 'Enables or disables the sale of personal data based on user consent'], 'parameter_configurations': [{'parameter_values': [{'cdns': 'false'}, {'cdns': 'true'}, {'cdns': 'none'}], 'conditions': ['The CCPA applies to the user'], 'effects': ["When cdns is false, Taboola can use the user's data as the user consented", "When cdns is true, Taboola must not use the user's data as the user did not consent", 'When cdns is none, CCPA does not apply and data usage is allowed']}, {'parameter_values': [{'cex': 'true'}, {'cex': 'false'}], 'conditions': ['The user is subject to GDPR', 'GDPR applies'], 'effects': ["When cex is false, Taboola must not use the user's data as the user did not provide consent", 'Indicates whether Taboola is allowed to process personal data based on user consent', "When cex is true, Taboola can use the user's data as the user provided consent"]}, {'parameter_values': [{'cdns': 'true'}, {'cdns': 'false'}, {'cdns': 'none'}], 'conditions': ['CCPA applies'], 'effects': ['Indicates whether Taboola is allowed to sell personal data or not, based on user consent']}]}</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
+          <t>https://developers.taboola.com/taboolasdk/v2/docs/android-sdk-gdpr;https://developers.taboola.com/taboolasdk/v2/docs/taboola-android-sdk-ccpa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TappX</t>
+          <t>Tapjoy</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>grantPersonalInfoConsent</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'API_name': 'grantPersonalInfoConsent', 'class_name': ['TappxPrivacyManager'], 'conditions': ['Consent must be requested before showing ads to the user', 'User consents to the use of their data', 'Must be called if the user consents to the use of their data', 'User has consented to the use of their data.'], 'effects': ['Grants consent for the use of personal data', 'Grants consent to collect personal information', 'Grants consent to use personal info of the user', 'Indicates that personal info consent has been granted.', "Grants permission to use the user's personal information for advertising"], 'parameter_configurations': [{'parameter_values': ['gdprConsentString'], 'conditions': ['User must have consented to the use of their data'], 'effects': []}, {'parameter_values': [], 'conditions': ['gdprConsentString must also be passed with the consent provided by the user'], 'effects': []}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': ['TJPrivacyPolicy'], 'conditions': ['Application has made its own determination as to whether GDPR is applicable to the user', 'The application has made its own determination regarding the applicability of GDPR', 'The application must make its own determination as to whether GDPR is applicable to the user.', 'The application has made its own determination as to whether GDPR is applicable to the user or not', 'Application must determine whether GDPR is applicable to the user'], 'effects': ['Sets the user consent status for data processing.', "Determines the user's consent status for data processing", "Sets the user's consent status for data processing", 'Sets user consent status for data processing', 'Sets the user consent status for data collection and processing'], 'parameter_configurations': [{'parameter_values': ['TJStatus.FALSE'], 'conditions': ['User does not consent to data processing.', 'User does not consent'], 'effects': ['Indicates that the user does not consent to data processing', "User's data will not be processed for interest-based advertising", 'Restricts the use of personal data for processing.', "User's data will not be processed based on consent"]}, {'parameter_values': ['TJStatus.TRUE'], 'conditions': ['User consents to data processing', 'User consents to data processing.', 'User consents'], 'effects': ['Allows for the use of personal data for processing.', "User's data can be processed based on consent", "User's data will be processed for interest-based advertising", 'Indicates that the user consents to data processing']}]}</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
+          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TappX</t>
+          <t>Tapjoy</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>denyPersonalInfoConsent</t>
+          <t>setSubjectToGDPR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'API_name': 'denyPersonalInfoConsent', 'class_name': ['TappxPrivacyManager'], 'conditions': ['Consent must be requested before showing ads to the user', 'Must be called if the user does NOT consent to use their data', 'User has not consented to the use of their data.', 'User does NOT consent to the use of their data'], 'effects': ['Denies consent to collect personal information', "Denies permission to use the user's personal information for advertising", 'Indicates that personal info consent has been denied.', 'Denies consent to use personal info of the user', 'Denies consent for the use of personal data'], 'parameter_configurations': [{'parameter_values': [], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['TJPrivacyPolicy'], 'conditions': ['Application has made its own determination as to whether GDPR is applicable to the user', 'The application must determine whether GDPR rules are applicable to the user.', 'The application has made its own determination as to whether GDPR is applicable to the user or not', 'Application must determine if GDPR rules apply to the user'], 'effects': ['Determines if the user is subject to GDPR rules', 'Specifies whether the user is subject to GDPR rules', 'Indicates whether the user is subject to GDPR', 'Indicates whether user data processing is subject to GDPR compliance.'], 'parameter_configurations': [{'parameter_values': ['TJStatus.TRUE'], 'conditions': ['User is determined to be subject to GDPR', 'User is subject to GDPR', 'User is determined to be subject to GDPR.', 'User is determined to be subject to GDPR rules'], 'effects': ["Enforces GDPR compliance for the user's data.", 'Tapjoy assumes GDPR rules apply to the user', "Tapjoy will handle the user's consent according to GDPR", 'Informs Tapjoy to treat the user as being subject to GDPR', 'Indicates that the user is subject to GDPR']}, {'parameter_values': ['TJStatus.FALSE'], 'conditions': ['User is determined to not be subject to GDPR rules', 'User is determined not to be subject to GDPR', 'User is not subject to GDPR', 'User is determined not to be subject to GDPR.'], 'effects': ['Informs Tapjoy to treat the user as not being subject to GDPR', 'No GDPR compliance enforcement required.', 'Indicates that the user is not subject to GDPR', 'Tapjoy assumes GDPR rules do not apply to the user', 'Tapjoy will assume user is not covered by GDPR']}]}</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
+          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TappX</t>
+          <t>Tapjoy</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>setCoppaCompliance</t>
+          <t>setBelowConsentAge</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCoppaCompliance', 'class_name': ['Tappx'], 'conditions': ['Content must be indicated as intended for children under 13', 'Must indicate whether the content of the app is intended for children under 13.', 'Application content is intended for children under 13 years of age', 'Set the child-specific content tag before starting the SDK integration', 'Must indicate whether app content targets children under 13'], 'effects': ['Activates advertising restrictions for child-targeted content', 'Activates or deactivates advertising restrictions according to COPPA regulations.', 'Enforces advertising restrictions based on the content targeting', 'Activates or deactivates advertising restrictions based on content intended for children under 13', 'Activates advertising restrictions according to COPPA guidelines'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Advertising restrictions are activated', 'Advertising restrictions are activated.', 'Activates advertising restrictions for children-targeted content']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Advertising restrictions are not activated', 'Deactivates advertising restrictions for children-targeted content', 'Advertising restrictions are not activated.']}]}</t>
+          <t>{'API_name': 'setBelowConsentAge', 'class_name': ['TJPrivacyPolicy'], 'conditions': [], 'effects': ['Indicates compliance with laws related to user age and consent', "Informs Tapjoy about the user's age with respect to legal compliance.", 'Informs whether the user is below the consent age for COPPA and other applicable laws', "Informs compliance regarding the user's age under COPPA or other regulations", "Informs Tapjoy of user's age related to consent requirements"], 'parameter_configurations': [{'parameter_values': ['TJStatus.TRUE'], 'conditions': [], 'effects': ['Indicates that the user is below the consent age', 'Indicates the user is below the consent age', 'Indicates user is below the consent age', 'Informs Tapjoy that this user is below the consent age for data processing.']}, {'parameter_values': ['TJStatus.FALSE'], 'conditions': [], 'effects': ['Indicates user is above the consent age', 'Indicates the user is above the consent age', 'Indicates that the user is above the consent age', 'Informs Tapjoy that this user is above the consent age for data processing.']}]}</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
+          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TappX</t>
+          <t>Tapjoy</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3609,34 +3609,34 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUSPrivacy', 'class_name': ['TappxPrivacyManager'], 'conditions': ['UserConsentString_Here must be a valid consent string from your CMP or tool to get the final user consent', 'User must provide a valid consent string from the CMP or tool', 'User must provide a valid consent string from a CMP or tool', 'User consent string must be a valid consent string from your CMP or tool.', 'Must provide a valid consent string from your CMP or tool to get the final user consent'], 'effects': ["Sets user's privacy preferences in accordance with US privacy regulations", 'Sets the US privacy consent status for data collection', 'Sets the US privacy status for the user based on the provided consent string.', 'Sets the US privacy status and allows the SDK to manage user data usage in compliance with US privacy laws', "Sets the user's privacy preferences regarding data usage in compliance with CCPA"], 'parameter_configurations': [{'parameter_values': ['User_Consent_String_Here'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'setUSPrivacy', 'class_name': ['TJPrivacyPolicy'], 'conditions': [], 'effects': ['Sets the US privacy status according to IAB’s US Privacy String Format', 'Sets the US Privacy flag for the user.', 'Sets the US privacy compliance status using the IAB’s US Privacy String Format', 'Sets the US privacy string status', "Sets the US privacy compliance status using IAB's US Privacy String Format"], 'parameter_configurations': [{'parameter_values': ['1YNN'], 'conditions': [], 'effects': ["Sets the user's privacy preferences according to IAB format", "Indicates the user's privacy preferences under US law", "Indicates the user's privacy status under US privacy regulations"]}, {'parameter_values': ['1YYY'], 'conditions': [], 'effects': ['Sets US privacy status based on the provided US Privacy String', "Indicates the user's privacy preferences in accordance with IAB's US Privacy String Format."]}]}</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
+          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TappX</t>
+          <t>Tapjoy</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>setGlobalPrivacyPlatform</t>
+          <t>optOutAdvertisingID</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGlobalPrivacyPlatform', 'class_name': ['TappxPrivacyManager'], 'conditions': ['UserConsentString_Here must be a valid consent string from your CMP or tool to get the final user consent', 'User must provide a valid consent string from the CMP or tool', 'User must provide a valid consent string from a CMP or tool', 'User consent string must be a valid consent string from your CMP or tool.', 'Must provide a valid consent string from a CMP or tool to get the final user consent'], 'effects': ["Sets the global privacy platform's consent status", 'Sets global privacy preferences for the user', 'Sets the global privacy platform consent status for the user.', "Links the user's consent to the Global Privacy Platform (GPP) requirements", 'Sets user privacy preferences in accordance with the Global Privacy Platform'], 'parameter_configurations': [{'parameter_values': ['User_Consent_String_Here'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'optOutAdvertisingID', 'class_name': ['Tapjoy'], 'conditions': ['User has elected to opt-out of allowing the app to access their advertising ID.'], 'effects': ['Sets a flag to prevent access to the advertising ID', "Indicates the user's choice to opt-out from using the advertising ID", 'Prevents the SDK from using the advertising ID for targeted advertising.', 'Opt-out of using the advertising ID for tracking', 'Opt-out the user from accessing the advertising ID'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User chooses to opt-out.', 'Application is targeting children'], 'effects': ['Disables the collection of the advertising ID.', 'User is opted out from accessing the advertising ID', 'Complies with Google Families Program rules', 'User opts out of advertising ID tracking']}, {'parameter_values': [False], 'conditions': ['User does not opt-out.'], 'effects': ['Enables the collection of the advertising ID.', 'User is not opted out from accessing the advertising ID', 'Allows access to the advertising ID', 'User does not opt out of advertising ID tracking']}, {'parameter_values': ['this', True], 'conditions': [], 'effects': ['Prevents the SDK from accessing the advertising ID']}, {'parameter_values': ['this', False], 'conditions': [], 'effects': ['Allows the SDK to access the advertising ID again']}]}</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
+          <t>https://dev.tapjoy.com/en/android-sdk/User-Privacy</t>
         </is>
       </c>
     </row>
@@ -3648,12 +3648,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>setGDPRConsent</t>
+          <t>grantPersonalInfoConsent</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGDPRConsent', 'class_name': ['TappxPrivacyManager'], 'conditions': ['User consent string (GDPR) must be passed when granted consent.', 'Must be called to set the GDPR consent string after the user has consented', 'gdprConsentString must be provided along with the grantPersonalInfoConsent call if consent is granted', 'User provides a valid GDPR consent string'], 'effects': ["Links the user's consent to the GDPR requirements", "Sets the user's consent string for GDPR compliance", 'Sets the GDPR consent status for the user based on the provided consent string.', 'Sets the GDPR consent status for data collection', 'Sets GDPR consent string for the user'], 'parameter_configurations': [{'parameter_values': ['gdprConsentString'], 'conditions': ['This should be called after granting consent.', 'Must call after obtaining user consent'], 'effects': []}, {'parameter_values': ['String'], 'conditions': ['Called only after user consent is obtained'], 'effects': []}]}</t>
+          <t>{'API_name': 'grantPersonalInfoConsent', 'class_name': ['TappxPrivacyManager'], 'conditions': ['Consent must be requested before showing ads to the user', 'User consents to the use of their data', 'Must be called if the user consents to the use of their data', 'User has consented to the use of their data.'], 'effects': ['Grants consent for the use of personal data', 'Grants consent to collect personal information', 'Grants consent to use personal info of the user', 'Indicates that personal info consent has been granted.', "Grants permission to use the user's personal information for advertising"], 'parameter_configurations': [{'parameter_values': ['gdprConsentString'], 'conditions': ['User must have consented to the use of their data'], 'effects': []}, {'parameter_values': [], 'conditions': ['gdprConsentString must also be passed with the consent provided by the user'], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3665,110 +3665,110 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tenjin</t>
+          <t>TappX</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>optIn</t>
+          <t>denyPersonalInfoConsent</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'API_name': 'optIn', 'class_name': ['TenjinSDK'], 'conditions': ['User has provided consent to track', 'User consent is required whether they allow tracking or not', 'User must give consent to allow tracking', 'User must consent to tracking', 'User must provide consent for tracking.'], 'effects': ['Enables event processing for the user who opted in', 'Allows tracking of events and processing of user data', 'Starts processing events for user who opted in', 'Enables tracking for the device/user.', "User's device is tracked for events"], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'denyPersonalInfoConsent', 'class_name': ['TappxPrivacyManager'], 'conditions': ['Consent must be requested before showing ads to the user', 'Must be called if the user does NOT consent to use their data', 'User has not consented to the use of their data.', 'User does NOT consent to the use of their data'], 'effects': ['Denies consent to collect personal information', "Denies permission to use the user's personal information for advertising", 'Indicates that personal info consent has been denied.', 'Denies consent to use personal info of the user', 'Denies consent for the use of personal data'], 'parameter_configurations': [{'parameter_values': [], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
+          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Tenjin</t>
+          <t>TappX</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>optOut</t>
+          <t>setCoppaCompliance</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOut', 'class_name': ['TenjinSDK'], 'conditions': ['User must not have given consent to tracking', 'User has opted out of tracking', 'User has chosen not to be tracked', 'User does not consent to tracking', 'User opts out of tracking.'], 'effects': ['Disables tracking of events and processing of user data', 'Will not send any API requests to Tenjin for events processing.', 'No API requests are sent to Tenjin, no tracking of events occurs', 'Stops processing events for user who opted out', 'Stops processing events for the user who opted out'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'setCoppaCompliance', 'class_name': ['Tappx'], 'conditions': ['Content must be indicated as intended for children under 13', 'Must indicate whether the content of the app is intended for children under 13.', 'Application content is intended for children under 13 years of age', 'Set the child-specific content tag before starting the SDK integration', 'Must indicate whether app content targets children under 13'], 'effects': ['Activates advertising restrictions for child-targeted content', 'Activates or deactivates advertising restrictions according to COPPA regulations.', 'Enforces advertising restrictions based on the content targeting', 'Activates or deactivates advertising restrictions based on content intended for children under 13', 'Activates advertising restrictions according to COPPA guidelines'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Advertising restrictions are activated', 'Advertising restrictions are activated.', 'Activates advertising restrictions for children-targeted content']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Advertising restrictions are not activated', 'Deactivates advertising restrictions for children-targeted content', 'Advertising restrictions are not activated.']}]}</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
+          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Tenjin</t>
+          <t>TappX</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>optInParams</t>
+          <t>setUSPrivacy</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'API_name': 'optInParams', 'class_name': ['TenjinSDK'], 'conditions': ['User must opt-in to specified device-related parameters', 'User must have opted in to begin the event processing', 'User must have opted in for parameters to be sent.'], 'effects': ['Only specified device-related parameters are sent to Tenjin', 'Sends only the specified device-related parameters', 'Only specified device-related parameters will be sent.', 'Only sends specified device-related parameters'], 'parameter_configurations': [{'parameter_values': [['ip_address', 'advertising_id', 'limit_ad_tracking', 'referrer']], 'conditions': [], 'effects': ['Only the specified parameters will be tracked and sent to Tenjin', 'Sends only the specified device-related parameters', 'Tracks only the specified device-related parameters', 'Enables sending specific device-related parameters.', 'Only these parameters will be sent for the opted-in user']}]}</t>
+          <t>{'API_name': 'setUSPrivacy', 'class_name': ['TappxPrivacyManager'], 'conditions': ['UserConsentString_Here must be a valid consent string from your CMP or tool to get the final user consent', 'User must provide a valid consent string from the CMP or tool', 'User must provide a valid consent string from a CMP or tool', 'User consent string must be a valid consent string from your CMP or tool.', 'Must provide a valid consent string from your CMP or tool to get the final user consent'], 'effects': ["Sets user's privacy preferences in accordance with US privacy regulations", 'Sets the US privacy consent status for data collection', 'Sets the US privacy status for the user based on the provided consent string.', 'Sets the US privacy status and allows the SDK to manage user data usage in compliance with US privacy laws', "Sets the user's privacy preferences regarding data usage in compliance with CCPA"], 'parameter_configurations': [{'parameter_values': ['User_Consent_String_Here'], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
+          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Tenjin</t>
+          <t>TappX</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>optOutParams</t>
+          <t>setGlobalPrivacyPlatform</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOutParams', 'class_name': ['TenjinSDK'], 'conditions': ['User must opt-out of specified device-related parameters', 'User must have opted out of certain parameters.', 'User must have opted out to exclude specific parameters'], 'effects': ['Sends all device-related parameters except those specified', 'Sends all device-related parameters excluding specified ones', 'Will send all device-related parameters except those specified.', 'All parameters except specified ones are sent to Tenjin'], 'parameter_configurations': [{'parameter_values': [['locale', 'timezone', 'build_id']], 'conditions': [], 'effects': ['Does not send specified parameters while sending all others', 'All parameters except the specified ones will be sent', 'Excludes specified parameters from being sent.', 'Tracks all parameters except the specified exclusions', 'All device-related parameters will be sent except the specified ones']}]}</t>
+          <t>{'API_name': 'setGlobalPrivacyPlatform', 'class_name': ['TappxPrivacyManager'], 'conditions': ['UserConsentString_Here must be a valid consent string from your CMP or tool to get the final user consent', 'User must provide a valid consent string from the CMP or tool', 'User must provide a valid consent string from a CMP or tool', 'User consent string must be a valid consent string from your CMP or tool.', 'Must provide a valid consent string from a CMP or tool to get the final user consent'], 'effects': ["Sets the global privacy platform's consent status", 'Sets global privacy preferences for the user', 'Sets the global privacy platform consent status for the user.', "Links the user's consent to the Global Privacy Platform (GPP) requirements", 'Sets user privacy preferences in accordance with the Global Privacy Platform'], 'parameter_configurations': [{'parameter_values': ['User_Consent_String_Here'], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
+          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Tenjin</t>
+          <t>TappX</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>setGoogleDMAParameters</t>
+          <t>setGDPRConsent</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGoogleDMAParameters', 'class_name': ['TenjinSDK'], 'conditions': ['Must manage Google DMA parameters either manually or through a CMP.'], 'effects': ['Sets personalization and user data collection parameters for advertising', 'Manages the collection of Google DMA parameters based on user preferences', 'Allows collection of DMA parameters with respect to user consent', 'Allows explicit management of Google DMA parameters.', 'Manages the collection of Google DMA parameters'], 'parameter_configurations': [{'parameter_values': [True, True], 'conditions': [], 'effects': ['User data will be collected for ad personalization and user data', 'Sets the parameters to opt in for ad personalization and ad user data.']}, {'parameter_values': [False, False], 'conditions': [], 'effects': ['No user data will be collected for ad personalization and user data']}, {'parameter_values': [True, False], 'conditions': [], 'effects': ['Explicitly opts in or opts out of Google DMA parameter collection', 'Adjusts Google DMA parameter collection settings based on provided inputs']}, {'parameter_values': [[True, True]], 'conditions': [], 'effects': ['Enables data personalization and user data collection']}, {'parameter_values': [[False, False]], 'conditions': [], 'effects': ['Disables data personalization and user data collection']}]}</t>
+          <t>{'API_name': 'setGDPRConsent', 'class_name': ['TappxPrivacyManager'], 'conditions': ['User consent string (GDPR) must be passed when granted consent.', 'Must be called to set the GDPR consent string after the user has consented', 'gdprConsentString must be provided along with the grantPersonalInfoConsent call if consent is granted', 'User provides a valid GDPR consent string'], 'effects': ["Links the user's consent to the GDPR requirements", "Sets the user's consent string for GDPR compliance", 'Sets the GDPR consent status for the user based on the provided consent string.', 'Sets the GDPR consent status for data collection', 'Sets GDPR consent string for the user'], 'parameter_configurations': [{'parameter_values': ['gdprConsentString'], 'conditions': ['This should be called after granting consent.', 'Must call after obtaining user consent'], 'effects': []}, {'parameter_values': ['String'], 'conditions': ['Called only after user consent is obtained'], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
+          <t>https://developers.tappx.com/en/android/sdk-tappx-android-gdpr-eu/1_manual_dev_android/;https://developers.tappx.com/en/android/sdk-tappx-android-gpp/1_manual_dev_android_gpp/;https://developers.tappx.com/en/android/sdk-tappx-android-ccpa/01_CCPA_Android_And_Manual/;https://developers.tappx.com/en/android/COPPA/</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>optInGoogleDMA</t>
+          <t>optIn</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'API_name': 'optInGoogleDMA', 'class_name': ['TenjinSDK'], 'conditions': [], 'effects': ['Opted in to Google DMA parameters collection', 'Opt-ins to the collection of Google DMA parameters'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'optIn', 'class_name': ['TenjinSDK'], 'conditions': ['User has provided consent to track', 'User consent is required whether they allow tracking or not', 'User must give consent to allow tracking', 'User must consent to tracking', 'User must provide consent for tracking.'], 'effects': ['Enables event processing for the user who opted in', 'Allows tracking of events and processing of user data', 'Starts processing events for user who opted in', 'Enables tracking for the device/user.', "User's device is tracked for events"], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>optOutGoogleDMA</t>
+          <t>optOut</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOutGoogleDMA', 'class_name': ['TenjinSDK'], 'conditions': [], 'effects': ['Opted out of Google DMA parameters collection', 'Opt-outs from the collection of Google DMA parameters'], 'parameter_configurations': []}</t>
+          <t>{'API_name': 'optOut', 'class_name': ['TenjinSDK'], 'conditions': ['User must not have given consent to tracking', 'User has opted out of tracking', 'User has chosen not to be tracked', 'User does not consent to tracking', 'User opts out of tracking.'], 'effects': ['Disables tracking of events and processing of user data', 'Will not send any API requests to Tenjin for events processing.', 'No API requests are sent to Tenjin, no tracking of events occurs', 'Stops processing events for user who opted out', 'Stops processing events for the user who opted out'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3819,1516 +3819,1780 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Unity Ads</t>
+          <t>Tenjin</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SetMetaData</t>
+          <t>checkOptInValue</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'API_name': 'SetMetaData', 'class_name': ['Advertisement', 'MetaData'], 'conditions': ['The user must express consent for targeted advertising.'], 'effects': ['Allows the developer to set user-specific metadata related to privacy preferences such as consent for targeted advertising.', 'Allows the passing of consent flags for data privacy laws compliance.'], 'parameter_configurations': [{'parameter_values': ['user.nonbehavioral', 'true'], 'conditions': ['If the user opts out of personalized ads.', 'User opts out of personalized ads.'], 'effects': ['User will not receive personalized ads.', 'User cannot receive personalized ads.']}, {'parameter_values': ['user.nonbehavioral', 'false'], 'conditions': ['If the user opts in to personalized ads.', 'User opts into personalized ads.'], 'effects': ['User will receive personalized ads.', 'User can receive personalized ads.']}, {'parameter_values': ['pipl.consent', 'true'], 'conditions': ['User opts into sending their personal identifiable information outside of China.', 'User opts in to sending their personal identifiable information outside of China.'], 'effects': ["Allows sending user's personal identifiable information as per PIPL compliance.", 'User consent is recorded for sending personal data.']}, {'parameter_values': ['gdpr.consent', 'true'], 'conditions': ['User opts in to targeted advertising under GDPR compliance.', 'User opts into targeted advertising under GDPR.'], 'effects': ['User consents to receiving targeted advertisements.', 'User consent is recorded for targeted advertising.']}, {'parameter_values': ['privacy.consent', 'true'], 'conditions': ['User opts in to targeted advertising under various consumer privacy acts.'], 'effects': ['User agrees to receive personalized ads under specified consumer privacy acts.']}, {'parameter_values': ['gdpr.consent', 'false'], 'conditions': ['User opts out of targeted advertising under GDPR.'], 'effects': ['User consent is recorded against targeted advertising.']}, {'parameter_values': ['pipl.consent', 'false'], 'conditions': ['User opts out of sending their personal identifiable information outside of China.'], 'effects': ['User consent is recorded against sending personal data.']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://docs.unity.com/ads/en-us/manual/COPPACompliance;https://docs.unity.com/ads/en-us/manual/PIPLCompliance;https://docs.unity.com/ads/en-us/manual/GDPRCompliance;https://docs.unity.com/ads/en-us/manual/CCPACompliance;https://docs.unity.com/ads/en-us/manual/GoogleFamiliesCompliance;https://docs.unity.com/ads/en-us/manual/ImplementingCustomAgeGates;https://docs.unity.com/ads/en-us/manual/GoogleDataSafety;https://docs.unity.com/ads/en-us/manual/ApplePrivacySurvey</t>
+          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Visual Studio App Center</t>
+          <t>Tenjin</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>setEnabled</t>
+          <t>optInParams</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'API_name': 'setEnabled', 'class_name': ['AppCenter'], 'conditions': ['Must be called after AppCenter has been started'], 'effects': ['Enables or disables all App Center services'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': [], 'effects': ["SDK won't forward any information to App Center"]}, {'parameter_values': [True], 'conditions': [], 'effects': ['Enables all App Center services again', 'Re-enables all App Center services']}]}</t>
+          <t>{'API_name': 'optInParams', 'class_name': ['TenjinSDK'], 'conditions': ['User must opt-in to specified device-related parameters', 'User must have opted in to begin the event processing', 'User must have opted in for parameters to be sent.'], 'effects': ['Only specified device-related parameters are sent to Tenjin', 'Sends only the specified device-related parameters', 'Only specified device-related parameters will be sent.', 'Only sends specified device-related parameters'], 'parameter_configurations': [{'parameter_values': [['ip_address', 'advertising_id', 'limit_ad_tracking', 'referrer']], 'conditions': [], 'effects': ['Only the specified parameters will be tracked and sent to Tenjin', 'Sends only the specified device-related parameters', 'Tracks only the specified device-related parameters', 'Enables sending specific device-related parameters.', 'Only these parameters will be sent for the opted-in user']}]}</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/appcenter/sdk/crashes/android#ask-for-the-users-consent-to-send-a-crash-log;https://learn.microsoft.com/en-us/appcenter/sdk/analytics/android#enable-or-disable-app-center-analytics-at-runtime;https://learn.microsoft.com/en-us/appcenter/sdk/other-apis/android</t>
+          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Visual Studio App Center</t>
+          <t>Tenjin</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>setNetworkRequestsAllowed</t>
+          <t>optOutParams</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'API_name': 'setNetworkRequestsAllowed', 'class_name': ['AppCenter'], 'conditions': ['Must be called after AppCenter has been started'], 'effects': ['Disallows automatic sending of data collected by the App Center SDK', 'Allows or disallows automatic sending of collected data'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': [], 'effects': ['Collects data but sends it only when network requests are allowed', 'Continues to collect data but sends it only when network requests are allowed']}, {'parameter_values': [True], 'conditions': [], 'effects': ['Allows the App Center SDK to send data automatically', 'Allows immediate sending of collected data']}]}</t>
+          <t>{'API_name': 'optOutParams', 'class_name': ['TenjinSDK'], 'conditions': ['User must opt-out of specified device-related parameters', 'User must have opted out of certain parameters.', 'User must have opted out to exclude specific parameters'], 'effects': ['Sends all device-related parameters except those specified', 'Sends all device-related parameters excluding specified ones', 'Will send all device-related parameters except those specified.', 'All parameters except specified ones are sent to Tenjin'], 'parameter_configurations': [{'parameter_values': [['locale', 'timezone', 'build_id']], 'conditions': [], 'effects': ['Does not send specified parameters while sending all others', 'All parameters except the specified ones will be sent', 'Excludes specified parameters from being sent.', 'Tracks all parameters except the specified exclusions', 'All device-related parameters will be sent except the specified ones']}]}</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/appcenter/sdk/crashes/android#ask-for-the-users-consent-to-send-a-crash-log;https://learn.microsoft.com/en-us/appcenter/sdk/analytics/android#enable-or-disable-app-center-analytics-at-runtime;https://learn.microsoft.com/en-us/appcenter/sdk/other-apis/android</t>
+          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Visual Studio App Center</t>
+          <t>Tenjin</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>notifyUserConfirmation</t>
+          <t>setGoogleDMAParameters</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'API_name': 'notifyUserConfirmation', 'class_name': ['Crashes'], 'conditions': [], 'effects': ["Notifies the SDK of the user's decision regarding crash report submission"], 'parameter_configurations': [{'parameter_values': ['Crashes.DONT_SEND'], 'conditions': [], 'effects': []}, {'parameter_values': ['Crashes.SEND'], 'conditions': [], 'effects': []}, {'parameter_values': ['Crashes.ALWAYS_SEND'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'setGoogleDMAParameters', 'class_name': ['TenjinSDK'], 'conditions': ['Must manage Google DMA parameters either manually or through a CMP.'], 'effects': ['Sets personalization and user data collection parameters for advertising', 'Manages the collection of Google DMA parameters based on user preferences', 'Allows collection of DMA parameters with respect to user consent', 'Allows explicit management of Google DMA parameters.', 'Manages the collection of Google DMA parameters'], 'parameter_configurations': [{'parameter_values': [True, True], 'conditions': [], 'effects': ['User data will be collected for ad personalization and user data', 'Sets the parameters to opt in for ad personalization and ad user data.']}, {'parameter_values': [False, False], 'conditions': [], 'effects': ['No user data will be collected for ad personalization and user data']}, {'parameter_values': [True, False], 'conditions': [], 'effects': ['Explicitly opts in or opts out of Google DMA parameter collection', 'Adjusts Google DMA parameter collection settings based on provided inputs']}, {'parameter_values': [[True, True]], 'conditions': [], 'effects': ['Enables data personalization and user data collection']}, {'parameter_values': [[False, False]], 'conditions': [], 'effects': ['Disables data personalization and user data collection']}]}</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/appcenter/sdk/crashes/android#ask-for-the-users-consent-to-send-a-crash-log;https://learn.microsoft.com/en-us/appcenter/sdk/analytics/android#enable-or-disable-app-center-analytics-at-runtime;https://learn.microsoft.com/en-us/appcenter/sdk/other-apis/android</t>
+          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Vpon</t>
+          <t>Tenjin</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>setLocation</t>
+          <t>optInGoogleDMA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLocation', 'class_name': ['VponAdRequest.Builder'], 'conditions': ["User's location is available", "User's location information is available"], 'effects': ["Sets the user's location for geographical ad targeting", "Sets the user's location for ad targeting", "Enables Vpon to deliver ads tailored to the user's location", 'Allows Vpon to deliver location-targeted ads', "Sets the user's location if available"], 'parameter_configurations': [{'parameter_values': ['Location'], 'conditions': ['User consent is obtained for collecting location data'], 'effects': ["User's location will be used for ad targeting"]}]}</t>
+          <t>{'API_name': 'optInGoogleDMA', 'class_name': ['TenjinSDK'], 'conditions': [], 'effects': ['Opted in to Google DMA parameters collection', 'Opt-ins to the collection of Google DMA parameters'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://wiki.vpon.com/android/custom-request-params/</t>
+          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Vpon</t>
+          <t>Tenjin</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>setTagForUnderAgeOfConsent</t>
+          <t>optOutGoogleDMA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'API_name': 'setTagForUnderAgeOfConsent', 'class_name': ['VponAdRequest.Builder'], 'conditions': [], 'effects': ['Sets whether ads will be displayed only to specific ages of audience', 'Sets if the ads will be displayed only to a specific age group', 'Specifies whether ads should be shown only to users above a certain age', 'Sets whether ads will be displayed only to a specific age audience'], 'parameter_configurations': [{'parameter_values': [-1], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'optOutGoogleDMA', 'class_name': ['TenjinSDK'], 'conditions': [], 'effects': ['Opted out of Google DMA parameters collection', 'Opt-outs from the collection of Google DMA parameters'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://wiki.vpon.com/android/custom-request-params/</t>
+          <t>https://docs.tenjin.com/docs/android-sdk#gdpr</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Vpon</t>
+          <t>Umeng</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>tagForChildDirectedTreatment</t>
+          <t>set</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'API_name': 'tagForChildDirectedTreatment', 'class_name': ['VponAdRequest.Builder'], 'conditions': [], 'effects': ['Sets ads to be directed towards children if applicable', 'Indicates if the ads will be specifically directed to children', 'Sets whether ads will be displayed to children specifically', 'Sets if the ads will be displayed specifically to children'], 'parameter_configurations': [{'parameter_values': [-1], 'conditions': [], 'effects': ['Children-specific ads will be displayed if set appropriately']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://wiki.vpon.com/android/custom-request-params/</t>
+          <t>https://developer.umeng.com/docs/119267/detail/118637</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Vpon</t>
+          <t>Unity Ads</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>setMaxAdContentRating</t>
+          <t>SetMetaData</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'API_name': 'setMaxAdContentRating', 'class_name': ['VponAdRequest.Builder'], 'conditions': [], 'effects': ['Sets the maximum content rating filter', 'Sets the maximum content rating filter for ads', 'Sets the maximum content rating for delivered ads', 'Sets the maximum content rating for the ads', 'Filters ads based on the content rating set by the user'], 'parameter_configurations': [{'parameter_values': ['String'], 'conditions': [], 'effects': ['Ads will be filtered based on the specified content rating']}]}</t>
+          <t>{'API_name': 'SetMetaData', 'class_name': ['Advertisement', 'MetaData'], 'conditions': ['The user must express consent for targeted advertising.'], 'effects': ['Allows the developer to set user-specific metadata related to privacy preferences such as consent for targeted advertising.', 'Allows the passing of consent flags for data privacy laws compliance.'], 'parameter_configurations': [{'parameter_values': ['user.nonbehavioral', 'true'], 'conditions': ['If the user opts out of personalized ads.', 'User opts out of personalized ads.'], 'effects': ['User will not receive personalized ads.', 'User cannot receive personalized ads.']}, {'parameter_values': ['user.nonbehavioral', 'false'], 'conditions': ['If the user opts in to personalized ads.', 'User opts into personalized ads.'], 'effects': ['User will receive personalized ads.', 'User can receive personalized ads.']}, {'parameter_values': ['pipl.consent', 'true'], 'conditions': ['User opts into sending their personal identifiable information outside of China.', 'User opts in to sending their personal identifiable information outside of China.'], 'effects': ["Allows sending user's personal identifiable information as per PIPL compliance.", 'User consent is recorded for sending personal data.']}, {'parameter_values': ['gdpr.consent', 'true'], 'conditions': ['User opts in to targeted advertising under GDPR compliance.', 'User opts into targeted advertising under GDPR.'], 'effects': ['User consents to receiving targeted advertisements.', 'User consent is recorded for targeted advertising.']}, {'parameter_values': ['privacy.consent', 'true'], 'conditions': ['User opts in to targeted advertising under various consumer privacy acts.'], 'effects': ['User agrees to receive personalized ads under specified consumer privacy acts.']}, {'parameter_values': ['gdpr.consent', 'false'], 'conditions': ['User opts out of targeted advertising under GDPR.'], 'effects': ['User consent is recorded against targeted advertising.']}, {'parameter_values': ['pipl.consent', 'false'], 'conditions': ['User opts out of sending their personal identifiable information outside of China.'], 'effects': ['User consent is recorded against sending personal data.']}]}</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://wiki.vpon.com/android/custom-request-params/</t>
+          <t>https://docs.unity.com/ads/en-us/manual/COPPACompliance;https://docs.unity.com/ads/en-us/manual/PIPLCompliance;https://docs.unity.com/ads/en-us/manual/GDPRCompliance;https://docs.unity.com/ads/en-us/manual/CCPACompliance;https://docs.unity.com/ads/en-us/manual/GoogleFamiliesCompliance;https://docs.unity.com/ads/en-us/manual/ImplementingCustomAgeGates;https://docs.unity.com/ads/en-us/manual/GoogleDataSafety;https://docs.unity.com/ads/en-us/manual/ApplePrivacySurvey</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Vungle(liftoff)</t>
+          <t>Visual Studio App Center</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>setGDPRStatus</t>
+          <t>setEnabled</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGDPRStatus', 'class_name': ['VunglePrivacySettings'], 'conditions': ['User consent status indicates whether user has opted in or opted out.', "User consent is collected using the publisher's mechanism or Vungle's consent dialog must be used for European users.", 'Consent message version must be provided', 'User must provide consent for data processing under GDPR regulations', 'The publisher controls the GDPR consent process', 'Publisher controls the GDPR consent process at the user level'], 'effects': ['Indicates whether the user has opted in or out of data processing under GDPR', 'Specifies whether the user has opted in or opted out for GDPR compliance', "Sets the user's consent status for GDPR compliance", "Sets the user's GDPR consent status to opted in or opted out.", "Specifies the user's consent status for GDPR compliance."], 'parameter_configurations': [{'parameter_values': [True, '1.0.0'], 'conditions': ['User opts in for GDPR.', 'User opts in for data processing', 'User has opted in for data processing'], 'effects': ['User consent status set to opted in.', 'User is considered opted in for GDPR.', 'User consent status registered as opted in', "User's consent status is set to opted in"]}, {'parameter_values': [False, '1.0.0'], 'conditions': ['User opts out of GDPR.', 'User has opted out of data processing', 'User opts out of data processing'], 'effects': ['User consent status set to opted out.', 'User consent status registered as opted out', 'User is considered opted out for GDPR.', "User's consent status is set to opted out"]}]}</t>
+          <t>{'API_name': 'setEnabled', 'class_name': ['AppCenter'], 'conditions': ['Must be called after AppCenter has been started'], 'effects': ['Enables or disables all App Center services'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': [], 'effects': ["SDK won't forward any information to App Center"]}, {'parameter_values': [True], 'conditions': [], 'effects': ['Enables all App Center services again', 'Re-enables all App Center services']}]}</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
+          <t>https://learn.microsoft.com/en-us/appcenter/sdk/crashes/android#ask-for-the-users-consent-to-send-a-crash-log;https://learn.microsoft.com/en-us/appcenter/sdk/analytics/android#enable-or-disable-app-center-analytics-at-runtime;https://learn.microsoft.com/en-us/appcenter/sdk/other-apis/android</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Vungle(liftoff)</t>
+          <t>Visual Studio App Center</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>setCOPPAStatus</t>
+          <t>setNetworkRequestsAllowed</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCOPPAStatus', 'class_name': ['VunglePrivacySettings'], 'conditions': ['Must comply with COPPA regulations', 'Used to indicate that a user is under or over age 13 in compliance with COPPA regulations.', 'App must comply with COPPA regulations', 'Must indicate if app is directed toward children under age 13', 'Called before initializing the Vungle SDK', "User's age is known."], 'effects': ["Updates the user's COPPA compliance status", 'Indicates whether a user is under age 13 and protected by COPPA regulations', "Provides Vungle with the user's COPPA status to ensure proper compliance with COPPA for targeted ads.", "Updates Vungle regarding the user's COPPA status.", 'Indicates whether the user is under COPPA protection'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under the age of 13', 'User is confirmed to be under age 13', 'User is under the age of 13.'], 'effects': ['Indicates the user is under age 13 and thus protected under COPPA.', 'User is treated as falling under COPPA regulations', 'User is treated as under COPPA regulations.', 'User is treated as under age 13', 'Treat user as under COPPA regulations']}, {'parameter_values': [False], 'conditions': ['User is 13 years of age or older', 'User is over the age of 13.', 'User is known to be over age 13'], 'effects': ['Indicates the user is over age 13 and not protected under COPPA.', 'User is treated as not under COPPA regulations.', 'User is treated as over age 13', 'User is not treated as falling under COPPA regulations', 'Does not treat user as under COPPA regulations']}]}</t>
+          <t>{'API_name': 'setNetworkRequestsAllowed', 'class_name': ['AppCenter'], 'conditions': ['Must be called after AppCenter has been started'], 'effects': ['Disallows automatic sending of data collected by the App Center SDK', 'Allows or disallows automatic sending of collected data'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': [], 'effects': ['Collects data but sends it only when network requests are allowed', 'Continues to collect data but sends it only when network requests are allowed']}, {'parameter_values': [True], 'conditions': [], 'effects': ['Allows the App Center SDK to send data automatically', 'Allows immediate sending of collected data']}]}</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
+          <t>https://learn.microsoft.com/en-us/appcenter/sdk/crashes/android#ask-for-the-users-consent-to-send-a-crash-log;https://learn.microsoft.com/en-us/appcenter/sdk/analytics/android#enable-or-disable-app-center-analytics-at-runtime;https://learn.microsoft.com/en-us/appcenter/sdk/other-apis/android</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Vungle(liftoff)</t>
+          <t>Visual Studio App Center</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>setCCPAStatus</t>
+          <t>notifyUserConfirmation</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCCPAStatus', 'class_name': ['VunglePrivacySettings'], 'conditions': ['Must update to SDK 6.7.0 or higher to comply with CCPA', 'Must have been updated to Android SDK 6.7.0 or higher to comply with CCPA.', 'Must update to Android SDK 6.7.0 to comply with CCPA', 'User consent status indicates whether user has opted in or opted out for CCPA.', 'User must provide consent for data processing under CCPA regulations'], 'effects': ['Specifies whether the user has opted in or opted out for CCPA compliance', "Sets the user's consent status for CCPA compliance", "Specifies the user's consent status for CCPA compliance.", "Sets the user's CCPA consent status to opted in or opted out.", 'Indicates whether the user has opted in or out under CCPA'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts in for CCPA.', 'User has opted in for data processing', 'User opts in to data processing'], 'effects': ['User status set to opted in for CCPA.', "User's CCPA status is set to opted in", 'User consent status set to opted in.', 'User consent status registered as opted in']}, {'parameter_values': [False], 'conditions': ['User has opted out of data processing', 'User opts out of CCPA.', 'User opts out of data processing'], 'effects': ['User consent status set to opted out.', 'User consent status registered as opted out', "User's CCPA status is set to opted out", 'User status set to opted out for CCPA.']}]}</t>
+          <t>{'API_name': 'notifyUserConfirmation', 'class_name': ['Crashes'], 'conditions': [], 'effects': ["Notifies the SDK of the user's decision regarding crash report submission"], 'parameter_configurations': [{'parameter_values': ['Crashes.DONT_SEND'], 'conditions': [], 'effects': []}, {'parameter_values': ['Crashes.SEND'], 'conditions': [], 'effects': []}, {'parameter_values': ['Crashes.ALWAYS_SEND'], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
+          <t>https://learn.microsoft.com/en-us/appcenter/sdk/crashes/android#ask-for-the-users-consent-to-send-a-crash-log;https://learn.microsoft.com/en-us/appcenter/sdk/analytics/android#enable-or-disable-app-center-analytics-at-runtime;https://learn.microsoft.com/en-us/appcenter/sdk/other-apis/android</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Vungle(liftoff)</t>
+          <t>Vpon</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>setPublishAndroidId</t>
+          <t>setLocation</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPublishAndroidId', 'class_name': ['VunglePrivacySettings'], 'conditions': ['Android SDK version is 6.4.11 or higher', 'User must opt in to Android ID collection', 'User must consent to the use of Android ID for advertisement targeting.', 'Must be called prior to initializing the SDK.'], 'effects': ['Determines whether the SDK will collect the Android ID.', 'Controls whether Android ID is collected.', 'Controls the publication of the Android ID', 'Controls whether Android ID is collected or not', 'Determines whether to collect the Android ID when Google Advertising ID is not available'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts in to Android ID collection.', 'Default opt-in for Android ID collection'], 'effects': ['Opt-in for the collection of Android ID', 'SDK will collect and publish the Android ID', 'Android ID can be collected by SDK', 'Opt in for Android ID collection.', 'Android ID will be collected.']}, {'parameter_values': [False], 'conditions': ['User opts out of Android ID collection', 'User opts out of Android ID collection.'], 'effects': ['SDK will not collect or publish the Android ID', 'Opt out for Android ID collection.', 'Android ID will not be collected.', 'Opt-out for the collection of Android ID', 'Android ID will not be collected by SDK']}]}</t>
+          <t>{'API_name': 'setLocation', 'class_name': ['VponAdRequest.Builder'], 'conditions': ["User's location is available", "User's location information is available"], 'effects': ["Sets the user's location for geographical ad targeting", "Sets the user's location for ad targeting", "Enables Vpon to deliver ads tailored to the user's location", 'Allows Vpon to deliver location-targeted ads', "Sets the user's location if available"], 'parameter_configurations': [{'parameter_values': ['Location'], 'conditions': ['User consent is obtained for collecting location data'], 'effects': ["User's location will be used for ad targeting"]}]}</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
+          <t>https://wiki.vpon.com/android/custom-request-params/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Yandex Metrica</t>
+          <t>Vpon</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>setAgeRestrictedUser</t>
+          <t>setTagForUnderAgeOfConsent</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAgeRestrictedUser', 'class_name': [''], 'conditions': ['Required to comply with COPPA', 'For children under the age of 13, data collection needs to be restricted.', 'Required to comply with COPPA for users under the age of 13.', "Data about the user's age must be transmitted to the SDK every time the application starts."], 'effects': ['Enables the restriction of the collection of information from children under the age of 13.', 'Restricts the collection of information from children under the age of 13.', 'Enables restriction of information collection from children under the age of 13.', 'Restricts collection of information from children under the age of 13.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under the age of 13', 'The user is under the age of 13.', 'The user is identified as under the age of 13.', 'The user is a child under the age of 13.'], 'effects': ['Prevents personal data collection from the user.', 'Prohibits the collection of personal information from the user.', 'Restrict collection of information from users under 13', 'Prevents the SDK from collecting personal information from the user.', 'Restricts data collection in accordance with COPPA.']}, {'parameter_values': [False], 'conditions': ['The user is age 13 or older.', 'User is 13 years or older', 'The user is identified as 13 years or older.', 'The user is 13 years of age or older.', 'User is 13 years of age or older'], 'effects': ['Allow collection of information from users 13 years or older', 'Allows normal data collection as per usual SDK functionality.', 'Allows normal data collection from the user.', 'Data collection is allowed.', 'Allows the collection of personal information from the user.']}]}</t>
+          <t>{'API_name': 'setTagForUnderAgeOfConsent', 'class_name': ['VponAdRequest.Builder'], 'conditions': [], 'effects': ['Sets whether ads will be displayed only to specific ages of audience', 'Sets if the ads will be displayed only to a specific age group', 'Specifies whether ads should be shown only to users above a certain age', 'Sets whether ads will be displayed only to a specific age audience'], 'parameter_configurations': [{'parameter_values': [-1], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://ads.yandex.com/helpcenter/en/dev/android/gdpr;https://ads.yandex.com/helpcenter/en/dev/android/coppa;https://ads.yandex.com/helpcenter/en/dev/android/context-data</t>
+          <t>https://wiki.vpon.com/android/custom-request-params/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Yandex Metrica</t>
+          <t>Vpon</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>tagForChildDirectedTreatment</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': [''], 'conditions': ["User's consent for processing personal data must be sent to the SDK each time the application is launched.", 'Required to comply with GDPR.', "User's consent for processing personal data must be sent to the SDK each time the application launches.", 'Required to comply with GDPR', "The user's consent for processing personal data must be sent to the SDK each time the application is launched.", 'This is necessary to comply with GDPR regulations.'], 'effects': ['Determines if user data from GDPR regions will be processed based on consent.', 'Data of users located in the GDPR region will be processed only if the user consents to data processing.', 'User data will be processed only if the user consents to data processing.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User gives consent for personal data processing.', 'User accepts the user agreement for personal data processing', 'User accepts the user agreement for personal data processing.', 'User agrees to the user agreement for personal data processing.', 'User accepts the data processing user agreement.'], 'effects': ["Allows processing of the user's personal data.", 'User data will be processed', 'Allows processing of personal data for users in the GDPR region.', "Enables processing of the user's personal data.", "Permits the processing of the user's personal data."]}, {'parameter_values': [False], 'conditions': ['User declines the user agreement for personal data processing', 'User declines the data processing user agreement.', 'User declines the user agreement for personal data processing.', 'User declines the user agreement.', 'User does not give consent for personal data processing.'], 'effects': ['User data will not be processed', "Prohibits the processing of the user's personal data.", "Prevents processing of the user's personal data.", "Disables processing of the user's personal data.", 'Prevents processing of personal data for users in the GDPR region.']}]}</t>
+          <t>{'API_name': 'tagForChildDirectedTreatment', 'class_name': ['VponAdRequest.Builder'], 'conditions': [], 'effects': ['Sets ads to be directed towards children if applicable', 'Indicates if the ads will be specifically directed to children', 'Sets whether ads will be displayed to children specifically', 'Sets if the ads will be displayed specifically to children'], 'parameter_configurations': [{'parameter_values': [-1], 'conditions': [], 'effects': ['Children-specific ads will be displayed if set appropriately']}]}</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://ads.yandex.com/helpcenter/en/dev/android/gdpr;https://ads.yandex.com/helpcenter/en/dev/android/coppa;https://ads.yandex.com/helpcenter/en/dev/android/context-data</t>
+          <t>https://wiki.vpon.com/android/custom-request-params/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>YouAppi</t>
+          <t>Vpon</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>setMaxAdContentRating</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'API_name': 'init', 'class_name': ['YouAPPi'], 'conditions': ['DOES_GDPR_APPLY should reflect if the user is subject to GDPR (e.g., EU resident)', "USER_CONSENT must be determined by the app developer according to the User's response to a Consent Request.", 'DOES_GDPR_APPLY is set according to if the user is subject to GDPR rules', 'USER_CONSENT indicates whether user consent is given', "USER_CONSENT is determined by the user's response to a Consent Request", "Requires USER_CONSENT based on user's response to a dialog asking for permission", 'USER_CONSENT should be set to user’s response to a consent request', 'DOES_GDPR_APPLY should be set based on whether the user is an EU residence', "DOES_GDPR_APPLY must be set according to the user's residency status", 'DOES_GDPR_APPLY determines if the GDPR rules apply to the user'], 'effects': ['Initializes the YouAppi SDK and allows it to process and store the user’s Personal Information if conditions are met', 'Initializes YouAppi SDK with app token and user consent information', 'Initializes YouAppi SDK with user consent and compliance with GDPR regulations', "Initializes YouAppi SDK and allows processing and storage of user's Personal Information", 'Initializes YouAppi SDK with user consent and compliance with GDPR.', "Allows processing and storage of user's personal information if consent is granted", 'Enables the SDK to access user private information, such as Advertising ID and IP address'], 'parameter_configurations': [{'parameter_values': ['context', '&lt;YOUR_APP_TOKEN&gt;', True, False], 'conditions': ['User is not subject to GDPR.'], 'effects': ['SDK is initialized successfully and prepared to load ads', 'Allows processing of personal information.', 'Enables processing of Personal Information for users who consent and are subject to GDPR rules']}, {'parameter_values': ['context', '&lt;YOUR_APP_TOKEN&gt;', False, True], 'conditions': ['User does not provide consent', 'User is subject to GDPR.'], 'effects': ['May not respond to ads as the user cannot be detected if they do not consent', 'The SDK may not respond to ad requests as user actions cannot be attributed', 'May not respond to ad requests as user cannot be detected.']}, {'parameter_values': ['&lt;YOUR_APP_TOKEN&gt;', True, False], 'conditions': ['User has provided consent for data processing', 'User is not subject to GDPR rules', 'If the user consent is given'], 'effects': ["User's Personal Information can be stored and processed", 'User data will be processed, and ads can be served']}, {'parameter_values': ['&lt;YOUR_APP_TOKEN&gt;', False, False], 'conditions': ['If the user does not provide consent'], 'effects': ['YouAppi may not respond to ad requests due to inability to associate actions with a user']}, {'parameter_values': ['&lt;YOUR_APP_TOKEN&gt;', False, True], 'conditions': ['User has denied consent for data processing', 'User is subject to GDPR rules'], 'effects': ["Ads may not be served as user's information cannot be tracked"]}]}</t>
+          <t>{'API_name': 'setMaxAdContentRating', 'class_name': ['VponAdRequest.Builder'], 'conditions': [], 'effects': ['Sets the maximum content rating filter', 'Sets the maximum content rating filter for ads', 'Sets the maximum content rating for delivered ads', 'Sets the maximum content rating for the ads', 'Filters ads based on the content rating set by the user'], 'parameter_configurations': [{'parameter_values': ['String'], 'conditions': [], 'effects': ['Ads will be filtered based on the specified content rating']}]}</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
+          <t>https://wiki.vpon.com/android/custom-request-params/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>YouAppi</t>
+          <t>Vungle(liftoff)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>setGDPRStatus</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': ['YouAPPi'], 'conditions': [], 'effects': ['Sets user consent for data processing', 'Sets the user consent status for data processing', 'Sets the user consent value for tracking and ad serving.', "Sets the user's consent status for data processing", 'Updates the user consent status within the SDK'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User consent is granted for data processing', 'Indicates that the user has given consent for data processing', 'Indicates that user consent is given', 'Indicates that the user consented to data processing.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Indicates that the user has denied consent for data processing', 'User consent is denied for data processing', 'Indicates that user consent is not given, potentially affecting ad requests', 'Indicates that the user did not consent to data processing.']}]}</t>
+          <t>{'API_name': 'setGDPRStatus', 'class_name': ['VunglePrivacySettings'], 'conditions': ['User consent status indicates whether user has opted in or opted out.', "User consent is collected using the publisher's mechanism or Vungle's consent dialog must be used for European users.", 'Consent message version must be provided', 'User must provide consent for data processing under GDPR regulations', 'The publisher controls the GDPR consent process', 'Publisher controls the GDPR consent process at the user level'], 'effects': ['Indicates whether the user has opted in or out of data processing under GDPR', 'Specifies whether the user has opted in or opted out for GDPR compliance', "Sets the user's consent status for GDPR compliance", "Sets the user's GDPR consent status to opted in or opted out.", "Specifies the user's consent status for GDPR compliance."], 'parameter_configurations': [{'parameter_values': [True, '1.0.0'], 'conditions': ['User opts in for GDPR.', 'User opts in for data processing', 'User has opted in for data processing'], 'effects': ['User consent status set to opted in.', 'User is considered opted in for GDPR.', 'User consent status registered as opted in', "User's consent status is set to opted in"]}, {'parameter_values': [False, '1.0.0'], 'conditions': ['User opts out of GDPR.', 'User has opted out of data processing', 'User opts out of data processing'], 'effects': ['User consent status set to opted out.', 'User consent status registered as opted out', 'User is considered opted out for GDPR.', "User's consent status is set to opted out"]}]}</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
+          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>YouAppi</t>
+          <t>Vungle(liftoff)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>setgdpr</t>
+          <t>setCOPPAStatus</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{'API_name': 'setgdpr', 'class_name': ['YouAPPi'], 'conditions': [], 'effects': ['Sets whether GDPR regulations apply.', 'Sets whether the GDPR rules apply for the user', 'Sets whether the user is subject to GDPR', 'Sets whether GDPR applies to the user or not', 'Sets whether GDPR regulations apply to the user'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Indicates that the user is subject to GDPR regulations, allowing data processing according to GDPR', 'Indicates an EU user, must comply with GDPR.', 'GDPR applies; requires consent for processing personal data', 'Indicates that GDPR applies, affecting how user data is handled', 'User is considered to be subject to GDPR rules']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Indicates that the user is not subject to GDPR regulations, potentially limiting data collection', 'Indicates that GDPR does not apply, allowing unrestricted data processing', 'Indicates a non-EU user, may process personal data.', 'User is considered not to be subject to GDPR rules, affecting ad requests', 'GDPR does not apply; may not restrict ad processing']}]}</t>
+          <t>{'API_name': 'setCOPPAStatus', 'class_name': ['VunglePrivacySettings'], 'conditions': ['Must comply with COPPA regulations', 'Used to indicate that a user is under or over age 13 in compliance with COPPA regulations.', 'App must comply with COPPA regulations', 'Must indicate if app is directed toward children under age 13', 'Called before initializing the Vungle SDK', "User's age is known."], 'effects': ["Updates the user's COPPA compliance status", 'Indicates whether a user is under age 13 and protected by COPPA regulations', "Provides Vungle with the user's COPPA status to ensure proper compliance with COPPA for targeted ads.", "Updates Vungle regarding the user's COPPA status.", 'Indicates whether the user is under COPPA protection'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under the age of 13', 'User is confirmed to be under age 13', 'User is under the age of 13.'], 'effects': ['Indicates the user is under age 13 and thus protected under COPPA.', 'User is treated as falling under COPPA regulations', 'User is treated as under COPPA regulations.', 'User is treated as under age 13', 'Treat user as under COPPA regulations']}, {'parameter_values': [False], 'conditions': ['User is 13 years of age or older', 'User is over the age of 13.', 'User is known to be over age 13'], 'effects': ['Indicates the user is over age 13 and not protected under COPPA.', 'User is treated as not under COPPA regulations.', 'User is treated as over age 13', 'User is not treated as falling under COPPA regulations', 'Does not treat user as under COPPA regulations']}]}</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
+          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>YouAppi</t>
+          <t>Vungle(liftoff)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>setAgeRestrictedUser</t>
+          <t>setCCPAStatus</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAgeRestrictedUser', 'class_name': ['YouAPPi'], 'conditions': ['User is known to be in an age-restricted class (e.g., under the age of 16 or 13)', 'User is known to be in an age-restricted class.', 'User is known to be in an age restricted category such as under 16 or under 13'], 'effects': ['Indicates whether the user falls within an age-restricted category', 'Marks the user as being age-restricted', 'Marks the user as age-restricted for ad targeting.', 'Indicates if the user is in an age-restricted category, which affects ad processing', 'Indicates whether the user falls into an age-restricted category'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under the age of 16 or under the age of 13 based on jurisdiction.', 'The user is confirmed to be under the specified age limit'], 'effects': ['User is treated as age-restricted, affecting ad targeting', 'Signals that the user is under a certain age threshold, requiring special data handling', "User's ad experiences may be modified to comply with age regulations", 'Indicates person is in an age-restricted category, potentially affecting ad delivery', 'Prevents ads targeted to children based on legal requirements.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User is not treated as age-restricted, allowing normal ad targeting', 'Signals that the user is not under a certain age threshold, allowing standard data handling']}]}</t>
+          <t>{'API_name': 'setCCPAStatus', 'class_name': ['VunglePrivacySettings'], 'conditions': ['Must update to SDK 6.7.0 or higher to comply with CCPA', 'Must have been updated to Android SDK 6.7.0 or higher to comply with CCPA.', 'Must update to Android SDK 6.7.0 to comply with CCPA', 'User consent status indicates whether user has opted in or opted out for CCPA.', 'User must provide consent for data processing under CCPA regulations'], 'effects': ['Specifies whether the user has opted in or opted out for CCPA compliance', "Sets the user's consent status for CCPA compliance", "Specifies the user's consent status for CCPA compliance.", "Sets the user's CCPA consent status to opted in or opted out.", 'Indicates whether the user has opted in or out under CCPA'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts in for CCPA.', 'User has opted in for data processing', 'User opts in to data processing'], 'effects': ['User status set to opted in for CCPA.', "User's CCPA status is set to opted in", 'User consent status set to opted in.', 'User consent status registered as opted in']}, {'parameter_values': [False], 'conditions': ['User has opted out of data processing', 'User opts out of CCPA.', 'User opts out of data processing'], 'effects': ['User consent status set to opted out.', 'User consent status registered as opted out', "User's CCPA status is set to opted out", 'User status set to opted out for CCPA.']}]}</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
+          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>adMost</t>
+          <t>Vungle(liftoff)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>setPublishAndroidId</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': ['AdMostConfiguration'], 'conditions': ['User must have provided consent', 'Consent must be collected from the user', 'User must provide consent for GDPR or CCPA compliance'], 'effects': ['Passes user consent to the SDK for GDPR or CCPA compliance', 'Sets the user consent for data processing as per GDPR and CCPA compliance.', "Passes user's consent to the AdMost SDK", 'Sets user consent for processing personal data'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User has provided consent for data processing', 'If the user has given consent'], 'effects': ['Indicates consent has been accepted.', 'SDK processes user data in compliance with regulations', 'User consent for data collection is acknowledged by AdMost', 'User consent is recorded as given for data processing']}, {'parameter_values': [False], 'conditions': ['User has not provided consent for data processing', 'If the user has not given consent'], 'effects': ['User consent is recorded as not given for data processing', 'Indicates consent has been denied.', 'User consent for data collection is not acknowledged by AdMost', 'SDK does not process user data for personalized ads']}]}</t>
+          <t>{'API_name': 'setPublishAndroidId', 'class_name': ['VunglePrivacySettings'], 'conditions': ['Android SDK version is 6.4.11 or higher', 'User must opt in to Android ID collection', 'User must consent to the use of Android ID for advertisement targeting.', 'Must be called prior to initializing the SDK.'], 'effects': ['Determines whether the SDK will collect the Android ID.', 'Controls whether Android ID is collected.', 'Controls the publication of the Android ID', 'Controls whether Android ID is collected or not', 'Determines whether to collect the Android ID when Google Advertising ID is not available'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User opts in to Android ID collection.', 'Default opt-in for Android ID collection'], 'effects': ['Opt-in for the collection of Android ID', 'SDK will collect and publish the Android ID', 'Android ID can be collected by SDK', 'Opt in for Android ID collection.', 'Android ID will be collected.']}, {'parameter_values': [False], 'conditions': ['User opts out of Android ID collection', 'User opts out of Android ID collection.'], 'effects': ['SDK will not collect or publish the Android ID', 'Opt out for Android ID collection.', 'Android ID will not be collected.', 'Opt-out for the collection of Android ID', 'Android ID will not be collected by SDK']}]}</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://admost.github.io/amrandroid/</t>
+          <t>https://support.vungle.com/hc/en-us/articles/360047780372-Advanced-Settings</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>adMost</t>
+          <t>Yandex Metrica</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>setSubjectToGDPR</t>
+          <t>setAgeRestrictedUser</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['AdMostConfiguration'], 'conditions': ['If the user is located in a region subject to GDPR', 'User is located within the European Economic Area or under the age of 16'], 'effects': ['Specifies whether the user is subject to GDPR', 'Specifies whether the user is subject to GDPR rules', 'Configures whether the user is subject to GDPR.', 'Defines whether the user should be treated under GDPR regulations'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['If the user is in the EU or another GDPR region', 'If the user is subject to GDPR'], 'effects': ['Sets user registration as subject to GDPR regulations', 'Admost will apply GDPR compliance measures', 'The SDK applies GDPR rules for data handling', 'Sets the user as subject to GDPR regulations.']}, {'parameter_values': [False], 'conditions': ['If the user is outside of GDPR regions', 'If the user is not subject to GDPR'], 'effects': ['The SDK does not apply GDPR rules for data handling', 'Sets the user as not subject to GDPR regulations.', 'Sets user registration as not subject to GDPR regulations', 'Admost will not apply GDPR compliance measures']}]}</t>
+          <t>{'API_name': 'setAgeRestrictedUser', 'class_name': [''], 'conditions': ['Required to comply with COPPA', 'For children under the age of 13, data collection needs to be restricted.', 'Required to comply with COPPA for users under the age of 13.', "Data about the user's age must be transmitted to the SDK every time the application starts."], 'effects': ['Enables the restriction of the collection of information from children under the age of 13.', 'Restricts the collection of information from children under the age of 13.', 'Enables restriction of information collection from children under the age of 13.', 'Restricts collection of information from children under the age of 13.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under the age of 13', 'The user is under the age of 13.', 'The user is identified as under the age of 13.', 'The user is a child under the age of 13.'], 'effects': ['Prevents personal data collection from the user.', 'Prohibits the collection of personal information from the user.', 'Restrict collection of information from users under 13', 'Prevents the SDK from collecting personal information from the user.', 'Restricts data collection in accordance with COPPA.']}, {'parameter_values': [False], 'conditions': ['The user is age 13 or older.', 'User is 13 years or older', 'The user is identified as 13 years or older.', 'The user is 13 years of age or older.', 'User is 13 years of age or older'], 'effects': ['Allow collection of information from users 13 years or older', 'Allows normal data collection as per usual SDK functionality.', 'Allows normal data collection from the user.', 'Data collection is allowed.', 'Allows the collection of personal information from the user.']}]}</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://admost.github.io/amrandroid/</t>
+          <t>https://ads.yandex.com/helpcenter/en/dev/android/gdpr;https://ads.yandex.com/helpcenter/en/dev/android/coppa;https://ads.yandex.com/helpcenter/en/dev/android/context-data</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>adMost</t>
+          <t>Yandex Metrica</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>setSubjectToCCPA</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSubjectToCCPA', 'class_name': ['AdMostConfiguration'], 'conditions': ['If the user is a California resident', 'User is a resident of California'], 'effects': ['Configures whether the user is subject to CCPA.', 'Defines whether the user should be treated under CCPA regulations', 'Specifies whether the user is subject to CCPA', 'Specifies whether the user is subject to CCPA regulations'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['If the user is a resident of California', 'If the user is subject to CCPA'], 'effects': ['The SDK applies CCPA rules for data handling', 'Sets user registration as subject to CCPA regulations', 'Admost will apply CCPA compliance measures', 'Indicates the user is subject to CCPA.']}, {'parameter_values': [False], 'conditions': ['If the user is not a California resident', 'If the user is not subject to CCPA'], 'effects': ['Admost will not apply CCPA compliance measures', 'Sets user registration as not subject to CCPA regulations', 'Indicates the user is not subject to CCPA.', 'The SDK does not apply CCPA rules for data handling']}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': [''], 'conditions': ["User's consent for processing personal data must be sent to the SDK each time the application is launched.", 'Required to comply with GDPR.', "User's consent for processing personal data must be sent to the SDK each time the application launches.", 'Required to comply with GDPR', "The user's consent for processing personal data must be sent to the SDK each time the application is launched.", 'This is necessary to comply with GDPR regulations.'], 'effects': ['Determines if user data from GDPR regions will be processed based on consent.', 'Data of users located in the GDPR region will be processed only if the user consents to data processing.', 'User data will be processed only if the user consents to data processing.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User gives consent for personal data processing.', 'User accepts the user agreement for personal data processing', 'User accepts the user agreement for personal data processing.', 'User agrees to the user agreement for personal data processing.', 'User accepts the data processing user agreement.'], 'effects': ["Allows processing of the user's personal data.", 'User data will be processed', 'Allows processing of personal data for users in the GDPR region.', "Enables processing of the user's personal data.", "Permits the processing of the user's personal data."]}, {'parameter_values': [False], 'conditions': ['User declines the user agreement for personal data processing', 'User declines the data processing user agreement.', 'User declines the user agreement for personal data processing.', 'User declines the user agreement.', 'User does not give consent for personal data processing.'], 'effects': ['User data will not be processed', "Prohibits the processing of the user's personal data.", "Prevents processing of the user's personal data.", "Disables processing of the user's personal data.", 'Prevents processing of personal data for users in the GDPR region.']}]}</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://admost.github.io/amrandroid/</t>
+          <t>https://ads.yandex.com/helpcenter/en/dev/android/gdpr;https://ads.yandex.com/helpcenter/en/dev/android/coppa;https://ads.yandex.com/helpcenter/en/dev/android/context-data</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>adMost</t>
+          <t>Yandex Metrica</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>setPrivacyConsentListener</t>
+          <t>contextualDataTracking</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPrivacyConsentListener', 'class_name': ['AdMost'], 'conditions': ['Listener must be set before checking for privacy consent'], 'effects': ['Sets a listener to check if privacy consent is required.', 'Sets a listener to determine if privacy consent is required', 'Sets a listener to check if the user is in a country subject to GDPR or CCPA', 'Allows the SDK to check if user consent is required'], 'parameter_configurations': [{'parameter_values': ['this', 'new AdMost.PrivacyConsentListener() { ... }'], 'conditions': [], 'effects': ['Receives callbacks regarding the privacy consent status of the user.', 'Receives callbacks about privacy consent status']}, {'parameter_values': ['this', 'new AdMost.PrivacyConsentListener()'], 'conditions': [], 'effects': ['Listener capable of handling consent requirements for GDPR and CCPA']}, {'parameter_values': ['this', 'new AdMost.PrivacyConsentListener() {}'], 'conditions': [], 'effects': ['Receives callbacks indicating whether privacy consent is required']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://admost.github.io/amrandroid/</t>
+          <t>https://ads.yandex.com/helpcenter/en/dev/android/gdpr;https://ads.yandex.com/helpcenter/en/dev/android/coppa;https://ads.yandex.com/helpcenter/en/dev/android/context-data</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>adMost</t>
+          <t>YouAppi</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>setUserChild</t>
+          <t>init</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserChild', 'class_name': ['AdMostConfiguration'], 'conditions': ['Only set true if you know the user is a child', 'User is considered to be a child under the age of 18', 'If the application targets users under 18'], 'effects': ['Signifies that the user is a child for compliance purposes', "Sets the flag for compliance with children's advertising regulations.", 'Defines whether the user should be treated as a child for ad purposes'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['If the developer knows the user is a child', 'The user is confirmed to be under 18', 'If you know the user is a child'], 'effects': ['Ads shown will comply with safeguards for children', 'Indicates the user is under the age of 18, requiring special ad serving rules.', 'Applies child-specific advertising regulations']}, {'parameter_values': [False], 'conditions': ['If the developer knows the user is not a child', 'If you know the user is not a child', 'The user is confirmed to be 18 or older'], 'effects': ['Indicates the user is over the age of 18.', 'Follows standard advertising regulations', 'Normal ad rules apply without child restrictions']}]}</t>
+          <t>{'API_name': 'init', 'class_name': ['YouAPPi'], 'conditions': ['DOES_GDPR_APPLY should reflect if the user is subject to GDPR (e.g., EU resident)', "USER_CONSENT must be determined by the app developer according to the User's response to a Consent Request.", 'DOES_GDPR_APPLY is set according to if the user is subject to GDPR rules', 'USER_CONSENT indicates whether user consent is given', "USER_CONSENT is determined by the user's response to a Consent Request", "Requires USER_CONSENT based on user's response to a dialog asking for permission", 'USER_CONSENT should be set to user’s response to a consent request', 'DOES_GDPR_APPLY should be set based on whether the user is an EU residence', "DOES_GDPR_APPLY must be set according to the user's residency status", 'DOES_GDPR_APPLY determines if the GDPR rules apply to the user'], 'effects': ['Initializes the YouAppi SDK and allows it to process and store the user’s Personal Information if conditions are met', 'Initializes YouAppi SDK with app token and user consent information', 'Initializes YouAppi SDK with user consent and compliance with GDPR regulations', "Initializes YouAppi SDK and allows processing and storage of user's Personal Information", 'Initializes YouAppi SDK with user consent and compliance with GDPR.', "Allows processing and storage of user's personal information if consent is granted", 'Enables the SDK to access user private information, such as Advertising ID and IP address'], 'parameter_configurations': [{'parameter_values': ['context', '&lt;YOUR_APP_TOKEN&gt;', True, False], 'conditions': ['User is not subject to GDPR.'], 'effects': ['SDK is initialized successfully and prepared to load ads', 'Allows processing of personal information.', 'Enables processing of Personal Information for users who consent and are subject to GDPR rules']}, {'parameter_values': ['context', '&lt;YOUR_APP_TOKEN&gt;', False, True], 'conditions': ['User does not provide consent', 'User is subject to GDPR.'], 'effects': ['May not respond to ads as the user cannot be detected if they do not consent', 'The SDK may not respond to ad requests as user actions cannot be attributed', 'May not respond to ad requests as user cannot be detected.']}, {'parameter_values': ['&lt;YOUR_APP_TOKEN&gt;', True, False], 'conditions': ['User has provided consent for data processing', 'User is not subject to GDPR rules', 'If the user consent is given'], 'effects': ["User's Personal Information can be stored and processed", 'User data will be processed, and ads can be served']}, {'parameter_values': ['&lt;YOUR_APP_TOKEN&gt;', False, False], 'conditions': ['If the user does not provide consent'], 'effects': ['YouAppi may not respond to ad requests due to inability to associate actions with a user']}, {'parameter_values': ['&lt;YOUR_APP_TOKEN&gt;', False, True], 'conditions': ['User has denied consent for data processing', 'User is subject to GDPR rules'], 'effects': ["Ads may not be served as user's information cannot be tracked"]}]}</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://admost.github.io/amrandroid/</t>
+          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>mixpanel</t>
+          <t>YouAppi</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>identify</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'API_name': 'identify', 'class_name': ['Mixpanel'], 'conditions': [], 'effects': ['associates a user ID with events without needing to know identifying information about users'], 'parameter_configurations': [{'parameter_values': ['hashed_user_id'], 'conditions': [], 'effects': ['Enables analysis of user behavior in aggregate without being able to drill down into individual users']}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': ['YouAPPi'], 'conditions': [], 'effects': ['Sets user consent for data processing', 'Sets the user consent status for data processing', 'Sets the user consent value for tracking and ad serving.', "Sets the user's consent status for data processing", 'Updates the user consent status within the SDK'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['User consent is granted for data processing', 'Indicates that the user has given consent for data processing', 'Indicates that user consent is given', 'Indicates that the user consented to data processing.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Indicates that the user has denied consent for data processing', 'User consent is denied for data processing', 'Indicates that user consent is not given, potentially affecting ad requests', 'Indicates that the user did not consent to data processing.']}]}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://docs.mixpanel.com/docs/privacy/protecting-user-data</t>
+          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Google Ad Manager</t>
+          <t>YouAppi</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>putPublisherFirstPartyIdEnabled</t>
+          <t>setgdpr</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'API_name': 'putPublisherFirstPartyIdEnabled', 'class_name': ['MobileAds'], 'conditions': ['Google Mobile Ads SDK version 21.4.0 or higher', 'requires Google Mobile Ads SDK 21.4.0 or higher', 'Publisher first-party ID feature is enabled by default', 'The Google Mobile Ads SDK version must be 21.4.0 or higher.'], 'effects': ['Enables or disables the Publisher first-party ID functionality', 'Enables or disables the Publisher first-party ID which is used for delivering more relevant and personalized ads.', 'Enables or disables the Publisher first-party ID for personalized ads', 'Enables or disables the Publisher first-party ID feature, which helps deliver more relevant and personalized ads', 'enables or disables the Publisher first-party ID feature for relevant and personalized ads'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['SDK version 21.4.0 or higher', 'Publishers wish to disable Publisher first-party ID to limit data sharing', 'When disabling the Publisher first-party ID functionality'], 'effects': ['Disables the Publisher first-party ID for use in Google Ads', 'Disables the Publisher first-party ID.', 'Data associated with the Publisher first-party ID is not sent, potentially impacting ad personalization', 'disables the use of Publisher first-party ID', 'Publisher first-party ID is disabled; no data will be collected through this means']}, {'parameter_values': [True], 'conditions': ['When enabling the Publisher first-party ID functionality'], 'effects': ['Enables the Publisher first-party ID.', 'Publisher first-party ID is enabled by default; data collected from apps will be utilized for ad personalization', 'Publisher first-party ID is enabled, allowing the collection of more relevant and personalized ads']}]}</t>
+          <t>{'API_name': 'setgdpr', 'class_name': ['YouAPPi'], 'conditions': [], 'effects': ['Sets whether GDPR regulations apply.', 'Sets whether the GDPR rules apply for the user', 'Sets whether the user is subject to GDPR', 'Sets whether GDPR applies to the user or not', 'Sets whether GDPR regulations apply to the user'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Indicates that the user is subject to GDPR regulations, allowing data processing according to GDPR', 'Indicates an EU user, must comply with GDPR.', 'GDPR applies; requires consent for processing personal data', 'Indicates that GDPR applies, affecting how user data is handled', 'User is considered to be subject to GDPR rules']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Indicates that the user is not subject to GDPR regulations, potentially limiting data collection', 'Indicates that GDPR does not apply, allowing unrestricted data processing', 'Indicates a non-EU user, may process personal data.', 'User is considered not to be subject to GDPR rules, affecting ad requests', 'GDPR does not apply; may not restrict ad processing']}]}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/strategies;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/precise-location;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/us-states</t>
+          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Google Ad Manager</t>
+          <t>YouAppi</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>addNetworkExtrasBundle</t>
+          <t>setAgeRestrictedUser</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'API_name': 'addNetworkExtrasBundle', 'class_name': ['AdManagerAdRequest.Builder'], 'conditions': ['When creating an ad request and wanting to specify additional parameters for RDP'], 'effects': ['Includes additional parameters in the ad request to inform Google of RDP settings'], 'parameter_configurations': [{'parameter_values': ['rdp', 1], 'conditions': ['To enable restricted data processing'], 'effects': ['Google will restrict the use of certain unique identifiers and serve non-personalized ads']}, {'parameter_values': ['IABUSPrivacy_String', 'IAB_STRING'], 'conditions': ['To inform Google of compliance with IAB specifications'], 'effects': ['Ensures that ad requests are compliant with IAB privacy regulations']}]}</t>
+          <t>{'API_name': 'setAgeRestrictedUser', 'class_name': ['YouAPPi'], 'conditions': ['User is known to be in an age-restricted class (e.g., under the age of 16 or 13)', 'User is known to be in an age-restricted class.', 'User is known to be in an age restricted category such as under 16 or under 13'], 'effects': ['Indicates whether the user falls within an age-restricted category', 'Marks the user as being age-restricted', 'Marks the user as age-restricted for ad targeting.', 'Indicates if the user is in an age-restricted category, which affects ad processing', 'Indicates whether the user falls into an age-restricted category'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is under the age of 16 or under the age of 13 based on jurisdiction.', 'The user is confirmed to be under the specified age limit'], 'effects': ['User is treated as age-restricted, affecting ad targeting', 'Signals that the user is under a certain age threshold, requiring special data handling', "User's ad experiences may be modified to comply with age regulations", 'Indicates person is in an age-restricted category, potentially affecting ad delivery', 'Prevents ads targeted to children based on legal requirements.']}, {'parameter_values': [False], 'conditions': [], 'effects': ['User is not treated as age-restricted, allowing normal ad targeting', 'Signals that the user is not under a certain age threshold, allowing standard data handling']}]}</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/strategies;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/precise-location;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/us-states</t>
+          <t>https://support.youappi.com/knowledgebase/android-sdk/#GDPR_Users_Consent</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Pangle</t>
+          <t>adMost</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>setChildDirected</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'API_name': 'setChildDirected', 'class_name': ['PAGConfig.Builder'], 'conditions': ['required to comply with COPPA', 'Required to comply with COPPA regulations'], 'effects': ['Sets the configuration of COPPA where 0 indicates adult and 1 indicates child', 'Sets the configuration of COPPA for user categorization as either adult (0) or child (1)', 'configures whether the app is directed at children under 13', 'Sets the configuration indicating if the app is directed to children', 'configures whether the app is directed to children or adults'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': ['When the app is intended for adults'], 'effects': ['indicates the content is intended for adults', 'User is categorized as an adult', 'User is considered an adult (not directed to children)', 'Allows for advertising strategies aimed at adult users', 'The app is considered adult-directed']}, {'parameter_values': [1], 'conditions': ['When the app is intended for children'], 'effects': ['User is considered a child (directed to children)', 'User is categorized as a child', 'indicates the content is intended for children', 'Adjusts advertising strategies to comply with child-directed regulations', 'The app is considered child-directed']}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': ['AdMostConfiguration'], 'conditions': ['User must have provided consent', 'Consent must be collected from the user', 'User must provide consent for GDPR or CCPA compliance'], 'effects': ['Passes user consent to the SDK for GDPR or CCPA compliance', 'Sets the user consent for data processing as per GDPR and CCPA compliance.', "Passes user's consent to the AdMost SDK", 'Sets user consent for processing personal data'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User has provided consent for data processing', 'If the user has given consent'], 'effects': ['Indicates consent has been accepted.', 'SDK processes user data in compliance with regulations', 'User consent for data collection is acknowledged by AdMost', 'User consent is recorded as given for data processing']}, {'parameter_values': [False], 'conditions': ['User has not provided consent for data processing', 'If the user has not given consent'], 'effects': ['User consent is recorded as not given for data processing', 'Indicates consent has been denied.', 'User consent for data collection is not acknowledged by AdMost', 'SDK does not process user data for personalized ads']}]}</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://www.pangleglobal.com/integration/android-initialize-pangle-sdk</t>
+          <t>https://admost.github.io/amrandroid/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Pangle</t>
+          <t>adMost</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>setGDPRConsent</t>
+          <t>setSubjectToGDPR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGDPRConsent', 'class_name': ['PAGConfig.Builder'], 'conditions': ['compliance with GDPR regulations', 'required to comply with GDPR regulations'], 'effects': ["Sets the configuration of GDPR consent where 0 means user hasn't granted consent and 1 means user has granted consent", "configures the user's consent status for GDPR", 'Sets the GDPR consent status for the user', "sets the user's consent status for data processing under GDPR", 'Sets the GDPR consent status, indicating whether the user has granted consent or not'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['User does not grant GDPR consent', 'User has not granted consent under GDPR', 'User has not granted GDPR consent', 'User does not grant consent under GDPR', 'user does not grant consent for data processing']}, {'parameter_values': [1], 'conditions': [], 'effects': ['user has granted consent for data processing', 'User has granted consent under GDPR', 'User has granted GDPR consent']}]}</t>
+          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['AdMostConfiguration'], 'conditions': ['If the user is located in a region subject to GDPR', 'User is located within the European Economic Area or under the age of 16'], 'effects': ['Specifies whether the user is subject to GDPR', 'Specifies whether the user is subject to GDPR rules', 'Configures whether the user is subject to GDPR.', 'Defines whether the user should be treated under GDPR regulations'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['If the user is in the EU or another GDPR region', 'If the user is subject to GDPR'], 'effects': ['Sets user registration as subject to GDPR regulations', 'Admost will apply GDPR compliance measures', 'The SDK applies GDPR rules for data handling', 'Sets the user as subject to GDPR regulations.']}, {'parameter_values': [False], 'conditions': ['If the user is outside of GDPR regions', 'If the user is not subject to GDPR'], 'effects': ['The SDK does not apply GDPR rules for data handling', 'Sets the user as not subject to GDPR regulations.', 'Sets user registration as not subject to GDPR regulations', 'Admost will not apply GDPR compliance measures']}]}</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://www.pangleglobal.com/integration/android-initialize-pangle-sdk</t>
+          <t>https://admost.github.io/amrandroid/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Pangle</t>
+          <t>adMost</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>setDoNotSell</t>
+          <t>setSubjectToCCPA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{'API_name': 'setDoNotSell', 'class_name': ['PAGConfig.Builder'], 'conditions': ['compliance with CCPA regulations', 'Required to comply with CCPA parameters', 'required to comply with CCPA regulations'], 'effects': ["configures the user's opt-out preference regarding the sale of personal information", "sets the user's choice regarding the sale of personal information", 'Sets the CCPA compliance for selling personal information, indicating whether the user has opted out or not', 'Sets the configuration regarding the sale of personal information', "Sets the configuration of CCPA where 0 means 'sale' of personal information is permitted and 1 means the user has opted out of the 'sale' of their personal information"], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ["User allows the 'sale' of their personal information", 'Sale of personal information is permitted', 'Allows the sale of personal information', "permits the 'sale' of personal information"]}, {'parameter_values': [1], 'conditions': [], 'effects': ["user has opted out of the 'sale' of personal information", 'User has opted out of the sale of personal information', "User opts out of the 'sale' of personal information", 'Opt-out of the sale of personal information']}]}</t>
+          <t>{'API_name': 'setSubjectToCCPA', 'class_name': ['AdMostConfiguration'], 'conditions': ['If the user is a California resident', 'User is a resident of California'], 'effects': ['Configures whether the user is subject to CCPA.', 'Defines whether the user should be treated under CCPA regulations', 'Specifies whether the user is subject to CCPA', 'Specifies whether the user is subject to CCPA regulations'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['If the user is a resident of California', 'If the user is subject to CCPA'], 'effects': ['The SDK applies CCPA rules for data handling', 'Sets user registration as subject to CCPA regulations', 'Admost will apply CCPA compliance measures', 'Indicates the user is subject to CCPA.']}, {'parameter_values': [False], 'conditions': ['If the user is not a California resident', 'If the user is not subject to CCPA'], 'effects': ['Admost will not apply CCPA compliance measures', 'Sets user registration as not subject to CCPA regulations', 'Indicates the user is not subject to CCPA.', 'The SDK does not apply CCPA rules for data handling']}]}</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://www.pangleglobal.com/integration/android-initialize-pangle-sdk</t>
+          <t>https://admost.github.io/amrandroid/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AD(X)</t>
+          <t>adMost</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>initialize</t>
+          <t>setPrivacyConsentListener</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{'API_name': 'initialize', 'class_name': ['ADXSdk'], 'conditions': ['GDPR compliance is required for users in the European Economic Area', 'must be completed before ad requests', 'Initialization must occur before any ad requests', 'SDK version must be 2.5.0 or higher to use UMP for GDPR consent management', 'Initialization must occur once when the app launches', 'must be called once at app launch', 'Must obtain user consent for GDPR compliance if serving EEA users', 'Ad requests must occur after initialization is complete', 'used for initializing the ADX SDK', 'must be called only once at app launch', 'GDPR compliance is required for EU users', 'GDPR compliance must be addressed', 'ad requests must be made after initialization is complete', 'GDPR compliance is required for services targeting EU users'], 'effects': ['initializes the SDK and prepares to handle advertising-related functionalities', 'Provides a framework for the ads to be displayed according to user consent', 'Sets up the SDK to manage user consent for GDPR', 'Enables the AD(X) SDK and provides functionality to obtain GDPR consent', 'initializes the SDK and handles GDPR consent for EU users', 'initializes the SDK and allows for the handling of GDPR consent'], 'parameter_configurations': [{'parameter_values': ['&lt;ADX_APP_ID&gt;', 'context', 'adxConfiguration'], 'conditions': ['GDPR consent is obtained before making ad requests'], 'effects': ['SDK can properly manage GDPR consent and make ad requests afterward']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_LOCATION', 'testDeviceIds'], 'conditions': ['User is from the European Economic Area (EEA)', 'Consent UI must use the context of an Activity'], 'effects': ["Displays a consent UI for GDPR compliance based on the user's location"]}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_DEBUG', 'testDeviceIds'], 'conditions': ['For testing purposes regardless of user location'], 'effects': ['Enables testing of the GDPR consent UI']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_NOT_REQUIRED', 'null'], 'conditions': ['User location does not require consent (EU outside)'], 'effects': ['Allows personalized ads to be shown without user consent']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_CONFIRM', 'null'], 'conditions': ['Directly obtained user consent in EU region'], 'effects': ['Allows personalized ads to be shown based on user consent']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_DENIED', 'null'], 'conditions': ['User has denied consent in the EU region'], 'effects': ['Prevents personalized ads from being displayed']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_LOCATION'], 'conditions': ['User is located in the EU and needs to confirm GDPR consent', "GDPR type must be set to 'POPUP_LOCATION' for users in the EU", 'must provide appropriate Activity context'], 'effects': ['displays consent popup to users in the EU for GDPR compliance', 'Displays a consent popup to the user for GDPR']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_CONFIRM'], 'conditions': ['User is not located in the EU or direct consent is obtained from the user', 'for regions where explicit consent was provided by the user'], 'effects': ["Directly confirms the user's consent for data processing under GDPR", 'enables personalized ads after user consent']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_NOT_REQUIRED'], 'conditions': ['User is located outside the EU where consent is not required', 'for regions where consent is not required'], 'effects': ['allows personalized ads without requiring user consent', 'No consent needed, ads can still be displayed']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_DEBUG'], 'conditions': ['For testing purposes to ensure the consent popup works regardless of user location', 'test environment for GDPR consent UI verification'], 'effects': ['displays consent UI regardless of user location for testing', 'Displays the consent popup for debugging']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_DENIED'], 'conditions': ['for regions where user has denied consent'], 'effects': ['disables personalized ads']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'POPUP_LOCATION'], 'conditions': ['User is from the EU'], 'effects': ['Displays a consent UI for GDPR compliance based on user location']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'POPUP_DEBUG'], 'conditions': ['Testing the consent UI regardless of user location'], 'effects': ['Allows testing of the GDPR consent UI']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'DIRECT_NOT_REQUIRED'], 'conditions': ['User is not from the EU'], 'effects': ['Consent is not required, and personalized ads are shown']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'DIRECT_DENIED'], 'conditions': ['User denies consent for personal data usage'], 'effects': ['Personalized ads are not shown']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'DIRECT_CONFIRM'], 'conditions': ['User consents to personal data usage'], 'effects': ['Personalized ads are shown']}]}</t>
+          <t>{'API_name': 'setPrivacyConsentListener', 'class_name': ['AdMost'], 'conditions': ['Listener must be set before checking for privacy consent'], 'effects': ['Sets a listener to check if privacy consent is required.', 'Sets a listener to determine if privacy consent is required', 'Sets a listener to check if the user is in a country subject to GDPR or CCPA', 'Allows the SDK to check if user consent is required'], 'parameter_configurations': [{'parameter_values': ['this', 'new AdMost.PrivacyConsentListener() { ... }'], 'conditions': [], 'effects': ['Receives callbacks regarding the privacy consent status of the user.', 'Receives callbacks about privacy consent status']}, {'parameter_values': ['this', 'new AdMost.PrivacyConsentListener()'], 'conditions': [], 'effects': ['Listener capable of handling consent requirements for GDPR and CCPA']}, {'parameter_values': ['this', 'new AdMost.PrivacyConsentListener() {}'], 'conditions': [], 'effects': ['Receives callbacks indicating whether privacy consent is required']}]}</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
+          <t>https://admost.github.io/amrandroid/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AD(X)</t>
+          <t>adMost</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>getPrivacyURL</t>
+          <t>trackIAP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{'API_name': 'getPrivacyURL', 'class_name': ['ADXGDPR', 'ADXGdprManager'], 'conditions': [], 'effects': ['retrieves the privacy policy URL', 'retrieves the URL of the privacy policy', 'Retrieves the URL of the privacy policy document', 'Retrieves the URL of the AD(X) privacy policy', 'returns the URL of the privacy policy document'], 'parameter_configurations': []}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
+          <t>https://admost.github.io/amrandroid/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AD(X)</t>
+          <t>adMost</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>getResultGDPR</t>
+          <t>setUserChild</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{'API_name': 'getResultGDPR', 'class_name': ['ADXGdprManager'], 'conditions': [], 'effects': ['returns the current GDPR consent state for the user', "retrieves the user's current GDPR consent status", 'Retrieves the current GDPR consent state of the user', 'retrieves the current consent status of the user concerning GDPR', 'Retrieves the current GDPR consent status of the user'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': [], 'effects': ['returns the consent state which can be ADXConsentStateUnknown, ADXConsentStateNotRequired, ADXConsentStateDenied, or ADXConsentStateConfirm']}]}</t>
+          <t>{'API_name': 'setUserChild', 'class_name': ['AdMostConfiguration'], 'conditions': ['Only set true if you know the user is a child', 'User is considered to be a child under the age of 18', 'If the application targets users under 18'], 'effects': ['Signifies that the user is a child for compliance purposes', "Sets the flag for compliance with children's advertising regulations.", 'Defines whether the user should be treated as a child for ad purposes'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['If the developer knows the user is a child', 'The user is confirmed to be under 18', 'If you know the user is a child'], 'effects': ['Ads shown will comply with safeguards for children', 'Indicates the user is under the age of 18, requiring special ad serving rules.', 'Applies child-specific advertising regulations']}, {'parameter_values': [False], 'conditions': ['If the developer knows the user is not a child', 'If you know the user is not a child', 'The user is confirmed to be 18 or older'], 'effects': ['Indicates the user is over the age of 18.', 'Follows standard advertising regulations', 'Normal ad rules apply without child restrictions']}]}</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
+          <t>https://admost.github.io/amrandroid/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AD(X)</t>
+          <t>mixpanel</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>saveResultGDPR</t>
+          <t>optOutTracking</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{'API_name': 'saveResultGDPR', 'class_name': ['ADXGdprManager'], 'conditions': ['GDPR consent state must be provided', 'Direct user consent must be gathered outside of the GDPR consent UI', 'consent must be set according to user interactions regarding data usage'], 'effects': ["updates the user's consent status", "sets or updates the user's consent status for GDPR", 'Updates the stored consent status of the user', "Allows direct setting of the user's GDPR consent state", 'changes the current GDPR consent state for the user'], 'parameter_configurations': [{'parameter_values': ['context', 'ADXConsentState'], 'conditions': ["the consent state must correctly reflect the user's choice"], 'effects': ['updates the consent state thereby allowing or disallowing personalized ads']}, {'parameter_values': ['ADXConsentState'], 'conditions': ['User consent state is determined'], 'effects': ['Changes the consent status accordingly', 'stores the updated consent state', 'Sets the specified consent state for the user']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
+          <t>https://docs.mixpanel.com/docs/privacy/protecting-user-data</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Batch.com</t>
+          <t>mixpanel</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>setGeoIPEnabled</t>
+          <t>identify</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGeoIPEnabled', 'class_name': ['Batch'], 'conditions': ['User consent required to enable GeoIP data collection.'], 'effects': ["Enables the resolution of the user's location from IP address."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ["Activates collection of user's location based on IP."]}, {'parameter_values': [False], 'conditions': [], 'effects': ["Disables collection of user's location based on IP."]}]}</t>
+          <t>{'API_name': 'identify', 'class_name': ['Mixpanel'], 'conditions': [], 'effects': ['associates a user ID with events without needing to know identifying information about users'], 'parameter_configurations': [{'parameter_values': ['hashed_user_id'], 'conditions': [], 'effects': ['Enables analysis of user behavior in aggregate without being able to drill down into individual users']}]}</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
+          <t>https://docs.mixpanel.com/docs/privacy/protecting-user-data</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Batch.com</t>
+          <t>Google Ad Manager</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>updateAutomaticDataCollection</t>
+          <t>presentConsentOverlay</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{'API_name': 'updateAutomaticDataCollection', 'class_name': ['Batch'], 'conditions': ['User consent is necessary to enable automatic data collection for device model, device brand, and GeoIP.', 'User has given consent for automatic data collection'], 'effects': ['Allows enabling or disabling automatic collection of specific user data based on user consent.', 'Enables or disables the collection of specific device data including GeoIP, device brand, and device model.', 'Allows fine-tuning of what data should be automatically collected.'], 'parameter_configurations': [{'parameter_values': [True, True, True], 'conditions': ['User wants to enable GeoIP resolution, device brand, and model information collection.', 'User has provided consent to enable GeoIP, device brand, and device model data collection.', 'GeoIP, device brand, and device model were previously disabled by default.'], 'effects': ["Enables resolution of the user's location from IP address, automatic collection of the device brand and model information.", 'GeoIP, device brand, and device model information will be captured automatically by the SDK.', "User's location can be resolved and the SDK can collect the device brand and model."]}, {'parameter_values': [False, False, False], 'conditions': ['User has revoked consent for collection.', 'User chooses to disable GeoIP, device brand, and device model collection.', 'User wants to disable GeoIP resolution, device brand, and model information collection.'], 'effects': ['GeoIP, device brand, and device model information will not be captured.', 'Disables collection of the specified data.', 'GeoIP resolution is not performed and device brand and model data are not collected.']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
+          <t>https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/strategies;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/precise-location;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/us-states</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Batch.com</t>
+          <t>Google Ad Manager</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>optOut</t>
+          <t>putPublisherFirstPartyIdEnabled</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOut', 'class_name': ['Batch'], 'conditions': ['Called after Batch.onStart(Activity) to ensure the SDK has started.', 'SDK has started via Batch.onStart(Activity)', 'SDK must have been started before opting out.'], 'effects': ['Disables all SDK functionalities including data collection, In-App campaigns, and network capabilities.', 'Prevents Batch from performing any operations, disabling all campaigns and network capabilities.', 'Prevents any network capability from the SDK, disables In-App campaigns, and rejects any related method calls.'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': ['User wants to opt-out from the SDK functionalities.'], 'effects': ['Prevents any SDK operations and network capabilities.', 'Will cease all operations associated with the Batch SDK.']}]}</t>
+          <t>{'API_name': 'putPublisherFirstPartyIdEnabled', 'class_name': ['MobileAds'], 'conditions': ['Google Mobile Ads SDK version 21.4.0 or higher', 'requires Google Mobile Ads SDK 21.4.0 or higher', 'Publisher first-party ID feature is enabled by default', 'The Google Mobile Ads SDK version must be 21.4.0 or higher.'], 'effects': ['Enables or disables the Publisher first-party ID functionality', 'Enables or disables the Publisher first-party ID which is used for delivering more relevant and personalized ads.', 'Enables or disables the Publisher first-party ID for personalized ads', 'Enables or disables the Publisher first-party ID feature, which helps deliver more relevant and personalized ads', 'enables or disables the Publisher first-party ID feature for relevant and personalized ads'], 'parameter_configurations': [{'parameter_values': [False], 'conditions': ['SDK version 21.4.0 or higher', 'Publishers wish to disable Publisher first-party ID to limit data sharing', 'When disabling the Publisher first-party ID functionality'], 'effects': ['Disables the Publisher first-party ID for use in Google Ads', 'Disables the Publisher first-party ID.', 'Data associated with the Publisher first-party ID is not sent, potentially impacting ad personalization', 'disables the use of Publisher first-party ID', 'Publisher first-party ID is disabled; no data will be collected through this means']}, {'parameter_values': [True], 'conditions': ['When enabling the Publisher first-party ID functionality'], 'effects': ['Enables the Publisher first-party ID.', 'Publisher first-party ID is enabled by default; data collected from apps will be utilized for ad personalization', 'Publisher first-party ID is enabled, allowing the collection of more relevant and personalized ads']}]}</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
+          <t>https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/strategies;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/precise-location;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/us-states</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Batch.com</t>
+          <t>Google Ad Manager</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>optOutAndWipeData</t>
+          <t>addNetworkExtrasBundle</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{'API_name': 'optOutAndWipeData', 'class_name': ['Batch'], 'conditions': ['SDK has started via Batch.onStart(Activity)', 'SDK must have been started before opting out.', 'Called after Batch.onStart(Activity).'], 'effects': ["Wipes local installation data and requests remote data removal for the user's Installation ID.", 'Disables the SDK, wipes local data, and requests remote removal of associated data.', 'Wipes local data and requests remote data removal for the associated Installation ID.'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': ['User wants to opt-out and delete all associated data.'], 'effects': ['Logs the user out and deletes local installation data.', 'User-level data associated with the Custom User ID will not be deleted, but Installation ID association will be removed.']}]}</t>
+          <t>{'API_name': 'addNetworkExtrasBundle', 'class_name': ['AdManagerAdRequest.Builder'], 'conditions': ['When creating an ad request and wanting to specify additional parameters for RDP'], 'effects': ['Includes additional parameters in the ad request to inform Google of RDP settings'], 'parameter_configurations': [{'parameter_values': ['rdp', 1], 'conditions': ['To enable restricted data processing'], 'effects': ['Google will restrict the use of certain unique identifiers and serve non-personalized ads']}, {'parameter_values': ['IABUSPrivacy_String', 'IAB_STRING'], 'conditions': ['To inform Google of compliance with IAB specifications'], 'effects': ['Ensures that ad requests are compliant with IAB privacy regulations']}]}</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
+          <t>https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/strategies;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/precise-location;https://developers.google.com/ad-manager/mobile-ads-sdk/android/privacy/us-states</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Batch.com</t>
+          <t>Pangle</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>optIn</t>
+          <t>setChildDirected</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{'API_name': 'optIn', 'class_name': ['Batch'], 'conditions': ['User has previously opted out.', 'Must be called after the user has opted out to re-enable SDK functionalities.', 'User has previously opted-out'], 'effects': ['Re-enables the SDK and allows its functionalities to be resumed.', 'Re-enables the SDK functionalities after an opt-out.', 'Re-enables SDK functionalities and functionalities like Batch.onStart(Activity) must be called.'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': ['User must call Batch.onStart() after opting-in.', 'User wants to opt-in to SDK functionalities again.'], 'effects': ['Restores access to SDK capabilities.', 'Restores the operation of the Batch SDK.']}]}</t>
+          <t>{'API_name': 'setChildDirected', 'class_name': ['PAGConfig.Builder'], 'conditions': ['required to comply with COPPA', 'Required to comply with COPPA regulations'], 'effects': ['Sets the configuration of COPPA where 0 indicates adult and 1 indicates child', 'Sets the configuration of COPPA for user categorization as either adult (0) or child (1)', 'configures whether the app is directed at children under 13', 'Sets the configuration indicating if the app is directed to children', 'configures whether the app is directed to children or adults'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': ['When the app is intended for adults'], 'effects': ['indicates the content is intended for adults', 'User is categorized as an adult', 'User is considered an adult (not directed to children)', 'Allows for advertising strategies aimed at adult users', 'The app is considered adult-directed']}, {'parameter_values': [1], 'conditions': ['When the app is intended for children'], 'effects': ['User is considered a child (directed to children)', 'User is categorized as a child', 'indicates the content is intended for children', 'Adjusts advertising strategies to comply with child-directed regulations', 'The app is considered child-directed']}]}</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
+          <t>https://www.pangleglobal.com/integration/android-initialize-pangle-sdk</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TopOn</t>
+          <t>Pangle</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>setGDPRUploadDataLevel</t>
+          <t>setGDPRConsent</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGDPRUploadDataLevel', 'class_name': ['ATSDK'], 'conditions': ['Required to be called after defining the GDPR consent', "Must call the method to set the GDPR reporting level after determining the user's consent"], 'effects': ['Sets the GDPR level for data reporting', 'Sets the GDPR reporting level internally for the third-party advertising platform', 'Sets the GDPR data reporting level for third-party advertising platforms'], 'parameter_configurations': [{'parameter_values': ['ATSDK.PERSONALIZED', 'ATSDK.NONPERSONALIZED', 'ATSDK.UNKNOWN'], 'conditions': [], 'effects': []}, {'parameter_values': ['context', 'ATSDK.PERSONALIZED'], 'conditions': [], 'effects': ['Allows device data reporting per GDPR regulations']}, {'parameter_values': ['context', 'ATSDK.NONPERSONALIZED'], 'conditions': [], 'effects': ['Disallows device data reporting per GDPR regulations']}, {'parameter_values': ['context', 'ATSDK.UNKNOWN'], 'conditions': [], 'effects': ['GDPR level is unknown; can only be retrieved using getGDPRDataLevel method']}, {'parameter_values': ['ATSDK.PERSONALIZED'], 'conditions': [], 'effects': ['Device data reporting is allowed']}, {'parameter_values': ['ATSDK.NONPERSONALIZED'], 'conditions': [], 'effects': ['Device data is not allowed to be reported']}, {'parameter_values': ['ATSDK.UNKNOWN'], 'conditions': [], 'effects': ['GDPR level remains unknown and can only be queried']}]}</t>
+          <t>{'API_name': 'setGDPRConsent', 'class_name': ['PAGConfig.Builder'], 'conditions': ['compliance with GDPR regulations', 'required to comply with GDPR regulations'], 'effects': ["Sets the configuration of GDPR consent where 0 means user hasn't granted consent and 1 means user has granted consent", "configures the user's consent status for GDPR", 'Sets the GDPR consent status for the user', "sets the user's consent status for data processing under GDPR", 'Sets the GDPR consent status, indicating whether the user has granted consent or not'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['User does not grant GDPR consent', 'User has not granted consent under GDPR', 'User has not granted GDPR consent', 'User does not grant consent under GDPR', 'user does not grant consent for data processing']}, {'parameter_values': [1], 'conditions': [], 'effects': ['user has granted consent for data processing', 'User has granted consent under GDPR', 'User has granted GDPR consent']}]}</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://help.toponad.com/docs/Domestic-privacy-configuration;https://help.toponad.com/docs/Overseas-privacy-configuration;https://help.toponad.com/docs/Google-Data-Security-Guidelines;https://help.toponad.com/docs/Google-UMP-SDK-Gudelines-oThF</t>
+          <t>https://www.pangleglobal.com/integration/android-initialize-pangle-sdk</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TopOn</t>
+          <t>Pangle</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>showGdprAuth</t>
+          <t>setDoNotSell</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{'API_name': 'showGdprAuth', 'class_name': ['ATSDK'], 'conditions': ['To be used when determining GDPR consent settings, usually after the app launches'], 'effects': ['Allows the user to set GDPR consent settings and initializes the SDK accordingly', "Presents the GDPR authorization page and sets data reporting level based on user's choice"], 'parameter_configurations': [{'parameter_values': ['activity', 'new ATGDPRAuthCallback()'], 'conditions': [], 'effects': ['The consent level is set based on user input, which affects data reporting to advertisers']}, {'parameter_values': ['activity', 'new ATGDPRAuthCallback() {...}'], 'conditions': [], 'effects': ['Sets GDPR level based on the onAuthResult callback']}]}</t>
+          <t>{'API_name': 'setDoNotSell', 'class_name': ['PAGConfig.Builder'], 'conditions': ['compliance with CCPA regulations', 'Required to comply with CCPA parameters', 'required to comply with CCPA regulations'], 'effects': ["configures the user's opt-out preference regarding the sale of personal information", "sets the user's choice regarding the sale of personal information", 'Sets the CCPA compliance for selling personal information, indicating whether the user has opted out or not', 'Sets the configuration regarding the sale of personal information', "Sets the configuration of CCPA where 0 means 'sale' of personal information is permitted and 1 means the user has opted out of the 'sale' of their personal information"], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ["User allows the 'sale' of their personal information", 'Sale of personal information is permitted', 'Allows the sale of personal information', "permits the 'sale' of personal information"]}, {'parameter_values': [1], 'conditions': [], 'effects': ["user has opted out of the 'sale' of personal information", 'User has opted out of the sale of personal information', "User opts out of the 'sale' of personal information", 'Opt-out of the sale of personal information']}]}</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://help.toponad.com/docs/Domestic-privacy-configuration;https://help.toponad.com/docs/Overseas-privacy-configuration;https://help.toponad.com/docs/Google-Data-Security-Guidelines;https://help.toponad.com/docs/Google-UMP-SDK-Gudelines-oThF</t>
+          <t>https://www.pangleglobal.com/integration/android-initialize-pangle-sdk</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TopOn</t>
+          <t>AD(X)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>deniedUploadDeviceInfo</t>
+          <t>initialize</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{'API_name': 'deniedUploadDeviceInfo', 'class_name': ['ATSDK'], 'conditions': ['Developers must call this code before initializing the SDK to limit the reporting of device privacy data', 'Called before initializing the SDK to limit the reporting of device privacy data'], 'effects': ['Limits the reporting of specified device data, which might affect ad filling and related functions', 'Restricts the reporting of specified device privacy data', 'Restricts user device data reporting, which may affect ad filling and normal usage of TopOn functions'], 'parameter_configurations': [{'parameter_values': ['DeviceDataInfo.DEVICE_SCREEN_SIZE', 'DeviceDataInfo.ANDROID_ID', 'DeviceDataInfo.APP_PACKAGE_NAME', 'DeviceDataInfo.APP_VERSION_CODE', 'DeviceDataInfo.APP_VERSION_NAME', 'DeviceDataInfo.BRAND', 'DeviceDataInfo.GAID', 'DeviceDataInfo.LANGUAGE', 'DeviceDataInfo.MCC', 'DeviceDataInfo.MNC', 'DeviceDataInfo.MODEL', 'DeviceDataInfo.ORIENTATION', 'DeviceDataInfo.OS_VERSION_CODE', 'DeviceDataInfo.OS_VERSION_NAME', 'DeviceDataInfo.TIMEZONE', 'DeviceDataInfo.USER_AGENT', 'DeviceDataInfo.NETWORK_TYPE', 'DeviceDataInfo.INSTALLER', 'ChinaDeviceDataInfo.MAC', 'ChinaDeviceDataInfo.IMEI', 'ChinaDeviceDataInfo.OAID', 'ChinaDeviceDataInfo.SSID', 'ChinaDeviceDataInfo.IMSI'], 'conditions': ['Called before initializing the SDK'], 'effects': ['User device data will not be uploaded, affecting data collected for advertising and analytics', 'Incoming information will be restricted from reporting']}]}</t>
+          <t>{'API_name': 'initialize', 'class_name': ['ADXSdk'], 'conditions': ['GDPR compliance is required for users in the European Economic Area', 'must be completed before ad requests', 'Initialization must occur before any ad requests', 'SDK version must be 2.5.0 or higher to use UMP for GDPR consent management', 'Initialization must occur once when the app launches', 'must be called once at app launch', 'Must obtain user consent for GDPR compliance if serving EEA users', 'Ad requests must occur after initialization is complete', 'used for initializing the ADX SDK', 'must be called only once at app launch', 'GDPR compliance is required for EU users', 'GDPR compliance must be addressed', 'ad requests must be made after initialization is complete', 'GDPR compliance is required for services targeting EU users'], 'effects': ['initializes the SDK and prepares to handle advertising-related functionalities', 'Provides a framework for the ads to be displayed according to user consent', 'Sets up the SDK to manage user consent for GDPR', 'Enables the AD(X) SDK and provides functionality to obtain GDPR consent', 'initializes the SDK and handles GDPR consent for EU users', 'initializes the SDK and allows for the handling of GDPR consent'], 'parameter_configurations': [{'parameter_values': ['&lt;ADX_APP_ID&gt;', 'context', 'adxConfiguration'], 'conditions': ['GDPR consent is obtained before making ad requests'], 'effects': ['SDK can properly manage GDPR consent and make ad requests afterward']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_LOCATION', 'testDeviceIds'], 'conditions': ['User is from the European Economic Area (EEA)', 'Consent UI must use the context of an Activity'], 'effects': ["Displays a consent UI for GDPR compliance based on the user's location"]}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_DEBUG', 'testDeviceIds'], 'conditions': ['For testing purposes regardless of user location'], 'effects': ['Enables testing of the GDPR consent UI']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_NOT_REQUIRED', 'null'], 'conditions': ['User location does not require consent (EU outside)'], 'effects': ['Allows personalized ads to be shown without user consent']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_CONFIRM', 'null'], 'conditions': ['Directly obtained user consent in EU region'], 'effects': ['Allows personalized ads to be shown based on user consent']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_DENIED', 'null'], 'conditions': ['User has denied consent in the EU region'], 'effects': ['Prevents personalized ads from being displayed']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_LOCATION'], 'conditions': ['User is located in the EU and needs to confirm GDPR consent', "GDPR type must be set to 'POPUP_LOCATION' for users in the EU", 'must provide appropriate Activity context'], 'effects': ['displays consent popup to users in the EU for GDPR compliance', 'Displays a consent popup to the user for GDPR']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_CONFIRM'], 'conditions': ['User is not located in the EU or direct consent is obtained from the user', 'for regions where explicit consent was provided by the user'], 'effects': ["Directly confirms the user's consent for data processing under GDPR", 'enables personalized ads after user consent']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_NOT_REQUIRED'], 'conditions': ['User is located outside the EU where consent is not required', 'for regions where consent is not required'], 'effects': ['allows personalized ads without requiring user consent', 'No consent needed, ads can still be displayed']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.POPUP_DEBUG'], 'conditions': ['For testing purposes to ensure the consent popup works regardless of user location', 'test environment for GDPR consent UI verification'], 'effects': ['displays consent UI regardless of user location for testing', 'Displays the consent popup for debugging']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'ADXConfiguration.GdprType.DIRECT_DENIED'], 'conditions': ['for regions where user has denied consent'], 'effects': ['disables personalized ads']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'POPUP_LOCATION'], 'conditions': ['User is from the EU'], 'effects': ['Displays a consent UI for GDPR compliance based on user location']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'POPUP_DEBUG'], 'conditions': ['Testing the consent UI regardless of user location'], 'effects': ['Allows testing of the GDPR consent UI']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'DIRECT_NOT_REQUIRED'], 'conditions': ['User is not from the EU'], 'effects': ['Consent is not required, and personalized ads are shown']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'DIRECT_DENIED'], 'conditions': ['User denies consent for personal data usage'], 'effects': ['Personalized ads are not shown']}, {'parameter_values': ['&lt;ADX_APP_ID&gt;', 'DIRECT_CONFIRM'], 'conditions': ['User consents to personal data usage'], 'effects': ['Personalized ads are shown']}]}</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://help.toponad.com/docs/Domestic-privacy-configuration;https://help.toponad.com/docs/Overseas-privacy-configuration;https://help.toponad.com/docs/Google-Data-Security-Guidelines;https://help.toponad.com/docs/Google-UMP-SDK-Gudelines-oThF</t>
+          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TradPlus</t>
+          <t>AD(X)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>setCCPADoNotSell</t>
+          <t>getPrivacyURL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCCPADoNotSell', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called after determining the user is in California.', 'should be set before initializing the SDK', 'Must be set if the current region is California for users below version 8.4.0.1', 'Required to comply with CCPA', 'Called when the monitoring callback indicates the region is California', 'only for California users', 'Must be set if the application is targeting California users'], 'effects': ['Defines whether California users can report data or not.', 'Users in California can opt to not sell their personal data', 'Determines whether California users can opt out of data selling', 'indicates whether California users do not want their data sold', 'Makes it possible for California users to opt out of data reporting'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Users have opted-in to allow data reporting'], 'effects': ['Accept reported data']}, {'parameter_values': [False], 'conditions': ['Users do not want their data reported'], 'effects': ['Do not report data']}, {'parameter_values': [True, 'context'], 'conditions': ['User opts to accept reported data', 'User opts in to allow data selling', 'User opts in to allow data reporting.', 'user accepts the sale of data'], 'effects': ["User's data can be reported", 'user data can be reported', "User's data is subject to selling", 'Allows data to be reported.']}, {'parameter_values': [False, 'context'], 'conditions': ['User opts out of allowing data selling', 'user does not accept the sale of data', 'User opts out of data reporting.', 'User opts out of data reporting'], 'effects': ['Prevents data from being reported.', 'user data will not be reported', "User's data is not sold", "User's data will not be reported"]}]}</t>
+          <t>{'API_name': 'getPrivacyURL', 'class_name': ['ADXGDPR', 'ADXGdprManager'], 'conditions': [], 'effects': ['retrieves the privacy policy URL', 'retrieves the URL of the privacy policy', 'Retrieves the URL of the privacy policy document', 'Retrieves the URL of the AD(X) privacy policy', 'returns the URL of the privacy policy document'], 'parameter_configurations': []}</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
+          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TradPlus</t>
+          <t>AD(X)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>setCOPPAIsAgeRestrictedUser</t>
+          <t>getResultGDPR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCOPPAIsAgeRestrictedUser', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called before initializing TradPlus SDK', 'Must be called before initializing the TradPlus SDK', 'Must be set before initializing the TradPlus SDK', 'must be called before initializing TradPlus SDK', 'If the app is for adults, set to false; otherwise true for child users', 'If the application is for adults, set to false'], 'effects': ['Indicates whether the user is a child under the age of 13', 'defines if the user is a child', 'Indicates whether the user is considered a child under COPPA', 'Indicates whether the user is a child under the COPPA guidelines', 'Indicates whether the application targets users under 13 years of age, complying with COPPA regulations.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Indicates that the user is a child']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Indicates that the user is not a child']}, {'parameter_values': [True, 'context'], 'conditions': ['User is a child (under 13 years old)', 'If the application targets children', 'the application is for children'], 'effects': ['Indicates that the user is a child.', "provides children's privacy protections", "Compliance with COPPA for children's online privacy", 'Compliance with COPPA provisions']}, {'parameter_values': [False, 'context'], 'conditions': ['If the application is for adults', 'User is not a child', 'the application is for adults'], 'effects': ['No COPPA restrictions apply', 'Indicates that the user is not a child.', 'No additional COPPA requirements need to be met', 'indicates that the user is not a child']}]}</t>
+          <t>{'API_name': 'getResultGDPR', 'class_name': ['ADXGdprManager'], 'conditions': [], 'effects': ['returns the current GDPR consent state for the user', "retrieves the user's current GDPR consent status", 'Retrieves the current GDPR consent state of the user', 'retrieves the current consent status of the user concerning GDPR', 'Retrieves the current GDPR consent status of the user'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': [], 'effects': ['returns the consent state which can be ADXConsentStateUnknown, ADXConsentStateNotRequired, ADXConsentStateDenied, or ADXConsentStateConfirm']}]}</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
+          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TradPlus</t>
+          <t>AD(X)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>setGDPRDataCollection</t>
+          <t>saveResultGDPR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGDPRDataCollection', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called before initializing the TradPlus SDK', 'Applicable to users in the EU region', 'called when in the EU region', 'Must be set based on the region (EU) and should be called before initializing the SDK', "Must be called to set the user's data collection preferences in compliance with GDPR.", 'must be called before initializing TradPlus SDK', 'Must be called for users in the EU region before initializing the SDK'], 'effects': ['determines the level of GDPR data collection consent', 'Defines whether personalized or non-personalized data can be reported.', 'Sets the level of data collection allowed under GDPR', 'Controls whether personalized device data can be reported', 'Controls the level of data collection based on user consent'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['Device data is allowed to be reported']}, {'parameter_values': [1], 'conditions': [], 'effects': ['Device data is not allowed to be reported']}, {'parameter_values': [0, 'context'], 'conditions': ['user agrees to personalized data reporting', 'User consents to personalized data reporting', 'User agrees to allow personalized device data to be reported'], 'effects': ['Personalized device data is allowed', 'personalized device data is allowed to be reported', 'Allows reporting of personalized device data.', 'Device data is allowed to be reported']}, {'parameter_values': [1, 'context'], 'conditions': ['user disagrees to personalized data reporting', 'User does not agree to allow personalized device data to be reported', 'User does not consent to data reporting'], 'effects': ['nonpersonalized device data is not allowed to be reported', 'Restricts reporting of personalized device data.', 'Non-personalized device data is not allowed', 'Device data is not allowed to be reported']}]}</t>
+          <t>{'API_name': 'saveResultGDPR', 'class_name': ['ADXGdprManager'], 'conditions': ['GDPR consent state must be provided', 'Direct user consent must be gathered outside of the GDPR consent UI', 'consent must be set according to user interactions regarding data usage'], 'effects': ["updates the user's consent status", "sets or updates the user's consent status for GDPR", 'Updates the stored consent status of the user', "Allows direct setting of the user's GDPR consent state", 'changes the current GDPR consent state for the user'], 'parameter_configurations': [{'parameter_values': ['context', 'ADXConsentState'], 'conditions': ["the consent state must correctly reflect the user's choice"], 'effects': ['updates the consent state thereby allowing or disallowing personalized ads']}, {'parameter_values': ['ADXConsentState'], 'conditions': ['User consent state is determined'], 'effects': ['Changes the consent status accordingly', 'stores the updated consent state', 'Sets the specified consent state for the user']}]}</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
+          <t>https://docs.adxcorp.kr/android/sdk-integration/initialize</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TradPlus</t>
+          <t>Batch.com</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>setLGPDConsent</t>
+          <t>setGeoIPEnabled</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLGPDConsent', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called before initializing TradPlus SDK', 'Only applicable in Brazil', 'must be called before initializing TradPlus SDK', 'only need to call in Brazil', 'Must be called before initializing TradPlus SDK in Brazil', 'Must be called before initializing the TradPlus SDK and only in Brazil', 'Must be called before initializing TradPlus SDK only in Brazil.'], 'effects': ['Controls whether device data is allowed to be reported under LGPD', 'determines the consent level under LGPD', 'Sets the level of data reporting consent required by LGPD', 'Defines whether device data reporting is allowed under LGPD.', "Sets the user's consent level under the LGPD"], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['Device data is allowed to be reported']}, {'parameter_values': [1], 'conditions': [], 'effects': ['Device data is not allowed to be reported']}, {'parameter_values': [0, 'context'], 'conditions': ['User agrees to allow device data to be reported', 'User consents to LGPD data reporting', 'data reporting is allowed'], 'effects': ['Allows device data to be reported.', 'Device data is allowed to be reported', 'device data is allowed to be reported']}, {'parameter_values': [1, 'context'], 'conditions': ['User does not consent to LGPD data reporting', 'data reporting is not allowed', 'User does not agree to allow device data to be reported'], 'effects': ['Device data is not allowed to be reported', 'device data is not allowed to be reported', 'Prevents device data from being reported.']}]}</t>
+          <t>{'API_name': 'setGeoIPEnabled', 'class_name': ['Batch'], 'conditions': ['User consent required to enable GeoIP data collection.'], 'effects': ["Enables the resolution of the user's location from IP address."], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ["Activates collection of user's location based on IP."]}, {'parameter_values': [False], 'conditions': [], 'effects': ["Disables collection of user's location based on IP."]}]}</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
+          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BidMachine</t>
+          <t>Batch.com</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>setCoppa</t>
+          <t>updateAutomaticDataCollection</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{'API_name': 'setCoppa', 'class_name': ['BidMachine'], 'conditions': ['To help ensure compliance with COPPA you must indicate whether a user falls within an age-restricted category.'], 'effects': ['Indicates whether the user is subject to COPPA regulations.', 'Indicates whether a user falls within an age-restricted category as per COPPA requirements.', 'Specifies whether COPPA regulations apply for the current user.', 'Indicates whether the SDK should comply with COPPA regulations.', 'Indicates whether a user falls within an age-restricted category for COPPA compliance.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The user is under the age of 13.', 'User is under 13 years of age.'], 'effects': ['User data is handled in compliance with COPPA.', 'Indicates that the user is under the age of 13 and is subject to COPPA regulations.', 'Indicates that the app is restricted for users under age 13.', 'The SDK will treat the user as a child under COPPA regulations.']}, {'parameter_values': [False], 'conditions': ['User is 13 years of age or older.', 'The user is 13 or older.'], 'effects': ['The SDK will not treat the user as a child under COPPA regulations.', 'User data is not handled under COPPA restrictions.', 'Indicates that the user is not under the age of 13 and is not subject to COPPA regulations.', 'No restrictions based on COPPA for this user.']}, {'parameter_values': [None], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'updateAutomaticDataCollection', 'class_name': ['Batch'], 'conditions': ['User consent is necessary to enable automatic data collection for device model, device brand, and GeoIP.', 'User has given consent for automatic data collection'], 'effects': ['Allows enabling or disabling automatic collection of specific user data based on user consent.', 'Enables or disables the collection of specific device data including GeoIP, device brand, and device model.', 'Allows fine-tuning of what data should be automatically collected.'], 'parameter_configurations': [{'parameter_values': [True, True, True], 'conditions': ['User wants to enable GeoIP resolution, device brand, and model information collection.', 'User has provided consent to enable GeoIP, device brand, and device model data collection.', 'GeoIP, device brand, and device model were previously disabled by default.'], 'effects': ["Enables resolution of the user's location from IP address, automatic collection of the device brand and model information.", 'GeoIP, device brand, and device model information will be captured automatically by the SDK.', "User's location can be resolved and the SDK can collect the device brand and model."]}, {'parameter_values': [False, False, False], 'conditions': ['User has revoked consent for collection.', 'User chooses to disable GeoIP, device brand, and device model collection.', 'User wants to disable GeoIP resolution, device brand, and model information collection.'], 'effects': ['GeoIP, device brand, and device model information will not be captured.', 'Disables collection of the specified data.', 'GeoIP resolution is not performed and device brand and model data are not collected.']}]}</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
+          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BidMachine</t>
+          <t>Batch.com</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>setSubjectToGDPR</t>
+          <t>optOut</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['BidMachine'], 'conditions': ['Publisher indicates if GDPR applies to the current user.', 'The Publisher needs to send a boolean flag indicating if GDPR applies to the current user.', 'Publisher needs to send a boolean flag indicating if GDPR applies to the current user.'], 'effects': ['Indicates whether the app must comply with GDPR.', 'Indicates whether the SDK needs to comply with GDPR regulations.', 'Indicates that GDPR regulations apply for the current user.', 'Indicates if GDPR regulations apply for user data processing.', 'Indicates if GDPR regulations apply to the current user.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is located in the European Union or subject to GDPR regulations.', 'The user is located in a region where GDPR applies.'], 'effects': ['The app must collect user consent prior to requesting any ads from the Exchange server.', 'Must collect user consent prior to processing data.', 'User data is processed in compliance with GDPR.', 'The SDK will enforce GDPR compliance for the user.']}, {'parameter_values': [False], 'conditions': ['User is not located in the European Union.', 'The user is not located in a region where GDPR applies.'], 'effects': ['No need to comply with GDPR for this user.', 'User data is not subject to GDPR regulations.', 'The SDK will not enforce GDPR compliance for the user.', 'The app is not required to follow GDPR regulations.']}, {'parameter_values': [None], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'optOut', 'class_name': ['Batch'], 'conditions': ['Called after Batch.onStart(Activity) to ensure the SDK has started.', 'SDK has started via Batch.onStart(Activity)', 'SDK must have been started before opting out.'], 'effects': ['Disables all SDK functionalities including data collection, In-App campaigns, and network capabilities.', 'Prevents Batch from performing any operations, disabling all campaigns and network capabilities.', 'Prevents any network capability from the SDK, disables In-App campaigns, and rejects any related method calls.'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': ['User wants to opt-out from the SDK functionalities.'], 'effects': ['Prevents any SDK operations and network capabilities.', 'Will cease all operations associated with the Batch SDK.']}]}</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
+          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BidMachine</t>
+          <t>Batch.com</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>setConsentConfig</t>
+          <t>optOutAndWipeData</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{'API_name': 'setConsentConfig', 'class_name': ['BidMachine'], 'conditions': ['User consent must be collected prior to requesting ads if GDPR regulations apply.'], 'effects': ['Sets the GDPR consent configuration for the user.', "Allows the app to configure the user's consent settings.", 'Configures user consent for GDPR compliance.', 'Sets the GDPR consent string to indicate user consent for data processing.'], 'parameter_configurations': [{'parameter_values': [True, '&lt;GDPR CONSENT STRING&gt;'], 'conditions': ['User has provided consent'], 'effects': ['Consent string is sent to the server indicating user consent.', 'Sets the consent string to indicate user consent according to GDPR.']}, {'parameter_values': [False, None], 'conditions': ['User has not provided consent.', 'User has not provided consent'], 'effects': ['No consent string is sent to the server.', 'User data processing is restricted.']}, {'parameter_values': [True, 'consent_string'], 'conditions': [], 'effects': ['Indicates consent for processing personal data under GDPR.']}, {'parameter_values': [False, 'consent_string'], 'conditions': [], 'effects': ['Indicates that consent has not been given for processing personal data.']}, {'parameter_values': [None, None], 'conditions': [], 'effects': []}, {'parameter_values': [False, '&lt;GDPR CONSENT STRING&gt;'], 'conditions': [], 'effects': ['Sets the consent string without user consent.']}, {'parameter_values': [True, 'exampleConsentString'], 'conditions': ['User has given consent according to GDPR regulations.'], 'effects': ['User consents to have their data processed for advertising.']}]}</t>
+          <t>{'API_name': 'optOutAndWipeData', 'class_name': ['Batch'], 'conditions': ['SDK has started via Batch.onStart(Activity)', 'SDK must have been started before opting out.', 'Called after Batch.onStart(Activity).'], 'effects': ["Wipes local installation data and requests remote data removal for the user's Installation ID.", 'Disables the SDK, wipes local data, and requests remote removal of associated data.', 'Wipes local data and requests remote data removal for the associated Installation ID.'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': ['User wants to opt-out and delete all associated data.'], 'effects': ['Logs the user out and deletes local installation data.', 'User-level data associated with the Custom User ID will not be deleted, but Installation ID association will be removed.']}]}</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
+          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BidMachine</t>
+          <t>Batch.com</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>setUSPrivacyString</t>
+          <t>optIn</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUSPrivacyString', 'class_name': ['BidMachine'], 'conditions': ['To comply with CCPA, the U.S. Privacy String must be set if applicable.', 'To pass CCPA U.S. Privacy String to BidMachine, use this method.', 'Used to pass the CCPA U.S. Privacy String.', 'To pass CCPA U.S. Privacy String to BidMachine.'], 'effects': ['Sets the U.S. Privacy String for compliance with CCPA.', "Sets the user's privacy consent status according to CCPA.", "Confirms the user's privacy preferences under CCPA.", 'Allows compliance with CCPA regulations.', 'Sets the CCPA U.S. Privacy String to indicate user consent or opt-out choice.'], 'parameter_configurations': [{'parameter_values': ['&lt;CCPA U.S. Privacy STRING&gt;'], 'conditions': [], 'effects': ['Sends the specified CCPA privacy string to the server.']}, {'parameter_values': ['privacy_string'], 'conditions': [], 'effects': ['Sets the U.S. Privacy String for processing user data under CCPA.']}, {'parameter_values': [None], 'conditions': ['User has not made a choice regarding the sale of their personal information.'], 'effects': ["User's personal information may be sold."]}, {'parameter_values': ['&lt;CCPA U.S. PRIVACY STRING&gt;'], 'conditions': [], 'effects': ['Sets the CCPA U.S. Privacy String for compliance.']}, {'parameter_values': ['1YNY'], 'conditions': ['User opts out of the sale of their personal information.'], 'effects': ["User's personal information is not sold."]}]}</t>
+          <t>{'API_name': 'optIn', 'class_name': ['Batch'], 'conditions': ['User has previously opted out.', 'Must be called after the user has opted out to re-enable SDK functionalities.', 'User has previously opted-out'], 'effects': ['Re-enables the SDK and allows its functionalities to be resumed.', 'Re-enables the SDK functionalities after an opt-out.', 'Re-enables SDK functionalities and functionalities like Batch.onStart(Activity) must be called.'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': ['User must call Batch.onStart() after opting-in.', 'User wants to opt-in to SDK functionalities again.'], 'effects': ['Restores access to SDK capabilities.', 'Restores the operation of the Batch SDK.']}]}</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
+          <t>https://doc.batch.com/android/data-privacy/data-collection/;https://doc.batch.com/android/data-privacy/opt-out/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BidMachine</t>
+          <t>TopOn</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>setGPP</t>
+          <t>setGDPRUploadDataLevel</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGPP', 'class_name': ['BidMachine'], 'conditions': ['To pass GPP information to BidMachine.'], 'effects': ['Sets the GPP string to indicate user consent for data processing in accordance with the Global Privacy Platform.', 'Sets the GPP string and IDs for global privacy compliance.', 'Sets the Global Privacy Platform information for compliance.', 'Enables setting of the Global Privacy Platform consent string.'], 'parameter_configurations': [{'parameter_values': ['&lt;GPP STRING&gt;', '&lt;GPP ID LIST&gt;'], 'conditions': [], 'effects': ['Passes the specified GPP information to the server.']}, {'parameter_values': ['gpp_string', []], 'conditions': [], 'effects': ['Sets GPP string for compliance with global privacy regulations.']}, {'parameter_values': [None, None], 'conditions': ['GPP does not apply.'], 'effects': []}, {'parameter_values': ['&lt;GPP STRING&gt;', '&lt;GPP IDs&gt;'], 'conditions': [], 'effects': ['Sets the GPP string and IDs for compliance.']}, {'parameter_values': ['gppStringExample', [1, 2, 3]], 'conditions': ['GPP applies for the current user.'], 'effects': ['User data processing complies with the GPP requirements.']}]}</t>
+          <t>{'API_name': 'setGDPRUploadDataLevel', 'class_name': ['ATSDK'], 'conditions': ['Required to be called after defining the GDPR consent', "Must call the method to set the GDPR reporting level after determining the user's consent"], 'effects': ['Sets the GDPR level for data reporting', 'Sets the GDPR reporting level internally for the third-party advertising platform', 'Sets the GDPR data reporting level for third-party advertising platforms'], 'parameter_configurations': [{'parameter_values': ['ATSDK.PERSONALIZED', 'ATSDK.NONPERSONALIZED', 'ATSDK.UNKNOWN'], 'conditions': [], 'effects': []}, {'parameter_values': ['context', 'ATSDK.PERSONALIZED'], 'conditions': [], 'effects': ['Allows device data reporting per GDPR regulations']}, {'parameter_values': ['context', 'ATSDK.NONPERSONALIZED'], 'conditions': [], 'effects': ['Disallows device data reporting per GDPR regulations']}, {'parameter_values': ['context', 'ATSDK.UNKNOWN'], 'conditions': [], 'effects': ['GDPR level is unknown; can only be retrieved using getGDPRDataLevel method']}, {'parameter_values': ['ATSDK.PERSONALIZED'], 'conditions': [], 'effects': ['Device data reporting is allowed']}, {'parameter_values': ['ATSDK.NONPERSONALIZED'], 'conditions': [], 'effects': ['Device data is not allowed to be reported']}, {'parameter_values': ['ATSDK.UNKNOWN'], 'conditions': [], 'effects': ['GDPR level remains unknown and can only be queried']}]}</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
+          <t>https://help.toponad.com/docs/Domestic-privacy-configuration;https://help.toponad.com/docs/Overseas-privacy-configuration;https://help.toponad.com/docs/Google-Data-Security-Guidelines;https://help.toponad.com/docs/Google-UMP-SDK-Gudelines-oThF</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MobileFuse</t>
+          <t>TopOn</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>setAllowLocation</t>
+          <t>showGdprAuth</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{'API_name': 'setAllowLocation', 'class_name': ['MobileFuseTargetingData'], 'conditions': ['Application must display a consent dialog for location tracking', 'Android Manifest must be configured to allow opt-in mode', 'must have user consent for location tracking', 'User must opt-in to location-based ad personalization', 'Required to display a consent dialog prior to location tracking', 'requires opt-in configuration in the Android Manifest if needed'], 'effects': ['Manages whether the SDK can use user location for ad personalization.', 'enables or disables location targeting for ad personalization', 'Enables or disables location tracking for ad personalization', 'Enables or disables location tracking for personalized ads'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['user has opted in to location-based ad personalization', 'User opts in to location-based ad personalization', 'User has opted in to location-based ad personalization'], 'effects': ['Location data may be collected and used for ad targeting', 'Enables location-based ad personalization', 'Enables location tracking for personalized ads.', 'the SDK will collect and use location data for personalized ads']}, {'parameter_values': [False], 'conditions': ['User opts out of location-based ad personalization', 'user has opted out of location-based ad personalization', 'User has opted out of location-based ad personalization'], 'effects': ['Disables location-based ad personalization', 'the SDK will not collect or transmit any location data', 'Location data is not collected or used for ad targeting', 'Disables location tracking and prevents the collection of location data.']}]}</t>
+          <t>{'API_name': 'showGdprAuth', 'class_name': ['ATSDK'], 'conditions': ['To be used when determining GDPR consent settings, usually after the app launches'], 'effects': ['Allows the user to set GDPR consent settings and initializes the SDK accordingly', "Presents the GDPR authorization page and sets data reporting level based on user's choice"], 'parameter_configurations': [{'parameter_values': ['activity', 'new ATGDPRAuthCallback()'], 'conditions': [], 'effects': ['The consent level is set based on user input, which affects data reporting to advertisers']}, {'parameter_values': ['activity', 'new ATGDPRAuthCallback() {...}'], 'conditions': [], 'effects': ['Sets GDPR level based on the onAuthResult callback']}]}</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://docs.mobilefuse.com/docs/android-sdk-data-privacy;https://docs.mobilefuse.com/docs/android-location-privacy</t>
+          <t>https://help.toponad.com/docs/Domestic-privacy-configuration;https://help.toponad.com/docs/Overseas-privacy-configuration;https://help.toponad.com/docs/Google-Data-Security-Guidelines;https://help.toponad.com/docs/Google-UMP-SDK-Gudelines-oThF</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MobileFuse</t>
+          <t>TopOn</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>setPrivacyPreferences</t>
+          <t>deniedUploadDeviceInfo</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPrivacyPreferences', 'class_name': ['MobileFuse'], 'conditions': ['The user is subject to CCPA or COPPA regulations', 'must indicate whether the user is subject to COPPA if under 13 years of age', 'must provide a GPP consent string', 'User must provide GPP Consent String or US Privacy Consent String', 'User needs to provide consent strings or do not track preferences', 'GPP or US Privacy Strings must be configured', 'User age must be verified for COPPA compliance'], 'effects': ['Sets the privacy preferences for the user, affecting data collection and ad targeting', 'Configures privacy preferences for the MobileFuse SDK based on user consent', 'configures the privacy preferences for the MobileFuse SDK including consent for data usage and COPPA compliance', 'Configures the privacy preferences of the user, affecting data collection for ads.'], 'parameter_configurations': [{'parameter_values': ['GPP Consent String', False, '&lt;US Privacy String&gt;'], 'conditions': ['User is not under 13 years of age'], 'effects': ['User consented to data collection under GPP and US privacy laws', "User's data is collected and used under the defined privacy settings"]}, {'parameter_values': ['GPP Consent String', True, '&lt;US Privacy String&gt;'], 'conditions': ['User is under 13 years of age'], 'effects': ['User is not tracked or collected against COPPA regulations']}, {'parameter_values': [None, True], 'conditions': ["The user opts out of tracking by setting 'do not track' option"], 'effects': ["User's data is not collected or used for personalized advertising"]}, {'parameter_values': ['null', True, 'null'], 'conditions': ['User opts out of tracking'], 'effects': ['User is opted out of data collection for ad personalization']}, {'parameter_values': ['DBACNYA~CPXxRfAPXxRfAAfKABENB-CgAAAAAAAAAAYgAAAAAAAA~1YNN', None, None], 'conditions': ['when providing a valid GPP Consent String'], 'effects': ["the MobileFuse SDK is configured to respect the user's privacy choices"]}, {'parameter_values': [None, False, '&lt;US Privacy String&gt;'], 'conditions': ['when the user is not subject to COPPA'], 'effects': ['ensures compliance with US Privacy regulations']}, {'parameter_values': [None, True, None], 'conditions': ["when user opts out of data tracking using 'do not track' option"], 'effects': ['user data is not collected or used for personalized ads']}, {'parameter_values': ['GPP Consent String', '&lt;US Privacy String&gt;', False], 'conditions': ['User is not under 13 years of age for COPPA compliance'], 'effects': ['Enables collection of user data for ad personalization.']}, {'parameter_values': [None, '&lt;US Privacy String&gt;', True], 'conditions': ['User opts for do not track'], 'effects': ['User is opted out of data collection for ads.']}]}</t>
+          <t>{'API_name': 'deniedUploadDeviceInfo', 'class_name': ['ATSDK'], 'conditions': ['Developers must call this code before initializing the SDK to limit the reporting of device privacy data', 'Called before initializing the SDK to limit the reporting of device privacy data'], 'effects': ['Limits the reporting of specified device data, which might affect ad filling and related functions', 'Restricts the reporting of specified device privacy data', 'Restricts user device data reporting, which may affect ad filling and normal usage of TopOn functions'], 'parameter_configurations': [{'parameter_values': ['DeviceDataInfo.DEVICE_SCREEN_SIZE', 'DeviceDataInfo.ANDROID_ID', 'DeviceDataInfo.APP_PACKAGE_NAME', 'DeviceDataInfo.APP_VERSION_CODE', 'DeviceDataInfo.APP_VERSION_NAME', 'DeviceDataInfo.BRAND', 'DeviceDataInfo.GAID', 'DeviceDataInfo.LANGUAGE', 'DeviceDataInfo.MCC', 'DeviceDataInfo.MNC', 'DeviceDataInfo.MODEL', 'DeviceDataInfo.ORIENTATION', 'DeviceDataInfo.OS_VERSION_CODE', 'DeviceDataInfo.OS_VERSION_NAME', 'DeviceDataInfo.TIMEZONE', 'DeviceDataInfo.USER_AGENT', 'DeviceDataInfo.NETWORK_TYPE', 'DeviceDataInfo.INSTALLER', 'ChinaDeviceDataInfo.MAC', 'ChinaDeviceDataInfo.IMEI', 'ChinaDeviceDataInfo.OAID', 'ChinaDeviceDataInfo.SSID', 'ChinaDeviceDataInfo.IMSI'], 'conditions': ['Called before initializing the SDK'], 'effects': ['User device data will not be uploaded, affecting data collected for advertising and analytics', 'Incoming information will be restricted from reporting']}]}</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://docs.mobilefuse.com/docs/android-sdk-data-privacy;https://docs.mobilefuse.com/docs/android-location-privacy</t>
+          <t>https://help.toponad.com/docs/Domestic-privacy-configuration;https://help.toponad.com/docs/Overseas-privacy-configuration;https://help.toponad.com/docs/Google-Data-Security-Guidelines;https://help.toponad.com/docs/Google-UMP-SDK-Gudelines-oThF</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Bigo Ads</t>
+          <t>TradPlus</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>setUserConsent</t>
+          <t>setCCPADoNotSell</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{'API_name': 'setUserConsent', 'class_name': ['BigoAdSdk'], 'conditions': ['The API must be called to pass the GDPR, CCPA, or LGPD consent', 'must pass user consent for processing personal information', 'User must provide consent for data processing', 'User must provide consent', 'User must provide consent for the processing of personal information.'], 'effects': ["Stores and processes the user's personal information based on the consent flag", 'determines whether user consent for GDPR, CCPA, or LGPD is stored', 'Indicates whether the user has given consent to store and process personal information.', 'Sets the user consent status for processing personal information', "Determines whether personal information can be stored and processed based on the user's consent status"], 'parameter_configurations': [{'parameter_values': ['context', 'ConsentOptions.GDPR', True], 'conditions': ['user gives consent under GDPR', 'User has given consent as per GDPR', 'User gives consent under GDPR.', 'User has given consent to store and process personal information'], 'effects': ['Consent to store and process personal information under GDPR', "User's personal information can be processed under GDPR guidelines", "User's consent is recorded for GDPR compliance", 'Consent for GDPR compliance is recorded.', 'consent is granted to store and process personal information']}, {'parameter_values': ['context', 'ConsentOptions.GDPR', False], 'conditions': ['user declines consent under GDPR', 'User declines consent under GDPR.', 'User has declined consent as per GDPR', 'User has declined consent to store and process personal information'], 'effects': ['No consent to store and process personal information under GDPR', "User's personal information cannot be processed under GDPR guidelines", "User's consent is recorded for GDPR compliance", 'consent is denied to store and process personal information', "User's personal information will not be stored or processed."]}, {'parameter_values': ['context', 'ConsentOptions.CCPA', True], 'conditions': ['User gives consent under CCPA.', 'User has given consent as per CCPA', 'user gives consent under CCPA', 'User has given consent to store and process personal information'], 'effects': ["User's consent is recorded for CCPA compliance", 'Consent for CCPA compliance is recorded.', 'Consent to store and process personal information under CCPA', "User's personal information can be processed under CCPA guidelines", 'consent is granted to store and process personal information']}, {'parameter_values': ['context', 'ConsentOptions.CCPA', False], 'conditions': ['User has declined consent as per CCPA', 'User declines consent under CCPA.', 'user declines consent under CCPA', 'User has declined consent to store and process personal information'], 'effects': ['No consent to store and process personal information under CCPA', "User's consent is recorded for CCPA compliance", 'consent is denied to store and process personal information', "User's personal information will not be stored or processed.", "User's personal information cannot be processed under CCPA guidelines"]}, {'parameter_values': ['context', 'ConsentOptions.LGPD', True], 'conditions': ['User gives consent under LGPD.', 'user gives consent under LGPD', 'User has given consent as per LGPD', 'User has given consent to store and process personal information'], 'effects': ["User's personal information can be processed under LGPD guidelines", 'Consent for LGPD compliance is recorded.', "User's consent is recorded for LGPD compliance", 'Consent to store and process personal information under LGPD', 'consent is granted to store and process personal information']}, {'parameter_values': ['context', 'ConsentOptions.LGPD', False], 'conditions': ['user declines consent under LGPD', 'User has declined consent as per LGPD', 'User declines consent under LGPD.', 'User has declined consent to store and process personal information'], 'effects': ["User's personal information will not be stored or processed.", "User's personal information cannot be processed under LGPD guidelines", 'consent is denied to store and process personal information', "User's consent is recorded for LGPD compliance", 'No consent to store and process personal information under LGPD']}]}</t>
+          <t>{'API_name': 'setCCPADoNotSell', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called after determining the user is in California.', 'should be set before initializing the SDK', 'Must be set if the current region is California for users below version 8.4.0.1', 'Required to comply with CCPA', 'Called when the monitoring callback indicates the region is California', 'only for California users', 'Must be set if the application is targeting California users'], 'effects': ['Defines whether California users can report data or not.', 'Users in California can opt to not sell their personal data', 'Determines whether California users can opt out of data selling', 'indicates whether California users do not want their data sold', 'Makes it possible for California users to opt out of data reporting'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Users have opted-in to allow data reporting'], 'effects': ['Accept reported data']}, {'parameter_values': [False], 'conditions': ['Users do not want their data reported'], 'effects': ['Do not report data']}, {'parameter_values': [True, 'context'], 'conditions': ['User opts to accept reported data', 'User opts in to allow data selling', 'User opts in to allow data reporting.', 'user accepts the sale of data'], 'effects': ["User's data can be reported", 'user data can be reported', "User's data is subject to selling", 'Allows data to be reported.']}, {'parameter_values': [False, 'context'], 'conditions': ['User opts out of allowing data selling', 'user does not accept the sale of data', 'User opts out of data reporting.', 'User opts out of data reporting'], 'effects': ['Prevents data from being reported.', 'user data will not be reported', "User's data is not sold", "User's data will not be reported"]}]}</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://www.bigossp.com/guide/sdk/android/document</t>
+          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>TradPlus</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>setGdprConsent</t>
+          <t>setCOPPAIsAgeRestrictedUser</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGdprConsent', 'class_name': ['RequestManager', 'NimbusAdManager', 'NimbusAdManager / RequestManager'], 'conditions': ['Consent string must be generated according to GDPR regulations', 'Consent string must be created and valid', 'Application must comply with GDPR regulations', 'Requires the user consent string to comply with GDPR regulations', "Required to manage user's consent for GDPR", 'Must be called after setting up a Consent Management Platform', 'User must provide a valid consent string according to GDPR regulations'], 'effects': ['Sets the GDPR consent string for the user', 'Allows the SDK to manage user consent for GDPR', 'Sets the GDPR consent string for the user for all requests', 'Overrides existing GDPR values set in SharedPreferences', 'Sets the GDPR consent string to manage user consent for data protection', 'Sets the GDPR consent string which will override any values set in SharedPreferences'], 'parameter_configurations': [{'parameter_values': ['consentString'], 'conditions': ['The app is required to manage user consent according to GDPR standards', 'The consentString is properly formatted as per GDPR requirements', 'The consent string must be in accordance with the IAB TCFv2 framework', "User's consent string must be defined", 'Called before initializing any Demand Providers'], 'effects': ['The consent string is now applied for all requests made by the Nimbus SDK', 'Enables the Nimbus SDK to append the GDPR consent details to outbound requests', "User's consent status for data protection is updated according to the consent string provided", 'The consent string is used for GDPR compliance in outbound requests', 'Overwrites existing values in SharedPreferences']}]}</t>
+          <t>{'API_name': 'setCOPPAIsAgeRestrictedUser', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called before initializing TradPlus SDK', 'Must be called before initializing the TradPlus SDK', 'Must be set before initializing the TradPlus SDK', 'must be called before initializing TradPlus SDK', 'If the app is for adults, set to false; otherwise true for child users', 'If the application is for adults, set to false'], 'effects': ['Indicates whether the user is a child under the age of 13', 'defines if the user is a child', 'Indicates whether the user is considered a child under COPPA', 'Indicates whether the user is a child under the COPPA guidelines', 'Indicates whether the application targets users under 13 years of age, complying with COPPA regulations.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Indicates that the user is a child']}, {'parameter_values': [False], 'conditions': [], 'effects': ['Indicates that the user is not a child']}, {'parameter_values': [True, 'context'], 'conditions': ['User is a child (under 13 years old)', 'If the application targets children', 'the application is for children'], 'effects': ['Indicates that the user is a child.', "provides children's privacy protections", "Compliance with COPPA for children's online privacy", 'Compliance with COPPA provisions']}, {'parameter_values': [False, 'context'], 'conditions': ['If the application is for adults', 'User is not a child', 'the application is for adults'], 'effects': ['No COPPA restrictions apply', 'Indicates that the user is not a child.', 'No additional COPPA requirements need to be met', 'indicates that the user is not a child']}]}</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://docs.adsbynimbus.com/docs/sdk/android/data-privacy-compliance</t>
+          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>TradPlus</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>usPrivacyString</t>
+          <t>setGDPRDataCollection</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{'API_name': 'usPrivacyString', 'class_name': ['Nimbus'], 'conditions': ['User must determine if they fall within a US Privacy jurisdiction'], 'effects': ['Sets the privacy string used for compliance with CCPA'], 'parameter_configurations': [{'parameter_values': ['privacyString'], 'conditions': ['Should be set before initializing any Demand Providers'], 'effects': ['The CCPA privacy string is utilized for managing user consent']}]}</t>
+          <t>{'API_name': 'setGDPRDataCollection', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called before initializing the TradPlus SDK', 'Applicable to users in the EU region', 'called when in the EU region', 'Must be set based on the region (EU) and should be called before initializing the SDK', "Must be called to set the user's data collection preferences in compliance with GDPR.", 'must be called before initializing TradPlus SDK', 'Must be called for users in the EU region before initializing the SDK'], 'effects': ['determines the level of GDPR data collection consent', 'Defines whether personalized or non-personalized data can be reported.', 'Sets the level of data collection allowed under GDPR', 'Controls whether personalized device data can be reported', 'Controls the level of data collection based on user consent'], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['Device data is allowed to be reported']}, {'parameter_values': [1], 'conditions': [], 'effects': ['Device data is not allowed to be reported']}, {'parameter_values': [0, 'context'], 'conditions': ['user agrees to personalized data reporting', 'User consents to personalized data reporting', 'User agrees to allow personalized device data to be reported'], 'effects': ['Personalized device data is allowed', 'personalized device data is allowed to be reported', 'Allows reporting of personalized device data.', 'Device data is allowed to be reported']}, {'parameter_values': [1, 'context'], 'conditions': ['user disagrees to personalized data reporting', 'User does not agree to allow personalized device data to be reported', 'User does not consent to data reporting'], 'effects': ['nonpersonalized device data is not allowed to be reported', 'Restricts reporting of personalized device data.', 'Non-personalized device data is not allowed', 'Device data is not allowed to be reported']}]}</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://docs.adsbynimbus.com/docs/sdk/android/data-privacy-compliance</t>
+          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>TradPlus</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>COPPA</t>
+          <t>setLGPDConsent</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{'API_name': 'COPPA', 'class_name': ['Nimbus'], 'conditions': ['Must be called after initialization of the SDK', 'App must be governed by COPPA regulations'], 'effects': ['Configures the SDK to send compliance information to demand partners', 'Configures SDK to send information to demand partners for compliance with COPPA'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The app is directed towards children under the age of 13', 'Call this function after SDK initialization'], 'effects': ['Enables COPPA compliance for data collection', 'Enables the SDK to comply with COPPA requirements']}]}</t>
+          <t>{'API_name': 'setLGPDConsent', 'class_name': ['TradPlusSdk'], 'conditions': ['Must be called before initializing TradPlus SDK', 'Only applicable in Brazil', 'must be called before initializing TradPlus SDK', 'only need to call in Brazil', 'Must be called before initializing TradPlus SDK in Brazil', 'Must be called before initializing the TradPlus SDK and only in Brazil', 'Must be called before initializing TradPlus SDK only in Brazil.'], 'effects': ['Controls whether device data is allowed to be reported under LGPD', 'determines the consent level under LGPD', 'Sets the level of data reporting consent required by LGPD', 'Defines whether device data reporting is allowed under LGPD.', "Sets the user's consent level under the LGPD"], 'parameter_configurations': [{'parameter_values': [0], 'conditions': [], 'effects': ['Device data is allowed to be reported']}, {'parameter_values': [1], 'conditions': [], 'effects': ['Device data is not allowed to be reported']}, {'parameter_values': [0, 'context'], 'conditions': ['User agrees to allow device data to be reported', 'User consents to LGPD data reporting', 'data reporting is allowed'], 'effects': ['Allows device data to be reported.', 'Device data is allowed to be reported', 'device data is allowed to be reported']}, {'parameter_values': [1, 'context'], 'conditions': ['User does not consent to LGPD data reporting', 'data reporting is not allowed', 'User does not agree to allow device data to be reported'], 'effects': ['Device data is not allowed to be reported', 'device data is not allowed to be reported', 'Prevents device data from being reported.']}]}</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://docs.adsbynimbus.com/docs/sdk/android/data-privacy-compliance</t>
+          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Digital Turbine FairBid</t>
+          <t>TradPlus</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>setGdprConsent</t>
+          <t>setCustomParams</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGdprConsent', 'class_name': ['UserInfo'], 'conditions': ['User is located in the EU, registered as an EU resident, or the app is specifically targeted to EU users', 'User is located in the EU', 'User is located in EU, registered as EU resident, or app is targeted to EU users', 'User has registered with the app as an EU resident', 'User is located in the EU, registered as an EU resident, or app is targeted to EU users', 'GDPR applies if the user is currently located in the EU, has registered as an EU resident, or the app is targeted to EU users', 'The app is specifically targeted to EU users'], 'effects': ['The SDK caches the consent for future sessions.', 'Determines whether to show contextual ads or personalized ads based on user consent', 'Determines whether to show contextual ads or targeted ads based on user consent', 'Determines whether the DT FairBid SDK shows contextual ads or personalized ads based on user consent', 'The SDK will show contextual ads only if consent is not given, potentially affecting revenue', 'If consent is not passed, only contextual ads will be shown, potentially negatively affecting revenue.'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User provides consent for data processing', 'User has given consent', 'User has provided consent'], 'effects': ['Consent is recorded and relevant ads can be shown', 'Personalized ads may be shown, affecting revenue positively', 'User sees personalized ads', 'Targeted ads will be shown', "User's consent is acknowledged and considered for ad personalization."]}, {'parameter_values': [False, 'context'], 'conditions': ['User does not provide consent', 'User has not given consent', 'User has not provided consent'], 'effects': ['Only contextual ads are shown, potentially reducing revenue', 'Only contextual ads are shown, which might negatively affect revenue', 'Only contextual ads will be shown to the user.', 'Only contextual ads will be shown, potentially negatively affecting revenue', 'Only contextual ads will be shown']}]}</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+          <t>https://docs.tradplusad.com/en/docs/tradplussdk_android_doc_v6/privacy_policy/os_privacy_policy</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Digital Turbine FairBid</t>
+          <t>BidMachine</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>setIabUsPrivacyString</t>
+          <t>setCoppa</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{'API_name': 'setIabUsPrivacyString', 'class_name': ['UserInfo'], 'conditions': ['User opts out or gives consent regarding their personal information', 'Applicable when a user opts out of data sharing under CCPA', 'User is a California resident', 'First time gathering user opt-out consent', 'User opt out or consent needs to be set before initializing SDK', 'User is a California resident or CCPA applies'], 'effects': ['Sets the privacy string according to CCPA regulations', 'Sets the IAB US privacy string affecting how user data is handled', "The SDK will respect the user's privacy choices based on the provided string", 'Sets the IAB US Privacy String for the SDK', 'The SDK takes the user’s opt-out into consideration when initializing.'], 'parameter_configurations': [{'parameter_values': ['1YNN', 'context'], 'conditions': ['User chooses not to opt out', 'User chooses NOT to opt out', 'User opts out of targeted advertising'], 'effects': ['Advertising is shown as usual', 'User can receive ads as usual', "User's data can be used for advertising as usual", 'User is allowed to receive personalized advertising.', "User's choice to restrict advertising is respected"]}, {'parameter_values': ['1YYN', 'context'], 'conditions': ['User opts out of advertising', 'User opts in to targeted advertising', 'User chooses to opt out'], 'effects': ["User's choice to allow advertising is respected", 'Restricts the advertising options for the user', "User's data will be restricted from advertising", "User's advertisement preferences are restricted.", 'Restricts advertising and opts out']}, {'parameter_values': ['1---', 'context'], 'conditions': ['CCPA does not apply (user not a resident of California)', 'CCPA does not apply (e.g., user is not a resident of California)', 'User is not a resident of California', 'CCPA does not apply (for example, the user is not a resident of California)', 'CCPA does not apply (user not a California resident)'], 'effects': ['No privacy string needs to be sent, either skip the API or use 1---', 'The privacy string can be skipped or set to this value', 'API call can be skipped or considered.', 'API may be skipped or set to this value', 'No specific privacy string is set']}]}</t>
+          <t>{'API_name': 'setCoppa', 'class_name': ['BidMachine'], 'conditions': ['To help ensure compliance with COPPA you must indicate whether a user falls within an age-restricted category.'], 'effects': ['Indicates whether the user is subject to COPPA regulations.', 'Indicates whether a user falls within an age-restricted category as per COPPA requirements.', 'Specifies whether COPPA regulations apply for the current user.', 'Indicates whether the SDK should comply with COPPA regulations.', 'Indicates whether a user falls within an age-restricted category for COPPA compliance.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The user is under the age of 13.', 'User is under 13 years of age.'], 'effects': ['User data is handled in compliance with COPPA.', 'Indicates that the user is under the age of 13 and is subject to COPPA regulations.', 'Indicates that the app is restricted for users under age 13.', 'The SDK will treat the user as a child under COPPA regulations.']}, {'parameter_values': [False], 'conditions': ['User is 13 years of age or older.', 'The user is 13 or older.'], 'effects': ['The SDK will not treat the user as a child under COPPA regulations.', 'User data is not handled under COPPA restrictions.', 'Indicates that the user is not under the age of 13 and is not subject to COPPA regulations.', 'No restrictions based on COPPA for this user.']}, {'parameter_values': [None], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Digital Turbine FairBid</t>
+          <t>BidMachine</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>setLgpdConsent</t>
+          <t>setSubjectToGDPR</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{'API_name': 'setLgpdConsent', 'class_name': ['UserInfo'], 'conditions': ['LGPD applies if the user is currently located in Brazil, has registered as a Brazilian resident, or the app is targeted to Brazilian users', 'User has registered with the app as a Brazilian resident', 'User is located in Brazil, registered as a Brazilian resident, or app is targeted to Brazilian users', 'User is located in Brazil, registered as a Brazilian resident, or the app is specifically targeted to Brazilian users', 'The app is specifically targeted to Brazilian users', 'User is located in Brazil'], 'effects': ['Determines whether the DT FairBid SDK shows contextual ads or personalized ads based on user consent under LGPD', 'The SDK caches the consent for future sessions.', 'Determines whether to show contextual ads or personalized ads based on user consent under LGPD', 'Determines whether to show contextual ads or targeted ads based on user consent', 'The SDK will show contextual ads only if consent is not given, potentially affecting revenue', 'If consent is not passed, only contextual ads will be shown, potentially negatively affecting revenue.'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User provides consent for data processing', 'User has given consent', 'User has provided consent'], 'effects': ['Consent is recorded and relevant ads can be shown', 'Personalized ads may be shown, affecting revenue positively', 'User sees personalized ads', 'Targeted ads will be shown', "User's consent is acknowledged and considered for ad personalization."]}, {'parameter_values': [False, 'context'], 'conditions': ['User does not provide consent', 'User has not given consent', 'User has not provided consent'], 'effects': ['Only contextual ads are shown, potentially reducing revenue', 'Only contextual ads are shown, which might negatively affect revenue', 'Only contextual ads will be shown to the user.', 'Only contextual ads will be shown, potentially negatively affecting revenue', 'Only contextual ads will be shown']}]}</t>
+          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['BidMachine'], 'conditions': ['Publisher indicates if GDPR applies to the current user.', 'The Publisher needs to send a boolean flag indicating if GDPR applies to the current user.', 'Publisher needs to send a boolean flag indicating if GDPR applies to the current user.'], 'effects': ['Indicates whether the app must comply with GDPR.', 'Indicates whether the SDK needs to comply with GDPR regulations.', 'Indicates that GDPR regulations apply for the current user.', 'Indicates if GDPR regulations apply for user data processing.', 'Indicates if GDPR regulations apply to the current user.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is located in the European Union or subject to GDPR regulations.', 'The user is located in a region where GDPR applies.'], 'effects': ['The app must collect user consent prior to requesting any ads from the Exchange server.', 'Must collect user consent prior to processing data.', 'User data is processed in compliance with GDPR.', 'The SDK will enforce GDPR compliance for the user.']}, {'parameter_values': [False], 'conditions': ['User is not located in the European Union.', 'The user is not located in a region where GDPR applies.'], 'effects': ['No need to comply with GDPR for this user.', 'User data is not subject to GDPR regulations.', 'The SDK will not enforce GDPR compliance for the user.', 'The app is not required to follow GDPR regulations.']}, {'parameter_values': [None], 'conditions': [], 'effects': []}]}</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Digital Turbine FairBid</t>
+          <t>BidMachine</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>setIabUsPrivacyString</t>
+          <t>setConsentConfig</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{'API_name': 'setIabUsPrivacyString', 'class_name': ['UserInfo'], 'conditions': ['User opts out or gives consent regarding their personal information', 'Applicable when a user opts out of data sharing under CCPA', 'User is a California resident', 'First time gathering user opt-out consent', 'User opt out or consent needs to be set before initializing SDK', 'User is a California resident or CCPA applies'], 'effects': ['Sets the privacy string according to CCPA regulations', 'Sets the IAB US privacy string affecting how user data is handled', "The SDK will respect the user's privacy choices based on the provided string", 'Sets the IAB US Privacy String for the SDK', 'The SDK takes the user’s opt-out into consideration when initializing.'], 'parameter_configurations': [{'parameter_values': ['1YNN', 'context'], 'conditions': ['User chooses not to opt out', 'User chooses NOT to opt out', 'User opts out of targeted advertising'], 'effects': ['Advertising is shown as usual', 'User can receive ads as usual', "User's data can be used for advertising as usual", 'User is allowed to receive personalized advertising.', "User's choice to restrict advertising is respected"]}, {'parameter_values': ['1YYN', 'context'], 'conditions': ['User opts out of advertising', 'User opts in to targeted advertising', 'User chooses to opt out'], 'effects': ["User's choice to allow advertising is respected", 'Restricts the advertising options for the user', "User's data will be restricted from advertising", "User's advertisement preferences are restricted.", 'Restricts advertising and opts out']}, {'parameter_values': ['1---', 'context'], 'conditions': ['CCPA does not apply (user not a resident of California)', 'CCPA does not apply (e.g., user is not a resident of California)', 'User is not a resident of California', 'CCPA does not apply (for example, the user is not a resident of California)', 'CCPA does not apply (user not a California resident)'], 'effects': ['No privacy string needs to be sent, either skip the API or use 1---', 'The privacy string can be skipped or set to this value', 'API call can be skipped or considered.', 'API may be skipped or set to this value', 'No specific privacy string is set']}]}</t>
+          <t>{'API_name': 'setConsentConfig', 'class_name': ['BidMachine'], 'conditions': ['User consent must be collected prior to requesting ads if GDPR regulations apply.'], 'effects': ['Sets the GDPR consent configuration for the user.', "Allows the app to configure the user's consent settings.", 'Configures user consent for GDPR compliance.', 'Sets the GDPR consent string to indicate user consent for data processing.'], 'parameter_configurations': [{'parameter_values': [True, '&lt;GDPR CONSENT STRING&gt;'], 'conditions': ['User has provided consent'], 'effects': ['Consent string is sent to the server indicating user consent.', 'Sets the consent string to indicate user consent according to GDPR.']}, {'parameter_values': [False, None], 'conditions': ['User has not provided consent.', 'User has not provided consent'], 'effects': ['No consent string is sent to the server.', 'User data processing is restricted.']}, {'parameter_values': [True, 'consent_string'], 'conditions': [], 'effects': ['Indicates consent for processing personal data under GDPR.']}, {'parameter_values': [False, 'consent_string'], 'conditions': [], 'effects': ['Indicates that consent has not been given for processing personal data.']}, {'parameter_values': [None, None], 'conditions': [], 'effects': []}, {'parameter_values': [False, '&lt;GDPR CONSENT STRING&gt;'], 'conditions': [], 'effects': ['Sets the consent string without user consent.']}, {'parameter_values': [True, 'exampleConsentString'], 'conditions': ['User has given consent according to GDPR regulations.'], 'effects': ['User consents to have their data processed for advertising.']}]}</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Digital Turbine FairBid</t>
+          <t>BidMachine</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>clearIabUsPrivacyString</t>
+          <t>setUSPrivacyString</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{'API_name': 'clearIabUsPrivacyString', 'class_name': ['UserInfo'], 'conditions': [], 'effects': ['Clears the previously set US Privacy String.', 'Clears any previously set IAB US privacy string', 'Clears the privacy string set for the user', 'Clears the previously set IAB US privacy string'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': [], 'effects': ['All privacy opt-out settings are reset']}]}</t>
+          <t>{'API_name': 'setUSPrivacyString', 'class_name': ['BidMachine'], 'conditions': ['To comply with CCPA, the U.S. Privacy String must be set if applicable.', 'To pass CCPA U.S. Privacy String to BidMachine, use this method.', 'Used to pass the CCPA U.S. Privacy String.', 'To pass CCPA U.S. Privacy String to BidMachine.'], 'effects': ['Sets the U.S. Privacy String for compliance with CCPA.', "Sets the user's privacy consent status according to CCPA.", "Confirms the user's privacy preferences under CCPA.", 'Allows compliance with CCPA regulations.', 'Sets the CCPA U.S. Privacy String to indicate user consent or opt-out choice.'], 'parameter_configurations': [{'parameter_values': ['&lt;CCPA U.S. Privacy STRING&gt;'], 'conditions': [], 'effects': ['Sends the specified CCPA privacy string to the server.']}, {'parameter_values': ['privacy_string'], 'conditions': [], 'effects': ['Sets the U.S. Privacy String for processing user data under CCPA.']}, {'parameter_values': [None], 'conditions': ['User has not made a choice regarding the sale of their personal information.'], 'effects': ["User's personal information may be sold."]}, {'parameter_values': ['&lt;CCPA U.S. PRIVACY STRING&gt;'], 'conditions': [], 'effects': ['Sets the CCPA U.S. Privacy String for compliance.']}, {'parameter_values': ['1YNY'], 'conditions': ['User opts out of the sale of their personal information.'], 'effects': ["User's personal information is not sold."]}]}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Digital Turbine FairBid</t>
+          <t>BidMachine</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>setGdprConsentString</t>
+          <t>setGPP</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGdprConsentString', 'class_name': ['UserInfo'], 'conditions': [], 'effects': [], 'parameter_configurations': [{'parameter_values': ['BOEFEAyOEFEAyAHABDENAI4AAAB9vABAASA', 'this'], 'conditions': [], 'effects': []}, {'parameter_values': ['BOEFEAyOEFEAyAHABDENAI4AAAB9vABAASA', 'context'], 'conditions': [], 'effects': []}]}</t>
+          <t>{'API_name': 'setGPP', 'class_name': ['BidMachine'], 'conditions': ['To pass GPP information to BidMachine.'], 'effects': ['Sets the GPP string to indicate user consent for data processing in accordance with the Global Privacy Platform.', 'Sets the GPP string and IDs for global privacy compliance.', 'Sets the Global Privacy Platform information for compliance.', 'Enables setting of the Global Privacy Platform consent string.'], 'parameter_configurations': [{'parameter_values': ['&lt;GPP STRING&gt;', '&lt;GPP ID LIST&gt;'], 'conditions': [], 'effects': ['Passes the specified GPP information to the server.']}, {'parameter_values': ['gpp_string', []], 'conditions': [], 'effects': ['Sets GPP string for compliance with global privacy regulations.']}, {'parameter_values': [None, None], 'conditions': ['GPP does not apply.'], 'effects': []}, {'parameter_values': ['&lt;GPP STRING&gt;', '&lt;GPP IDs&gt;'], 'conditions': [], 'effects': ['Sets the GPP string and IDs for compliance.']}, {'parameter_values': ['gppStringExample', [1, 2, 3]], 'conditions': ['GPP applies for the current user.'], 'effects': ['User data processing complies with the GPP requirements.']}]}</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+          <t>https://docs.bidmachine.io/docs/in-house-mediation-android</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Prebid</t>
+          <t>MobileFuse</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>setSubjectToGDPR</t>
+          <t>setAllowLocation</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['TargetingParams'], 'conditions': ['This method is used when the user is subject to GDPR.', 'Publisher must ensure compliance with GDPR', 'Publisher needs to indicate whether the user is subject to GDPR.', 'The user is located in a region subject to GDPR', 'The user is subject to GDPR regulations'], 'effects': ['Indicates that GDPR applies to the current user session', 'Specifies that the user is subject to GDPR regulations.', 'Indicates whether the user is subject to GDPR regulations', 'Indicates that the user is subject to GDPR regulations', 'This flag will be sent to Prebid Server in the bid request.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is located in the EU and procedures must be followed for data collection as per GDPR'], 'effects': ['Changes the regulations applicable for the user under GDPR', 'The Prebid SDK will send GDPR-related information to the Prebid Server', 'User data will be handled in accordance with GDPR regulations']}, {'parameter_values': [False], 'conditions': ['User is not located in the EU'], 'effects': ['User data will not be subject to GDPR regulations', 'The Prebid SDK will not send GDPR-related information']}]}</t>
+          <t>{'API_name': 'setAllowLocation', 'class_name': ['MobileFuseTargetingData'], 'conditions': ['Application must display a consent dialog for location tracking', 'Android Manifest must be configured to allow opt-in mode', 'must have user consent for location tracking', 'User must opt-in to location-based ad personalization', 'Required to display a consent dialog prior to location tracking', 'requires opt-in configuration in the Android Manifest if needed'], 'effects': ['Manages whether the SDK can use user location for ad personalization.', 'enables or disables location targeting for ad personalization', 'Enables or disables location tracking for ad personalization', 'Enables or disables location tracking for personalized ads'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['user has opted in to location-based ad personalization', 'User opts in to location-based ad personalization', 'User has opted in to location-based ad personalization'], 'effects': ['Location data may be collected and used for ad targeting', 'Enables location-based ad personalization', 'Enables location tracking for personalized ads.', 'the SDK will collect and use location data for personalized ads']}, {'parameter_values': [False], 'conditions': ['User opts out of location-based ad personalization', 'user has opted out of location-based ad personalization', 'User has opted out of location-based ad personalization'], 'effects': ['Disables location-based ad personalization', 'the SDK will not collect or transmit any location data', 'Location data is not collected or used for ad targeting', 'Disables location tracking and prevents the collection of location data.']}]}</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+          <t>https://docs.mobilefuse.com/docs/android-sdk-data-privacy;https://docs.mobilefuse.com/docs/android-location-privacy</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Prebid</t>
+          <t>MobileFuse</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>setGDPRConsentString</t>
+          <t>setPrivacyPreferences</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{'API_name': 'setGDPRConsentString', 'class_name': ['TargetingParams'], 'conditions': ['Publisher needs to provide a consent string for GDPR compliance.', 'Consent Management Platform (CMP) must be in place or explicit user consent must be acquired', 'User must provide consent under GDPR', "The app is required to report the user's GDPR consent string", 'The consent string must be provided for GDPR compliance.'], 'effects': ['Sets the user’s consent string for GDPR enforcement.', 'The consent string is included in the bid requests sent to the Prebid Server', 'Sends the consent string to indicate user consent regarding data processing under GDPR', 'Sets the consent string required for GDPR compliance', 'This consent string will be sent to Prebid Server in the bid request.'], 'parameter_configurations': [{'parameter_values': ['BOMyQRvOMyQRvABABBAAABAAAAAAEA'], 'conditions': ['Consent must be previously obtained from the user'], 'effects': ['The provided consent string is sent with all relevant requests', 'Allows for tracking under GDPR if valid consent is given', 'Valid consent allows data processing under GDPR']}]}</t>
+          <t>{'API_name': 'setPrivacyPreferences', 'class_name': ['MobileFuse'], 'conditions': ['The user is subject to CCPA or COPPA regulations', 'must indicate whether the user is subject to COPPA if under 13 years of age', 'must provide a GPP consent string', 'User must provide GPP Consent String or US Privacy Consent String', 'User needs to provide consent strings or do not track preferences', 'GPP or US Privacy Strings must be configured', 'User age must be verified for COPPA compliance'], 'effects': ['Sets the privacy preferences for the user, affecting data collection and ad targeting', 'Configures privacy preferences for the MobileFuse SDK based on user consent', 'configures the privacy preferences for the MobileFuse SDK including consent for data usage and COPPA compliance', 'Configures the privacy preferences of the user, affecting data collection for ads.'], 'parameter_configurations': [{'parameter_values': ['GPP Consent String', False, '&lt;US Privacy String&gt;'], 'conditions': ['User is not under 13 years of age'], 'effects': ['User consented to data collection under GPP and US privacy laws', "User's data is collected and used under the defined privacy settings"]}, {'parameter_values': ['GPP Consent String', True, '&lt;US Privacy String&gt;'], 'conditions': ['User is under 13 years of age'], 'effects': ['User is not tracked or collected against COPPA regulations']}, {'parameter_values': [None, True], 'conditions': ["The user opts out of tracking by setting 'do not track' option"], 'effects': ["User's data is not collected or used for personalized advertising"]}, {'parameter_values': ['null', True, 'null'], 'conditions': ['User opts out of tracking'], 'effects': ['User is opted out of data collection for ad personalization']}, {'parameter_values': ['DBACNYA~CPXxRfAPXxRfAAfKABENB-CgAAAAAAAAAAYgAAAAAAAA~1YNN', None, None], 'conditions': ['when providing a valid GPP Consent String'], 'effects': ["the MobileFuse SDK is configured to respect the user's privacy choices"]}, {'parameter_values': [None, False, '&lt;US Privacy String&gt;'], 'conditions': ['when the user is not subject to COPPA'], 'effects': ['ensures compliance with US Privacy regulations']}, {'parameter_values': [None, True, None], 'conditions': ["when user opts out of data tracking using 'do not track' option"], 'effects': ['user data is not collected or used for personalized ads']}, {'parameter_values': ['GPP Consent String', '&lt;US Privacy String&gt;', False], 'conditions': ['User is not under 13 years of age for COPPA compliance'], 'effects': ['Enables collection of user data for ad personalization.']}, {'parameter_values': [None, '&lt;US Privacy String&gt;', True], 'conditions': ['User opts for do not track'], 'effects': ['User is opted out of data collection for ads.']}]}</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+          <t>https://docs.mobilefuse.com/docs/android-sdk-data-privacy;https://docs.mobilefuse.com/docs/android-location-privacy</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Prebid</t>
+          <t>Bigo Ads</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>setPurposeConsents</t>
+          <t>setUserConsent</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{'API_name': 'setPurposeConsents', 'class_name': ['TargetingParams'], 'conditions': ["Purpose consents must match the user's consent preferences.", 'Publisher indicates purposes of data processing as per GDPR.'], 'effects': ['Purpose consent information will be included in the bid request.', 'Sets the user’s consent status for purposes defined under GDPR.', 'Sets the consent statuses for different purposes under GDPR'], 'parameter_configurations': [{'parameter_values': ['100000000000000000000000'], 'conditions': [], 'effects': ['Indicates user approval for various processing purposes under GDPR']}]}</t>
+          <t>{'API_name': 'setUserConsent', 'class_name': ['BigoAdSdk'], 'conditions': ['The API must be called to pass the GDPR, CCPA, or LGPD consent', 'must pass user consent for processing personal information', 'User must provide consent for data processing', 'User must provide consent', 'User must provide consent for the processing of personal information.'], 'effects': ["Stores and processes the user's personal information based on the consent flag", 'determines whether user consent for GDPR, CCPA, or LGPD is stored', 'Indicates whether the user has given consent to store and process personal information.', 'Sets the user consent status for processing personal information', "Determines whether personal information can be stored and processed based on the user's consent status"], 'parameter_configurations': [{'parameter_values': ['context', 'ConsentOptions.GDPR', True], 'conditions': ['user gives consent under GDPR', 'User has given consent as per GDPR', 'User gives consent under GDPR.', 'User has given consent to store and process personal information'], 'effects': ['Consent to store and process personal information under GDPR', "User's personal information can be processed under GDPR guidelines", "User's consent is recorded for GDPR compliance", 'Consent for GDPR compliance is recorded.', 'consent is granted to store and process personal information']}, {'parameter_values': ['context', 'ConsentOptions.GDPR', False], 'conditions': ['user declines consent under GDPR', 'User declines consent under GDPR.', 'User has declined consent as per GDPR', 'User has declined consent to store and process personal information'], 'effects': ['No consent to store and process personal information under GDPR', "User's personal information cannot be processed under GDPR guidelines", "User's consent is recorded for GDPR compliance", 'consent is denied to store and process personal information', "User's personal information will not be stored or processed."]}, {'parameter_values': ['context', 'ConsentOptions.CCPA', True], 'conditions': ['User gives consent under CCPA.', 'User has given consent as per CCPA', 'user gives consent under CCPA', 'User has given consent to store and process personal information'], 'effects': ["User's consent is recorded for CCPA compliance", 'Consent for CCPA compliance is recorded.', 'Consent to store and process personal information under CCPA', "User's personal information can be processed under CCPA guidelines", 'consent is granted to store and process personal information']}, {'parameter_values': ['context', 'ConsentOptions.CCPA', False], 'conditions': ['User has declined consent as per CCPA', 'User declines consent under CCPA.', 'user declines consent under CCPA', 'User has declined consent to store and process personal information'], 'effects': ['No consent to store and process personal information under CCPA', "User's consent is recorded for CCPA compliance", 'consent is denied to store and process personal information', "User's personal information will not be stored or processed.", "User's personal information cannot be processed under CCPA guidelines"]}, {'parameter_values': ['context', 'ConsentOptions.LGPD', True], 'conditions': ['User gives consent under LGPD.', 'user gives consent under LGPD', 'User has given consent as per LGPD', 'User has given consent to store and process personal information'], 'effects': ["User's personal information can be processed under LGPD guidelines", 'Consent for LGPD compliance is recorded.', "User's consent is recorded for LGPD compliance", 'Consent to store and process personal information under LGPD', 'consent is granted to store and process personal information']}, {'parameter_values': ['context', 'ConsentOptions.LGPD', False], 'conditions': ['user declines consent under LGPD', 'User has declined consent as per LGPD', 'User declines consent under LGPD.', 'User has declined consent to store and process personal information'], 'effects': ["User's personal information will not be stored or processed.", "User's personal information cannot be processed under LGPD guidelines", 'consent is denied to store and process personal information', "User's consent is recorded for LGPD compliance", 'No consent to store and process personal information under LGPD']}]}</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+          <t>https://www.bigossp.com/guide/sdk/android/document</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Prebid</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>setSubjectToCOPPA</t>
+          <t>setGdprConsent</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>{'API_name': 'setSubjectToCOPPA', 'class_name': ['TargetingParams'], 'conditions': ['The publisher ascertains the content is aimed at children under the age of 13', 'The app content is aimed at children under 13', 'The method is used when the app is aimed at children under 13.', 'Indicates whether the current content falls under COPPA regulations.', 'The content targets children under the age of 13'], 'effects': ['Indicates compliance with COPPA regulations', 'Indicates that the app must follow COPPA regulations', 'Indicates that the app is compliant with COPPA regulations.', 'Indicates that the platform is subject to COPPA regulations', 'This flag will be passed in the bid requests to Prebid Server.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Content is directed towards children', 'Content is aimed at children.'], 'effects': ['Triggers additional privacy protections for underage users', 'Imposes additional privacy protections for children', 'Adherence to COPPA regulations concerning data privacy for children']}, {'parameter_values': [False], 'conditions': ['Content is not directed towards children'], 'effects': ['No need to follow COPPA regulations', 'No additional COPPA-based protections are implemented']}]}</t>
+          <t>{'API_name': 'setGdprConsent', 'class_name': ['RequestManager', 'NimbusAdManager', 'NimbusAdManager / RequestManager'], 'conditions': ['Consent string must be generated according to GDPR regulations', 'Consent string must be created and valid', 'Application must comply with GDPR regulations', 'Requires the user consent string to comply with GDPR regulations', "Required to manage user's consent for GDPR", 'Must be called after setting up a Consent Management Platform', 'User must provide a valid consent string according to GDPR regulations'], 'effects': ['Sets the GDPR consent string for the user', 'Allows the SDK to manage user consent for GDPR', 'Sets the GDPR consent string for the user for all requests', 'Overrides existing GDPR values set in SharedPreferences', 'Sets the GDPR consent string to manage user consent for data protection', 'Sets the GDPR consent string which will override any values set in SharedPreferences'], 'parameter_configurations': [{'parameter_values': ['consentString'], 'conditions': ['The app is required to manage user consent according to GDPR standards', 'The consentString is properly formatted as per GDPR requirements', 'The consent string must be in accordance with the IAB TCFv2 framework', "User's consent string must be defined", 'Called before initializing any Demand Providers'], 'effects': ['The consent string is now applied for all requests made by the Nimbus SDK', 'Enables the Nimbus SDK to append the GDPR consent details to outbound requests', "User's consent status for data protection is updated according to the consent string provided", 'The consent string is used for GDPR compliance in outbound requests', 'Overwrites existing values in SharedPreferences']}]}</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+          <t>https://docs.adsbynimbus.com/docs/sdk/android/data-privacy-compliance</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Prebid</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>setShareGeoLocation</t>
+          <t>usPrivacyString</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>{'API_name': 'setShareGeoLocation', 'class_name': ['Prebid'], 'conditions': ['The app is permitted to collect user’s geographical location data'], 'effects': ['Enables sharing of user’s lat/long data with the Prebid Server'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Shares user location for targeted ads']}]}</t>
+          <t>{'API_name': 'usPrivacyString', 'class_name': ['Nimbus'], 'conditions': ['User must determine if they fall within a US Privacy jurisdiction'], 'effects': ['Sets the privacy string used for compliance with CCPA'], 'parameter_configurations': [{'parameter_values': ['privacyString'], 'conditions': ['Should be set before initializing any Demand Providers'], 'effects': ['The CCPA privacy string is utilized for managing user consent']}]}</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+          <t>https://docs.adsbynimbus.com/docs/sdk/android/data-privacy-compliance</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AdMob UMP</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>setTagForUnderAgeOfConsent</t>
+          <t>COPPA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{'API_name': 'setTagForUnderAgeOfConsent', 'class_name': ['ConsentRequestParameters.Builder'], 'conditions': ['Must be set when user is under the age of consent', 'Required to comply with GDPR', 'Set to true to indicate that the user is under the age of consent.', 'Mixed audience apps should set this parameter for child users.', 'must be set when indicating that a user is under the age of consent', 'This tag is necessary when the app has users under the legal age of consent'], 'effects': ['Indicates whether a user is under the age of consent', 'Indicates whether a user is under the age of consent; consent is not requested from the user when set to true.', 'Consent is not requested from the user if set to true', 'prevents the user from being prompted for consent', 'When true, consent is not requested from the user.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['used for mixed audience apps to not request consent from child users', 'For child users in mixed audience apps.'], 'effects': ['ensures no consent request is made', 'No request for consent is made.', 'Consent is not requested from the user', 'The SDK does not prompt for user consent.', 'Prevents consent request for users under the age of consent']}, {'parameter_values': [False], 'conditions': ['used when the user is 18 years or older to request consent', 'For users of age.'], 'effects': ['triggers the consent request dialog', 'Indicates potential request for consent.', 'Consent request occurs', 'The SDK will prompt for user consent.', 'Consent request will be made for users above the age of consent']}]}</t>
+          <t>{'API_name': 'COPPA', 'class_name': ['Nimbus'], 'conditions': ['Must be called after initialization of the SDK', 'App must be governed by COPPA regulations'], 'effects': ['Configures the SDK to send compliance information to demand partners', 'Configures SDK to send information to demand partners for compliance with COPPA'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['The app is directed towards children under the age of 13', 'Call this function after SDK initialization'], 'effects': ['Enables COPPA compliance for data collection', 'Enables the SDK to comply with COPPA requirements']}]}</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://developers.google.com/admob/android/privacy/gdpr</t>
+          <t>https://docs.adsbynimbus.com/docs/sdk/android/data-privacy-compliance</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>Digital Turbine FairBid</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>setGdprConsent</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setGdprConsent', 'class_name': ['UserInfo'], 'conditions': ['User is located in the EU, registered as an EU resident, or the app is specifically targeted to EU users', 'User is located in the EU', 'User is located in EU, registered as EU resident, or app is targeted to EU users', 'User has registered with the app as an EU resident', 'User is located in the EU, registered as an EU resident, or app is targeted to EU users', 'GDPR applies if the user is currently located in the EU, has registered as an EU resident, or the app is targeted to EU users', 'The app is specifically targeted to EU users'], 'effects': ['The SDK caches the consent for future sessions.', 'Determines whether to show contextual ads or personalized ads based on user consent', 'Determines whether to show contextual ads or targeted ads based on user consent', 'Determines whether the DT FairBid SDK shows contextual ads or personalized ads based on user consent', 'The SDK will show contextual ads only if consent is not given, potentially affecting revenue', 'If consent is not passed, only contextual ads will be shown, potentially negatively affecting revenue.'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User provides consent for data processing', 'User has given consent', 'User has provided consent'], 'effects': ['Consent is recorded and relevant ads can be shown', 'Personalized ads may be shown, affecting revenue positively', 'User sees personalized ads', 'Targeted ads will be shown', "User's consent is acknowledged and considered for ad personalization."]}, {'parameter_values': [False, 'context'], 'conditions': ['User does not provide consent', 'User has not given consent', 'User has not provided consent'], 'effects': ['Only contextual ads are shown, potentially reducing revenue', 'Only contextual ads are shown, which might negatively affect revenue', 'Only contextual ads will be shown to the user.', 'Only contextual ads will be shown, potentially negatively affecting revenue', 'Only contextual ads will be shown']}]}</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Digital Turbine FairBid</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>setIabUsPrivacyString</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setIabUsPrivacyString', 'class_name': ['UserInfo'], 'conditions': ['User opts out or gives consent regarding their personal information', 'Applicable when a user opts out of data sharing under CCPA', 'User is a California resident', 'First time gathering user opt-out consent', 'User opt out or consent needs to be set before initializing SDK', 'User is a California resident or CCPA applies'], 'effects': ['Sets the privacy string according to CCPA regulations', 'Sets the IAB US privacy string affecting how user data is handled', "The SDK will respect the user's privacy choices based on the provided string", 'Sets the IAB US Privacy String for the SDK', 'The SDK takes the user’s opt-out into consideration when initializing.'], 'parameter_configurations': [{'parameter_values': ['1YNN', 'context'], 'conditions': ['User chooses not to opt out', 'User chooses NOT to opt out', 'User opts out of targeted advertising'], 'effects': ['Advertising is shown as usual', 'User can receive ads as usual', "User's data can be used for advertising as usual", 'User is allowed to receive personalized advertising.', "User's choice to restrict advertising is respected"]}, {'parameter_values': ['1YYN', 'context'], 'conditions': ['User opts out of advertising', 'User opts in to targeted advertising', 'User chooses to opt out'], 'effects': ["User's choice to allow advertising is respected", 'Restricts the advertising options for the user', "User's data will be restricted from advertising", "User's advertisement preferences are restricted.", 'Restricts advertising and opts out']}, {'parameter_values': ['1---', 'context'], 'conditions': ['CCPA does not apply (user not a resident of California)', 'CCPA does not apply (e.g., user is not a resident of California)', 'User is not a resident of California', 'CCPA does not apply (for example, the user is not a resident of California)', 'CCPA does not apply (user not a California resident)'], 'effects': ['No privacy string needs to be sent, either skip the API or use 1---', 'The privacy string can be skipped or set to this value', 'API call can be skipped or considered.', 'API may be skipped or set to this value', 'No specific privacy string is set']}]}</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Digital Turbine FairBid</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>setLgpdConsent</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setLgpdConsent', 'class_name': ['UserInfo'], 'conditions': ['LGPD applies if the user is currently located in Brazil, has registered as a Brazilian resident, or the app is targeted to Brazilian users', 'User has registered with the app as a Brazilian resident', 'User is located in Brazil, registered as a Brazilian resident, or app is targeted to Brazilian users', 'User is located in Brazil, registered as a Brazilian resident, or the app is specifically targeted to Brazilian users', 'The app is specifically targeted to Brazilian users', 'User is located in Brazil'], 'effects': ['Determines whether the DT FairBid SDK shows contextual ads or personalized ads based on user consent under LGPD', 'The SDK caches the consent for future sessions.', 'Determines whether to show contextual ads or personalized ads based on user consent under LGPD', 'Determines whether to show contextual ads or targeted ads based on user consent', 'The SDK will show contextual ads only if consent is not given, potentially affecting revenue', 'If consent is not passed, only contextual ads will be shown, potentially negatively affecting revenue.'], 'parameter_configurations': [{'parameter_values': [True, 'context'], 'conditions': ['User provides consent for data processing', 'User has given consent', 'User has provided consent'], 'effects': ['Consent is recorded and relevant ads can be shown', 'Personalized ads may be shown, affecting revenue positively', 'User sees personalized ads', 'Targeted ads will be shown', "User's consent is acknowledged and considered for ad personalization."]}, {'parameter_values': [False, 'context'], 'conditions': ['User does not provide consent', 'User has not given consent', 'User has not provided consent'], 'effects': ['Only contextual ads are shown, potentially reducing revenue', 'Only contextual ads are shown, which might negatively affect revenue', 'Only contextual ads will be shown to the user.', 'Only contextual ads will be shown, potentially negatively affecting revenue', 'Only contextual ads will be shown']}]}</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Digital Turbine FairBid</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>setIabUsPrivacyString</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setIabUsPrivacyString', 'class_name': ['UserInfo'], 'conditions': ['User opts out or gives consent regarding their personal information', 'Applicable when a user opts out of data sharing under CCPA', 'User is a California resident', 'First time gathering user opt-out consent', 'User opt out or consent needs to be set before initializing SDK', 'User is a California resident or CCPA applies'], 'effects': ['Sets the privacy string according to CCPA regulations', 'Sets the IAB US privacy string affecting how user data is handled', "The SDK will respect the user's privacy choices based on the provided string", 'Sets the IAB US Privacy String for the SDK', 'The SDK takes the user’s opt-out into consideration when initializing.'], 'parameter_configurations': [{'parameter_values': ['1YNN', 'context'], 'conditions': ['User chooses not to opt out', 'User chooses NOT to opt out', 'User opts out of targeted advertising'], 'effects': ['Advertising is shown as usual', 'User can receive ads as usual', "User's data can be used for advertising as usual", 'User is allowed to receive personalized advertising.', "User's choice to restrict advertising is respected"]}, {'parameter_values': ['1YYN', 'context'], 'conditions': ['User opts out of advertising', 'User opts in to targeted advertising', 'User chooses to opt out'], 'effects': ["User's choice to allow advertising is respected", 'Restricts the advertising options for the user', "User's data will be restricted from advertising", "User's advertisement preferences are restricted.", 'Restricts advertising and opts out']}, {'parameter_values': ['1---', 'context'], 'conditions': ['CCPA does not apply (user not a resident of California)', 'CCPA does not apply (e.g., user is not a resident of California)', 'User is not a resident of California', 'CCPA does not apply (for example, the user is not a resident of California)', 'CCPA does not apply (user not a California resident)'], 'effects': ['No privacy string needs to be sent, either skip the API or use 1---', 'The privacy string can be skipped or set to this value', 'API call can be skipped or considered.', 'API may be skipped or set to this value', 'No specific privacy string is set']}]}</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Digital Turbine FairBid</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>clearIabUsPrivacyString</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>{'API_name': 'clearIabUsPrivacyString', 'class_name': ['UserInfo'], 'conditions': [], 'effects': ['Clears the previously set US Privacy String.', 'Clears any previously set IAB US privacy string', 'Clears the privacy string set for the user', 'Clears the previously set IAB US privacy string'], 'parameter_configurations': [{'parameter_values': ['context'], 'conditions': [], 'effects': ['All privacy opt-out settings are reset']}]}</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Digital Turbine FairBid</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>setGdprConsentString</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setGdprConsentString', 'class_name': ['UserInfo'], 'conditions': [], 'effects': [], 'parameter_configurations': [{'parameter_values': ['BOEFEAyOEFEAyAHABDENAI4AAAB9vABAASA', 'this'], 'conditions': [], 'effects': []}, {'parameter_values': ['BOEFEAyOEFEAyAHABDENAI4AAAB9vABAASA', 'context'], 'conditions': [], 'effects': []}]}</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://developer.digitalturbine.com/hc/en-us/articles/360010251818-GDPR;https://developer.digitalturbine.com/hc/en-us/articles/360010251878-CCPA-Privacy-String;https://developer.digitalturbine.com/hc/en-us/articles/7019733520913-LGPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Prebid</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>setSubjectToGDPR</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setSubjectToGDPR', 'class_name': ['TargetingParams'], 'conditions': ['This method is used when the user is subject to GDPR.', 'Publisher must ensure compliance with GDPR', 'Publisher needs to indicate whether the user is subject to GDPR.', 'The user is located in a region subject to GDPR', 'The user is subject to GDPR regulations'], 'effects': ['Indicates that GDPR applies to the current user session', 'Specifies that the user is subject to GDPR regulations.', 'Indicates whether the user is subject to GDPR regulations', 'Indicates that the user is subject to GDPR regulations', 'This flag will be sent to Prebid Server in the bid request.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['User is located in the EU and procedures must be followed for data collection as per GDPR'], 'effects': ['Changes the regulations applicable for the user under GDPR', 'The Prebid SDK will send GDPR-related information to the Prebid Server', 'User data will be handled in accordance with GDPR regulations']}, {'parameter_values': [False], 'conditions': ['User is not located in the EU'], 'effects': ['User data will not be subject to GDPR regulations', 'The Prebid SDK will not send GDPR-related information']}]}</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Prebid</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>setGDPRConsentString</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setGDPRConsentString', 'class_name': ['TargetingParams'], 'conditions': ['Publisher needs to provide a consent string for GDPR compliance.', 'Consent Management Platform (CMP) must be in place or explicit user consent must be acquired', 'User must provide consent under GDPR', "The app is required to report the user's GDPR consent string", 'The consent string must be provided for GDPR compliance.'], 'effects': ['Sets the user’s consent string for GDPR enforcement.', 'The consent string is included in the bid requests sent to the Prebid Server', 'Sends the consent string to indicate user consent regarding data processing under GDPR', 'Sets the consent string required for GDPR compliance', 'This consent string will be sent to Prebid Server in the bid request.'], 'parameter_configurations': [{'parameter_values': ['BOMyQRvOMyQRvABABBAAABAAAAAAEA'], 'conditions': ['Consent must be previously obtained from the user'], 'effects': ['The provided consent string is sent with all relevant requests', 'Allows for tracking under GDPR if valid consent is given', 'Valid consent allows data processing under GDPR']}]}</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Prebid</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>setPurposeConsents</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setPurposeConsents', 'class_name': ['TargetingParams'], 'conditions': ["Purpose consents must match the user's consent preferences.", 'Publisher indicates purposes of data processing as per GDPR.'], 'effects': ['Purpose consent information will be included in the bid request.', 'Sets the user’s consent status for purposes defined under GDPR.', 'Sets the consent statuses for different purposes under GDPR'], 'parameter_configurations': [{'parameter_values': ['100000000000000000000000'], 'conditions': [], 'effects': ['Indicates user approval for various processing purposes under GDPR']}]}</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Prebid</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>setSubjectToCOPPA</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setSubjectToCOPPA', 'class_name': ['TargetingParams'], 'conditions': ['The publisher ascertains the content is aimed at children under the age of 13', 'The app content is aimed at children under 13', 'The method is used when the app is aimed at children under 13.', 'Indicates whether the current content falls under COPPA regulations.', 'The content targets children under the age of 13'], 'effects': ['Indicates compliance with COPPA regulations', 'Indicates that the app must follow COPPA regulations', 'Indicates that the app is compliant with COPPA regulations.', 'Indicates that the platform is subject to COPPA regulations', 'This flag will be passed in the bid requests to Prebid Server.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['Content is directed towards children', 'Content is aimed at children.'], 'effects': ['Triggers additional privacy protections for underage users', 'Imposes additional privacy protections for children', 'Adherence to COPPA regulations concerning data privacy for children']}, {'parameter_values': [False], 'conditions': ['Content is not directed towards children'], 'effects': ['No need to follow COPPA regulations', 'No additional COPPA-based protections are implemented']}]}</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Prebid</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>setShareGeoLocation</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setShareGeoLocation', 'class_name': ['Prebid'], 'conditions': ['The app is permitted to collect user’s geographical location data'], 'effects': ['Enables sharing of user’s lat/long data with the Prebid Server'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': [], 'effects': ['Shares user location for targeted ads']}]}</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://docs.prebid.org/prebid-mobile/pbm-api/android/pbm-targeting-params-android.html#consent-management-parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
           <t>AdMob UMP</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>setTagForUnderAgeOfConsent</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>{'API_name': 'setTagForUnderAgeOfConsent', 'class_name': ['ConsentRequestParameters.Builder'], 'conditions': ['Must be set when user is under the age of consent', 'Required to comply with GDPR', 'Set to true to indicate that the user is under the age of consent.', 'Mixed audience apps should set this parameter for child users.', 'must be set when indicating that a user is under the age of consent', 'This tag is necessary when the app has users under the legal age of consent'], 'effects': ['Indicates whether a user is under the age of consent', 'Indicates whether a user is under the age of consent; consent is not requested from the user when set to true.', 'Consent is not requested from the user if set to true', 'prevents the user from being prompted for consent', 'When true, consent is not requested from the user.'], 'parameter_configurations': [{'parameter_values': [True], 'conditions': ['used for mixed audience apps to not request consent from child users', 'For child users in mixed audience apps.'], 'effects': ['ensures no consent request is made', 'No request for consent is made.', 'Consent is not requested from the user', 'The SDK does not prompt for user consent.', 'Prevents consent request for users under the age of consent']}, {'parameter_values': [False], 'conditions': ['used when the user is 18 years or older to request consent', 'For users of age.'], 'effects': ['triggers the consent request dialog', 'Indicates potential request for consent.', 'Consent request occurs', 'The SDK will prompt for user consent.', 'Consent request will be made for users above the age of consent']}]}</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://developers.google.com/admob/android/privacy/gdpr</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>AdMob UMP</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
         <is>
           <t>requestConsentInfoUpdate</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>{'API_name': 'requestConsentInfoUpdate', 'class_name': ['ConsentInformation'], 'conditions': ['ConsentRequestParameters must be properly set', 'must be called to request user consent information update', 'Must have the consent request parameters set before calling this method.', 'Requires proper configuration of ConsentRequestParameters.', 'Must provide consent request parameters', 'User must have previously set consent status'], 'effects': ['Updates the consent information based on provided parameters.', 'triggers an update to the consent status', 'Requests updated consent information from users', 'Updates consent information and triggers success or failure callbacks.', 'Updates consent information based on user consent parameters'], 'parameter_configurations': [{'parameter_values': ['context', 'params', 'successListener', 'failureListener'], 'conditions': [], 'effects': ['Triggers the process to fetch consent status.']}, {'parameter_values': ['this', 'params', '(OnConsentInfoUpdateSuccessListener)', '(OnConsentInfoUpdateFailureListener)'], 'conditions': ['success function must handle the successful update of consent information', 'failure function must handle the error case'], 'effects': ['Consent information is either updated successfully or an error is reported']}, {'parameter_values': ['this', 'params', 'OnConsentInfoUpdateSuccessListener', 'OnConsentInfoUpdateFailureListener'], 'conditions': [], 'effects': ['Callback will execute on success or failure of the consent information update.']}, {'parameter_values': ['context', 'params', 'OnConsentInfoUpdateSuccessListener', 'OnConsentInfoUpdateFailureListener'], 'conditions': ['parameters must contain valid context and consent request parameters'], 'effects': ['successful update of consent information or triggers failure listener on error']}]}</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>https://developers.google.com/admob/android/privacy/gdpr</t>
         </is>
